--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="113_{1398BFE9-7F31-4A84-A4C4-391DE17DDF9A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{3402415C-7B21-45D3-8856-1636A6034240}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="113_{1398BFE9-7F31-4A84-A4C4-391DE17DDF9A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{32615D49-DDB2-4395-B9C5-C09D8CFD59FB}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="598">
   <si>
     <t>Nome account</t>
   </si>
@@ -1811,6 +1811,12 @@
   </si>
   <si>
     <t>APOLLO SAN SEVERO SRL</t>
+  </si>
+  <si>
+    <t>ORTA ENERGY 34 SRL</t>
+  </si>
+  <si>
+    <t>VIALE DON LUIGI STURZO 43</t>
   </si>
 </sst>
 </file>
@@ -2235,7 +2241,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G239"/>
+  <dimension ref="A1:G240"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -5907,30 +5913,30 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>515</v>
+        <v>596</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>29</v>
+        <v>597</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F160" s="5">
-        <v>39100</v>
+        <v>20154</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>232</v>
+        <v>515</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>28</v>
@@ -5944,8 +5950,8 @@
       <c r="E161" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F161" s="5" t="s">
-        <v>31</v>
+      <c r="F161" s="5">
+        <v>39100</v>
       </c>
       <c r="G161" s="4" t="s">
         <v>32</v>
@@ -5953,30 +5959,30 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>34</v>
@@ -5985,13 +5991,13 @@
         <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="E163" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G163" s="4" t="s">
         <v>38</v>
@@ -5999,7 +6005,7 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>441</v>
+        <v>56</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>34</v>
@@ -6008,136 +6014,136 @@
         <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>442</v>
+        <v>57</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="F164" s="5">
-        <v>20038</v>
+        <v>36</v>
+      </c>
+      <c r="F164" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>236</v>
+        <v>442</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>81</v>
+        <v>443</v>
       </c>
       <c r="F165" s="5">
-        <v>10121</v>
+        <v>20038</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>95</v>
+        <v>426</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>97</v>
+        <v>236</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>99</v>
+        <v>81</v>
+      </c>
+      <c r="F166" s="5">
+        <v>10121</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>377</v>
+        <v>95</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>378</v>
+        <v>96</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>379</v>
+        <v>97</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="F167" s="5">
-        <v>64020</v>
+        <v>98</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>580</v>
+        <v>377</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>9</v>
+        <v>378</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>581</v>
+        <v>379</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F168" s="8" t="s">
-        <v>582</v>
+        <v>380</v>
+      </c>
+      <c r="F168" s="5">
+        <v>64020</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>410</v>
+        <v>580</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>211</v>
+        <v>581</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F169" s="5">
-        <v>20121</v>
+        <v>10</v>
+      </c>
+      <c r="F169" s="8" t="s">
+        <v>582</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>133</v>
+        <v>410</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>34</v>
@@ -6146,21 +6152,21 @@
         <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>134</v>
+        <v>211</v>
       </c>
       <c r="E170" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F170" s="5" t="s">
-        <v>135</v>
+      <c r="F170" s="5">
+        <v>20121</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>34</v>
@@ -6169,67 +6175,67 @@
         <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>258</v>
+        <v>134</v>
       </c>
       <c r="E171" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>340</v>
+        <v>257</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>342</v>
+        <v>258</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="F172" s="5">
-        <v>37045</v>
+        <v>36</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>343</v>
+        <v>38</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>166</v>
+        <v>340</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>167</v>
+        <v>342</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>168</v>
+        <v>528</v>
+      </c>
+      <c r="F173" s="5">
+        <v>37045</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>159</v>
+        <v>343</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>529</v>
+        <v>166</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>34</v>
@@ -6243,8 +6249,8 @@
       <c r="E174" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F174" s="5">
-        <v>20126</v>
+      <c r="F174" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G174" s="4" t="s">
         <v>159</v>
@@ -6252,7 +6258,7 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>594</v>
+        <v>529</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>34</v>
@@ -6261,21 +6267,21 @@
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>394</v>
+        <v>167</v>
       </c>
       <c r="E175" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F175" s="5">
-        <v>20123</v>
+        <v>20126</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>471</v>
+        <v>594</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>34</v>
@@ -6284,21 +6290,21 @@
         <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>260</v>
+        <v>394</v>
       </c>
       <c r="E176" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F176" s="5">
-        <v>20135</v>
+        <v>20123</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>262</v>
+        <v>38</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>405</v>
+        <v>471</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>34</v>
@@ -6321,53 +6327,53 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>204</v>
+        <v>405</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F178" s="5" t="s">
-        <v>187</v>
+        <v>36</v>
+      </c>
+      <c r="F178" s="5">
+        <v>20135</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>453</v>
+        <v>204</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>454</v>
+        <v>205</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F179" s="5">
-        <v>20144</v>
+        <v>186</v>
+      </c>
+      <c r="F179" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>38</v>
+        <v>319</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>223</v>
+        <v>453</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>34</v>
@@ -6376,297 +6382,297 @@
         <v>8</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>224</v>
+        <v>454</v>
       </c>
       <c r="E180" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F180" s="5" t="s">
-        <v>135</v>
+      <c r="F180" s="5">
+        <v>20144</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>285</v>
+        <v>223</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>317</v>
+        <v>224</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F181" s="5">
-        <v>40026</v>
+        <v>36</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>323</v>
+        <v>318</v>
+      </c>
+      <c r="F182" s="5">
+        <v>40026</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>533</v>
+        <v>286</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>29</v>
+        <v>320</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F183" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F183" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>367</v>
+        <v>533</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>368</v>
+        <v>29</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F184" s="5">
-        <v>20123</v>
+        <v>39100</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>321</v>
+        <v>368</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>322</v>
+        <v>36</v>
       </c>
       <c r="F185" s="5">
-        <v>12020</v>
+        <v>20123</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>39</v>
+        <v>287</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>40</v>
+        <v>308</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>41</v>
+        <v>321</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F186" s="5" t="s">
-        <v>43</v>
+        <v>322</v>
+      </c>
+      <c r="F186" s="5">
+        <v>12020</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>421</v>
+        <v>39</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>422</v>
+        <v>40</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>423</v>
+        <v>41</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="F187" s="5">
-        <v>28053</v>
+        <v>42</v>
+      </c>
+      <c r="F187" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>136</v>
+        <v>44</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>172</v>
+        <v>421</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>34</v>
+        <v>422</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>169</v>
+        <v>423</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F188" s="5" t="s">
-        <v>171</v>
+        <v>424</v>
+      </c>
+      <c r="F188" s="5">
+        <v>28053</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>560</v>
+        <v>172</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>561</v>
+        <v>169</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F189" s="10">
-        <v>39100</v>
+        <v>170</v>
+      </c>
+      <c r="F189" s="10" t="s">
+        <v>171</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>198</v>
+        <v>560</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>199</v>
+        <v>561</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F190" s="10" t="s">
-        <v>200</v>
+        <v>30</v>
+      </c>
+      <c r="F190" s="10">
+        <v>39100</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="F191" s="10" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>244</v>
+        <v>207</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F192" s="10" t="s">
-        <v>58</v>
+        <v>209</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>534</v>
+        <v>244</v>
       </c>
       <c r="B193" s="9" t="s">
         <v>34</v>
@@ -6680,8 +6686,8 @@
       <c r="E193" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F193" s="10">
-        <v>20121</v>
+      <c r="F193" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="G193" s="9" t="s">
         <v>38</v>
@@ -6689,7 +6695,7 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
-        <v>578</v>
+        <v>534</v>
       </c>
       <c r="B194" s="9" t="s">
         <v>34</v>
@@ -6698,7 +6704,7 @@
         <v>8</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>579</v>
+        <v>177</v>
       </c>
       <c r="E194" s="9" t="s">
         <v>36</v>
@@ -6712,260 +6718,260 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="C195" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>447</v>
+        <v>579</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>448</v>
+        <v>36</v>
       </c>
       <c r="F195" s="10">
-        <v>53048</v>
+        <v>20121</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>449</v>
+        <v>38</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
-        <v>516</v>
+        <v>445</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>509</v>
+        <v>446</v>
       </c>
       <c r="C196" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>517</v>
+        <v>447</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>518</v>
+        <v>448</v>
       </c>
       <c r="F196" s="10">
-        <v>35011</v>
+        <v>53048</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>505</v>
+        <v>449</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>243</v>
+        <v>516</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>34</v>
+        <v>509</v>
       </c>
       <c r="C197" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>177</v>
+        <v>517</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F197" s="10" t="s">
-        <v>58</v>
+        <v>518</v>
+      </c>
+      <c r="F197" s="10">
+        <v>35011</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>38</v>
+        <v>505</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>131</v>
+        <v>243</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C198" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F198" s="10" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>531</v>
+        <v>131</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C199" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>532</v>
+        <v>132</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F199" s="10">
-        <v>20121</v>
+        <v>30</v>
+      </c>
+      <c r="F199" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="B200" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C200" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D200" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="E200" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F200" s="10">
+        <v>20121</v>
+      </c>
+      <c r="G200" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A201" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B200" s="9" t="s">
+      <c r="B201" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C200" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D200" s="9" t="s">
+      <c r="C201" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D201" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E200" s="9" t="s">
+      <c r="E201" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F200" s="10" t="s">
+      <c r="F201" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G200" s="9" t="s">
+      <c r="G201" s="9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A201" s="3" t="s">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A202" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="B201" s="3" t="s">
+      <c r="B202" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C201" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D201" s="3" t="s">
+      <c r="C202" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D202" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="E201" s="3" t="s">
+      <c r="E202" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F201" s="11" t="s">
+      <c r="F202" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="G201" s="3" t="s">
+      <c r="G202" s="3" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A202" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="B202" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C202" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D202" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="E202" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="F202" s="10">
-        <v>20089</v>
-      </c>
-      <c r="G202" s="9" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="9" t="s">
-        <v>475</v>
+        <v>381</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C203" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D203" s="9" t="s">
-        <v>476</v>
+        <v>382</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F203" s="12" t="s">
-        <v>477</v>
+        <v>383</v>
+      </c>
+      <c r="F203" s="10">
+        <v>20089</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
-        <v>212</v>
+        <v>475</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C204" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D204" s="9" t="s">
-        <v>202</v>
+        <v>476</v>
       </c>
       <c r="E204" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F204" s="10" t="s">
-        <v>203</v>
+        <v>10</v>
+      </c>
+      <c r="F204" s="12" t="s">
+        <v>477</v>
       </c>
       <c r="G204" s="9" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B205" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C205" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D205" s="9" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="E205" s="9" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F205" s="10" t="s">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="G205" s="9" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="9" t="s">
-        <v>438</v>
+        <v>214</v>
       </c>
       <c r="B206" s="9" t="s">
         <v>34</v>
@@ -6979,8 +6985,8 @@
       <c r="E206" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F206" s="10">
-        <v>20124</v>
+      <c r="F206" s="10" t="s">
+        <v>158</v>
       </c>
       <c r="G206" s="9" t="s">
         <v>159</v>
@@ -6988,7 +6994,7 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
-        <v>229</v>
+        <v>438</v>
       </c>
       <c r="B207" s="9" t="s">
         <v>34</v>
@@ -6997,21 +7003,21 @@
         <v>8</v>
       </c>
       <c r="D207" s="9" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E207" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F207" s="10" t="s">
-        <v>231</v>
+      <c r="F207" s="10">
+        <v>20124</v>
       </c>
       <c r="G207" s="9" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="9" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="B208" s="9" t="s">
         <v>34</v>
@@ -7034,7 +7040,7 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="9" t="s">
-        <v>472</v>
+        <v>256</v>
       </c>
       <c r="B209" s="9" t="s">
         <v>34</v>
@@ -7043,21 +7049,21 @@
         <v>8</v>
       </c>
       <c r="D209" s="9" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E209" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F209" s="10">
-        <v>20129</v>
+      <c r="F209" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="G209" s="9" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="9" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="B210" s="9" t="s">
         <v>34</v>
@@ -7080,7 +7086,7 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="9" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="B211" s="9" t="s">
         <v>34</v>
@@ -7103,7 +7109,7 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B212" s="9" t="s">
         <v>34</v>
@@ -7126,7 +7132,7 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="9" t="s">
-        <v>176</v>
+        <v>474</v>
       </c>
       <c r="B213" s="9" t="s">
         <v>34</v>
@@ -7135,435 +7141,435 @@
         <v>8</v>
       </c>
       <c r="D213" s="9" t="s">
-        <v>177</v>
+        <v>464</v>
       </c>
       <c r="E213" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F213" s="10" t="s">
-        <v>58</v>
+      <c r="F213" s="10">
+        <v>20129</v>
       </c>
       <c r="G213" s="9" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="9" t="s">
-        <v>331</v>
+        <v>176</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C214" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D214" s="9" t="s">
-        <v>332</v>
+        <v>177</v>
       </c>
       <c r="E214" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="F214" s="10">
-        <v>40026</v>
+        <v>36</v>
+      </c>
+      <c r="F214" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="G214" s="9" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="9" t="s">
-        <v>288</v>
+        <v>331</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C215" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D215" s="9" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="E215" s="9" t="s">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="F215" s="10">
-        <v>20124</v>
+        <v>40026</v>
       </c>
       <c r="G215" s="9" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="9" t="s">
-        <v>450</v>
+        <v>288</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C216" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D216" s="9" t="s">
-        <v>451</v>
+        <v>324</v>
       </c>
       <c r="E216" s="9" t="s">
-        <v>452</v>
+        <v>36</v>
       </c>
       <c r="F216" s="10">
-        <v>12011</v>
+        <v>20124</v>
       </c>
       <c r="G216" s="9" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
-        <v>151</v>
+        <v>450</v>
       </c>
       <c r="B217" s="9" t="s">
-        <v>152</v>
+        <v>308</v>
       </c>
       <c r="C217" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D217" s="9" t="s">
-        <v>153</v>
+        <v>451</v>
       </c>
       <c r="E217" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="F217" s="10" t="s">
-        <v>155</v>
+        <v>452</v>
+      </c>
+      <c r="F217" s="10">
+        <v>12011</v>
       </c>
       <c r="G217" s="9" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="9" t="s">
-        <v>419</v>
+        <v>151</v>
       </c>
       <c r="B218" s="9" t="s">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="C218" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D218" s="9" t="s">
-        <v>420</v>
+        <v>153</v>
       </c>
       <c r="E218" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F218" s="10">
-        <v>20123</v>
+        <v>154</v>
+      </c>
+      <c r="F218" s="10" t="s">
+        <v>155</v>
       </c>
       <c r="G218" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="9" t="s">
-        <v>491</v>
+        <v>419</v>
       </c>
       <c r="B219" s="9" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C219" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D219" s="9" t="s">
-        <v>492</v>
+        <v>420</v>
       </c>
       <c r="E219" s="9" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F219" s="10">
-        <v>90141</v>
+        <v>20123</v>
       </c>
       <c r="G219" s="9" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="B220" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C220" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D220" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="E220" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F220" s="10">
+        <v>90141</v>
+      </c>
+      <c r="G220" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A221" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="B220" s="9" t="s">
+      <c r="B221" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C220" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D220" s="9" t="s">
+      <c r="C221" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D221" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="E220" s="9" t="s">
+      <c r="E221" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F220" s="12" t="s">
+      <c r="F221" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="G220" s="9" t="s">
+      <c r="G221" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A221" s="3" t="s">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A222" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="B221" s="3" t="s">
+      <c r="B222" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C221" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D221" s="3" t="s">
+      <c r="C222" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D222" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="E221" s="3" t="s">
+      <c r="E222" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F221" s="11" t="s">
+      <c r="F222" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="G221" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A222" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="B222" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C222" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D222" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="E222" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F222" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="G222" s="9" t="s">
+      <c r="G222" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="B223" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C223" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D223" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="E223" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F223" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="G223" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A224" s="9" t="s">
         <v>465</v>
       </c>
-      <c r="B223" s="9" t="s">
+      <c r="B224" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C223" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D223" s="9" t="s">
+      <c r="C224" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D224" s="9" t="s">
         <v>466</v>
       </c>
-      <c r="E223" s="9" t="s">
+      <c r="E224" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="F223" s="10">
+      <c r="F224" s="10">
         <v>38055</v>
       </c>
-      <c r="G223" s="9" t="s">
+      <c r="G224" s="9" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A224" s="3" t="s">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A225" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="B224" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C224" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D224" s="3" t="s">
+      <c r="B225" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D225" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E224" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F224" s="7">
+      <c r="E225" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F225" s="7">
         <v>20145</v>
       </c>
-      <c r="G224" s="3" t="s">
+      <c r="G225" s="3" t="s">
         <v>136</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A225" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="B225" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C225" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D225" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="E225" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="F225" s="10">
-        <v>25010</v>
-      </c>
-      <c r="G225" s="9" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="9" t="s">
-        <v>393</v>
+        <v>427</v>
       </c>
       <c r="B226" s="9" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="C226" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D226" s="9" t="s">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="E226" s="9" t="s">
-        <v>36</v>
+        <v>429</v>
       </c>
       <c r="F226" s="10">
-        <v>20123</v>
+        <v>25010</v>
       </c>
       <c r="G226" s="9" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="9" t="s">
-        <v>416</v>
+        <v>393</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="C227" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D227" s="9" t="s">
-        <v>417</v>
+        <v>394</v>
       </c>
       <c r="E227" s="9" t="s">
-        <v>418</v>
+        <v>36</v>
       </c>
       <c r="F227" s="10">
-        <v>71016</v>
+        <v>20123</v>
       </c>
       <c r="G227" s="9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="9" t="s">
-        <v>16</v>
+        <v>416</v>
       </c>
       <c r="B228" s="9" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="C228" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D228" s="9" t="s">
-        <v>18</v>
+        <v>417</v>
       </c>
       <c r="E228" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F228" s="10" t="s">
-        <v>20</v>
+        <v>418</v>
+      </c>
+      <c r="F228" s="10">
+        <v>71016</v>
       </c>
       <c r="G228" s="9" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B229" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C229" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D229" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E229" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F229" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G229" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A230" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="B229" s="9" t="s">
+      <c r="B230" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="C229" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D229" s="9" t="s">
+      <c r="C230" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D230" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="E229" s="9" t="s">
+      <c r="E230" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="F229" s="10" t="s">
+      <c r="F230" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="G229" s="9" t="s">
+      <c r="G230" s="9" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A230" s="3" t="s">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A231" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="B230" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C230" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D230" s="3" t="s">
+      <c r="B231" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D231" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="E230" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F230" s="7">
+      <c r="E231" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F231" s="7">
         <v>20122</v>
       </c>
-      <c r="G230" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A231" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="B231" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C231" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D231" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="E231" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F231" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="G231" s="9" t="s">
+      <c r="G231" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="9" t="s">
-        <v>478</v>
+        <v>277</v>
       </c>
       <c r="B232" s="9" t="s">
         <v>34</v>
@@ -7572,67 +7578,67 @@
         <v>8</v>
       </c>
       <c r="D232" s="9" t="s">
-        <v>479</v>
+        <v>278</v>
       </c>
       <c r="E232" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F232" s="10">
-        <v>20123</v>
+      <c r="F232" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="G232" s="9" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A233" s="3" t="s">
+      <c r="A233" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="B233" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C233" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D233" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="E233" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F233" s="10">
+        <v>20123</v>
+      </c>
+      <c r="G233" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A234" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="B233" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C233" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D233" s="3" t="s">
+      <c r="B234" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D234" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="E233" s="3" t="s">
+      <c r="E234" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="F233" s="7">
+      <c r="F234" s="7">
         <v>20094</v>
       </c>
-      <c r="G233" s="3" t="s">
+      <c r="G234" s="3" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A234" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="B234" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C234" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D234" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="E234" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F234" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="G234" s="9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="9" t="s">
-        <v>216</v>
+        <v>396</v>
       </c>
       <c r="B235" s="9" t="s">
         <v>9</v>
@@ -7655,53 +7661,53 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" s="9" t="s">
-        <v>160</v>
+        <v>216</v>
       </c>
       <c r="B236" s="9" t="s">
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="C236" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D236" s="9" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="E236" s="9" t="s">
-        <v>163</v>
+        <v>10</v>
       </c>
       <c r="F236" s="10" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="G236" s="9" t="s">
-        <v>165</v>
+        <v>11</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="9" t="s">
-        <v>434</v>
+        <v>160</v>
       </c>
       <c r="B237" s="9" t="s">
-        <v>9</v>
+        <v>161</v>
       </c>
       <c r="C237" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D237" s="9" t="s">
-        <v>217</v>
+        <v>162</v>
       </c>
       <c r="E237" s="9" t="s">
-        <v>10</v>
+        <v>163</v>
       </c>
       <c r="F237" s="10" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="G237" s="9" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="9" t="s">
-        <v>255</v>
+        <v>434</v>
       </c>
       <c r="B238" s="9" t="s">
         <v>9</v>
@@ -7724,30 +7730,53 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B239" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C239" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D239" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E239" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F239" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G239" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A240" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B239" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C239" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D239" s="9" t="s">
+      <c r="B240" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C240" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D240" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E239" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F239" s="10" t="s">
+      <c r="E240" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F240" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G239" s="9" t="s">
+      <c r="G240" s="9" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G218" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G239">
+    <sortState ref="A2:G240">
       <sortCondition ref="A1:A218"/>
     </sortState>
   </autoFilter>
@@ -7760,23 +7789,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F040406D9EE34E48977C379A242BB45D" ma:contentTypeVersion="15" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="1ab2d492e43f6bec9a26aa4599c840e9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="877b7d34-4df7-40bf-9eb1-208952470e96" xmlns:ns4="05fc27dd-4454-4248-9c78-3d72b2b155c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebc604e5d4aadf5a992ba83f8d4fb519" ns3:_="" ns4:_="">
     <xsd:import namespace="877b7d34-4df7-40bf-9eb1-208952470e96"/>
@@ -8009,32 +8021,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBC6436E-C4E7-4E8D-94E8-64DAEC05792B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8051,4 +8055,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="113_{1398BFE9-7F31-4A84-A4C4-391DE17DDF9A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{32615D49-DDB2-4395-B9C5-C09D8CFD59FB}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="113_{1398BFE9-7F31-4A84-A4C4-391DE17DDF9A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{CAC9979C-EB25-4F45-BBAC-891B54D6A2E5}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="603">
   <si>
     <t>Nome account</t>
   </si>
@@ -1817,6 +1817,21 @@
   </si>
   <si>
     <t>VIALE DON LUIGI STURZO 43</t>
+  </si>
+  <si>
+    <t>GR VALUE BRINDISI 2 SRL</t>
+  </si>
+  <si>
+    <t>VIA DURINI 9</t>
+  </si>
+  <si>
+    <t>ALTA CAPITAL 10 SRL</t>
+  </si>
+  <si>
+    <t>RENPV6 SRL</t>
+  </si>
+  <si>
+    <t>VIA GIANFRANCO MALIPIERO 16-18</t>
   </si>
 </sst>
 </file>
@@ -2241,7 +2256,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G240"/>
+  <dimension ref="A1:G243"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -2509,7 +2524,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>235</v>
+        <v>600</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>79</v>
@@ -2523,8 +2538,8 @@
       <c r="E12" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>237</v>
+      <c r="F12" s="5">
+        <v>10121</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>83</v>
@@ -2532,22 +2547,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>495</v>
+        <v>235</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>496</v>
+        <v>236</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>497</v>
-      </c>
-      <c r="F13" s="5">
-        <v>10098</v>
+        <v>81</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>83</v>
@@ -2555,76 +2570,76 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>45</v>
+        <v>495</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>47</v>
+        <v>496</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>49</v>
+        <v>497</v>
+      </c>
+      <c r="F14" s="5">
+        <v>10098</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>9</v>
@@ -2647,7 +2662,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>9</v>
@@ -2670,7 +2685,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>482</v>
+        <v>196</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>9</v>
@@ -2684,7 +2699,7 @@
       <c r="E19" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="5" t="s">
         <v>180</v>
       </c>
       <c r="G19" s="4" t="s">
@@ -2693,7 +2708,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>197</v>
+        <v>482</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>9</v>
@@ -2707,7 +2722,7 @@
       <c r="E20" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="8" t="s">
         <v>180</v>
       </c>
       <c r="G20" s="4" t="s">
@@ -2716,7 +2731,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>9</v>
@@ -2739,30 +2754,30 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>403</v>
+        <v>183</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>404</v>
+        <v>179</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>595</v>
+        <v>403</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>28</v>
@@ -2785,76 +2800,76 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>399</v>
+        <v>595</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F24" s="5">
-        <v>20124</v>
+        <v>39100</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>468</v>
+        <v>399</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>469</v>
+        <v>400</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>470</v>
+        <v>36</v>
+      </c>
+      <c r="F25" s="5">
+        <v>20124</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>305</v>
+        <v>469</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F26" s="5">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>470</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>349</v>
+        <v>436</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>34</v>
@@ -2863,13 +2878,13 @@
         <v>8</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>350</v>
+        <v>305</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F27" s="5">
-        <v>20122</v>
+        <v>20123</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>38</v>
@@ -2877,53 +2892,53 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>67</v>
+        <v>349</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>18</v>
+        <v>350</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="F28" s="5">
+        <v>20122</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>398</v>
+        <v>67</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F29" s="5">
-        <v>10123</v>
+        <v>19</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>78</v>
+        <v>398</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>79</v>
@@ -2937,8 +2952,8 @@
       <c r="E30" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F30" s="5" t="s">
-        <v>82</v>
+      <c r="F30" s="5">
+        <v>10123</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>83</v>
@@ -2946,76 +2961,76 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>546</v>
+        <v>78</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>511</v>
+        <v>79</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>547</v>
+        <v>80</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="F31" s="5">
-        <v>33100</v>
+        <v>81</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>514</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>279</v>
+        <v>546</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>28</v>
+        <v>511</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>289</v>
+        <v>547</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>290</v>
+        <v>548</v>
       </c>
       <c r="F32" s="5">
-        <v>39042</v>
+        <v>33100</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>32</v>
+        <v>514</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>523</v>
+        <v>279</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>339</v>
+        <v>289</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>36</v>
+        <v>290</v>
       </c>
       <c r="F33" s="5">
-        <v>20121</v>
+        <v>39042</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>338</v>
+        <v>523</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>34</v>
@@ -3038,7 +3053,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>33</v>
+        <v>338</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>34</v>
@@ -3047,13 +3062,13 @@
         <v>8</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>35</v>
+        <v>339</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F35" s="5" t="s">
-        <v>37</v>
+      <c r="F35" s="5">
+        <v>20121</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>38</v>
@@ -3061,45 +3076,45 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>221</v>
+        <v>33</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>222</v>
+        <v>35</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>180</v>
+        <v>37</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>116</v>
+        <v>221</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>118</v>
+        <v>222</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>119</v>
+        <v>10</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>77</v>
@@ -3107,7 +3122,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>527</v>
+        <v>116</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>117</v>
@@ -3121,8 +3136,8 @@
       <c r="E38" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F38" s="5">
-        <v>65125</v>
+      <c r="F38" s="5" t="s">
+        <v>120</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>77</v>
@@ -3130,7 +3145,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>254</v>
+        <v>527</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>117</v>
@@ -3144,8 +3159,8 @@
       <c r="E39" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F39" s="5" t="s">
-        <v>120</v>
+      <c r="F39" s="5">
+        <v>65125</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>77</v>
@@ -3153,145 +3168,145 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>62</v>
+        <v>254</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>150</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>521</v>
+        <v>145</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>522</v>
+        <v>147</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F42" s="5">
-        <v>20033</v>
+        <v>148</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>291</v>
+        <v>521</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>292</v>
+        <v>34</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>293</v>
+        <v>522</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>294</v>
+        <v>36</v>
       </c>
       <c r="F43" s="5">
-        <v>60035</v>
+        <v>20033</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>585</v>
+        <v>291</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>117</v>
+        <v>292</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>118</v>
+        <v>293</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>119</v>
+        <v>294</v>
       </c>
       <c r="F44" s="5">
-        <v>65125</v>
+        <v>60035</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>77</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>215</v>
+        <v>118</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>36</v>
+        <v>119</v>
       </c>
       <c r="F45" s="5">
-        <v>20124</v>
+        <v>65125</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>541</v>
+        <v>557</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>34</v>
@@ -3300,21 +3315,21 @@
         <v>8</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>542</v>
+        <v>215</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F46" s="5">
-        <v>20121</v>
+        <v>20124</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>34</v>
@@ -3337,7 +3352,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>34</v>
@@ -3360,53 +3375,53 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>499</v>
+        <v>559</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C49" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>500</v>
+        <v>542</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F49" s="5">
-        <v>10143</v>
+        <v>20121</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>389</v>
+        <v>499</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C50" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F50" s="5">
-        <v>20123</v>
+        <v>10143</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>437</v>
+        <v>389</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>34</v>
@@ -3429,7 +3444,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>397</v>
+        <v>437</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>34</v>
@@ -3452,7 +3467,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>269</v>
+        <v>397</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>34</v>
@@ -3466,8 +3481,8 @@
       <c r="E53" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F53" s="5" t="s">
-        <v>61</v>
+      <c r="F53" s="5">
+        <v>20123</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>38</v>
@@ -3475,7 +3490,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>137</v>
+        <v>269</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>34</v>
@@ -3484,13 +3499,13 @@
         <v>8</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>38</v>
@@ -3498,7 +3513,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>409</v>
+        <v>137</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>34</v>
@@ -3512,8 +3527,8 @@
       <c r="E55" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F55" s="5">
-        <v>20121</v>
+      <c r="F55" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>38</v>
@@ -3521,214 +3536,214 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>138</v>
+        <v>409</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>142</v>
+        <v>36</v>
+      </c>
+      <c r="F56" s="5">
+        <v>20121</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>444</v>
+        <v>125</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F58" s="5">
-        <v>20158</v>
+        <v>19</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>225</v>
+        <v>444</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F59" s="5">
+        <v>20158</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>86</v>
+        <v>226</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>583</v>
+        <v>84</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>264</v>
+        <v>85</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>584</v>
+        <v>86</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="F61" s="5">
-        <v>38123</v>
+        <v>87</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>268</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>544</v>
+        <v>583</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>9</v>
+        <v>264</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>545</v>
+        <v>584</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>180</v>
+        <v>408</v>
+      </c>
+      <c r="F62" s="5">
+        <v>38123</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>77</v>
+        <v>268</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>487</v>
+        <v>544</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>488</v>
+        <v>9</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>489</v>
+        <v>545</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="F63" s="5">
-        <v>26015</v>
+        <v>10</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>558</v>
+        <v>487</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>9</v>
+        <v>488</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>335</v>
+        <v>489</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>218</v>
+        <v>490</v>
+      </c>
+      <c r="F64" s="5">
+        <v>26015</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>334</v>
+        <v>558</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>9</v>
@@ -3742,7 +3757,7 @@
       <c r="E65" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F65" s="5" t="s">
+      <c r="F65" s="8" t="s">
         <v>218</v>
       </c>
       <c r="G65" s="4" t="s">
@@ -3751,145 +3766,145 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>592</v>
+        <v>334</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>593</v>
+        <v>335</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F66" s="5">
-        <v>20122</v>
+        <v>10</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>300</v>
+        <v>592</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>296</v>
+        <v>34</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>301</v>
+        <v>593</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>302</v>
+        <v>36</v>
       </c>
       <c r="F67" s="5">
-        <v>56025</v>
+        <v>20122</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>299</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>9</v>
+        <v>296</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>273</v>
+        <v>302</v>
+      </c>
+      <c r="F68" s="5">
+        <v>56025</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>11</v>
+        <v>299</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>375</v>
+        <v>271</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>376</v>
+        <v>272</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F69" s="5">
-        <v>20121</v>
+        <v>10</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>280</v>
+        <v>375</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>303</v>
+        <v>376</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>304</v>
+        <v>36</v>
       </c>
       <c r="F70" s="5">
-        <v>24060</v>
+        <v>20121</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>150</v>
+        <v>38</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>481</v>
+        <v>280</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>36</v>
+        <v>304</v>
       </c>
       <c r="F71" s="5">
-        <v>20121</v>
+        <v>24060</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>175</v>
+        <v>481</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>34</v>
@@ -3898,21 +3913,21 @@
         <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>157</v>
+        <v>258</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F72" s="5" t="s">
-        <v>158</v>
+      <c r="F72" s="5">
+        <v>20121</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>34</v>
@@ -3935,7 +3950,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>253</v>
+        <v>156</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>34</v>
@@ -3944,21 +3959,21 @@
         <v>8</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>439</v>
+        <v>253</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>34</v>
@@ -3967,228 +3982,228 @@
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>440</v>
+        <v>230</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F75" s="5">
-        <v>20122</v>
+      <c r="F75" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>245</v>
+        <v>439</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>247</v>
+        <v>440</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>249</v>
+        <v>36</v>
+      </c>
+      <c r="F76" s="5">
+        <v>20122</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>250</v>
+        <v>38</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>81</v>
+        <v>248</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>83</v>
+        <v>250</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>362</v>
+        <v>251</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>364</v>
+        <v>252</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="F78" s="5">
-        <v>76123</v>
+        <v>81</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>425</v>
+        <v>362</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>28</v>
+        <v>363</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>132</v>
+        <v>364</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>30</v>
+        <v>365</v>
       </c>
       <c r="F79" s="5">
-        <v>39100</v>
+        <v>76123</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>551</v>
+        <v>425</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>552</v>
+        <v>28</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>553</v>
+        <v>132</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>555</v>
+        <v>30</v>
+      </c>
+      <c r="F80" s="5">
+        <v>39100</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>391</v>
+        <v>551</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>40</v>
+        <v>552</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>392</v>
+        <v>553</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F81" s="5">
-        <v>70043</v>
+        <v>554</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>555</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>219</v>
+        <v>391</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>220</v>
+        <v>392</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
+      </c>
+      <c r="F82" s="5">
+        <v>70043</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>50</v>
+        <v>219</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>34</v>
@@ -4197,13 +4212,13 @@
         <v>8</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G85" s="4" t="s">
         <v>38</v>
@@ -4211,7 +4226,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>34</v>
@@ -4234,7 +4249,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>34</v>
@@ -4257,99 +4272,99 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>371</v>
+        <v>130</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>372</v>
+        <v>34</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>373</v>
+        <v>122</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="F88" s="5">
-        <v>61121</v>
+        <v>36</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>201</v>
+        <v>371</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>34</v>
+        <v>372</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>189</v>
+        <v>373</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>190</v>
+        <v>374</v>
+      </c>
+      <c r="F89" s="5">
+        <v>61121</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>506</v>
+        <v>201</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="C90" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C90" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>508</v>
+        <v>189</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="F90" s="5">
-        <v>35010</v>
+        <v>36</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>505</v>
+        <v>159</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>281</v>
+        <v>506</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C91" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>305</v>
+        <v>508</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>36</v>
+        <v>507</v>
       </c>
       <c r="F91" s="5">
-        <v>20123</v>
+        <v>35010</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>38</v>
+        <v>505</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>565</v>
+        <v>281</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>34</v>
@@ -4358,13 +4373,13 @@
         <v>8</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>564</v>
+        <v>305</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F92" s="5">
-        <v>20122</v>
+        <v>20123</v>
       </c>
       <c r="G92" s="4" t="s">
         <v>38</v>
@@ -4372,25 +4387,25 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>351</v>
+        <v>565</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>353</v>
+        <v>564</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>354</v>
+        <v>36</v>
       </c>
       <c r="F93" s="5">
-        <v>15033</v>
+        <v>20122</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
@@ -4418,76 +4433,76 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>535</v>
+        <v>351</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>117</v>
+        <v>352</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>536</v>
+        <v>353</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>119</v>
+        <v>354</v>
       </c>
       <c r="F95" s="5">
-        <v>65127</v>
+        <v>15033</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>59</v>
+        <v>535</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>60</v>
+        <v>536</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>61</v>
+        <v>119</v>
+      </c>
+      <c r="F96" s="5">
+        <v>65127</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>336</v>
+        <v>59</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>337</v>
+        <v>60</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F97" s="5">
-        <v>10153</v>
+        <v>36</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>430</v>
+        <v>336</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>79</v>
@@ -4510,76 +4525,76 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>573</v>
+        <v>430</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>574</v>
+        <v>337</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F99" s="5">
-        <v>20154</v>
+        <v>10153</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>159</v>
+        <v>83</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>282</v>
+        <v>573</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>306</v>
+        <v>574</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F100" s="5">
-        <v>183</v>
+        <v>20154</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>307</v>
+        <v>159</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>210</v>
+        <v>282</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>211</v>
+        <v>306</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>58</v>
+        <v>10</v>
+      </c>
+      <c r="F101" s="5">
+        <v>183</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>549</v>
+        <v>210</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>34</v>
@@ -4588,21 +4603,21 @@
         <v>8</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>550</v>
+        <v>211</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F102" s="5">
-        <v>20154</v>
+      <c r="F102" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>275</v>
+        <v>549</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>34</v>
@@ -4611,13 +4626,13 @@
         <v>8</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>276</v>
+        <v>550</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F103" s="5" t="s">
-        <v>158</v>
+      <c r="F103" s="5">
+        <v>20154</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>159</v>
@@ -4625,30 +4640,30 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>128</v>
+        <v>275</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>129</v>
+        <v>276</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>242</v>
+        <v>128</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>28</v>
@@ -4671,168 +4686,168 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>414</v>
+        <v>242</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>415</v>
+        <v>129</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>180</v>
+        <v>31</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>274</v>
+        <v>414</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>29</v>
+        <v>415</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>31</v>
+        <v>180</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>239</v>
+        <v>29</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>241</v>
+        <v>31</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>150</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>537</v>
+        <v>238</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>538</v>
+        <v>146</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>539</v>
+        <v>239</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="F109" s="5">
-        <v>34133</v>
+        <v>240</v>
+      </c>
+      <c r="F109" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>514</v>
+        <v>150</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>435</v>
+        <v>598</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>129</v>
+        <v>599</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F110" s="5">
-        <v>39100</v>
+        <v>20122</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>206</v>
+        <v>537</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>34</v>
+        <v>538</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>60</v>
+        <v>539</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F111" s="5" t="s">
-        <v>61</v>
+        <v>540</v>
+      </c>
+      <c r="F111" s="5">
+        <v>34133</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>38</v>
+        <v>514</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>366</v>
+        <v>435</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F112" s="5">
-        <v>20123</v>
+        <v>39100</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>101</v>
+        <v>206</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>34</v>
@@ -4855,122 +4870,122 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>493</v>
+        <v>366</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>494</v>
+        <v>60</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F114" s="8" t="s">
-        <v>273</v>
+        <v>36</v>
+      </c>
+      <c r="F114" s="5">
+        <v>20123</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>519</v>
+        <v>101</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>520</v>
+        <v>60</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F115" s="5">
-        <v>80121</v>
+        <v>36</v>
+      </c>
+      <c r="F115" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>406</v>
+        <v>493</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>407</v>
+        <v>494</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="F116" s="5">
-        <v>38121</v>
+        <v>10</v>
+      </c>
+      <c r="F116" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>369</v>
+        <v>519</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>370</v>
+        <v>520</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F117" s="5">
-        <v>20123</v>
+        <v>80121</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>360</v>
+        <v>406</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>17</v>
+        <v>264</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>361</v>
+        <v>407</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>19</v>
+        <v>408</v>
       </c>
       <c r="F118" s="5">
-        <v>90139</v>
+        <v>38121</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>12</v>
+        <v>268</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>34</v>
@@ -4979,7 +4994,7 @@
         <v>8</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>195</v>
+        <v>370</v>
       </c>
       <c r="E119" s="4" t="s">
         <v>36</v>
@@ -4993,53 +5008,53 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>455</v>
+        <v>360</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>456</v>
+        <v>361</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F120" s="8" t="s">
-        <v>180</v>
+        <v>19</v>
+      </c>
+      <c r="F120" s="5">
+        <v>90139</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>283</v>
+        <v>345</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>309</v>
+        <v>195</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>310</v>
+        <v>36</v>
       </c>
       <c r="F121" s="5">
-        <v>12037</v>
+        <v>20123</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>13</v>
+        <v>455</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>9</v>
@@ -5048,90 +5063,90 @@
         <v>8</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>14</v>
+        <v>456</v>
       </c>
       <c r="E122" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F122" s="5" t="s">
-        <v>15</v>
+      <c r="F122" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>123</v>
+        <v>283</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>28</v>
+        <v>308</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>55</v>
+        <v>309</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F123" s="5" t="s">
-        <v>31</v>
+        <v>310</v>
+      </c>
+      <c r="F123" s="5">
+        <v>12037</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>32</v>
+        <v>307</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>28</v>
@@ -5140,7 +5155,7 @@
         <v>8</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E126" s="4" t="s">
         <v>30</v>
@@ -5154,122 +5169,122 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>498</v>
+        <v>74</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C127" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C127" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F127" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>233</v>
+        <v>27</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>234</v>
+        <v>29</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>218</v>
+        <v>31</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>590</v>
+        <v>498</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C129" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>591</v>
+        <v>29</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F129" s="5">
-        <v>20122</v>
+        <v>39100</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>188</v>
+        <v>233</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>189</v>
+        <v>234</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>483</v>
+        <v>590</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>484</v>
+        <v>34</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>485</v>
+        <v>591</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>486</v>
+        <v>36</v>
       </c>
       <c r="F131" s="5">
-        <v>66020</v>
+        <v>20122</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>576</v>
+        <v>188</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>34</v>
@@ -5278,13 +5293,13 @@
         <v>8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>577</v>
+        <v>189</v>
       </c>
       <c r="E132" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F132" s="5">
-        <v>20124</v>
+      <c r="F132" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G132" s="4" t="s">
         <v>159</v>
@@ -5292,168 +5307,168 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>411</v>
+        <v>483</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>341</v>
+        <v>484</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>412</v>
+        <v>485</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>413</v>
+        <v>486</v>
       </c>
       <c r="F133" s="5">
-        <v>37137</v>
+        <v>66020</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>343</v>
+        <v>77</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>460</v>
+        <v>576</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>461</v>
+        <v>577</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F134" s="8" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F134" s="5">
+        <v>20124</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>295</v>
+        <v>411</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>296</v>
+        <v>341</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>297</v>
+        <v>412</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>298</v>
+        <v>413</v>
       </c>
       <c r="F135" s="5">
-        <v>56010</v>
+        <v>37137</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>299</v>
+        <v>343</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>311</v>
+        <v>460</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>312</v>
+        <v>461</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="F136" s="5">
-        <v>40060</v>
+        <v>10</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>384</v>
+        <v>295</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>36</v>
+        <v>298</v>
       </c>
       <c r="F137" s="5">
-        <v>20121</v>
+        <v>56010</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>38</v>
+        <v>299</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>386</v>
+        <v>311</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>385</v>
+        <v>312</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>58</v>
+        <v>313</v>
+      </c>
+      <c r="F138" s="5">
+        <v>40060</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>213</v>
+        <v>384</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>179</v>
+        <v>385</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F139" s="5" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F139" s="5">
+        <v>20121</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>575</v>
+        <v>386</v>
       </c>
       <c r="B140" s="4" t="s">
         <v>34</v>
@@ -5462,228 +5477,228 @@
         <v>8</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>192</v>
+        <v>385</v>
       </c>
       <c r="E140" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F140" s="5">
-        <v>20124</v>
+      <c r="F140" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>589</v>
+        <v>213</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F141" s="5">
-        <v>20124</v>
+        <v>10</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>68</v>
+        <v>575</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>72</v>
+        <v>36</v>
+      </c>
+      <c r="F142" s="5">
+        <v>20124</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>284</v>
+        <v>589</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>314</v>
+        <v>34</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>315</v>
+        <v>192</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>316</v>
+        <v>36</v>
       </c>
       <c r="F143" s="5">
-        <v>57021</v>
+        <v>20124</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>299</v>
+        <v>159</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>179</v>
+        <v>70</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>462</v>
+        <v>284</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>9</v>
+        <v>314</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>179</v>
+        <v>315</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F145" s="8" t="s">
-        <v>180</v>
+        <v>316</v>
+      </c>
+      <c r="F145" s="5">
+        <v>57021</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>77</v>
+        <v>299</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>346</v>
+        <v>462</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>347</v>
+        <v>179</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="F147" s="5">
-        <v>70124</v>
+        <v>10</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>333</v>
+        <v>89</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F148" s="5">
-        <v>20158</v>
+        <v>92</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>159</v>
+        <v>94</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>308</v>
+        <v>40</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="F149" s="5">
-        <v>12084</v>
+        <v>70124</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>307</v>
+        <v>44</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>34</v>
@@ -5692,182 +5707,182 @@
         <v>8</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F150" s="5" t="s">
-        <v>61</v>
+      <c r="F150" s="5">
+        <v>20158</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>227</v>
+        <v>357</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>228</v>
+        <v>358</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F151" s="5" t="s">
-        <v>37</v>
+        <v>359</v>
+      </c>
+      <c r="F151" s="5">
+        <v>12084</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>457</v>
+        <v>194</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>458</v>
+        <v>195</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F152" s="8" t="s">
-        <v>459</v>
+        <v>36</v>
+      </c>
+      <c r="F152" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>108</v>
+        <v>227</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="F154" s="5">
-        <v>12100</v>
+        <v>10</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>459</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>395</v>
+        <v>108</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F155" s="5">
-        <v>40127</v>
+        <v>111</v>
+      </c>
+      <c r="F155" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>355</v>
+        <v>431</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>356</v>
+        <v>432</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>36</v>
+        <v>433</v>
       </c>
       <c r="F156" s="5">
-        <v>20121</v>
+        <v>12100</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>556</v>
+        <v>395</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>525</v>
+        <v>23</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F157" s="5">
-        <v>20154</v>
+        <v>40127</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>526</v>
+        <v>355</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>34</v>
@@ -5876,21 +5891,21 @@
         <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>525</v>
+        <v>356</v>
       </c>
       <c r="E158" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F158" s="5">
-        <v>20154</v>
+        <v>20121</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>524</v>
+        <v>556</v>
       </c>
       <c r="B159" s="4" t="s">
         <v>34</v>
@@ -5913,7 +5928,7 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>596</v>
+        <v>526</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>34</v>
@@ -5922,7 +5937,7 @@
         <v>8</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>597</v>
+        <v>525</v>
       </c>
       <c r="E160" s="4" t="s">
         <v>36</v>
@@ -5936,99 +5951,99 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>29</v>
+        <v>525</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F161" s="5">
-        <v>39100</v>
+        <v>20154</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>232</v>
+        <v>596</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>29</v>
+        <v>597</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F162" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F162" s="5">
+        <v>20154</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>143</v>
+        <v>515</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>37</v>
+        <v>30</v>
+      </c>
+      <c r="F163" s="5">
+        <v>39100</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>56</v>
+        <v>232</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>441</v>
+        <v>143</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>34</v>
@@ -6037,159 +6052,159 @@
         <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>442</v>
+        <v>144</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="F165" s="5">
-        <v>20038</v>
+        <v>36</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>426</v>
+        <v>56</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F166" s="5">
-        <v>10121</v>
+        <v>36</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>95</v>
+        <v>441</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>97</v>
+        <v>442</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>99</v>
+        <v>443</v>
+      </c>
+      <c r="F167" s="5">
+        <v>20038</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>377</v>
+        <v>426</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>379</v>
+        <v>236</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>380</v>
+        <v>81</v>
       </c>
       <c r="F168" s="5">
-        <v>64020</v>
+        <v>10121</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>580</v>
+        <v>95</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>581</v>
+        <v>97</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F169" s="8" t="s">
-        <v>582</v>
+        <v>98</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>11</v>
+        <v>100</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>34</v>
+        <v>378</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>211</v>
+        <v>379</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>36</v>
+        <v>380</v>
       </c>
       <c r="F170" s="5">
-        <v>20121</v>
+        <v>64020</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>133</v>
+        <v>580</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>134</v>
+        <v>581</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F171" s="5" t="s">
-        <v>135</v>
+        <v>10</v>
+      </c>
+      <c r="F171" s="8" t="s">
+        <v>582</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>136</v>
+        <v>11</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>257</v>
+        <v>410</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>34</v>
@@ -6198,13 +6213,13 @@
         <v>8</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>258</v>
+        <v>211</v>
       </c>
       <c r="E172" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F172" s="5" t="s">
-        <v>58</v>
+      <c r="F172" s="5">
+        <v>20121</v>
       </c>
       <c r="G172" s="4" t="s">
         <v>38</v>
@@ -6212,30 +6227,30 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>340</v>
+        <v>133</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>342</v>
+        <v>134</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="F173" s="5">
-        <v>37045</v>
+        <v>36</v>
+      </c>
+      <c r="F173" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>343</v>
+        <v>136</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>166</v>
+        <v>257</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>34</v>
@@ -6244,44 +6259,44 @@
         <v>8</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>167</v>
+        <v>258</v>
       </c>
       <c r="E174" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>168</v>
+        <v>58</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>529</v>
+        <v>340</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>167</v>
+        <v>342</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>36</v>
+        <v>528</v>
       </c>
       <c r="F175" s="5">
-        <v>20126</v>
+        <v>37045</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>159</v>
+        <v>343</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>594</v>
+        <v>166</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>34</v>
@@ -6290,21 +6305,21 @@
         <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>394</v>
+        <v>167</v>
       </c>
       <c r="E176" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F176" s="5">
-        <v>20123</v>
+      <c r="F176" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>471</v>
+        <v>529</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>34</v>
@@ -6313,21 +6328,21 @@
         <v>8</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E177" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F177" s="5">
-        <v>20135</v>
+        <v>20126</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>405</v>
+        <v>601</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>34</v>
@@ -6336,13 +6351,13 @@
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>260</v>
+        <v>602</v>
       </c>
       <c r="E178" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F178" s="5">
-        <v>20135</v>
+        <v>20138</v>
       </c>
       <c r="G178" s="4" t="s">
         <v>262</v>
@@ -6350,30 +6365,30 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>204</v>
+        <v>594</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>205</v>
+        <v>394</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F179" s="5" t="s">
-        <v>187</v>
+        <v>36</v>
+      </c>
+      <c r="F179" s="5">
+        <v>20123</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>319</v>
+        <v>38</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>34</v>
@@ -6382,21 +6397,21 @@
         <v>8</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>454</v>
+        <v>260</v>
       </c>
       <c r="E180" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F180" s="5">
-        <v>20144</v>
+        <v>20135</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>223</v>
+        <v>405</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>34</v>
@@ -6405,389 +6420,389 @@
         <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="E181" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F181" s="5" t="s">
-        <v>135</v>
+      <c r="F181" s="5">
+        <v>20135</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>136</v>
+        <v>262</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>285</v>
+        <v>204</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>22</v>
+        <v>185</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>317</v>
+        <v>205</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F182" s="5">
-        <v>40026</v>
+        <v>186</v>
+      </c>
+      <c r="F182" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>26</v>
+        <v>319</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>286</v>
+        <v>453</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>320</v>
+        <v>454</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F183" s="5" t="s">
-        <v>323</v>
+        <v>36</v>
+      </c>
+      <c r="F183" s="5">
+        <v>20144</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>533</v>
+        <v>223</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F184" s="5">
-        <v>39100</v>
+        <v>36</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>32</v>
+        <v>136</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>367</v>
+        <v>285</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>368</v>
+        <v>317</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="F185" s="5">
-        <v>20123</v>
+        <v>40026</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="F186" s="5">
-        <v>12020</v>
+        <v>10</v>
+      </c>
+      <c r="F186" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>307</v>
+        <v>11</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>39</v>
+        <v>533</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F187" s="5" t="s">
-        <v>43</v>
+        <v>30</v>
+      </c>
+      <c r="F187" s="5">
+        <v>39100</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>422</v>
+        <v>34</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>423</v>
+        <v>368</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>424</v>
+        <v>36</v>
       </c>
       <c r="F188" s="5">
-        <v>28053</v>
+        <v>20123</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>172</v>
+        <v>287</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>169</v>
+        <v>321</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F189" s="10" t="s">
-        <v>171</v>
+        <v>322</v>
+      </c>
+      <c r="F189" s="10">
+        <v>12020</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>159</v>
+        <v>307</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>560</v>
+        <v>39</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>561</v>
+        <v>41</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F190" s="10">
-        <v>39100</v>
+        <v>42</v>
+      </c>
+      <c r="F190" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>198</v>
+        <v>421</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>22</v>
+        <v>422</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>199</v>
+        <v>423</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F191" s="10" t="s">
-        <v>200</v>
+        <v>424</v>
+      </c>
+      <c r="F191" s="10">
+        <v>28053</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="F192" s="10" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>244</v>
+        <v>560</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>177</v>
+        <v>561</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F193" s="10" t="s">
-        <v>58</v>
+        <v>30</v>
+      </c>
+      <c r="F193" s="10">
+        <v>39100</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
-        <v>534</v>
+        <v>198</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C194" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="E194" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F194" s="10">
-        <v>20121</v>
+        <v>24</v>
+      </c>
+      <c r="F194" s="10" t="s">
+        <v>200</v>
       </c>
       <c r="G194" s="9" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
-        <v>578</v>
+        <v>207</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C195" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>579</v>
+        <v>208</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F195" s="10">
-        <v>20121</v>
+        <v>71</v>
+      </c>
+      <c r="F195" s="10" t="s">
+        <v>209</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
-        <v>445</v>
+        <v>244</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="C196" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>447</v>
+        <v>177</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="F196" s="10">
-        <v>53048</v>
+        <v>36</v>
+      </c>
+      <c r="F196" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>449</v>
+        <v>38</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>509</v>
+        <v>34</v>
       </c>
       <c r="C197" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>517</v>
+        <v>177</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>518</v>
+        <v>36</v>
       </c>
       <c r="F197" s="10">
-        <v>35011</v>
+        <v>20121</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>505</v>
+        <v>38</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>243</v>
+        <v>578</v>
       </c>
       <c r="B198" s="9" t="s">
         <v>34</v>
@@ -6796,13 +6811,13 @@
         <v>8</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>177</v>
+        <v>579</v>
       </c>
       <c r="E198" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F198" s="10" t="s">
-        <v>58</v>
+      <c r="F198" s="10">
+        <v>20121</v>
       </c>
       <c r="G198" s="9" t="s">
         <v>38</v>
@@ -6810,99 +6825,99 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>131</v>
+        <v>445</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>28</v>
+        <v>446</v>
       </c>
       <c r="C199" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>132</v>
+        <v>447</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F199" s="10" t="s">
-        <v>31</v>
+        <v>448</v>
+      </c>
+      <c r="F199" s="10">
+        <v>53048</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>32</v>
+        <v>449</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
-        <v>531</v>
+        <v>516</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>34</v>
+        <v>509</v>
       </c>
       <c r="C200" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>532</v>
+        <v>517</v>
       </c>
       <c r="E200" s="9" t="s">
-        <v>36</v>
+        <v>518</v>
       </c>
       <c r="F200" s="10">
-        <v>20121</v>
+        <v>35011</v>
       </c>
       <c r="G200" s="9" t="s">
-        <v>38</v>
+        <v>505</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="9" t="s">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C201" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D201" s="9" t="s">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F201" s="10" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A202" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="B202" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C202" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D202" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="E202" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F202" s="11" t="s">
-        <v>568</v>
-      </c>
-      <c r="G202" s="3" t="s">
-        <v>77</v>
+      <c r="A202" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B202" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C202" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D202" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E202" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F202" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G202" s="9" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="9" t="s">
-        <v>381</v>
+        <v>531</v>
       </c>
       <c r="B203" s="9" t="s">
         <v>34</v>
@@ -6911,13 +6926,13 @@
         <v>8</v>
       </c>
       <c r="D203" s="9" t="s">
-        <v>382</v>
+        <v>532</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>383</v>
+        <v>36</v>
       </c>
       <c r="F203" s="10">
-        <v>20089</v>
+        <v>20121</v>
       </c>
       <c r="G203" s="9" t="s">
         <v>38</v>
@@ -6925,53 +6940,53 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
-        <v>475</v>
+        <v>21</v>
       </c>
       <c r="B204" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C204" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D204" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E204" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F204" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G204" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A205" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B205" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C204" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D204" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="E204" s="9" t="s">
+      <c r="C205" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="E205" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F204" s="12" t="s">
-        <v>477</v>
-      </c>
-      <c r="G204" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A205" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="B205" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C205" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D205" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="E205" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F205" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="G205" s="9" t="s">
-        <v>26</v>
+      <c r="F205" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="9" t="s">
-        <v>214</v>
+        <v>381</v>
       </c>
       <c r="B206" s="9" t="s">
         <v>34</v>
@@ -6980,67 +6995,67 @@
         <v>8</v>
       </c>
       <c r="D206" s="9" t="s">
-        <v>215</v>
+        <v>382</v>
       </c>
       <c r="E206" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F206" s="10" t="s">
-        <v>158</v>
+        <v>383</v>
+      </c>
+      <c r="F206" s="10">
+        <v>20089</v>
       </c>
       <c r="G206" s="9" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C207" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D207" s="9" t="s">
-        <v>215</v>
+        <v>476</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F207" s="10">
-        <v>20124</v>
+        <v>10</v>
+      </c>
+      <c r="F207" s="12" t="s">
+        <v>477</v>
       </c>
       <c r="G207" s="9" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="9" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C208" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D208" s="9" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="E208" s="9" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F208" s="10" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="G208" s="9" t="s">
-        <v>136</v>
+        <v>26</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="9" t="s">
-        <v>256</v>
+        <v>214</v>
       </c>
       <c r="B209" s="9" t="s">
         <v>34</v>
@@ -7049,21 +7064,21 @@
         <v>8</v>
       </c>
       <c r="D209" s="9" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E209" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F209" s="10" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G209" s="9" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="9" t="s">
-        <v>472</v>
+        <v>438</v>
       </c>
       <c r="B210" s="9" t="s">
         <v>34</v>
@@ -7072,21 +7087,21 @@
         <v>8</v>
       </c>
       <c r="D210" s="9" t="s">
-        <v>464</v>
+        <v>215</v>
       </c>
       <c r="E210" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F210" s="10">
-        <v>20129</v>
+        <v>20124</v>
       </c>
       <c r="G210" s="9" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="9" t="s">
-        <v>463</v>
+        <v>229</v>
       </c>
       <c r="B211" s="9" t="s">
         <v>34</v>
@@ -7095,21 +7110,21 @@
         <v>8</v>
       </c>
       <c r="D211" s="9" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E211" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F211" s="10">
-        <v>20129</v>
+      <c r="F211" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="G211" s="9" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="9" t="s">
-        <v>473</v>
+        <v>256</v>
       </c>
       <c r="B212" s="9" t="s">
         <v>34</v>
@@ -7118,21 +7133,21 @@
         <v>8</v>
       </c>
       <c r="D212" s="9" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E212" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F212" s="10">
-        <v>20129</v>
+      <c r="F212" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="G212" s="9" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="9" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B213" s="9" t="s">
         <v>34</v>
@@ -7155,7 +7170,7 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="9" t="s">
-        <v>176</v>
+        <v>463</v>
       </c>
       <c r="B214" s="9" t="s">
         <v>34</v>
@@ -7164,128 +7179,128 @@
         <v>8</v>
       </c>
       <c r="D214" s="9" t="s">
-        <v>177</v>
+        <v>464</v>
       </c>
       <c r="E214" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F214" s="10" t="s">
-        <v>58</v>
+      <c r="F214" s="10">
+        <v>20129</v>
       </c>
       <c r="G214" s="9" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="9" t="s">
-        <v>331</v>
+        <v>473</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C215" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D215" s="9" t="s">
-        <v>332</v>
+        <v>464</v>
       </c>
       <c r="E215" s="9" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F215" s="10">
-        <v>40026</v>
+        <v>20129</v>
       </c>
       <c r="G215" s="9" t="s">
-        <v>26</v>
+        <v>262</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="9" t="s">
-        <v>288</v>
+        <v>474</v>
       </c>
       <c r="B216" s="9" t="s">
         <v>34</v>
       </c>
       <c r="C216" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D216" s="9" t="s">
-        <v>324</v>
+        <v>464</v>
       </c>
       <c r="E216" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F216" s="10">
-        <v>20124</v>
+        <v>20129</v>
       </c>
       <c r="G216" s="9" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
-        <v>450</v>
+        <v>176</v>
       </c>
       <c r="B217" s="9" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C217" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D217" s="9" t="s">
-        <v>451</v>
+        <v>177</v>
       </c>
       <c r="E217" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="F217" s="10">
-        <v>12011</v>
+        <v>36</v>
+      </c>
+      <c r="F217" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="G217" s="9" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="9" t="s">
-        <v>151</v>
+        <v>331</v>
       </c>
       <c r="B218" s="9" t="s">
-        <v>152</v>
+        <v>22</v>
       </c>
       <c r="C218" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D218" s="9" t="s">
-        <v>153</v>
+        <v>332</v>
       </c>
       <c r="E218" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="F218" s="10" t="s">
-        <v>155</v>
+        <v>318</v>
+      </c>
+      <c r="F218" s="10">
+        <v>40026</v>
       </c>
       <c r="G218" s="9" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="9" t="s">
-        <v>419</v>
+        <v>288</v>
       </c>
       <c r="B219" s="9" t="s">
         <v>34</v>
       </c>
       <c r="C219" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D219" s="9" t="s">
-        <v>420</v>
+        <v>324</v>
       </c>
       <c r="E219" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F219" s="10">
-        <v>20123</v>
+        <v>20124</v>
       </c>
       <c r="G219" s="9" t="s">
         <v>38</v>
@@ -7293,329 +7308,329 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="9" t="s">
-        <v>491</v>
+        <v>450</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="C220" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D220" s="9" t="s">
-        <v>492</v>
+        <v>451</v>
       </c>
       <c r="E220" s="9" t="s">
-        <v>19</v>
+        <v>452</v>
       </c>
       <c r="F220" s="10">
-        <v>90141</v>
+        <v>12011</v>
       </c>
       <c r="G220" s="9" t="s">
-        <v>12</v>
+        <v>307</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="9" t="s">
-        <v>480</v>
+        <v>151</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>9</v>
+        <v>152</v>
       </c>
       <c r="C221" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D221" s="9" t="s">
-        <v>388</v>
+        <v>153</v>
       </c>
       <c r="E221" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F221" s="12" t="s">
-        <v>390</v>
+        <v>154</v>
+      </c>
+      <c r="F221" s="10" t="s">
+        <v>155</v>
       </c>
       <c r="G221" s="9" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A222" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="B222" s="3" t="s">
-        <v>9</v>
+      <c r="A222" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="B222" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="C222" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D222" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E222" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F222" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="G222" s="3" t="s">
-        <v>11</v>
+      <c r="D222" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="E222" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F222" s="10">
+        <v>20123</v>
+      </c>
+      <c r="G222" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="9" t="s">
-        <v>387</v>
+        <v>491</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C223" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D223" s="9" t="s">
-        <v>388</v>
+        <v>492</v>
       </c>
       <c r="E223" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F223" s="10" t="s">
-        <v>390</v>
+        <v>19</v>
+      </c>
+      <c r="F223" s="10">
+        <v>90141</v>
       </c>
       <c r="G223" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="9" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
       <c r="C224" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D224" s="9" t="s">
-        <v>466</v>
+        <v>388</v>
       </c>
       <c r="E224" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="F224" s="10">
-        <v>38055</v>
+        <v>10</v>
+      </c>
+      <c r="F224" s="12" t="s">
+        <v>390</v>
       </c>
       <c r="G224" s="9" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="3" t="s">
-        <v>572</v>
+        <v>530</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C225" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C225" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>134</v>
+        <v>388</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F225" s="7">
-        <v>20145</v>
+        <v>10</v>
+      </c>
+      <c r="F225" s="11" t="s">
+        <v>390</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>136</v>
+        <v>11</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="9" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
       <c r="B226" s="9" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="C226" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D226" s="9" t="s">
-        <v>428</v>
+        <v>388</v>
       </c>
       <c r="E226" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="F226" s="10">
-        <v>25010</v>
+        <v>10</v>
+      </c>
+      <c r="F226" s="10" t="s">
+        <v>390</v>
       </c>
       <c r="G226" s="9" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="9" t="s">
-        <v>393</v>
+        <v>465</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C227" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D227" s="9" t="s">
-        <v>394</v>
+        <v>466</v>
       </c>
       <c r="E227" s="9" t="s">
-        <v>36</v>
+        <v>467</v>
       </c>
       <c r="F227" s="10">
-        <v>20123</v>
+        <v>38055</v>
       </c>
       <c r="G227" s="9" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A228" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="B228" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C228" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D228" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="E228" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="F228" s="10">
-        <v>71016</v>
-      </c>
-      <c r="G228" s="9" t="s">
-        <v>44</v>
+      <c r="A228" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F228" s="7">
+        <v>20145</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="9" t="s">
-        <v>16</v>
+        <v>427</v>
       </c>
       <c r="B229" s="9" t="s">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="C229" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D229" s="9" t="s">
-        <v>18</v>
+        <v>428</v>
       </c>
       <c r="E229" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F229" s="10" t="s">
-        <v>20</v>
+        <v>429</v>
+      </c>
+      <c r="F229" s="10">
+        <v>25010</v>
       </c>
       <c r="G229" s="9" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="9" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>326</v>
+        <v>34</v>
       </c>
       <c r="C230" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D230" s="9" t="s">
-        <v>327</v>
+        <v>394</v>
       </c>
       <c r="E230" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="F230" s="10" t="s">
-        <v>329</v>
+        <v>36</v>
+      </c>
+      <c r="F230" s="10">
+        <v>20123</v>
       </c>
       <c r="G230" s="9" t="s">
-        <v>330</v>
+        <v>38</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A231" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="B231" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C231" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D231" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="E231" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F231" s="7">
-        <v>20122</v>
-      </c>
-      <c r="G231" s="3" t="s">
-        <v>38</v>
+      <c r="A231" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="B231" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C231" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D231" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="E231" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="F231" s="10">
+        <v>71016</v>
+      </c>
+      <c r="G231" s="9" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="9" t="s">
-        <v>277</v>
+        <v>16</v>
       </c>
       <c r="B232" s="9" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C232" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D232" s="9" t="s">
-        <v>278</v>
+        <v>18</v>
       </c>
       <c r="E232" s="9" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F232" s="10" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G232" s="9" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="9" t="s">
-        <v>478</v>
+        <v>325</v>
       </c>
       <c r="B233" s="9" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="C233" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D233" s="9" t="s">
-        <v>479</v>
+        <v>327</v>
       </c>
       <c r="E233" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F233" s="10">
-        <v>20123</v>
+        <v>328</v>
+      </c>
+      <c r="F233" s="10" t="s">
+        <v>329</v>
       </c>
       <c r="G233" s="9" t="s">
-        <v>38</v>
+        <v>330</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="3" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>34</v>
@@ -7624,13 +7639,13 @@
         <v>8</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>571</v>
+        <v>36</v>
       </c>
       <c r="F234" s="7">
-        <v>20094</v>
+        <v>20122</v>
       </c>
       <c r="G234" s="3" t="s">
         <v>38</v>
@@ -7638,76 +7653,76 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="9" t="s">
-        <v>396</v>
+        <v>277</v>
       </c>
       <c r="B235" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C235" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D235" s="9" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="E235" s="9" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F235" s="10" t="s">
-        <v>218</v>
+        <v>37</v>
       </c>
       <c r="G235" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" s="9" t="s">
-        <v>216</v>
+        <v>478</v>
       </c>
       <c r="B236" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C236" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D236" s="9" t="s">
-        <v>217</v>
+        <v>479</v>
       </c>
       <c r="E236" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F236" s="10" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F236" s="10">
+        <v>20123</v>
       </c>
       <c r="G236" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A237" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="B237" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C237" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D237" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="E237" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="F237" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G237" s="9" t="s">
-        <v>165</v>
+      <c r="A237" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="F237" s="7">
+        <v>20094</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="9" t="s">
-        <v>434</v>
+        <v>396</v>
       </c>
       <c r="B238" s="9" t="s">
         <v>9</v>
@@ -7730,7 +7745,7 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" s="9" t="s">
-        <v>255</v>
+        <v>216</v>
       </c>
       <c r="B239" s="9" t="s">
         <v>9</v>
@@ -7753,30 +7768,99 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B240" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C240" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D240" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E240" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F240" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G240" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A241" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="B241" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C241" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D241" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E241" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F241" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G241" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A242" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B242" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C242" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D242" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E242" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F242" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G242" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A243" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B240" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C240" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D240" s="9" t="s">
+      <c r="B243" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C243" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D243" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E240" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F240" s="10" t="s">
+      <c r="E243" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F243" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G240" s="9" t="s">
+      <c r="G243" s="9" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G218" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G240">
+    <sortState ref="A2:G243">
       <sortCondition ref="A1:A218"/>
     </sortState>
   </autoFilter>
@@ -7789,6 +7873,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F040406D9EE34E48977C379A242BB45D" ma:contentTypeVersion="15" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="1ab2d492e43f6bec9a26aa4599c840e9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="877b7d34-4df7-40bf-9eb1-208952470e96" xmlns:ns4="05fc27dd-4454-4248-9c78-3d72b2b155c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebc604e5d4aadf5a992ba83f8d4fb519" ns3:_="" ns4:_="">
     <xsd:import namespace="877b7d34-4df7-40bf-9eb1-208952470e96"/>
@@ -8021,24 +8122,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBC6436E-C4E7-4E8D-94E8-64DAEC05792B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8055,29 +8164,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="113_{1398BFE9-7F31-4A84-A4C4-391DE17DDF9A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{CAC9979C-EB25-4F45-BBAC-891B54D6A2E5}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{355E0604-0E56-4EB2-AB6D-13C0C65CE765}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="611">
   <si>
     <t>Nome account</t>
   </si>
@@ -1832,6 +1832,30 @@
   </si>
   <si>
     <t>VIA GIANFRANCO MALIPIERO 16-18</t>
+  </si>
+  <si>
+    <t>LANGA SIPSMITH SRL</t>
+  </si>
+  <si>
+    <t>VIA LEONE XIII 14</t>
+  </si>
+  <si>
+    <t>REDEN ALFA SRL</t>
+  </si>
+  <si>
+    <t>PIAZZA CAVOUR 17</t>
+  </si>
+  <si>
+    <t>00193</t>
+  </si>
+  <si>
+    <t>AG 37 SRL</t>
+  </si>
+  <si>
+    <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+  </si>
+  <si>
+    <t>VIA FELICE CAVALLOTTI 13</t>
   </si>
 </sst>
 </file>
@@ -2256,7 +2280,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G243"/>
+  <dimension ref="A1:G247"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -2432,122 +2456,122 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>181</v>
+        <v>608</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>182</v>
+        <v>402</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F8" s="5">
+        <v>20123</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>259</v>
+        <v>181</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>260</v>
+        <v>182</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>262</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>510</v>
+        <v>259</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>511</v>
+        <v>34</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>512</v>
+        <v>260</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="F10" s="5">
-        <v>33050</v>
+        <v>36</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>261</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>514</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>263</v>
+        <v>510</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>264</v>
+        <v>511</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>265</v>
+        <v>512</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>267</v>
+        <v>513</v>
+      </c>
+      <c r="F11" s="5">
+        <v>33050</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>268</v>
+        <v>514</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>600</v>
+        <v>263</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F12" s="5">
-        <v>10121</v>
+        <v>266</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>267</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>83</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>235</v>
+        <v>600</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>79</v>
@@ -2561,8 +2585,8 @@
       <c r="E13" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>237</v>
+      <c r="F13" s="5">
+        <v>10121</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>83</v>
@@ -2570,22 +2594,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>495</v>
+        <v>235</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>496</v>
+        <v>236</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>497</v>
-      </c>
-      <c r="F14" s="5">
-        <v>10098</v>
+        <v>81</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>83</v>
@@ -2593,76 +2617,76 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>45</v>
+        <v>495</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>47</v>
+        <v>496</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>49</v>
+        <v>497</v>
+      </c>
+      <c r="F15" s="5">
+        <v>10098</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>9</v>
@@ -2685,7 +2709,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>9</v>
@@ -2708,7 +2732,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>482</v>
+        <v>196</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>9</v>
@@ -2722,7 +2746,7 @@
       <c r="E20" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="5" t="s">
         <v>180</v>
       </c>
       <c r="G20" s="4" t="s">
@@ -2731,7 +2755,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>197</v>
+        <v>482</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>9</v>
@@ -2745,7 +2769,7 @@
       <c r="E21" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="8" t="s">
         <v>180</v>
       </c>
       <c r="G21" s="4" t="s">
@@ -2754,7 +2778,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>9</v>
@@ -2777,30 +2801,30 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>403</v>
+        <v>183</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>404</v>
+        <v>179</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F23" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>595</v>
+        <v>403</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>28</v>
@@ -2823,76 +2847,76 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>399</v>
+        <v>595</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F25" s="5">
-        <v>20124</v>
+        <v>39100</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>468</v>
+        <v>399</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>469</v>
+        <v>400</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>470</v>
+        <v>36</v>
+      </c>
+      <c r="F26" s="5">
+        <v>20124</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>305</v>
+        <v>469</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F27" s="5">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>470</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>349</v>
+        <v>436</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>34</v>
@@ -2901,13 +2925,13 @@
         <v>8</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>350</v>
+        <v>305</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F28" s="5">
-        <v>20122</v>
+        <v>20123</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>38</v>
@@ -2915,53 +2939,53 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>67</v>
+        <v>349</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>18</v>
+        <v>350</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="F29" s="5">
+        <v>20122</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>398</v>
+        <v>67</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F30" s="5">
-        <v>10123</v>
+        <v>19</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>78</v>
+        <v>398</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>79</v>
@@ -2975,8 +2999,8 @@
       <c r="E31" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>82</v>
+      <c r="F31" s="5">
+        <v>10123</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>83</v>
@@ -2984,76 +3008,76 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>546</v>
+        <v>78</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>511</v>
+        <v>79</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>547</v>
+        <v>80</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="F32" s="5">
-        <v>33100</v>
+        <v>81</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>514</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>279</v>
+        <v>546</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>28</v>
+        <v>511</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>289</v>
+        <v>547</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>290</v>
+        <v>548</v>
       </c>
       <c r="F33" s="5">
-        <v>39042</v>
+        <v>33100</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>32</v>
+        <v>514</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>523</v>
+        <v>279</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>339</v>
+        <v>289</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>36</v>
+        <v>290</v>
       </c>
       <c r="F34" s="5">
-        <v>20121</v>
+        <v>39042</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>338</v>
+        <v>523</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>34</v>
@@ -3076,7 +3100,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>33</v>
+        <v>338</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>34</v>
@@ -3085,13 +3109,13 @@
         <v>8</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>35</v>
+        <v>339</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F36" s="5" t="s">
-        <v>37</v>
+      <c r="F36" s="5">
+        <v>20121</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>38</v>
@@ -3099,45 +3123,45 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>221</v>
+        <v>33</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>222</v>
+        <v>35</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>180</v>
+        <v>37</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>116</v>
+        <v>221</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>118</v>
+        <v>222</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>119</v>
+        <v>10</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>77</v>
@@ -3145,7 +3169,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>527</v>
+        <v>116</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>117</v>
@@ -3159,8 +3183,8 @@
       <c r="E39" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F39" s="5">
-        <v>65125</v>
+      <c r="F39" s="5" t="s">
+        <v>120</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>77</v>
@@ -3168,7 +3192,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>254</v>
+        <v>527</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>117</v>
@@ -3182,8 +3206,8 @@
       <c r="E40" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F40" s="5" t="s">
-        <v>120</v>
+      <c r="F40" s="5">
+        <v>65125</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>77</v>
@@ -3191,145 +3215,145 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>62</v>
+        <v>254</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>150</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>521</v>
+        <v>145</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>522</v>
+        <v>147</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F43" s="5">
-        <v>20033</v>
+        <v>148</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>291</v>
+        <v>521</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>292</v>
+        <v>34</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>293</v>
+        <v>522</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>294</v>
+        <v>36</v>
       </c>
       <c r="F44" s="5">
-        <v>60035</v>
+        <v>20033</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>585</v>
+        <v>291</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>117</v>
+        <v>292</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>118</v>
+        <v>293</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>119</v>
+        <v>294</v>
       </c>
       <c r="F45" s="5">
-        <v>65125</v>
+        <v>60035</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>77</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>215</v>
+        <v>118</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>36</v>
+        <v>119</v>
       </c>
       <c r="F46" s="5">
-        <v>20124</v>
+        <v>65125</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>541</v>
+        <v>557</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>34</v>
@@ -3338,21 +3362,21 @@
         <v>8</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>542</v>
+        <v>215</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F47" s="5">
-        <v>20121</v>
+        <v>20124</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>34</v>
@@ -3375,7 +3399,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>34</v>
@@ -3398,53 +3422,53 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>499</v>
+        <v>559</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C50" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>500</v>
+        <v>542</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F50" s="5">
-        <v>10143</v>
+        <v>20121</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>389</v>
+        <v>499</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C51" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F51" s="5">
-        <v>20123</v>
+        <v>10143</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>437</v>
+        <v>389</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>34</v>
@@ -3467,7 +3491,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>397</v>
+        <v>437</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>34</v>
@@ -3490,7 +3514,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>269</v>
+        <v>397</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>34</v>
@@ -3504,8 +3528,8 @@
       <c r="E54" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F54" s="5" t="s">
-        <v>61</v>
+      <c r="F54" s="5">
+        <v>20123</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>38</v>
@@ -3513,7 +3537,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>137</v>
+        <v>269</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>34</v>
@@ -3522,13 +3546,13 @@
         <v>8</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>38</v>
@@ -3536,7 +3560,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>409</v>
+        <v>137</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>34</v>
@@ -3550,8 +3574,8 @@
       <c r="E56" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F56" s="5">
-        <v>20121</v>
+      <c r="F56" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>38</v>
@@ -3559,214 +3583,214 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>138</v>
+        <v>409</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>142</v>
+        <v>36</v>
+      </c>
+      <c r="F57" s="5">
+        <v>20121</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>444</v>
+        <v>125</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F59" s="5">
-        <v>20158</v>
+        <v>19</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>225</v>
+        <v>444</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F60" s="5">
+        <v>20158</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>86</v>
+        <v>226</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>583</v>
+        <v>84</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>264</v>
+        <v>85</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>584</v>
+        <v>86</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="F62" s="5">
-        <v>38123</v>
+        <v>87</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>268</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>544</v>
+        <v>583</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>9</v>
+        <v>264</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>545</v>
+        <v>584</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>180</v>
+        <v>408</v>
+      </c>
+      <c r="F63" s="5">
+        <v>38123</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>77</v>
+        <v>268</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>487</v>
+        <v>544</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>488</v>
+        <v>9</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>489</v>
+        <v>545</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="F64" s="5">
-        <v>26015</v>
+        <v>10</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>558</v>
+        <v>487</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>9</v>
+        <v>488</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>335</v>
+        <v>489</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>218</v>
+        <v>490</v>
+      </c>
+      <c r="F65" s="5">
+        <v>26015</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>334</v>
+        <v>558</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>9</v>
@@ -3780,7 +3804,7 @@
       <c r="E66" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F66" s="5" t="s">
+      <c r="F66" s="8" t="s">
         <v>218</v>
       </c>
       <c r="G66" s="4" t="s">
@@ -3789,145 +3813,145 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>592</v>
+        <v>334</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>593</v>
+        <v>335</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F67" s="5">
-        <v>20122</v>
+        <v>10</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>300</v>
+        <v>592</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>296</v>
+        <v>34</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>301</v>
+        <v>593</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>302</v>
+        <v>36</v>
       </c>
       <c r="F68" s="5">
-        <v>56025</v>
+        <v>20122</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>299</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>9</v>
+        <v>296</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>273</v>
+        <v>302</v>
+      </c>
+      <c r="F69" s="5">
+        <v>56025</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>11</v>
+        <v>299</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>375</v>
+        <v>271</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>376</v>
+        <v>272</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F70" s="5">
-        <v>20121</v>
+        <v>10</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>280</v>
+        <v>375</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>303</v>
+        <v>376</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>304</v>
+        <v>36</v>
       </c>
       <c r="F71" s="5">
-        <v>24060</v>
+        <v>20121</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>150</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>481</v>
+        <v>280</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>36</v>
+        <v>304</v>
       </c>
       <c r="F72" s="5">
-        <v>20121</v>
+        <v>24060</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>175</v>
+        <v>481</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>34</v>
@@ -3936,21 +3960,21 @@
         <v>8</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>157</v>
+        <v>258</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F73" s="5" t="s">
-        <v>158</v>
+      <c r="F73" s="5">
+        <v>20121</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>34</v>
@@ -3973,7 +3997,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>253</v>
+        <v>156</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>34</v>
@@ -3982,21 +4006,21 @@
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>439</v>
+        <v>253</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>34</v>
@@ -4005,228 +4029,228 @@
         <v>8</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>440</v>
+        <v>230</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F76" s="5">
-        <v>20122</v>
+      <c r="F76" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>245</v>
+        <v>439</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>247</v>
+        <v>440</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>249</v>
+        <v>36</v>
+      </c>
+      <c r="F77" s="5">
+        <v>20122</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>250</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>81</v>
+        <v>248</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>83</v>
+        <v>250</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>362</v>
+        <v>251</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>364</v>
+        <v>252</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="F79" s="5">
-        <v>76123</v>
+        <v>81</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>425</v>
+        <v>362</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>28</v>
+        <v>363</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>132</v>
+        <v>364</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>30</v>
+        <v>365</v>
       </c>
       <c r="F80" s="5">
-        <v>39100</v>
+        <v>76123</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>551</v>
+        <v>425</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>552</v>
+        <v>28</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>553</v>
+        <v>132</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>555</v>
+        <v>30</v>
+      </c>
+      <c r="F81" s="5">
+        <v>39100</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>391</v>
+        <v>551</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>40</v>
+        <v>552</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>392</v>
+        <v>553</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F82" s="5">
-        <v>70043</v>
+        <v>554</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>555</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>219</v>
+        <v>391</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>220</v>
+        <v>392</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
+      </c>
+      <c r="F83" s="5">
+        <v>70043</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>50</v>
+        <v>219</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>34</v>
@@ -4235,13 +4259,13 @@
         <v>8</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G86" s="4" t="s">
         <v>38</v>
@@ -4249,7 +4273,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>34</v>
@@ -4272,7 +4296,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>34</v>
@@ -4295,99 +4319,99 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>371</v>
+        <v>130</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>372</v>
+        <v>34</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>373</v>
+        <v>122</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="F89" s="5">
-        <v>61121</v>
+        <v>36</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>201</v>
+        <v>371</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>34</v>
+        <v>372</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>189</v>
+        <v>373</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>190</v>
+        <v>374</v>
+      </c>
+      <c r="F90" s="5">
+        <v>61121</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>506</v>
+        <v>201</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="C91" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C91" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>508</v>
+        <v>189</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="F91" s="5">
-        <v>35010</v>
+        <v>36</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>505</v>
+        <v>159</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>281</v>
+        <v>506</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C92" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>305</v>
+        <v>508</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>36</v>
+        <v>507</v>
       </c>
       <c r="F92" s="5">
-        <v>20123</v>
+        <v>35010</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>38</v>
+        <v>505</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>565</v>
+        <v>281</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>34</v>
@@ -4396,13 +4420,13 @@
         <v>8</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>564</v>
+        <v>305</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F93" s="5">
-        <v>20122</v>
+        <v>20123</v>
       </c>
       <c r="G93" s="4" t="s">
         <v>38</v>
@@ -4410,25 +4434,25 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>351</v>
+        <v>565</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>353</v>
+        <v>564</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>354</v>
+        <v>36</v>
       </c>
       <c r="F94" s="5">
-        <v>15033</v>
+        <v>20122</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
@@ -4456,76 +4480,76 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>535</v>
+        <v>351</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>117</v>
+        <v>352</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>536</v>
+        <v>353</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>119</v>
+        <v>354</v>
       </c>
       <c r="F96" s="5">
-        <v>65127</v>
+        <v>15033</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>59</v>
+        <v>535</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>60</v>
+        <v>536</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>61</v>
+        <v>119</v>
+      </c>
+      <c r="F97" s="5">
+        <v>65127</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>336</v>
+        <v>59</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>337</v>
+        <v>60</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F98" s="5">
-        <v>10153</v>
+        <v>36</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>430</v>
+        <v>336</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>79</v>
@@ -4548,76 +4572,76 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>573</v>
+        <v>430</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>574</v>
+        <v>337</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F100" s="5">
-        <v>20154</v>
+        <v>10153</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>159</v>
+        <v>83</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>282</v>
+        <v>573</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>306</v>
+        <v>574</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F101" s="5">
-        <v>183</v>
+        <v>20154</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>307</v>
+        <v>159</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>210</v>
+        <v>282</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>211</v>
+        <v>306</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F102" s="5" t="s">
-        <v>58</v>
+        <v>10</v>
+      </c>
+      <c r="F102" s="5">
+        <v>183</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>549</v>
+        <v>210</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>34</v>
@@ -4626,21 +4650,21 @@
         <v>8</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>550</v>
+        <v>211</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F103" s="5">
-        <v>20154</v>
+      <c r="F103" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>275</v>
+        <v>549</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>34</v>
@@ -4649,13 +4673,13 @@
         <v>8</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>276</v>
+        <v>550</v>
       </c>
       <c r="E104" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F104" s="5" t="s">
-        <v>158</v>
+      <c r="F104" s="5">
+        <v>20154</v>
       </c>
       <c r="G104" s="4" t="s">
         <v>159</v>
@@ -4663,30 +4687,30 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>128</v>
+        <v>275</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>129</v>
+        <v>276</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>242</v>
+        <v>128</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>28</v>
@@ -4709,168 +4733,168 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>414</v>
+        <v>242</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>415</v>
+        <v>129</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>180</v>
+        <v>31</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>274</v>
+        <v>414</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>29</v>
+        <v>415</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>31</v>
+        <v>180</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>239</v>
+        <v>29</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>241</v>
+        <v>31</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>150</v>
+        <v>32</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>598</v>
+        <v>238</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>599</v>
+        <v>239</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F110" s="5">
-        <v>20122</v>
+        <v>240</v>
+      </c>
+      <c r="F110" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>537</v>
+        <v>598</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>538</v>
+        <v>34</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>539</v>
+        <v>599</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>540</v>
+        <v>36</v>
       </c>
       <c r="F111" s="5">
-        <v>34133</v>
+        <v>20122</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>514</v>
+        <v>38</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>435</v>
+        <v>537</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>28</v>
+        <v>538</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>129</v>
+        <v>539</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>30</v>
+        <v>540</v>
       </c>
       <c r="F112" s="5">
-        <v>39100</v>
+        <v>34133</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>32</v>
+        <v>514</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>206</v>
+        <v>435</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>61</v>
+        <v>30</v>
+      </c>
+      <c r="F113" s="5">
+        <v>39100</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>366</v>
+        <v>206</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>34</v>
@@ -4884,8 +4908,8 @@
       <c r="E114" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F114" s="5">
-        <v>20123</v>
+      <c r="F114" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G114" s="4" t="s">
         <v>38</v>
@@ -4893,7 +4917,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>101</v>
+        <v>366</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>34</v>
@@ -4907,8 +4931,8 @@
       <c r="E115" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F115" s="5" t="s">
-        <v>61</v>
+      <c r="F115" s="5">
+        <v>20123</v>
       </c>
       <c r="G115" s="4" t="s">
         <v>38</v>
@@ -4916,237 +4940,237 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>493</v>
+        <v>101</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>494</v>
+        <v>60</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F116" s="8" t="s">
-        <v>273</v>
+        <v>36</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>520</v>
+        <v>494</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F117" s="5">
-        <v>80121</v>
+        <v>10</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>406</v>
+        <v>519</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>264</v>
+        <v>69</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>407</v>
+        <v>520</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>408</v>
+        <v>71</v>
       </c>
       <c r="F118" s="5">
-        <v>38121</v>
+        <v>80121</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>268</v>
+        <v>73</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>369</v>
+        <v>406</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>36</v>
+        <v>408</v>
       </c>
       <c r="F119" s="5">
-        <v>20123</v>
+        <v>38121</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F120" s="5">
-        <v>90139</v>
+        <v>20123</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>195</v>
+        <v>361</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F121" s="5">
-        <v>20123</v>
+        <v>90139</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>455</v>
+        <v>345</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>456</v>
+        <v>195</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F122" s="8" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F122" s="5">
+        <v>20123</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>283</v>
+        <v>455</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>309</v>
+        <v>456</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="F123" s="5">
-        <v>12037</v>
+        <v>10</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>13</v>
+        <v>283</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>9</v>
+        <v>308</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>14</v>
+        <v>309</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>15</v>
+        <v>310</v>
+      </c>
+      <c r="F124" s="5">
+        <v>12037</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>11</v>
+        <v>307</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>123</v>
+        <v>13</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>28</v>
@@ -5169,58 +5193,58 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>498</v>
+        <v>27</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="C129" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
@@ -5229,8 +5253,8 @@
       <c r="E129" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F129" s="5">
-        <v>39100</v>
+      <c r="F129" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G129" s="4" t="s">
         <v>32</v>
@@ -5238,53 +5262,53 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>233</v>
+        <v>498</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C130" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C130" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>234</v>
+        <v>29</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F130" s="5" t="s">
-        <v>218</v>
+        <v>30</v>
+      </c>
+      <c r="F130" s="5">
+        <v>39100</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>590</v>
+        <v>233</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>591</v>
+        <v>234</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F131" s="5">
-        <v>20122</v>
+        <v>10</v>
+      </c>
+      <c r="F131" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>188</v>
+        <v>590</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>34</v>
@@ -5293,159 +5317,159 @@
         <v>8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>189</v>
+        <v>591</v>
       </c>
       <c r="E132" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F132" s="5" t="s">
-        <v>190</v>
+      <c r="F132" s="5">
+        <v>20122</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>483</v>
+        <v>188</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>484</v>
+        <v>34</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>485</v>
+        <v>189</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="F133" s="5">
-        <v>66020</v>
+        <v>36</v>
+      </c>
+      <c r="F133" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>576</v>
+        <v>483</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>34</v>
+        <v>484</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>577</v>
+        <v>485</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>36</v>
+        <v>486</v>
       </c>
       <c r="F134" s="5">
-        <v>20124</v>
+        <v>66020</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>411</v>
+        <v>576</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>412</v>
+        <v>577</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>413</v>
+        <v>36</v>
       </c>
       <c r="F135" s="5">
-        <v>37137</v>
+        <v>20124</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>343</v>
+        <v>159</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>460</v>
+        <v>411</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>9</v>
+        <v>341</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>461</v>
+        <v>412</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F136" s="8" t="s">
-        <v>218</v>
+        <v>413</v>
+      </c>
+      <c r="F136" s="5">
+        <v>37137</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>11</v>
+        <v>343</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>295</v>
+        <v>460</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>297</v>
+        <v>461</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="F137" s="5">
-        <v>56010</v>
+        <v>10</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>299</v>
+        <v>11</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>22</v>
+        <v>296</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="F138" s="5">
-        <v>40060</v>
+        <v>56010</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>26</v>
+        <v>299</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>384</v>
+        <v>603</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>34</v>
@@ -5454,67 +5478,67 @@
         <v>8</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>385</v>
+        <v>604</v>
       </c>
       <c r="E139" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F139" s="5">
-        <v>20121</v>
+        <v>20145</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>386</v>
+        <v>311</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>385</v>
+        <v>312</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>58</v>
+        <v>313</v>
+      </c>
+      <c r="F140" s="5">
+        <v>40060</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>213</v>
+        <v>384</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>179</v>
+        <v>385</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F141" s="5">
+        <v>20121</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>575</v>
+        <v>386</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>34</v>
@@ -5523,228 +5547,228 @@
         <v>8</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>192</v>
+        <v>385</v>
       </c>
       <c r="E142" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F142" s="5">
-        <v>20124</v>
+      <c r="F142" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>589</v>
+        <v>213</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F143" s="5">
-        <v>20124</v>
+        <v>10</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>68</v>
+        <v>575</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>72</v>
+        <v>36</v>
+      </c>
+      <c r="F144" s="5">
+        <v>20124</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>284</v>
+        <v>589</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>314</v>
+        <v>34</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>315</v>
+        <v>192</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>316</v>
+        <v>36</v>
       </c>
       <c r="F145" s="5">
-        <v>57021</v>
+        <v>20124</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>299</v>
+        <v>159</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>179</v>
+        <v>70</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>462</v>
+        <v>284</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>9</v>
+        <v>314</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>179</v>
+        <v>315</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F147" s="8" t="s">
-        <v>180</v>
+        <v>316</v>
+      </c>
+      <c r="F147" s="5">
+        <v>57021</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>77</v>
+        <v>299</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>346</v>
+        <v>462</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>347</v>
+        <v>179</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="F149" s="5">
-        <v>70124</v>
+        <v>10</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>333</v>
+        <v>89</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F150" s="5">
-        <v>20158</v>
+        <v>92</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>159</v>
+        <v>94</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>308</v>
+        <v>40</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="F151" s="5">
-        <v>12084</v>
+        <v>70124</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>307</v>
+        <v>44</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>34</v>
@@ -5753,182 +5777,182 @@
         <v>8</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E152" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F152" s="5" t="s">
-        <v>61</v>
+      <c r="F152" s="5">
+        <v>20158</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>227</v>
+        <v>357</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>228</v>
+        <v>358</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F153" s="5" t="s">
-        <v>37</v>
+        <v>359</v>
+      </c>
+      <c r="F153" s="5">
+        <v>12084</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>457</v>
+        <v>194</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>458</v>
+        <v>195</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F154" s="8" t="s">
-        <v>459</v>
+        <v>36</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>108</v>
+        <v>227</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="F156" s="5">
-        <v>12100</v>
+        <v>10</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>459</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>395</v>
+        <v>108</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F157" s="5">
-        <v>40127</v>
+        <v>111</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>355</v>
+        <v>431</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>356</v>
+        <v>432</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>36</v>
+        <v>433</v>
       </c>
       <c r="F158" s="5">
-        <v>20121</v>
+        <v>12100</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>556</v>
+        <v>395</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>525</v>
+        <v>23</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F159" s="5">
-        <v>20154</v>
+        <v>40127</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>526</v>
+        <v>355</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>34</v>
@@ -5937,21 +5961,21 @@
         <v>8</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>525</v>
+        <v>356</v>
       </c>
       <c r="E160" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F160" s="5">
-        <v>20154</v>
+        <v>20121</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>524</v>
+        <v>556</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>34</v>
@@ -5974,7 +5998,7 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>596</v>
+        <v>526</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>34</v>
@@ -5983,7 +6007,7 @@
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>597</v>
+        <v>525</v>
       </c>
       <c r="E162" s="4" t="s">
         <v>36</v>
@@ -5997,99 +6021,99 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>29</v>
+        <v>525</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F163" s="5">
-        <v>39100</v>
+        <v>20154</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>232</v>
+        <v>596</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>29</v>
+        <v>597</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F164" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F164" s="5">
+        <v>20154</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>143</v>
+        <v>515</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F165" s="5" t="s">
-        <v>37</v>
+        <v>30</v>
+      </c>
+      <c r="F165" s="5">
+        <v>39100</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>56</v>
+        <v>232</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>441</v>
+        <v>143</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>34</v>
@@ -6098,159 +6122,159 @@
         <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>442</v>
+        <v>144</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="F167" s="5">
-        <v>20038</v>
+        <v>36</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>426</v>
+        <v>56</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F168" s="5">
-        <v>10121</v>
+        <v>36</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>95</v>
+        <v>441</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>97</v>
+        <v>442</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>99</v>
+        <v>443</v>
+      </c>
+      <c r="F169" s="5">
+        <v>20038</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>377</v>
+        <v>426</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>379</v>
+        <v>236</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>380</v>
+        <v>81</v>
       </c>
       <c r="F170" s="5">
-        <v>64020</v>
+        <v>10121</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>580</v>
+        <v>95</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>581</v>
+        <v>97</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F171" s="8" t="s">
-        <v>582</v>
+        <v>98</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>11</v>
+        <v>100</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>34</v>
+        <v>378</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>211</v>
+        <v>379</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>36</v>
+        <v>380</v>
       </c>
       <c r="F172" s="5">
-        <v>20121</v>
+        <v>64020</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>133</v>
+        <v>580</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>134</v>
+        <v>581</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>135</v>
+        <v>10</v>
+      </c>
+      <c r="F173" s="8" t="s">
+        <v>582</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>136</v>
+        <v>11</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>257</v>
+        <v>410</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>34</v>
@@ -6259,13 +6283,13 @@
         <v>8</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>258</v>
+        <v>211</v>
       </c>
       <c r="E174" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F174" s="5" t="s">
-        <v>58</v>
+      <c r="F174" s="5">
+        <v>20121</v>
       </c>
       <c r="G174" s="4" t="s">
         <v>38</v>
@@ -6273,53 +6297,53 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>340</v>
+        <v>133</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>342</v>
+        <v>134</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="F175" s="5">
-        <v>37045</v>
+        <v>36</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>343</v>
+        <v>136</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>166</v>
+        <v>605</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>167</v>
+        <v>606</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>168</v>
+        <v>10</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>607</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>529</v>
+        <v>257</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>34</v>
@@ -6328,44 +6352,44 @@
         <v>8</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>167</v>
+        <v>258</v>
       </c>
       <c r="E177" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F177" s="5">
-        <v>20126</v>
+      <c r="F177" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>601</v>
+        <v>340</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>602</v>
+        <v>342</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>36</v>
+        <v>528</v>
       </c>
       <c r="F178" s="5">
-        <v>20138</v>
+        <v>37045</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>262</v>
+        <v>343</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>594</v>
+        <v>166</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>34</v>
@@ -6374,21 +6398,21 @@
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>394</v>
+        <v>167</v>
       </c>
       <c r="E179" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F179" s="5">
-        <v>20123</v>
+      <c r="F179" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>471</v>
+        <v>529</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>34</v>
@@ -6397,21 +6421,21 @@
         <v>8</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E180" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F180" s="5">
-        <v>20135</v>
+        <v>20126</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>405</v>
+        <v>601</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>34</v>
@@ -6420,13 +6444,13 @@
         <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>260</v>
+        <v>602</v>
       </c>
       <c r="E181" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F181" s="5">
-        <v>20135</v>
+        <v>20138</v>
       </c>
       <c r="G181" s="4" t="s">
         <v>262</v>
@@ -6434,30 +6458,30 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>204</v>
+        <v>609</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>205</v>
+        <v>610</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>187</v>
+        <v>36</v>
+      </c>
+      <c r="F182" s="5">
+        <v>20122</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>319</v>
+        <v>38</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>453</v>
+        <v>594</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>34</v>
@@ -6466,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>454</v>
+        <v>394</v>
       </c>
       <c r="E183" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F183" s="5">
-        <v>20144</v>
+        <v>20123</v>
       </c>
       <c r="G183" s="4" t="s">
         <v>38</v>
@@ -6480,7 +6504,7 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>223</v>
+        <v>471</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>34</v>
@@ -6489,90 +6513,90 @@
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="E184" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F184" s="5" t="s">
-        <v>135</v>
+      <c r="F184" s="5">
+        <v>20135</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>136</v>
+        <v>262</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>285</v>
+        <v>405</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>317</v>
+        <v>260</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F185" s="5">
-        <v>40026</v>
+        <v>20135</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>26</v>
+        <v>262</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>286</v>
+        <v>204</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>9</v>
+        <v>185</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>320</v>
+        <v>205</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>10</v>
+        <v>186</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>323</v>
+        <v>187</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>11</v>
+        <v>319</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>533</v>
+        <v>453</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>29</v>
+        <v>454</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F187" s="5">
-        <v>39100</v>
+        <v>20144</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>367</v>
+        <v>223</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>34</v>
@@ -6581,90 +6605,90 @@
         <v>8</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>368</v>
+        <v>224</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F188" s="5">
-        <v>20123</v>
+      <c r="F188" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>308</v>
+        <v>22</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F189" s="10">
-        <v>12020</v>
+        <v>40026</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>307</v>
+        <v>26</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>39</v>
+        <v>286</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>41</v>
+        <v>320</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="F190" s="10" t="s">
-        <v>43</v>
+        <v>323</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>421</v>
+        <v>533</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>422</v>
+        <v>28</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>423</v>
+        <v>29</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>424</v>
+        <v>30</v>
       </c>
       <c r="F191" s="10">
-        <v>28053</v>
+        <v>39100</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>172</v>
+        <v>367</v>
       </c>
       <c r="B192" s="9" t="s">
         <v>34</v>
@@ -6673,90 +6697,90 @@
         <v>8</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>169</v>
+        <v>368</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F192" s="10" t="s">
-        <v>171</v>
+        <v>36</v>
+      </c>
+      <c r="F192" s="10">
+        <v>20123</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>560</v>
+        <v>287</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>28</v>
+        <v>308</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>561</v>
+        <v>321</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>30</v>
+        <v>322</v>
       </c>
       <c r="F193" s="10">
-        <v>39100</v>
+        <v>12020</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>32</v>
+        <v>307</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
-        <v>198</v>
+        <v>39</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C194" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>199</v>
+        <v>41</v>
       </c>
       <c r="E194" s="9" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F194" s="10" t="s">
-        <v>200</v>
+        <v>43</v>
       </c>
       <c r="G194" s="9" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
-        <v>207</v>
+        <v>421</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>69</v>
+        <v>422</v>
       </c>
       <c r="C195" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>208</v>
+        <v>423</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="F195" s="10" t="s">
-        <v>209</v>
+        <v>424</v>
+      </c>
+      <c r="F195" s="10">
+        <v>28053</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>73</v>
+        <v>136</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
-        <v>244</v>
+        <v>172</v>
       </c>
       <c r="B196" s="9" t="s">
         <v>34</v>
@@ -6765,113 +6789,113 @@
         <v>8</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="F196" s="10" t="s">
-        <v>58</v>
+        <v>171</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>534</v>
+        <v>560</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C197" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>177</v>
+        <v>561</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F197" s="10">
-        <v>20121</v>
+        <v>39100</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>578</v>
+        <v>198</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C198" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>579</v>
+        <v>199</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F198" s="10">
-        <v>20121</v>
+        <v>24</v>
+      </c>
+      <c r="F198" s="10" t="s">
+        <v>200</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>445</v>
+        <v>207</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>446</v>
+        <v>69</v>
       </c>
       <c r="C199" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>447</v>
+        <v>208</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="F199" s="10">
-        <v>53048</v>
+        <v>71</v>
+      </c>
+      <c r="F199" s="10" t="s">
+        <v>209</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>449</v>
+        <v>73</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
-        <v>516</v>
+        <v>244</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>509</v>
+        <v>34</v>
       </c>
       <c r="C200" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>517</v>
+        <v>177</v>
       </c>
       <c r="E200" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="F200" s="10">
-        <v>35011</v>
+        <v>36</v>
+      </c>
+      <c r="F200" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="G200" s="9" t="s">
-        <v>505</v>
+        <v>38</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="9" t="s">
-        <v>243</v>
+        <v>534</v>
       </c>
       <c r="B201" s="9" t="s">
         <v>34</v>
@@ -6885,8 +6909,8 @@
       <c r="E201" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F201" s="10" t="s">
-        <v>58</v>
+      <c r="F201" s="10">
+        <v>20121</v>
       </c>
       <c r="G201" s="9" t="s">
         <v>38</v>
@@ -6894,145 +6918,145 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
-        <v>131</v>
+        <v>578</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C202" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>132</v>
+        <v>579</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F202" s="10" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F202" s="10">
+        <v>20121</v>
       </c>
       <c r="G202" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="9" t="s">
-        <v>531</v>
+        <v>445</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>34</v>
+        <v>446</v>
       </c>
       <c r="C203" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D203" s="9" t="s">
-        <v>532</v>
+        <v>447</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>36</v>
+        <v>448</v>
       </c>
       <c r="F203" s="10">
-        <v>20121</v>
+        <v>53048</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>38</v>
+        <v>449</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
-        <v>21</v>
+        <v>516</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>22</v>
+        <v>509</v>
       </c>
       <c r="C204" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D204" s="9" t="s">
-        <v>23</v>
+        <v>517</v>
       </c>
       <c r="E204" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F204" s="10" t="s">
-        <v>25</v>
+        <v>518</v>
+      </c>
+      <c r="F204" s="10">
+        <v>35011</v>
       </c>
       <c r="G204" s="9" t="s">
-        <v>26</v>
+        <v>505</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A205" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="B205" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C205" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D205" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="E205" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F205" s="11" t="s">
-        <v>568</v>
-      </c>
-      <c r="G205" s="3" t="s">
-        <v>77</v>
+      <c r="A205" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="B205" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C205" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D205" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="E205" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F205" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G205" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="9" t="s">
-        <v>381</v>
+        <v>131</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C206" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D206" s="9" t="s">
-        <v>382</v>
+        <v>132</v>
       </c>
       <c r="E206" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="F206" s="10">
-        <v>20089</v>
+        <v>30</v>
+      </c>
+      <c r="F206" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="G206" s="9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
-        <v>475</v>
+        <v>531</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C207" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D207" s="9" t="s">
-        <v>476</v>
+        <v>532</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F207" s="12" t="s">
-        <v>477</v>
+        <v>36</v>
+      </c>
+      <c r="F207" s="10">
+        <v>20121</v>
       </c>
       <c r="G207" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="9" t="s">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="B208" s="9" t="s">
         <v>22</v>
@@ -7041,44 +7065,44 @@
         <v>8</v>
       </c>
       <c r="D208" s="9" t="s">
-        <v>202</v>
+        <v>23</v>
       </c>
       <c r="E208" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F208" s="10" t="s">
-        <v>203</v>
+        <v>25</v>
       </c>
       <c r="G208" s="9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A209" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="B209" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C209" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D209" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="E209" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F209" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="G209" s="9" t="s">
-        <v>159</v>
+      <c r="A209" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F209" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="G209" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="9" t="s">
-        <v>438</v>
+        <v>381</v>
       </c>
       <c r="B210" s="9" t="s">
         <v>34</v>
@@ -7087,67 +7111,67 @@
         <v>8</v>
       </c>
       <c r="D210" s="9" t="s">
-        <v>215</v>
+        <v>382</v>
       </c>
       <c r="E210" s="9" t="s">
-        <v>36</v>
+        <v>383</v>
       </c>
       <c r="F210" s="10">
-        <v>20124</v>
+        <v>20089</v>
       </c>
       <c r="G210" s="9" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="9" t="s">
-        <v>229</v>
+        <v>475</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C211" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D211" s="9" t="s">
-        <v>230</v>
+        <v>476</v>
       </c>
       <c r="E211" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F211" s="10" t="s">
-        <v>231</v>
+        <v>10</v>
+      </c>
+      <c r="F211" s="12" t="s">
+        <v>477</v>
       </c>
       <c r="G211" s="9" t="s">
-        <v>136</v>
+        <v>11</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="9" t="s">
-        <v>256</v>
+        <v>212</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C212" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D212" s="9" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="E212" s="9" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F212" s="10" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="G212" s="9" t="s">
-        <v>136</v>
+        <v>26</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="9" t="s">
-        <v>472</v>
+        <v>214</v>
       </c>
       <c r="B213" s="9" t="s">
         <v>34</v>
@@ -7156,21 +7180,21 @@
         <v>8</v>
       </c>
       <c r="D213" s="9" t="s">
-        <v>464</v>
+        <v>215</v>
       </c>
       <c r="E213" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F213" s="10">
-        <v>20129</v>
+      <c r="F213" s="10" t="s">
+        <v>158</v>
       </c>
       <c r="G213" s="9" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="9" t="s">
-        <v>463</v>
+        <v>438</v>
       </c>
       <c r="B214" s="9" t="s">
         <v>34</v>
@@ -7179,21 +7203,21 @@
         <v>8</v>
       </c>
       <c r="D214" s="9" t="s">
-        <v>464</v>
+        <v>215</v>
       </c>
       <c r="E214" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F214" s="10">
-        <v>20129</v>
+        <v>20124</v>
       </c>
       <c r="G214" s="9" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="9" t="s">
-        <v>473</v>
+        <v>229</v>
       </c>
       <c r="B215" s="9" t="s">
         <v>34</v>
@@ -7202,21 +7226,21 @@
         <v>8</v>
       </c>
       <c r="D215" s="9" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E215" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F215" s="10">
-        <v>20129</v>
+      <c r="F215" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="G215" s="9" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="9" t="s">
-        <v>474</v>
+        <v>256</v>
       </c>
       <c r="B216" s="9" t="s">
         <v>34</v>
@@ -7225,21 +7249,21 @@
         <v>8</v>
       </c>
       <c r="D216" s="9" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E216" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F216" s="10">
-        <v>20129</v>
+      <c r="F216" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="G216" s="9" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
-        <v>176</v>
+        <v>472</v>
       </c>
       <c r="B217" s="9" t="s">
         <v>34</v>
@@ -7248,573 +7272,573 @@
         <v>8</v>
       </c>
       <c r="D217" s="9" t="s">
-        <v>177</v>
+        <v>464</v>
       </c>
       <c r="E217" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F217" s="10" t="s">
-        <v>58</v>
+      <c r="F217" s="10">
+        <v>20129</v>
       </c>
       <c r="G217" s="9" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="9" t="s">
-        <v>331</v>
+        <v>463</v>
       </c>
       <c r="B218" s="9" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C218" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D218" s="9" t="s">
-        <v>332</v>
+        <v>464</v>
       </c>
       <c r="E218" s="9" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F218" s="10">
-        <v>40026</v>
+        <v>20129</v>
       </c>
       <c r="G218" s="9" t="s">
-        <v>26</v>
+        <v>262</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="9" t="s">
-        <v>288</v>
+        <v>473</v>
       </c>
       <c r="B219" s="9" t="s">
         <v>34</v>
       </c>
       <c r="C219" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D219" s="9" t="s">
-        <v>324</v>
+        <v>464</v>
       </c>
       <c r="E219" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F219" s="10">
-        <v>20124</v>
+        <v>20129</v>
       </c>
       <c r="G219" s="9" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="9" t="s">
-        <v>450</v>
+        <v>474</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C220" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D220" s="9" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="E220" s="9" t="s">
-        <v>452</v>
+        <v>36</v>
       </c>
       <c r="F220" s="10">
-        <v>12011</v>
+        <v>20129</v>
       </c>
       <c r="G220" s="9" t="s">
-        <v>307</v>
+        <v>262</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="9" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="C221" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D221" s="9" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="E221" s="9" t="s">
-        <v>154</v>
+        <v>36</v>
       </c>
       <c r="F221" s="10" t="s">
-        <v>155</v>
+        <v>58</v>
       </c>
       <c r="G221" s="9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="9" t="s">
-        <v>419</v>
+        <v>331</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C222" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D222" s="9" t="s">
-        <v>420</v>
+        <v>332</v>
       </c>
       <c r="E222" s="9" t="s">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="F222" s="10">
-        <v>20123</v>
+        <v>40026</v>
       </c>
       <c r="G222" s="9" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="9" t="s">
-        <v>491</v>
+        <v>288</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C223" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D223" s="9" t="s">
-        <v>492</v>
+        <v>324</v>
       </c>
       <c r="E223" s="9" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F223" s="10">
-        <v>90141</v>
+        <v>20124</v>
       </c>
       <c r="G223" s="9" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="9" t="s">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>9</v>
+        <v>308</v>
       </c>
       <c r="C224" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D224" s="9" t="s">
-        <v>388</v>
+        <v>451</v>
       </c>
       <c r="E224" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F224" s="12" t="s">
-        <v>390</v>
+        <v>452</v>
+      </c>
+      <c r="F224" s="10">
+        <v>12011</v>
       </c>
       <c r="G224" s="9" t="s">
-        <v>11</v>
+        <v>307</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A225" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="B225" s="3" t="s">
-        <v>9</v>
+      <c r="A225" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="B225" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="C225" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D225" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E225" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F225" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="G225" s="3" t="s">
-        <v>11</v>
+      <c r="D225" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E225" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="F225" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="G225" s="9" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="9" t="s">
-        <v>387</v>
+        <v>419</v>
       </c>
       <c r="B226" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C226" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D226" s="9" t="s">
-        <v>388</v>
+        <v>420</v>
       </c>
       <c r="E226" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F226" s="10" t="s">
-        <v>390</v>
+        <v>36</v>
+      </c>
+      <c r="F226" s="10">
+        <v>20123</v>
       </c>
       <c r="G226" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="9" t="s">
-        <v>465</v>
+        <v>491</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>264</v>
+        <v>17</v>
       </c>
       <c r="C227" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D227" s="9" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
       <c r="E227" s="9" t="s">
-        <v>467</v>
+        <v>19</v>
       </c>
       <c r="F227" s="10">
-        <v>38055</v>
+        <v>90141</v>
       </c>
       <c r="G227" s="9" t="s">
-        <v>268</v>
+        <v>12</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A228" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="B228" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C228" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D228" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E228" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F228" s="7">
-        <v>20145</v>
-      </c>
-      <c r="G228" s="3" t="s">
-        <v>136</v>
+      <c r="A228" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="B228" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C228" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D228" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="E228" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F228" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="G228" s="9" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A229" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="B229" s="9" t="s">
-        <v>103</v>
+      <c r="A229" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C229" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D229" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="E229" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="F229" s="10">
-        <v>25010</v>
-      </c>
-      <c r="G229" s="9" t="s">
-        <v>107</v>
+      <c r="D229" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F229" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="9" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C230" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D230" s="9" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="E230" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F230" s="10">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F230" s="10" t="s">
+        <v>390</v>
       </c>
       <c r="G230" s="9" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="9" t="s">
-        <v>416</v>
+        <v>465</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>85</v>
+        <v>264</v>
       </c>
       <c r="C231" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D231" s="9" t="s">
-        <v>417</v>
+        <v>466</v>
       </c>
       <c r="E231" s="9" t="s">
-        <v>418</v>
+        <v>467</v>
       </c>
       <c r="F231" s="10">
-        <v>71016</v>
+        <v>38055</v>
       </c>
       <c r="G231" s="9" t="s">
-        <v>44</v>
+        <v>268</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A232" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B232" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C232" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D232" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E232" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F232" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G232" s="9" t="s">
-        <v>12</v>
+      <c r="A232" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F232" s="7">
+        <v>20145</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="9" t="s">
-        <v>325</v>
+        <v>427</v>
       </c>
       <c r="B233" s="9" t="s">
-        <v>326</v>
+        <v>103</v>
       </c>
       <c r="C233" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D233" s="9" t="s">
-        <v>327</v>
+        <v>428</v>
       </c>
       <c r="E233" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="F233" s="10" t="s">
-        <v>329</v>
+        <v>429</v>
+      </c>
+      <c r="F233" s="10">
+        <v>25010</v>
       </c>
       <c r="G233" s="9" t="s">
-        <v>330</v>
+        <v>107</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A234" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="B234" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C234" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D234" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="E234" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F234" s="7">
-        <v>20122</v>
-      </c>
-      <c r="G234" s="3" t="s">
+      <c r="A234" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="B234" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C234" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D234" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="E234" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F234" s="10">
+        <v>20123</v>
+      </c>
+      <c r="G234" s="9" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="9" t="s">
-        <v>277</v>
+        <v>416</v>
       </c>
       <c r="B235" s="9" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="C235" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D235" s="9" t="s">
-        <v>278</v>
+        <v>417</v>
       </c>
       <c r="E235" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F235" s="10" t="s">
-        <v>37</v>
+        <v>418</v>
+      </c>
+      <c r="F235" s="10">
+        <v>71016</v>
       </c>
       <c r="G235" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" s="9" t="s">
-        <v>478</v>
+        <v>16</v>
       </c>
       <c r="B236" s="9" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C236" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D236" s="9" t="s">
-        <v>479</v>
+        <v>18</v>
       </c>
       <c r="E236" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F236" s="10">
-        <v>20123</v>
+        <v>19</v>
+      </c>
+      <c r="F236" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="G236" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A237" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="B237" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="C237" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D237" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E237" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="F237" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="G237" s="9" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A238" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F238" s="7">
+        <v>20122</v>
+      </c>
+      <c r="G238" s="3" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A237" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="B237" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C237" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D237" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="E237" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="F237" s="7">
-        <v>20094</v>
-      </c>
-      <c r="G237" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A238" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="B238" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C238" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D238" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="E238" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F238" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="G238" s="9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" s="9" t="s">
-        <v>216</v>
+        <v>277</v>
       </c>
       <c r="B239" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C239" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D239" s="9" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="E239" s="9" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F239" s="10" t="s">
-        <v>218</v>
+        <v>37</v>
       </c>
       <c r="G239" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="9" t="s">
-        <v>160</v>
+        <v>478</v>
       </c>
       <c r="B240" s="9" t="s">
-        <v>161</v>
+        <v>34</v>
       </c>
       <c r="C240" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D240" s="9" t="s">
-        <v>162</v>
+        <v>479</v>
       </c>
       <c r="E240" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="F240" s="10" t="s">
-        <v>164</v>
+        <v>36</v>
+      </c>
+      <c r="F240" s="10">
+        <v>20123</v>
       </c>
       <c r="G240" s="9" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A241" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="B241" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C241" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D241" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="E241" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F241" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="G241" s="9" t="s">
-        <v>11</v>
+      <c r="A241" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="F241" s="7">
+        <v>20094</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" s="9" t="s">
-        <v>255</v>
+        <v>396</v>
       </c>
       <c r="B242" s="9" t="s">
         <v>9</v>
@@ -7837,30 +7861,122 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B243" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C243" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D243" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E243" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F243" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G243" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A244" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B244" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C244" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D244" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E244" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F244" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G244" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A245" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="B245" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C245" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D245" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E245" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F245" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G245" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A246" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B246" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C246" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D246" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E246" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F246" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G246" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A247" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B243" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C243" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D243" s="9" t="s">
+      <c r="B247" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C247" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D247" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E243" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F243" s="10" t="s">
+      <c r="E247" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F247" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G243" s="9" t="s">
+      <c r="G247" s="9" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G218" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G243">
+    <sortState ref="A2:G247">
       <sortCondition ref="A1:A218"/>
     </sortState>
   </autoFilter>
@@ -7873,23 +7989,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F040406D9EE34E48977C379A242BB45D" ma:contentTypeVersion="15" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="1ab2d492e43f6bec9a26aa4599c840e9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="877b7d34-4df7-40bf-9eb1-208952470e96" xmlns:ns4="05fc27dd-4454-4248-9c78-3d72b2b155c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebc604e5d4aadf5a992ba83f8d4fb519" ns3:_="" ns4:_="">
     <xsd:import namespace="877b7d34-4df7-40bf-9eb1-208952470e96"/>
@@ -8122,32 +8221,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBC6436E-C4E7-4E8D-94E8-64DAEC05792B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8164,4 +8255,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{355E0604-0E56-4EB2-AB6D-13C0C65CE765}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{46003179-19A0-467C-BD15-1431E9467DA7}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="616">
   <si>
     <t>Nome account</t>
   </si>
@@ -1856,6 +1856,21 @@
   </si>
   <si>
     <t>VIA FELICE CAVALLOTTI 13</t>
+  </si>
+  <si>
+    <t>OPDENERGY TAVOLIERE 1 SRL</t>
+  </si>
+  <si>
+    <t>VIALE ANTONIO SILVANI 2</t>
+  </si>
+  <si>
+    <t>SOLAR PV 1 SRL</t>
+  </si>
+  <si>
+    <t>D2M GREEN ENERGY - FIUMETTO SRL</t>
+  </si>
+  <si>
+    <t>AIEM GREEN SRL</t>
   </si>
 </sst>
 </file>
@@ -2280,7 +2295,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G247"/>
+  <dimension ref="A1:G251"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -2525,76 +2540,76 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>510</v>
+        <v>615</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="F11" s="5">
-        <v>33050</v>
+        <v>45100</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>263</v>
+        <v>510</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>264</v>
+        <v>511</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>265</v>
+        <v>512</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>267</v>
+        <v>513</v>
+      </c>
+      <c r="F12" s="5">
+        <v>33050</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>268</v>
+        <v>514</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>600</v>
+        <v>263</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F13" s="5">
-        <v>10121</v>
+        <v>266</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>267</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>83</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>235</v>
+        <v>600</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>79</v>
@@ -2608,8 +2623,8 @@
       <c r="E14" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>237</v>
+      <c r="F14" s="5">
+        <v>10121</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>83</v>
@@ -2617,22 +2632,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>495</v>
+        <v>235</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>496</v>
+        <v>236</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>497</v>
-      </c>
-      <c r="F15" s="5">
-        <v>10098</v>
+        <v>81</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>83</v>
@@ -2640,76 +2655,76 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>45</v>
+        <v>495</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>47</v>
+        <v>496</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>49</v>
+        <v>497</v>
+      </c>
+      <c r="F16" s="5">
+        <v>10098</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>9</v>
@@ -2732,7 +2747,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>9</v>
@@ -2755,7 +2770,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>482</v>
+        <v>196</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>9</v>
@@ -2769,7 +2784,7 @@
       <c r="E21" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="5" t="s">
         <v>180</v>
       </c>
       <c r="G21" s="4" t="s">
@@ -2778,7 +2793,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>197</v>
+        <v>482</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>9</v>
@@ -2792,7 +2807,7 @@
       <c r="E22" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="8" t="s">
         <v>180</v>
       </c>
       <c r="G22" s="4" t="s">
@@ -2801,7 +2816,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>9</v>
@@ -2824,30 +2839,30 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>403</v>
+        <v>183</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>404</v>
+        <v>179</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F24" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>595</v>
+        <v>403</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>28</v>
@@ -2870,76 +2885,76 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>399</v>
+        <v>595</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F26" s="5">
-        <v>20124</v>
+        <v>39100</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>468</v>
+        <v>399</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>469</v>
+        <v>400</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>470</v>
+        <v>36</v>
+      </c>
+      <c r="F27" s="5">
+        <v>20124</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>305</v>
+        <v>469</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F28" s="5">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>470</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>349</v>
+        <v>436</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>34</v>
@@ -2948,13 +2963,13 @@
         <v>8</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>350</v>
+        <v>305</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F29" s="5">
-        <v>20122</v>
+        <v>20123</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>38</v>
@@ -2962,53 +2977,53 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>67</v>
+        <v>349</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>18</v>
+        <v>350</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="F30" s="5">
+        <v>20122</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>398</v>
+        <v>67</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F31" s="5">
-        <v>10123</v>
+        <v>19</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>78</v>
+        <v>398</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>79</v>
@@ -3022,8 +3037,8 @@
       <c r="E32" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F32" s="5" t="s">
-        <v>82</v>
+      <c r="F32" s="5">
+        <v>10123</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>83</v>
@@ -3031,76 +3046,76 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>546</v>
+        <v>78</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>511</v>
+        <v>79</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>547</v>
+        <v>80</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="F33" s="5">
-        <v>33100</v>
+        <v>81</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>514</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>279</v>
+        <v>546</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>28</v>
+        <v>511</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>289</v>
+        <v>547</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>290</v>
+        <v>548</v>
       </c>
       <c r="F34" s="5">
-        <v>39042</v>
+        <v>33100</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>32</v>
+        <v>514</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>523</v>
+        <v>279</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>339</v>
+        <v>289</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>36</v>
+        <v>290</v>
       </c>
       <c r="F35" s="5">
-        <v>20121</v>
+        <v>39042</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>338</v>
+        <v>523</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>34</v>
@@ -3123,7 +3138,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>33</v>
+        <v>338</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>34</v>
@@ -3132,13 +3147,13 @@
         <v>8</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>35</v>
+        <v>339</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F37" s="5" t="s">
-        <v>37</v>
+      <c r="F37" s="5">
+        <v>20121</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>38</v>
@@ -3146,45 +3161,45 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>221</v>
+        <v>33</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>222</v>
+        <v>35</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>180</v>
+        <v>37</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>116</v>
+        <v>221</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>118</v>
+        <v>222</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>119</v>
+        <v>10</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>77</v>
@@ -3192,7 +3207,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>527</v>
+        <v>116</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>117</v>
@@ -3206,8 +3221,8 @@
       <c r="E40" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F40" s="5">
-        <v>65125</v>
+      <c r="F40" s="5" t="s">
+        <v>120</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>77</v>
@@ -3215,7 +3230,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>254</v>
+        <v>527</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>117</v>
@@ -3229,8 +3244,8 @@
       <c r="E41" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F41" s="5" t="s">
-        <v>120</v>
+      <c r="F41" s="5">
+        <v>65125</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>77</v>
@@ -3238,145 +3253,145 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>62</v>
+        <v>254</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>150</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>521</v>
+        <v>145</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>522</v>
+        <v>147</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F44" s="5">
-        <v>20033</v>
+        <v>148</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>291</v>
+        <v>521</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>292</v>
+        <v>34</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>293</v>
+        <v>522</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>294</v>
+        <v>36</v>
       </c>
       <c r="F45" s="5">
-        <v>60035</v>
+        <v>20033</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>585</v>
+        <v>291</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>117</v>
+        <v>292</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>118</v>
+        <v>293</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>119</v>
+        <v>294</v>
       </c>
       <c r="F46" s="5">
-        <v>65125</v>
+        <v>60035</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>77</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>215</v>
+        <v>118</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>36</v>
+        <v>119</v>
       </c>
       <c r="F47" s="5">
-        <v>20124</v>
+        <v>65125</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>541</v>
+        <v>557</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>34</v>
@@ -3385,21 +3400,21 @@
         <v>8</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>542</v>
+        <v>215</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F48" s="5">
-        <v>20121</v>
+        <v>20124</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>34</v>
@@ -3422,7 +3437,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>34</v>
@@ -3445,53 +3460,53 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>499</v>
+        <v>559</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C51" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>500</v>
+        <v>542</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F51" s="5">
-        <v>10143</v>
+        <v>20121</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>389</v>
+        <v>499</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C52" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F52" s="5">
-        <v>20123</v>
+        <v>10143</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>437</v>
+        <v>389</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>34</v>
@@ -3514,7 +3529,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>397</v>
+        <v>437</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>34</v>
@@ -3537,7 +3552,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>269</v>
+        <v>397</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>34</v>
@@ -3551,8 +3566,8 @@
       <c r="E55" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F55" s="5" t="s">
-        <v>61</v>
+      <c r="F55" s="5">
+        <v>20123</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>38</v>
@@ -3560,7 +3575,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>137</v>
+        <v>269</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>34</v>
@@ -3569,13 +3584,13 @@
         <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>38</v>
@@ -3583,7 +3598,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>409</v>
+        <v>137</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>34</v>
@@ -3597,8 +3612,8 @@
       <c r="E57" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F57" s="5">
-        <v>20121</v>
+      <c r="F57" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>38</v>
@@ -3606,191 +3621,191 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>138</v>
+        <v>409</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>142</v>
+        <v>36</v>
+      </c>
+      <c r="F58" s="5">
+        <v>20121</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>444</v>
+        <v>125</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F60" s="5">
-        <v>20158</v>
+        <v>19</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>225</v>
+        <v>614</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>226</v>
+        <v>126</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>31</v>
+        <v>19</v>
+      </c>
+      <c r="F61" s="5">
+        <v>90139</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>84</v>
+        <v>444</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>86</v>
+        <v>189</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>88</v>
+        <v>36</v>
+      </c>
+      <c r="F62" s="5">
+        <v>20158</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>44</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>583</v>
+        <v>225</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>264</v>
+        <v>28</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>584</v>
+        <v>226</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="F63" s="5">
-        <v>38123</v>
+        <v>30</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>268</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>544</v>
+        <v>84</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>545</v>
+        <v>86</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>180</v>
+        <v>87</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>487</v>
+        <v>583</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>488</v>
+        <v>264</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>489</v>
+        <v>584</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>490</v>
+        <v>408</v>
       </c>
       <c r="F65" s="5">
-        <v>26015</v>
+        <v>38123</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>107</v>
+        <v>268</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>9</v>
@@ -3799,159 +3814,159 @@
         <v>8</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>335</v>
+        <v>545</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>218</v>
+        <v>180</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>334</v>
+        <v>487</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>9</v>
+        <v>488</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>335</v>
+        <v>489</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>218</v>
+        <v>490</v>
+      </c>
+      <c r="F67" s="5">
+        <v>26015</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>592</v>
+        <v>558</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>593</v>
+        <v>335</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F68" s="5">
-        <v>20122</v>
+        <v>10</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="F69" s="5">
-        <v>56025</v>
+        <v>10</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>299</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>271</v>
+        <v>592</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>272</v>
+        <v>593</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>273</v>
+        <v>36</v>
+      </c>
+      <c r="F70" s="5">
+        <v>20122</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>376</v>
+        <v>301</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>36</v>
+        <v>302</v>
       </c>
       <c r="F71" s="5">
-        <v>20121</v>
+        <v>56025</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>38</v>
+        <v>299</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>146</v>
+        <v>9</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="F72" s="5">
-        <v>24060</v>
+        <v>10</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>150</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>481</v>
+        <v>375</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>34</v>
@@ -3960,7 +3975,7 @@
         <v>8</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>258</v>
+        <v>376</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>36</v>
@@ -3974,30 +3989,30 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>175</v>
+        <v>280</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>157</v>
+        <v>303</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>158</v>
+        <v>304</v>
+      </c>
+      <c r="F74" s="5">
+        <v>24060</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>156</v>
+        <v>481</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>34</v>
@@ -4006,21 +4021,21 @@
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>157</v>
+        <v>258</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F75" s="5" t="s">
-        <v>158</v>
+      <c r="F75" s="5">
+        <v>20121</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>253</v>
+        <v>175</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>34</v>
@@ -4029,21 +4044,21 @@
         <v>8</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>439</v>
+        <v>156</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>34</v>
@@ -4052,205 +4067,205 @@
         <v>8</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>440</v>
+        <v>157</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F77" s="5">
-        <v>20122</v>
+      <c r="F77" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>248</v>
+        <v>36</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>250</v>
+        <v>136</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>251</v>
+        <v>439</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>252</v>
+        <v>440</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>237</v>
+        <v>36</v>
+      </c>
+      <c r="F79" s="5">
+        <v>20122</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>362</v>
+        <v>245</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>363</v>
+        <v>246</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>364</v>
+        <v>247</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="F80" s="5">
-        <v>76123</v>
+        <v>248</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>44</v>
+        <v>250</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>425</v>
+        <v>251</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>132</v>
+        <v>252</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F81" s="5">
-        <v>39100</v>
+        <v>81</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>551</v>
+        <v>362</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>552</v>
+        <v>363</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>553</v>
+        <v>364</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>555</v>
+        <v>365</v>
+      </c>
+      <c r="F82" s="5">
+        <v>76123</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>391</v>
+        <v>425</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>392</v>
+        <v>132</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F83" s="5">
-        <v>70043</v>
+        <v>39100</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>219</v>
+        <v>551</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>34</v>
+        <v>552</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>220</v>
+        <v>553</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>37</v>
+        <v>554</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>555</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>50</v>
+        <v>391</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>47</v>
+        <v>392</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
+      </c>
+      <c r="F85" s="5">
+        <v>70043</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>51</v>
+        <v>219</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>34</v>
@@ -4259,13 +4274,13 @@
         <v>8</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>52</v>
+        <v>220</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="G86" s="4" t="s">
         <v>38</v>
@@ -4273,30 +4288,30 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>34</v>
@@ -4305,13 +4320,13 @@
         <v>8</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G88" s="4" t="s">
         <v>38</v>
@@ -4319,7 +4334,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>34</v>
@@ -4342,30 +4357,30 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>371</v>
+        <v>124</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>372</v>
+        <v>34</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>373</v>
+        <v>122</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="F90" s="5">
-        <v>61121</v>
+        <v>36</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>201</v>
+        <v>130</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>34</v>
@@ -4374,44 +4389,44 @@
         <v>8</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>189</v>
+        <v>122</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>190</v>
+        <v>58</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>506</v>
+        <v>371</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="C92" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>508</v>
+        <v>373</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>507</v>
+        <v>374</v>
       </c>
       <c r="F92" s="5">
-        <v>35010</v>
+        <v>61121</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>505</v>
+        <v>165</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>281</v>
+        <v>201</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>34</v>
@@ -4420,228 +4435,228 @@
         <v>8</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>305</v>
+        <v>189</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F93" s="5">
-        <v>20123</v>
+      <c r="F93" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>565</v>
+        <v>506</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C94" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>564</v>
+        <v>508</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>36</v>
+        <v>507</v>
       </c>
       <c r="F94" s="5">
-        <v>20122</v>
+        <v>35010</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>38</v>
+        <v>505</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>351</v>
+        <v>281</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>353</v>
+        <v>305</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>354</v>
+        <v>36</v>
       </c>
       <c r="F95" s="5">
-        <v>15033</v>
+        <v>20123</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>351</v>
+        <v>565</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>353</v>
+        <v>564</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>354</v>
+        <v>36</v>
       </c>
       <c r="F96" s="5">
-        <v>15033</v>
+        <v>20122</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>535</v>
+        <v>351</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>117</v>
+        <v>352</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>536</v>
+        <v>353</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>119</v>
+        <v>354</v>
       </c>
       <c r="F97" s="5">
-        <v>65127</v>
+        <v>15033</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>59</v>
+        <v>351</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>34</v>
+        <v>352</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>60</v>
+        <v>353</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>61</v>
+        <v>354</v>
+      </c>
+      <c r="F98" s="5">
+        <v>15033</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>336</v>
+        <v>535</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>337</v>
+        <v>536</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="F99" s="5">
-        <v>10153</v>
+        <v>65127</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>430</v>
+        <v>59</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>337</v>
+        <v>60</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F100" s="5">
-        <v>10153</v>
+        <v>36</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>573</v>
+        <v>336</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>574</v>
+        <v>337</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F101" s="5">
-        <v>20154</v>
+        <v>10153</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>159</v>
+        <v>83</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>282</v>
+        <v>430</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="F102" s="5">
-        <v>183</v>
+        <v>10153</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>307</v>
+        <v>83</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>210</v>
+        <v>573</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>34</v>
@@ -4650,44 +4665,44 @@
         <v>8</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>211</v>
+        <v>574</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F103" s="5" t="s">
-        <v>58</v>
+      <c r="F103" s="5">
+        <v>20154</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>549</v>
+        <v>282</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>550</v>
+        <v>306</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F104" s="5">
-        <v>20154</v>
+        <v>183</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>159</v>
+        <v>307</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>275</v>
+        <v>210</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>34</v>
@@ -4696,90 +4711,90 @@
         <v>8</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>276</v>
+        <v>211</v>
       </c>
       <c r="E105" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>128</v>
+        <v>549</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>129</v>
+        <v>550</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F106" s="5">
+        <v>20154</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>242</v>
+        <v>275</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>129</v>
+        <v>276</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>414</v>
+        <v>128</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>415</v>
+        <v>129</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>180</v>
+        <v>31</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>28</v>
@@ -4788,7 +4803,7 @@
         <v>8</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>30</v>
@@ -4802,145 +4817,145 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>238</v>
+        <v>414</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>146</v>
+        <v>9</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>239</v>
+        <v>415</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>241</v>
+        <v>180</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>598</v>
+        <v>274</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>599</v>
+        <v>29</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F111" s="5">
-        <v>20122</v>
+        <v>30</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>537</v>
+        <v>238</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>538</v>
+        <v>146</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>539</v>
+        <v>239</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="F112" s="5">
-        <v>34133</v>
+        <v>240</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>514</v>
+        <v>150</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>435</v>
+        <v>598</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>129</v>
+        <v>599</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F113" s="5">
-        <v>39100</v>
+        <v>20122</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>206</v>
+        <v>537</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>34</v>
+        <v>538</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>60</v>
+        <v>539</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>61</v>
+        <v>540</v>
+      </c>
+      <c r="F114" s="5">
+        <v>34133</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>38</v>
+        <v>514</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>366</v>
+        <v>435</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F115" s="5">
-        <v>20123</v>
+        <v>39100</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>101</v>
+        <v>206</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>34</v>
@@ -4963,122 +4978,122 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>493</v>
+        <v>366</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>494</v>
+        <v>60</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F117" s="8" t="s">
-        <v>273</v>
+        <v>36</v>
+      </c>
+      <c r="F117" s="5">
+        <v>20123</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>519</v>
+        <v>101</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>520</v>
+        <v>60</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F118" s="5">
-        <v>80121</v>
+        <v>36</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>406</v>
+        <v>493</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>407</v>
+        <v>494</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="F119" s="5">
-        <v>38121</v>
+        <v>10</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>369</v>
+        <v>519</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>370</v>
+        <v>520</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F120" s="5">
-        <v>20123</v>
+        <v>80121</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>360</v>
+        <v>406</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>17</v>
+        <v>264</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>361</v>
+        <v>407</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>19</v>
+        <v>408</v>
       </c>
       <c r="F121" s="5">
-        <v>90139</v>
+        <v>38121</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>12</v>
+        <v>268</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>34</v>
@@ -5087,7 +5102,7 @@
         <v>8</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>195</v>
+        <v>370</v>
       </c>
       <c r="E122" s="4" t="s">
         <v>36</v>
@@ -5101,53 +5116,53 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>455</v>
+        <v>360</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>456</v>
+        <v>361</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F123" s="8" t="s">
-        <v>180</v>
+        <v>19</v>
+      </c>
+      <c r="F123" s="5">
+        <v>90139</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>283</v>
+        <v>345</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>309</v>
+        <v>195</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>310</v>
+        <v>36</v>
       </c>
       <c r="F124" s="5">
-        <v>12037</v>
+        <v>20123</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>13</v>
+        <v>455</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>9</v>
@@ -5156,90 +5171,90 @@
         <v>8</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>14</v>
+        <v>456</v>
       </c>
       <c r="E125" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F125" s="5" t="s">
-        <v>15</v>
+      <c r="F125" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>123</v>
+        <v>283</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>28</v>
+        <v>308</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>55</v>
+        <v>309</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F126" s="5" t="s">
-        <v>31</v>
+        <v>310</v>
+      </c>
+      <c r="F126" s="5">
+        <v>12037</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>32</v>
+        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>28</v>
@@ -5248,7 +5263,7 @@
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>30</v>
@@ -5262,122 +5277,122 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>498</v>
+        <v>74</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C130" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C130" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F130" s="5">
-        <v>39100</v>
+        <v>10</v>
+      </c>
+      <c r="F130" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>233</v>
+        <v>27</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>234</v>
+        <v>29</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>218</v>
+        <v>31</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>590</v>
+        <v>498</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C132" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C132" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>591</v>
+        <v>29</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F132" s="5">
-        <v>20122</v>
+        <v>39100</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>188</v>
+        <v>233</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>189</v>
+        <v>234</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>483</v>
+        <v>590</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>484</v>
+        <v>34</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>485</v>
+        <v>591</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>486</v>
+        <v>36</v>
       </c>
       <c r="F134" s="5">
-        <v>66020</v>
+        <v>20122</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>576</v>
+        <v>188</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>34</v>
@@ -5386,13 +5401,13 @@
         <v>8</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>577</v>
+        <v>189</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F135" s="5">
-        <v>20124</v>
+      <c r="F135" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G135" s="4" t="s">
         <v>159</v>
@@ -5400,122 +5415,122 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>411</v>
+        <v>483</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>341</v>
+        <v>484</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>412</v>
+        <v>485</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>413</v>
+        <v>486</v>
       </c>
       <c r="F136" s="5">
-        <v>37137</v>
+        <v>66020</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>343</v>
+        <v>77</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>460</v>
+        <v>576</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>461</v>
+        <v>577</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F137" s="8" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F137" s="5">
+        <v>20124</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>295</v>
+        <v>411</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>296</v>
+        <v>341</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>297</v>
+        <v>412</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>298</v>
+        <v>413</v>
       </c>
       <c r="F138" s="5">
-        <v>56010</v>
+        <v>37137</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>299</v>
+        <v>343</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>603</v>
+        <v>460</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>604</v>
+        <v>461</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F139" s="5">
-        <v>20145</v>
+        <v>10</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>136</v>
+        <v>11</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>22</v>
+        <v>296</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="F140" s="5">
-        <v>40060</v>
+        <v>56010</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>26</v>
+        <v>299</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>384</v>
+        <v>603</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>34</v>
@@ -5524,67 +5539,67 @@
         <v>8</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>385</v>
+        <v>604</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F141" s="5">
-        <v>20121</v>
+        <v>20145</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>386</v>
+        <v>311</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>385</v>
+        <v>312</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>58</v>
+        <v>313</v>
+      </c>
+      <c r="F142" s="5">
+        <v>40060</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>213</v>
+        <v>384</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>179</v>
+        <v>385</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F143" s="5" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F143" s="5">
+        <v>20121</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>575</v>
+        <v>386</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>34</v>
@@ -5593,228 +5608,228 @@
         <v>8</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>192</v>
+        <v>385</v>
       </c>
       <c r="E144" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F144" s="5">
-        <v>20124</v>
+      <c r="F144" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>589</v>
+        <v>213</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F145" s="5">
-        <v>20124</v>
+        <v>10</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>68</v>
+        <v>575</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>72</v>
+        <v>36</v>
+      </c>
+      <c r="F146" s="5">
+        <v>20124</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>284</v>
+        <v>589</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>314</v>
+        <v>34</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>315</v>
+        <v>192</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>316</v>
+        <v>36</v>
       </c>
       <c r="F147" s="5">
-        <v>57021</v>
+        <v>20124</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>299</v>
+        <v>159</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>179</v>
+        <v>70</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>462</v>
+        <v>284</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>9</v>
+        <v>314</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>179</v>
+        <v>315</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F149" s="8" t="s">
-        <v>180</v>
+        <v>316</v>
+      </c>
+      <c r="F149" s="5">
+        <v>57021</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>77</v>
+        <v>299</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>346</v>
+        <v>462</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>347</v>
+        <v>179</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="F151" s="5">
-        <v>70124</v>
+        <v>10</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>333</v>
+        <v>89</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F152" s="5">
-        <v>20158</v>
+        <v>92</v>
+      </c>
+      <c r="F152" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>159</v>
+        <v>94</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>308</v>
+        <v>40</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="F153" s="5">
-        <v>12084</v>
+        <v>70124</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>307</v>
+        <v>44</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="B154" s="4" t="s">
         <v>34</v>
@@ -5823,205 +5838,205 @@
         <v>8</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E154" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F154" s="5" t="s">
-        <v>61</v>
+      <c r="F154" s="5">
+        <v>20158</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>227</v>
+        <v>357</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>228</v>
+        <v>358</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F155" s="5" t="s">
-        <v>37</v>
+        <v>359</v>
+      </c>
+      <c r="F155" s="5">
+        <v>12084</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>457</v>
+        <v>194</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>458</v>
+        <v>195</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F156" s="8" t="s">
-        <v>459</v>
+        <v>36</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>108</v>
+        <v>227</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="F158" s="5">
-        <v>12100</v>
+        <v>10</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>459</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>395</v>
+        <v>108</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F159" s="5">
-        <v>40127</v>
+        <v>111</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>355</v>
+        <v>431</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>356</v>
+        <v>432</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>36</v>
+        <v>433</v>
       </c>
       <c r="F160" s="5">
-        <v>20121</v>
+        <v>12100</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>556</v>
+        <v>395</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>525</v>
+        <v>23</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F161" s="5">
-        <v>20154</v>
+        <v>40127</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>526</v>
+        <v>611</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>525</v>
+        <v>612</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F162" s="5">
-        <v>20154</v>
+        <v>40122</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>524</v>
+        <v>355</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>34</v>
@@ -6030,21 +6045,21 @@
         <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>525</v>
+        <v>356</v>
       </c>
       <c r="E163" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F163" s="5">
-        <v>20154</v>
+        <v>20121</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>596</v>
+        <v>556</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>34</v>
@@ -6053,7 +6068,7 @@
         <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>597</v>
+        <v>525</v>
       </c>
       <c r="E164" s="4" t="s">
         <v>36</v>
@@ -6067,53 +6082,53 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>29</v>
+        <v>525</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F165" s="5">
-        <v>39100</v>
+        <v>20154</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>232</v>
+        <v>524</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>29</v>
+        <v>525</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="F166" s="5">
+        <v>20154</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>143</v>
+        <v>596</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>34</v>
@@ -6122,205 +6137,205 @@
         <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>144</v>
+        <v>597</v>
       </c>
       <c r="E167" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F167" s="5" t="s">
-        <v>37</v>
+      <c r="F167" s="5">
+        <v>20154</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>56</v>
+        <v>515</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>58</v>
+        <v>30</v>
+      </c>
+      <c r="F168" s="5">
+        <v>39100</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>441</v>
+        <v>232</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>442</v>
+        <v>29</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="F169" s="5">
-        <v>20038</v>
+        <v>30</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>426</v>
+        <v>143</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>236</v>
+        <v>144</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F170" s="5">
-        <v>10121</v>
+        <v>36</v>
+      </c>
+      <c r="F170" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>377</v>
+        <v>441</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>378</v>
+        <v>34</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>379</v>
+        <v>442</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>380</v>
+        <v>443</v>
       </c>
       <c r="F172" s="5">
-        <v>64020</v>
+        <v>20038</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>77</v>
+        <v>136</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>580</v>
+        <v>426</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>581</v>
+        <v>236</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F173" s="8" t="s">
-        <v>582</v>
+        <v>81</v>
+      </c>
+      <c r="F173" s="5">
+        <v>10121</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>410</v>
+        <v>95</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>211</v>
+        <v>97</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F174" s="5">
-        <v>20121</v>
+        <v>98</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>133</v>
+        <v>377</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>34</v>
+        <v>378</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>134</v>
+        <v>379</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F175" s="5" t="s">
-        <v>135</v>
+        <v>380</v>
+      </c>
+      <c r="F175" s="5">
+        <v>64020</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>605</v>
+        <v>580</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>9</v>
@@ -6329,13 +6344,13 @@
         <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>606</v>
+        <v>581</v>
       </c>
       <c r="E176" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F176" s="8" t="s">
-        <v>607</v>
+        <v>582</v>
       </c>
       <c r="G176" s="4" t="s">
         <v>11</v>
@@ -6343,7 +6358,7 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>257</v>
+        <v>410</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>34</v>
@@ -6352,13 +6367,13 @@
         <v>8</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>258</v>
+        <v>211</v>
       </c>
       <c r="E177" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F177" s="5" t="s">
-        <v>58</v>
+      <c r="F177" s="5">
+        <v>20121</v>
       </c>
       <c r="G177" s="4" t="s">
         <v>38</v>
@@ -6366,53 +6381,53 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>340</v>
+        <v>133</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>342</v>
+        <v>134</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="F178" s="5">
-        <v>37045</v>
+        <v>36</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>343</v>
+        <v>136</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>166</v>
+        <v>605</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>167</v>
+        <v>606</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F179" s="5" t="s">
-        <v>168</v>
+        <v>10</v>
+      </c>
+      <c r="F179" s="8" t="s">
+        <v>607</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>529</v>
+        <v>257</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>34</v>
@@ -6421,44 +6436,44 @@
         <v>8</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>167</v>
+        <v>258</v>
       </c>
       <c r="E180" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F180" s="5">
-        <v>20126</v>
+      <c r="F180" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>601</v>
+        <v>340</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>602</v>
+        <v>342</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>36</v>
+        <v>528</v>
       </c>
       <c r="F181" s="5">
-        <v>20138</v>
+        <v>37045</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>262</v>
+        <v>343</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>609</v>
+        <v>166</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>34</v>
@@ -6467,21 +6482,21 @@
         <v>8</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>610</v>
+        <v>167</v>
       </c>
       <c r="E182" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F182" s="5">
-        <v>20122</v>
+      <c r="F182" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>594</v>
+        <v>529</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>34</v>
@@ -6490,21 +6505,21 @@
         <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>394</v>
+        <v>167</v>
       </c>
       <c r="E183" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F183" s="5">
-        <v>20123</v>
+        <v>20126</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>471</v>
+        <v>601</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>34</v>
@@ -6513,13 +6528,13 @@
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>260</v>
+        <v>602</v>
       </c>
       <c r="E184" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F184" s="5">
-        <v>20135</v>
+        <v>20138</v>
       </c>
       <c r="G184" s="4" t="s">
         <v>262</v>
@@ -6527,7 +6542,7 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>405</v>
+        <v>609</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>34</v>
@@ -6536,44 +6551,44 @@
         <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>260</v>
+        <v>610</v>
       </c>
       <c r="E185" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F185" s="5">
-        <v>20135</v>
+        <v>20122</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>262</v>
+        <v>38</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>204</v>
+        <v>594</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>205</v>
+        <v>394</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F186" s="5" t="s">
-        <v>187</v>
+        <v>36</v>
+      </c>
+      <c r="F186" s="5">
+        <v>20123</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>319</v>
+        <v>38</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>34</v>
@@ -6582,21 +6597,21 @@
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>454</v>
+        <v>260</v>
       </c>
       <c r="E187" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F187" s="5">
-        <v>20144</v>
+        <v>20135</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>223</v>
+        <v>405</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>34</v>
@@ -6605,389 +6620,389 @@
         <v>8</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F188" s="5" t="s">
-        <v>135</v>
+      <c r="F188" s="5">
+        <v>20135</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>136</v>
+        <v>262</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>285</v>
+        <v>204</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>22</v>
+        <v>185</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>317</v>
+        <v>205</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="F189" s="10">
-        <v>40026</v>
+        <v>186</v>
+      </c>
+      <c r="F189" s="10" t="s">
+        <v>187</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>26</v>
+        <v>319</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>286</v>
+        <v>453</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>320</v>
+        <v>454</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F190" s="10" t="s">
-        <v>323</v>
+        <v>36</v>
+      </c>
+      <c r="F190" s="10">
+        <v>20144</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>533</v>
+        <v>223</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F191" s="10">
-        <v>39100</v>
+        <v>36</v>
+      </c>
+      <c r="F191" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>32</v>
+        <v>136</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>367</v>
+        <v>285</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>368</v>
+        <v>317</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="F192" s="10">
-        <v>20123</v>
+        <v>40026</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="F193" s="10">
-        <v>12020</v>
+        <v>10</v>
+      </c>
+      <c r="F193" s="10" t="s">
+        <v>323</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>307</v>
+        <v>11</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
-        <v>39</v>
+        <v>533</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C194" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E194" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="F194" s="10" t="s">
-        <v>43</v>
+        <v>30</v>
+      </c>
+      <c r="F194" s="10">
+        <v>39100</v>
       </c>
       <c r="G194" s="9" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>422</v>
+        <v>34</v>
       </c>
       <c r="C195" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>423</v>
+        <v>368</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>424</v>
+        <v>36</v>
       </c>
       <c r="F195" s="10">
-        <v>28053</v>
+        <v>20123</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
-        <v>172</v>
+        <v>287</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C196" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>169</v>
+        <v>321</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F196" s="10" t="s">
-        <v>171</v>
+        <v>322</v>
+      </c>
+      <c r="F196" s="10">
+        <v>12020</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>159</v>
+        <v>307</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>560</v>
+        <v>39</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C197" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>561</v>
+        <v>41</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F197" s="10">
-        <v>39100</v>
+        <v>42</v>
+      </c>
+      <c r="F197" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>198</v>
+        <v>421</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>22</v>
+        <v>422</v>
       </c>
       <c r="C198" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>199</v>
+        <v>423</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F198" s="10" t="s">
-        <v>200</v>
+        <v>424</v>
+      </c>
+      <c r="F198" s="10">
+        <v>28053</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C199" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="F199" s="10" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
-        <v>244</v>
+        <v>560</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C200" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>177</v>
+        <v>561</v>
       </c>
       <c r="E200" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F200" s="10" t="s">
-        <v>58</v>
+        <v>30</v>
+      </c>
+      <c r="F200" s="10">
+        <v>39100</v>
       </c>
       <c r="G200" s="9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="9" t="s">
-        <v>534</v>
+        <v>198</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C201" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D201" s="9" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F201" s="10">
-        <v>20121</v>
+        <v>24</v>
+      </c>
+      <c r="F201" s="10" t="s">
+        <v>200</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
-        <v>578</v>
+        <v>207</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C202" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>579</v>
+        <v>208</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F202" s="10">
-        <v>20121</v>
+        <v>71</v>
+      </c>
+      <c r="F202" s="10" t="s">
+        <v>209</v>
       </c>
       <c r="G202" s="9" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="9" t="s">
-        <v>445</v>
+        <v>244</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="C203" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D203" s="9" t="s">
-        <v>447</v>
+        <v>177</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="F203" s="10">
-        <v>53048</v>
+        <v>36</v>
+      </c>
+      <c r="F203" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>449</v>
+        <v>38</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>509</v>
+        <v>34</v>
       </c>
       <c r="C204" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D204" s="9" t="s">
-        <v>517</v>
+        <v>177</v>
       </c>
       <c r="E204" s="9" t="s">
-        <v>518</v>
+        <v>36</v>
       </c>
       <c r="F204" s="10">
-        <v>35011</v>
+        <v>20121</v>
       </c>
       <c r="G204" s="9" t="s">
-        <v>505</v>
+        <v>38</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="9" t="s">
-        <v>243</v>
+        <v>578</v>
       </c>
       <c r="B205" s="9" t="s">
         <v>34</v>
@@ -6996,13 +7011,13 @@
         <v>8</v>
       </c>
       <c r="D205" s="9" t="s">
-        <v>177</v>
+        <v>579</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F205" s="10" t="s">
-        <v>58</v>
+      <c r="F205" s="10">
+        <v>20121</v>
       </c>
       <c r="G205" s="9" t="s">
         <v>38</v>
@@ -7010,114 +7025,114 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="9" t="s">
-        <v>131</v>
+        <v>445</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>28</v>
+        <v>446</v>
       </c>
       <c r="C206" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D206" s="9" t="s">
-        <v>132</v>
+        <v>447</v>
       </c>
       <c r="E206" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F206" s="10" t="s">
-        <v>31</v>
+        <v>448</v>
+      </c>
+      <c r="F206" s="10">
+        <v>53048</v>
       </c>
       <c r="G206" s="9" t="s">
-        <v>32</v>
+        <v>449</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
-        <v>531</v>
+        <v>516</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>34</v>
+        <v>509</v>
       </c>
       <c r="C207" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D207" s="9" t="s">
-        <v>532</v>
+        <v>517</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>36</v>
+        <v>518</v>
       </c>
       <c r="F207" s="10">
-        <v>20121</v>
+        <v>35011</v>
       </c>
       <c r="G207" s="9" t="s">
-        <v>38</v>
+        <v>505</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="9" t="s">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C208" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D208" s="9" t="s">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="E208" s="9" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F208" s="10" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G208" s="9" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A209" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="B209" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C209" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D209" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="E209" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F209" s="11" t="s">
-        <v>568</v>
-      </c>
-      <c r="G209" s="3" t="s">
-        <v>77</v>
+      <c r="A209" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B209" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C209" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D209" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E209" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F209" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G209" s="9" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A210" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="B210" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C210" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D210" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="E210" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="F210" s="10">
-        <v>20089</v>
+      <c r="A210" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F210" s="7">
+        <v>20121</v>
       </c>
       <c r="G210" s="9" t="s">
         <v>38</v>
@@ -7125,30 +7140,30 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="9" t="s">
-        <v>475</v>
+        <v>531</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C211" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D211" s="9" t="s">
-        <v>476</v>
+        <v>532</v>
       </c>
       <c r="E211" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F211" s="12" t="s">
-        <v>477</v>
+        <v>36</v>
+      </c>
+      <c r="F211" s="10">
+        <v>20121</v>
       </c>
       <c r="G211" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="9" t="s">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="B212" s="9" t="s">
         <v>22</v>
@@ -7157,44 +7172,44 @@
         <v>8</v>
       </c>
       <c r="D212" s="9" t="s">
-        <v>202</v>
+        <v>23</v>
       </c>
       <c r="E212" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F212" s="10" t="s">
-        <v>203</v>
+        <v>25</v>
       </c>
       <c r="G212" s="9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A213" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="B213" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C213" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D213" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="E213" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F213" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="G213" s="9" t="s">
-        <v>159</v>
+      <c r="A213" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F213" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="9" t="s">
-        <v>438</v>
+        <v>381</v>
       </c>
       <c r="B214" s="9" t="s">
         <v>34</v>
@@ -7203,67 +7218,67 @@
         <v>8</v>
       </c>
       <c r="D214" s="9" t="s">
-        <v>215</v>
+        <v>382</v>
       </c>
       <c r="E214" s="9" t="s">
-        <v>36</v>
+        <v>383</v>
       </c>
       <c r="F214" s="10">
-        <v>20124</v>
+        <v>20089</v>
       </c>
       <c r="G214" s="9" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="9" t="s">
-        <v>229</v>
+        <v>475</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C215" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D215" s="9" t="s">
-        <v>230</v>
+        <v>476</v>
       </c>
       <c r="E215" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F215" s="10" t="s">
-        <v>231</v>
+        <v>10</v>
+      </c>
+      <c r="F215" s="12" t="s">
+        <v>477</v>
       </c>
       <c r="G215" s="9" t="s">
-        <v>136</v>
+        <v>11</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="9" t="s">
-        <v>256</v>
+        <v>212</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C216" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D216" s="9" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="E216" s="9" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F216" s="10" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="G216" s="9" t="s">
-        <v>136</v>
+        <v>26</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
-        <v>472</v>
+        <v>214</v>
       </c>
       <c r="B217" s="9" t="s">
         <v>34</v>
@@ -7272,21 +7287,21 @@
         <v>8</v>
       </c>
       <c r="D217" s="9" t="s">
-        <v>464</v>
+        <v>215</v>
       </c>
       <c r="E217" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F217" s="10">
-        <v>20129</v>
+      <c r="F217" s="10" t="s">
+        <v>158</v>
       </c>
       <c r="G217" s="9" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="9" t="s">
-        <v>463</v>
+        <v>438</v>
       </c>
       <c r="B218" s="9" t="s">
         <v>34</v>
@@ -7295,21 +7310,21 @@
         <v>8</v>
       </c>
       <c r="D218" s="9" t="s">
-        <v>464</v>
+        <v>215</v>
       </c>
       <c r="E218" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F218" s="10">
-        <v>20129</v>
+        <v>20124</v>
       </c>
       <c r="G218" s="9" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="9" t="s">
-        <v>473</v>
+        <v>229</v>
       </c>
       <c r="B219" s="9" t="s">
         <v>34</v>
@@ -7318,21 +7333,21 @@
         <v>8</v>
       </c>
       <c r="D219" s="9" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E219" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F219" s="10">
-        <v>20129</v>
+      <c r="F219" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="G219" s="9" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="9" t="s">
-        <v>474</v>
+        <v>256</v>
       </c>
       <c r="B220" s="9" t="s">
         <v>34</v>
@@ -7341,21 +7356,21 @@
         <v>8</v>
       </c>
       <c r="D220" s="9" t="s">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="E220" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F220" s="10">
-        <v>20129</v>
+      <c r="F220" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="G220" s="9" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="9" t="s">
-        <v>176</v>
+        <v>472</v>
       </c>
       <c r="B221" s="9" t="s">
         <v>34</v>
@@ -7364,573 +7379,573 @@
         <v>8</v>
       </c>
       <c r="D221" s="9" t="s">
-        <v>177</v>
+        <v>464</v>
       </c>
       <c r="E221" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F221" s="10" t="s">
-        <v>58</v>
+      <c r="F221" s="10">
+        <v>20129</v>
       </c>
       <c r="G221" s="9" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="9" t="s">
-        <v>331</v>
+        <v>463</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C222" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D222" s="9" t="s">
-        <v>332</v>
+        <v>464</v>
       </c>
       <c r="E222" s="9" t="s">
-        <v>318</v>
+        <v>36</v>
       </c>
       <c r="F222" s="10">
-        <v>40026</v>
+        <v>20129</v>
       </c>
       <c r="G222" s="9" t="s">
-        <v>26</v>
+        <v>262</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="9" t="s">
-        <v>288</v>
+        <v>473</v>
       </c>
       <c r="B223" s="9" t="s">
         <v>34</v>
       </c>
       <c r="C223" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D223" s="9" t="s">
-        <v>324</v>
+        <v>464</v>
       </c>
       <c r="E223" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F223" s="10">
-        <v>20124</v>
+        <v>20129</v>
       </c>
       <c r="G223" s="9" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="9" t="s">
-        <v>450</v>
+        <v>474</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C224" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D224" s="9" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="E224" s="9" t="s">
-        <v>452</v>
+        <v>36</v>
       </c>
       <c r="F224" s="10">
-        <v>12011</v>
+        <v>20129</v>
       </c>
       <c r="G224" s="9" t="s">
-        <v>307</v>
+        <v>262</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="9" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="B225" s="9" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="C225" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D225" s="9" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="E225" s="9" t="s">
-        <v>154</v>
+        <v>36</v>
       </c>
       <c r="F225" s="10" t="s">
-        <v>155</v>
+        <v>58</v>
       </c>
       <c r="G225" s="9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="9" t="s">
-        <v>419</v>
+        <v>331</v>
       </c>
       <c r="B226" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C226" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D226" s="9" t="s">
-        <v>420</v>
+        <v>332</v>
       </c>
       <c r="E226" s="9" t="s">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="F226" s="10">
-        <v>20123</v>
+        <v>40026</v>
       </c>
       <c r="G226" s="9" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="9" t="s">
-        <v>491</v>
+        <v>288</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C227" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D227" s="9" t="s">
-        <v>492</v>
+        <v>324</v>
       </c>
       <c r="E227" s="9" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F227" s="10">
-        <v>90141</v>
+        <v>20124</v>
       </c>
       <c r="G227" s="9" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="9" t="s">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="B228" s="9" t="s">
-        <v>9</v>
+        <v>308</v>
       </c>
       <c r="C228" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D228" s="9" t="s">
-        <v>388</v>
+        <v>451</v>
       </c>
       <c r="E228" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F228" s="12" t="s">
-        <v>390</v>
+        <v>452</v>
+      </c>
+      <c r="F228" s="10">
+        <v>12011</v>
       </c>
       <c r="G228" s="9" t="s">
-        <v>11</v>
+        <v>307</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A229" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="B229" s="3" t="s">
-        <v>9</v>
+      <c r="A229" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="B229" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="C229" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D229" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E229" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F229" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="G229" s="3" t="s">
-        <v>11</v>
+      <c r="D229" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E229" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="F229" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="G229" s="9" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="9" t="s">
-        <v>387</v>
+        <v>419</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C230" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D230" s="9" t="s">
-        <v>388</v>
+        <v>420</v>
       </c>
       <c r="E230" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F230" s="10" t="s">
-        <v>390</v>
+        <v>36</v>
+      </c>
+      <c r="F230" s="10">
+        <v>20123</v>
       </c>
       <c r="G230" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="9" t="s">
-        <v>465</v>
+        <v>491</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>264</v>
+        <v>17</v>
       </c>
       <c r="C231" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D231" s="9" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
       <c r="E231" s="9" t="s">
-        <v>467</v>
+        <v>19</v>
       </c>
       <c r="F231" s="10">
-        <v>38055</v>
+        <v>90141</v>
       </c>
       <c r="G231" s="9" t="s">
-        <v>268</v>
+        <v>12</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A232" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="B232" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C232" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D232" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E232" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F232" s="7">
-        <v>20145</v>
-      </c>
-      <c r="G232" s="3" t="s">
-        <v>136</v>
+      <c r="A232" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="B232" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C232" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D232" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="E232" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F232" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="G232" s="9" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A233" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="B233" s="9" t="s">
-        <v>103</v>
+      <c r="A233" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C233" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D233" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="E233" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="F233" s="10">
-        <v>25010</v>
-      </c>
-      <c r="G233" s="9" t="s">
-        <v>107</v>
+      <c r="D233" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F233" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="9" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B234" s="9" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C234" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D234" s="9" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="E234" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F234" s="10">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F234" s="10" t="s">
+        <v>390</v>
       </c>
       <c r="G234" s="9" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="9" t="s">
-        <v>416</v>
+        <v>465</v>
       </c>
       <c r="B235" s="9" t="s">
-        <v>85</v>
+        <v>264</v>
       </c>
       <c r="C235" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D235" s="9" t="s">
-        <v>417</v>
+        <v>466</v>
       </c>
       <c r="E235" s="9" t="s">
-        <v>418</v>
+        <v>467</v>
       </c>
       <c r="F235" s="10">
-        <v>71016</v>
+        <v>38055</v>
       </c>
       <c r="G235" s="9" t="s">
-        <v>44</v>
+        <v>268</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A236" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B236" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C236" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D236" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E236" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F236" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G236" s="9" t="s">
-        <v>12</v>
+      <c r="A236" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F236" s="7">
+        <v>20145</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="9" t="s">
-        <v>325</v>
+        <v>427</v>
       </c>
       <c r="B237" s="9" t="s">
-        <v>326</v>
+        <v>103</v>
       </c>
       <c r="C237" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D237" s="9" t="s">
-        <v>327</v>
+        <v>428</v>
       </c>
       <c r="E237" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="F237" s="10" t="s">
-        <v>329</v>
+        <v>429</v>
+      </c>
+      <c r="F237" s="10">
+        <v>25010</v>
       </c>
       <c r="G237" s="9" t="s">
-        <v>330</v>
+        <v>107</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A238" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="B238" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C238" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D238" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="E238" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F238" s="7">
-        <v>20122</v>
-      </c>
-      <c r="G238" s="3" t="s">
+      <c r="A238" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="B238" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C238" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D238" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="E238" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F238" s="10">
+        <v>20123</v>
+      </c>
+      <c r="G238" s="9" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" s="9" t="s">
-        <v>277</v>
+        <v>416</v>
       </c>
       <c r="B239" s="9" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="C239" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D239" s="9" t="s">
-        <v>278</v>
+        <v>417</v>
       </c>
       <c r="E239" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F239" s="10" t="s">
-        <v>37</v>
+        <v>418</v>
+      </c>
+      <c r="F239" s="10">
+        <v>71016</v>
       </c>
       <c r="G239" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="9" t="s">
-        <v>478</v>
+        <v>16</v>
       </c>
       <c r="B240" s="9" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C240" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D240" s="9" t="s">
-        <v>479</v>
+        <v>18</v>
       </c>
       <c r="E240" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F240" s="10">
-        <v>20123</v>
+        <v>19</v>
+      </c>
+      <c r="F240" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="G240" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A241" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="B241" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="C241" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D241" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E241" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="F241" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="G241" s="9" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A242" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="E242" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F242" s="7">
+        <v>20122</v>
+      </c>
+      <c r="G242" s="3" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A241" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="B241" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C241" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D241" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="E241" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="F241" s="7">
-        <v>20094</v>
-      </c>
-      <c r="G241" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A242" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="B242" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C242" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D242" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="E242" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F242" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="G242" s="9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" s="9" t="s">
-        <v>216</v>
+        <v>277</v>
       </c>
       <c r="B243" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C243" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D243" s="9" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="E243" s="9" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F243" s="10" t="s">
-        <v>218</v>
+        <v>37</v>
       </c>
       <c r="G243" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" s="9" t="s">
-        <v>160</v>
+        <v>478</v>
       </c>
       <c r="B244" s="9" t="s">
-        <v>161</v>
+        <v>34</v>
       </c>
       <c r="C244" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D244" s="9" t="s">
-        <v>162</v>
+        <v>479</v>
       </c>
       <c r="E244" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="F244" s="10" t="s">
-        <v>164</v>
+        <v>36</v>
+      </c>
+      <c r="F244" s="10">
+        <v>20123</v>
       </c>
       <c r="G244" s="9" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A245" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="B245" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C245" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D245" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="E245" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F245" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="G245" s="9" t="s">
-        <v>11</v>
+      <c r="A245" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="E245" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="F245" s="7">
+        <v>20094</v>
+      </c>
+      <c r="G245" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" s="9" t="s">
-        <v>255</v>
+        <v>396</v>
       </c>
       <c r="B246" s="9" t="s">
         <v>9</v>
@@ -7953,30 +7968,122 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B247" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C247" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D247" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E247" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F247" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G247" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A248" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B248" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C248" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D248" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E248" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F248" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G248" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A249" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="B249" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C249" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D249" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E249" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F249" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G249" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A250" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B250" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C250" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D250" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E250" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F250" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G250" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A251" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B247" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C247" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D247" s="9" t="s">
+      <c r="B251" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C251" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D251" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E247" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F247" s="10" t="s">
+      <c r="E251" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F251" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G247" s="9" t="s">
+      <c r="G251" s="9" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G218" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G247">
+    <sortState ref="A2:G251">
       <sortCondition ref="A1:A218"/>
     </sortState>
   </autoFilter>
@@ -7989,6 +8096,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F040406D9EE34E48977C379A242BB45D" ma:contentTypeVersion="15" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="1ab2d492e43f6bec9a26aa4599c840e9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="877b7d34-4df7-40bf-9eb1-208952470e96" xmlns:ns4="05fc27dd-4454-4248-9c78-3d72b2b155c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebc604e5d4aadf5a992ba83f8d4fb519" ns3:_="" ns4:_="">
     <xsd:import namespace="877b7d34-4df7-40bf-9eb1-208952470e96"/>
@@ -8221,24 +8345,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBC6436E-C4E7-4E8D-94E8-64DAEC05792B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8255,29 +8387,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{46003179-19A0-467C-BD15-1431E9467DA7}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{18C4CF28-FFF8-4500-B8A9-D0C46F5ADB3D}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="655">
   <si>
     <t>Nome account</t>
   </si>
@@ -1871,6 +1871,123 @@
   </si>
   <si>
     <t>AIEM GREEN SRL</t>
+  </si>
+  <si>
+    <t>EDERA SOL SRL</t>
+  </si>
+  <si>
+    <t>COGEME NUOVE ENERGIE SRL</t>
+  </si>
+  <si>
+    <t>VIA XXV APRILE 18</t>
+  </si>
+  <si>
+    <t>ROVATO</t>
+  </si>
+  <si>
+    <t>TRINA SOLAR TOSCANA 1 SRL</t>
+  </si>
+  <si>
+    <t>IPC SOLAR BELT SRL</t>
+  </si>
+  <si>
+    <t>REVALUE PV 11 SRL</t>
+  </si>
+  <si>
+    <t>SORGENIA PEGASO SRL</t>
+  </si>
+  <si>
+    <t>APOLLO SOLAR 7 SRL</t>
+  </si>
+  <si>
+    <t>SWISSPOWER RINNOVABILI SRL</t>
+  </si>
+  <si>
+    <t>VIA SAN PROSPERO 4</t>
+  </si>
+  <si>
+    <t>APICE VERDE SRL</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
+    <t>VIA VALSUGANA 102</t>
+  </si>
+  <si>
+    <t>CASSOLA</t>
+  </si>
+  <si>
+    <t>LUNER INVEST SRL</t>
+  </si>
+  <si>
+    <t>VIA SANKT PROKULUS 6/C</t>
+  </si>
+  <si>
+    <t>NATURNO</t>
+  </si>
+  <si>
+    <t>REVALUE PV 2 SRL</t>
+  </si>
+  <si>
+    <t>SORGENIA GREEN SOLUTIONS SRL</t>
+  </si>
+  <si>
+    <t>VIA LUNGO SERIO 17</t>
+  </si>
+  <si>
+    <t>RONCELLO CAPITAL SRL</t>
+  </si>
+  <si>
+    <t>VIA LOMBARDIA 2/A</t>
+  </si>
+  <si>
+    <t>PESCHIERA BORROMEO</t>
+  </si>
+  <si>
+    <t>VATT ENERGY SRL</t>
+  </si>
+  <si>
+    <t>VIA GIOVANNI BOCCACCIO 7</t>
+  </si>
+  <si>
+    <t>TEP RENEWABLES (BONDENO PV) SRL</t>
+  </si>
+  <si>
+    <t>SOLAR ENERGY VENTUNO SRL</t>
+  </si>
+  <si>
+    <t>RINNOVABILI SUD DUE SRL</t>
+  </si>
+  <si>
+    <t>VIA DELLA CHIMICA 103</t>
+  </si>
+  <si>
+    <t>MESAGNE SRL</t>
+  </si>
+  <si>
+    <t>VIALE AMEDEO DUCA D'AOSTA 51</t>
+  </si>
+  <si>
+    <t>ENEL GREEN POWER ITALIA SRL</t>
+  </si>
+  <si>
+    <t>VIALE REGINA MARGHERITA, 125</t>
+  </si>
+  <si>
+    <t>CCEN IRSINA SRL</t>
+  </si>
+  <si>
+    <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
+  </si>
+  <si>
+    <t>CORSO GIUSEPPE GARIBALDI 49</t>
+  </si>
+  <si>
+    <t>ICUBE DEVELOPMENT 16 SRL</t>
+  </si>
+  <si>
+    <t>PIAZZA LINA BO BARDI 3</t>
   </si>
 </sst>
 </file>
@@ -2295,7 +2412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G251"/>
+  <dimension ref="A1:G274"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -2862,30 +2979,30 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>403</v>
+        <v>627</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>28</v>
+        <v>628</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>404</v>
+        <v>629</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>30</v>
+        <v>630</v>
       </c>
       <c r="F25" s="5">
-        <v>39100</v>
+        <v>36022</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>32</v>
+        <v>505</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>595</v>
+        <v>403</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>28</v>
@@ -2908,53 +3025,53 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>399</v>
+        <v>595</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F27" s="5">
-        <v>20124</v>
+        <v>39100</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>468</v>
+        <v>624</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>469</v>
+        <v>404</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>470</v>
+        <v>30</v>
+      </c>
+      <c r="F28" s="5">
+        <v>39100</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>436</v>
+        <v>399</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>34</v>
@@ -2963,205 +3080,205 @@
         <v>8</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>305</v>
+        <v>400</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F29" s="5">
-        <v>20123</v>
+        <v>20124</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>349</v>
+        <v>468</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>350</v>
+        <v>469</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F30" s="5">
-        <v>20122</v>
+        <v>10</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>470</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>67</v>
+        <v>436</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>18</v>
+        <v>305</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="F31" s="5">
+        <v>20123</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>398</v>
+        <v>349</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F32" s="5">
-        <v>10123</v>
+        <v>20122</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>546</v>
+        <v>398</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>511</v>
+        <v>79</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>547</v>
+        <v>80</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>548</v>
+        <v>81</v>
       </c>
       <c r="F34" s="5">
-        <v>33100</v>
+        <v>10123</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>514</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>279</v>
+        <v>78</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="F35" s="5">
-        <v>39042</v>
+        <v>81</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>523</v>
+        <v>546</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>34</v>
+        <v>511</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>339</v>
+        <v>547</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>36</v>
+        <v>548</v>
       </c>
       <c r="F36" s="5">
-        <v>20121</v>
+        <v>33100</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>38</v>
+        <v>514</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>338</v>
+        <v>279</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>339</v>
+        <v>289</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>36</v>
+        <v>290</v>
       </c>
       <c r="F37" s="5">
-        <v>20121</v>
+        <v>39042</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>33</v>
+        <v>523</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>34</v>
@@ -3170,13 +3287,13 @@
         <v>8</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>35</v>
+        <v>339</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F38" s="5" t="s">
-        <v>37</v>
+      <c r="F38" s="5">
+        <v>20121</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>38</v>
@@ -3184,68 +3301,68 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>221</v>
+        <v>338</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>222</v>
+        <v>339</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F39" s="5">
+        <v>20121</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>116</v>
+        <v>33</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>117</v>
+        <v>34</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>527</v>
+        <v>221</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>118</v>
+        <v>222</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F41" s="5">
-        <v>65125</v>
+        <v>10</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>77</v>
@@ -3253,7 +3370,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>254</v>
+        <v>116</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>117</v>
@@ -3276,191 +3393,191 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>62</v>
+        <v>527</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>66</v>
+        <v>119</v>
+      </c>
+      <c r="F43" s="5">
+        <v>65125</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>145</v>
+        <v>254</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>521</v>
+        <v>62</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>522</v>
+        <v>64</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F45" s="5">
-        <v>20033</v>
+        <v>65</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>159</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>291</v>
+        <v>145</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>292</v>
+        <v>146</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>293</v>
+        <v>147</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="F46" s="5">
-        <v>60035</v>
+        <v>148</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>585</v>
+        <v>521</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>117</v>
+        <v>34</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>118</v>
+        <v>522</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="F47" s="5">
-        <v>65125</v>
+        <v>20033</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>557</v>
+        <v>291</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>34</v>
+        <v>292</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>215</v>
+        <v>293</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>36</v>
+        <v>294</v>
       </c>
       <c r="F48" s="5">
-        <v>20124</v>
+        <v>60035</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>541</v>
+        <v>650</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>542</v>
+        <v>29</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F49" s="5">
-        <v>20121</v>
+        <v>39100</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>543</v>
+        <v>585</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>542</v>
+        <v>118</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>36</v>
+        <v>119</v>
       </c>
       <c r="F50" s="5">
-        <v>20121</v>
+        <v>65125</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>34</v>
@@ -3469,44 +3586,44 @@
         <v>8</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>542</v>
+        <v>215</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F51" s="5">
-        <v>20121</v>
+        <v>20124</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>499</v>
+        <v>541</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C52" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>500</v>
+        <v>542</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F52" s="5">
-        <v>10143</v>
+        <v>20121</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>389</v>
+        <v>543</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>34</v>
@@ -3515,13 +3632,13 @@
         <v>8</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>270</v>
+        <v>542</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F53" s="5">
-        <v>20123</v>
+        <v>20121</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>38</v>
@@ -3529,7 +3646,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>437</v>
+        <v>559</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>34</v>
@@ -3538,13 +3655,13 @@
         <v>8</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>270</v>
+        <v>542</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F54" s="5">
-        <v>20123</v>
+        <v>20121</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>38</v>
@@ -3552,53 +3669,53 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>397</v>
+        <v>499</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C55" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F55" s="5">
-        <v>20123</v>
+        <v>10143</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>269</v>
+        <v>617</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>270</v>
+        <v>618</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>61</v>
+        <v>619</v>
+      </c>
+      <c r="F56" s="5">
+        <v>25038</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>137</v>
+        <v>389</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>34</v>
@@ -3607,13 +3724,13 @@
         <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F57" s="5" t="s">
-        <v>58</v>
+      <c r="F57" s="5">
+        <v>20123</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>38</v>
@@ -3621,7 +3738,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>34</v>
@@ -3630,13 +3747,13 @@
         <v>8</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F58" s="5">
-        <v>20121</v>
+        <v>20123</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>38</v>
@@ -3644,76 +3761,76 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>138</v>
+        <v>397</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>140</v>
+        <v>270</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>142</v>
+        <v>36</v>
+      </c>
+      <c r="F59" s="5">
+        <v>20123</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>125</v>
+        <v>269</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>126</v>
+        <v>270</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>614</v>
+        <v>137</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F61" s="5">
-        <v>90139</v>
+        <v>36</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>444</v>
+        <v>409</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>34</v>
@@ -3722,228 +3839,228 @@
         <v>8</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>189</v>
+        <v>122</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F62" s="5">
-        <v>20158</v>
+        <v>20121</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>225</v>
+        <v>138</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>28</v>
+        <v>139</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>226</v>
+        <v>140</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>30</v>
+        <v>141</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>583</v>
+        <v>614</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>264</v>
+        <v>17</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>584</v>
+        <v>126</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>408</v>
+        <v>19</v>
       </c>
       <c r="F65" s="5">
-        <v>38123</v>
+        <v>90139</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>268</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>544</v>
+        <v>444</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>545</v>
+        <v>189</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F66" s="5">
+        <v>20158</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>487</v>
+        <v>225</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>488</v>
+        <v>28</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>489</v>
+        <v>226</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="F67" s="5">
-        <v>26015</v>
+        <v>30</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>558</v>
+        <v>84</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>335</v>
+        <v>86</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>218</v>
+        <v>87</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>334</v>
+        <v>583</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>9</v>
+        <v>264</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>335</v>
+        <v>584</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>218</v>
+        <v>408</v>
+      </c>
+      <c r="F69" s="5">
+        <v>38123</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>11</v>
+        <v>268</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>592</v>
+        <v>544</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>593</v>
+        <v>545</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F70" s="5">
-        <v>20122</v>
+        <v>10</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>300</v>
+        <v>487</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>296</v>
+        <v>488</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>301</v>
+        <v>489</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>302</v>
+        <v>490</v>
       </c>
       <c r="F71" s="5">
-        <v>56025</v>
+        <v>26015</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>299</v>
+        <v>107</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>271</v>
+        <v>558</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>9</v>
@@ -3952,13 +4069,13 @@
         <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>272</v>
+        <v>335</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F72" s="5" t="s">
-        <v>273</v>
+      <c r="F72" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>11</v>
@@ -3966,99 +4083,99 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>375</v>
+        <v>334</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>376</v>
+        <v>335</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F73" s="5">
-        <v>20121</v>
+        <v>10</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>280</v>
+        <v>592</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>303</v>
+        <v>593</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>304</v>
+        <v>36</v>
       </c>
       <c r="F74" s="5">
-        <v>24060</v>
+        <v>20122</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>150</v>
+        <v>38</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>481</v>
+        <v>300</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>258</v>
+        <v>301</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>36</v>
+        <v>302</v>
       </c>
       <c r="F75" s="5">
-        <v>20121</v>
+        <v>56025</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>38</v>
+        <v>299</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>175</v>
+        <v>271</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>157</v>
+        <v>272</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>158</v>
+        <v>273</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>156</v>
+        <v>375</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>34</v>
@@ -4067,44 +4184,44 @@
         <v>8</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>157</v>
+        <v>376</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F77" s="5" t="s">
-        <v>158</v>
+      <c r="F77" s="5">
+        <v>20121</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>230</v>
+        <v>303</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>231</v>
+        <v>304</v>
+      </c>
+      <c r="F78" s="5">
+        <v>24060</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>439</v>
+        <v>616</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>34</v>
@@ -4113,366 +4230,366 @@
         <v>8</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>440</v>
+        <v>189</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F79" s="5">
-        <v>20122</v>
+        <v>20158</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>245</v>
+        <v>481</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>249</v>
+        <v>36</v>
+      </c>
+      <c r="F80" s="5">
+        <v>20121</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>250</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>251</v>
+        <v>175</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>252</v>
+        <v>157</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>237</v>
+        <v>158</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>83</v>
+        <v>159</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>362</v>
+        <v>156</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>363</v>
+        <v>34</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>364</v>
+        <v>157</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="F82" s="5">
-        <v>76123</v>
+        <v>36</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>44</v>
+        <v>159</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>425</v>
+        <v>253</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>132</v>
+        <v>230</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F83" s="5">
-        <v>39100</v>
+        <v>36</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>32</v>
+        <v>136</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>551</v>
+        <v>439</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>552</v>
+        <v>34</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>553</v>
+        <v>440</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="F84" s="8" t="s">
-        <v>555</v>
+        <v>36</v>
+      </c>
+      <c r="F84" s="5">
+        <v>20122</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>391</v>
+        <v>245</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>40</v>
+        <v>246</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>392</v>
+        <v>247</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F85" s="5">
-        <v>70043</v>
+        <v>248</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>44</v>
+        <v>250</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>219</v>
+        <v>251</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>37</v>
+        <v>237</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>50</v>
+        <v>362</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>46</v>
+        <v>363</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>47</v>
+        <v>364</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>49</v>
+        <v>365</v>
+      </c>
+      <c r="F87" s="5">
+        <v>76123</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>51</v>
+        <v>425</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>53</v>
+        <v>30</v>
+      </c>
+      <c r="F88" s="5">
+        <v>39100</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>121</v>
+        <v>551</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>34</v>
+        <v>552</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>122</v>
+        <v>553</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>58</v>
+        <v>554</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>555</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>124</v>
+        <v>648</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>122</v>
+        <v>649</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>58</v>
+        <v>10</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>130</v>
+        <v>391</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>122</v>
+        <v>392</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>58</v>
+        <v>42</v>
+      </c>
+      <c r="F91" s="5">
+        <v>70043</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>371</v>
+        <v>219</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>372</v>
+        <v>34</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>373</v>
+        <v>220</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="F92" s="5">
-        <v>61121</v>
+        <v>36</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>201</v>
+        <v>50</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>189</v>
+        <v>47</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>190</v>
+        <v>49</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>506</v>
+        <v>51</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="C94" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>508</v>
+        <v>52</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="F94" s="5">
-        <v>35010</v>
+        <v>36</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>505</v>
+        <v>38</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>281</v>
+        <v>121</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>34</v>
@@ -4481,13 +4598,13 @@
         <v>8</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>305</v>
+        <v>122</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F95" s="5">
-        <v>20123</v>
+      <c r="F95" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G95" s="4" t="s">
         <v>38</v>
@@ -4495,7 +4612,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>565</v>
+        <v>124</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>34</v>
@@ -4504,13 +4621,13 @@
         <v>8</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>564</v>
+        <v>122</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F96" s="5">
-        <v>20122</v>
+      <c r="F96" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G96" s="4" t="s">
         <v>38</v>
@@ -4518,237 +4635,237 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>351</v>
+        <v>130</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>353</v>
+        <v>122</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="F97" s="5">
-        <v>15033</v>
+        <v>36</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="F98" s="5">
-        <v>15033</v>
+        <v>61121</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>83</v>
+        <v>165</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>535</v>
+        <v>201</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>117</v>
+        <v>34</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>536</v>
+        <v>189</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F99" s="5">
-        <v>65127</v>
+        <v>36</v>
+      </c>
+      <c r="F99" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>59</v>
+        <v>506</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C100" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>60</v>
+        <v>508</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>61</v>
+        <v>507</v>
+      </c>
+      <c r="F100" s="5">
+        <v>35010</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>38</v>
+        <v>505</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>336</v>
+        <v>281</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>337</v>
+        <v>305</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F101" s="5">
-        <v>10153</v>
+        <v>20123</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>430</v>
+        <v>565</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F102" s="5">
-        <v>10153</v>
+        <v>20122</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>573</v>
+        <v>351</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>34</v>
+        <v>352</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>574</v>
+        <v>353</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>36</v>
+        <v>354</v>
       </c>
       <c r="F103" s="5">
-        <v>20154</v>
+        <v>15033</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>159</v>
+        <v>83</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>282</v>
+        <v>351</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>9</v>
+        <v>352</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>306</v>
+        <v>353</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>10</v>
+        <v>354</v>
       </c>
       <c r="F104" s="5">
-        <v>183</v>
+        <v>15033</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>307</v>
+        <v>83</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>210</v>
+        <v>351</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>34</v>
+        <v>352</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>211</v>
+        <v>353</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F105" s="5" t="s">
-        <v>58</v>
+        <v>354</v>
+      </c>
+      <c r="F105" s="5">
+        <v>15033</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>550</v>
+        <v>536</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>36</v>
+        <v>119</v>
       </c>
       <c r="F106" s="5">
-        <v>20154</v>
+        <v>65127</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>275</v>
+        <v>59</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>34</v>
@@ -4757,136 +4874,136 @@
         <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>276</v>
+        <v>60</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>158</v>
+        <v>61</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>128</v>
+        <v>336</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>129</v>
+        <v>337</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>31</v>
+        <v>81</v>
+      </c>
+      <c r="F108" s="5">
+        <v>10153</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>242</v>
+        <v>430</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>129</v>
+        <v>337</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F109" s="5" t="s">
-        <v>31</v>
+        <v>81</v>
+      </c>
+      <c r="F109" s="5">
+        <v>10153</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>414</v>
+        <v>573</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>415</v>
+        <v>574</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F110" s="5" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F110" s="5">
+        <v>20154</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>29</v>
+        <v>306</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F111" s="5" t="s">
-        <v>31</v>
+        <v>10</v>
+      </c>
+      <c r="F111" s="5">
+        <v>183</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>32</v>
+        <v>307</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>240</v>
+        <v>36</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>241</v>
+        <v>58</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>150</v>
+        <v>38</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>598</v>
+        <v>549</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>34</v>
@@ -4895,44 +5012,44 @@
         <v>8</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>599</v>
+        <v>550</v>
       </c>
       <c r="E113" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F113" s="5">
-        <v>20122</v>
+        <v>20154</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>537</v>
+        <v>275</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>538</v>
+        <v>34</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>539</v>
+        <v>276</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="F114" s="5">
-        <v>34133</v>
+        <v>36</v>
+      </c>
+      <c r="F114" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>514</v>
+        <v>159</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>435</v>
+        <v>128</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>28</v>
@@ -4946,8 +5063,8 @@
       <c r="E115" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F115" s="5">
-        <v>39100</v>
+      <c r="F115" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G115" s="4" t="s">
         <v>32</v>
@@ -4955,191 +5072,191 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>366</v>
+        <v>414</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>60</v>
+        <v>415</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F117" s="5">
-        <v>20123</v>
+        <v>10</v>
+      </c>
+      <c r="F117" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>101</v>
+        <v>274</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>493</v>
+        <v>238</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>9</v>
+        <v>146</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>494</v>
+        <v>239</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F119" s="8" t="s">
-        <v>273</v>
+        <v>240</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>11</v>
+        <v>150</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>519</v>
+        <v>598</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>520</v>
+        <v>599</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="F120" s="5">
-        <v>80121</v>
+        <v>20122</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>406</v>
+        <v>537</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>264</v>
+        <v>538</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>407</v>
+        <v>539</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>408</v>
+        <v>540</v>
       </c>
       <c r="F121" s="5">
-        <v>38121</v>
+        <v>34133</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>268</v>
+        <v>514</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>369</v>
+        <v>435</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>370</v>
+        <v>129</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F122" s="5">
-        <v>20123</v>
+        <v>39100</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>360</v>
+        <v>651</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>361</v>
+        <v>652</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F123" s="5">
-        <v>90139</v>
+        <v>20121</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>345</v>
+        <v>206</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>34</v>
@@ -5148,13 +5265,13 @@
         <v>8</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>195</v>
+        <v>60</v>
       </c>
       <c r="E124" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F124" s="5">
-        <v>20123</v>
+      <c r="F124" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G124" s="4" t="s">
         <v>38</v>
@@ -5162,53 +5279,53 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>455</v>
+        <v>366</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>456</v>
+        <v>60</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F125" s="8" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F125" s="5">
+        <v>20123</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>283</v>
+        <v>101</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>309</v>
+        <v>60</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="F126" s="5">
-        <v>12037</v>
+        <v>36</v>
+      </c>
+      <c r="F126" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>13</v>
+        <v>493</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>9</v>
@@ -5217,13 +5334,13 @@
         <v>8</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>14</v>
+        <v>494</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F127" s="5" t="s">
-        <v>15</v>
+      <c r="F127" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="G127" s="4" t="s">
         <v>11</v>
@@ -5231,122 +5348,122 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>123</v>
+        <v>519</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>55</v>
+        <v>520</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F128" s="5" t="s">
-        <v>31</v>
+        <v>71</v>
+      </c>
+      <c r="F128" s="5">
+        <v>80121</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>54</v>
+        <v>406</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>28</v>
+        <v>264</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>55</v>
+        <v>407</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F129" s="5" t="s">
-        <v>31</v>
+        <v>408</v>
+      </c>
+      <c r="F129" s="5">
+        <v>38121</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>32</v>
+        <v>268</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>74</v>
+        <v>369</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>75</v>
+        <v>370</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F130" s="5" t="s">
-        <v>76</v>
+        <v>36</v>
+      </c>
+      <c r="F130" s="5">
+        <v>20123</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>27</v>
+        <v>360</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>29</v>
+        <v>361</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F131" s="5" t="s">
-        <v>31</v>
+        <v>19</v>
+      </c>
+      <c r="F131" s="5">
+        <v>90139</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>498</v>
+        <v>345</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C132" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C132" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>29</v>
+        <v>195</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F132" s="5">
-        <v>39100</v>
+        <v>20123</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>233</v>
+        <v>455</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>9</v>
@@ -5355,228 +5472,228 @@
         <v>8</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>234</v>
+        <v>456</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F133" s="5" t="s">
-        <v>218</v>
+      <c r="F133" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>590</v>
+        <v>283</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>591</v>
+        <v>309</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>36</v>
+        <v>310</v>
       </c>
       <c r="F134" s="5">
-        <v>20122</v>
+        <v>12037</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>188</v>
+        <v>13</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>189</v>
+        <v>14</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>190</v>
+        <v>15</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>483</v>
+        <v>123</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>484</v>
+        <v>28</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>485</v>
+        <v>55</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="F136" s="5">
-        <v>66020</v>
+        <v>30</v>
+      </c>
+      <c r="F136" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>576</v>
+        <v>54</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>577</v>
+        <v>55</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F137" s="5">
-        <v>20124</v>
+        <v>30</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>411</v>
+        <v>74</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>341</v>
+        <v>9</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>412</v>
+        <v>75</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="F138" s="5">
-        <v>37137</v>
+        <v>10</v>
+      </c>
+      <c r="F138" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>343</v>
+        <v>77</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>460</v>
+        <v>653</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>461</v>
+        <v>654</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F139" s="8" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F139" s="5">
+        <v>20124</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>296</v>
+        <v>28</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>297</v>
+        <v>29</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="F140" s="5">
-        <v>56010</v>
+        <v>30</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>299</v>
+        <v>32</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>603</v>
+        <v>498</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C141" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C141" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>604</v>
+        <v>29</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F141" s="5">
-        <v>20145</v>
+        <v>39100</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>311</v>
+        <v>233</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>312</v>
+        <v>234</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="F142" s="5">
-        <v>40060</v>
+        <v>10</v>
+      </c>
+      <c r="F142" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>384</v>
+        <v>590</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>34</v>
@@ -5585,13 +5702,13 @@
         <v>8</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>385</v>
+        <v>591</v>
       </c>
       <c r="E143" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F143" s="5">
-        <v>20121</v>
+        <v>20122</v>
       </c>
       <c r="G143" s="4" t="s">
         <v>38</v>
@@ -5599,7 +5716,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>386</v>
+        <v>188</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>34</v>
@@ -5608,36 +5725,36 @@
         <v>8</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>385</v>
+        <v>189</v>
       </c>
       <c r="E144" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>58</v>
+        <v>190</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>213</v>
+        <v>483</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>9</v>
+        <v>484</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>179</v>
+        <v>485</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>180</v>
+        <v>486</v>
+      </c>
+      <c r="F145" s="5">
+        <v>66020</v>
       </c>
       <c r="G145" s="4" t="s">
         <v>77</v>
@@ -5645,30 +5762,30 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>575</v>
+        <v>621</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>34</v>
+        <v>484</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>192</v>
+        <v>485</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>36</v>
+        <v>486</v>
       </c>
       <c r="F146" s="5">
-        <v>20124</v>
+        <v>66020</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>34</v>
@@ -5677,7 +5794,7 @@
         <v>8</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>192</v>
+        <v>577</v>
       </c>
       <c r="E147" s="4" t="s">
         <v>36</v>
@@ -5691,145 +5808,145 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>68</v>
+        <v>411</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>69</v>
+        <v>341</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>70</v>
+        <v>412</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>72</v>
+        <v>413</v>
+      </c>
+      <c r="F148" s="5">
+        <v>37137</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>73</v>
+        <v>343</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>284</v>
+        <v>460</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>314</v>
+        <v>9</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>315</v>
+        <v>461</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="F149" s="5">
-        <v>57021</v>
+        <v>10</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>299</v>
+        <v>11</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>184</v>
+        <v>295</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>9</v>
+        <v>296</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>179</v>
+        <v>297</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F150" s="5" t="s">
-        <v>180</v>
+        <v>298</v>
+      </c>
+      <c r="F150" s="5">
+        <v>56010</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>77</v>
+        <v>299</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>462</v>
+        <v>603</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>179</v>
+        <v>604</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F151" s="8" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="F151" s="5">
+        <v>20145</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>77</v>
+        <v>136</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>89</v>
+        <v>311</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>91</v>
+        <v>312</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F152" s="5" t="s">
-        <v>93</v>
+        <v>313</v>
+      </c>
+      <c r="F152" s="5">
+        <v>40060</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>346</v>
+        <v>384</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>347</v>
+        <v>385</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>348</v>
+        <v>36</v>
       </c>
       <c r="F153" s="5">
-        <v>70124</v>
+        <v>20121</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>333</v>
+        <v>386</v>
       </c>
       <c r="B154" s="4" t="s">
         <v>34</v>
@@ -5838,44 +5955,44 @@
         <v>8</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>189</v>
+        <v>385</v>
       </c>
       <c r="E154" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F154" s="5">
-        <v>20158</v>
+      <c r="F154" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>357</v>
+        <v>213</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>358</v>
+        <v>179</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="F155" s="5">
-        <v>12084</v>
+        <v>10</v>
+      </c>
+      <c r="F155" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>194</v>
+        <v>575</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>34</v>
@@ -5884,21 +6001,21 @@
         <v>8</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E156" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F156" s="5" t="s">
-        <v>61</v>
+      <c r="F156" s="5">
+        <v>20124</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>227</v>
+        <v>589</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>34</v>
@@ -5907,182 +6024,182 @@
         <v>8</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>228</v>
+        <v>192</v>
       </c>
       <c r="E157" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F157" s="5" t="s">
-        <v>37</v>
+      <c r="F157" s="5">
+        <v>20124</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>457</v>
+        <v>631</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>458</v>
+        <v>632</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F158" s="8" t="s">
-        <v>459</v>
+        <v>633</v>
+      </c>
+      <c r="F158" s="5">
+        <v>39025</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>431</v>
+        <v>284</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>432</v>
+        <v>315</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>433</v>
+        <v>316</v>
       </c>
       <c r="F160" s="5">
-        <v>12100</v>
+        <v>57021</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>395</v>
+        <v>184</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>23</v>
+        <v>179</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F161" s="5">
-        <v>40127</v>
+        <v>10</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>611</v>
+        <v>462</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>612</v>
+        <v>179</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F162" s="5">
-        <v>40122</v>
+        <v>10</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>355</v>
+        <v>89</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>356</v>
+        <v>91</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F163" s="5">
-        <v>20121</v>
+        <v>92</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>556</v>
+        <v>346</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>525</v>
+        <v>347</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>36</v>
+        <v>348</v>
       </c>
       <c r="F164" s="5">
-        <v>20154</v>
+        <v>70124</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>159</v>
+        <v>44</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>526</v>
+        <v>333</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>34</v>
@@ -6091,13 +6208,13 @@
         <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>525</v>
+        <v>189</v>
       </c>
       <c r="E165" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F165" s="5">
-        <v>20154</v>
+        <v>20158</v>
       </c>
       <c r="G165" s="4" t="s">
         <v>159</v>
@@ -6105,260 +6222,260 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>524</v>
+        <v>646</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>525</v>
+        <v>647</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F166" s="5">
-        <v>20154</v>
+        <v>39100</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>596</v>
+        <v>357</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>597</v>
+        <v>358</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>36</v>
+        <v>359</v>
       </c>
       <c r="F167" s="5">
-        <v>20154</v>
+        <v>12084</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>159</v>
+        <v>307</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>515</v>
+        <v>194</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>29</v>
+        <v>195</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F168" s="5">
-        <v>39100</v>
+        <v>36</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>29</v>
+        <v>228</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>143</v>
+        <v>457</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>144</v>
+        <v>458</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F170" s="5" t="s">
-        <v>37</v>
+        <v>10</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>459</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>38</v>
+        <v>113</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="F172" s="5">
-        <v>20038</v>
+        <v>12100</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>136</v>
+        <v>307</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>426</v>
+        <v>395</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>236</v>
+        <v>23</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="F173" s="5">
-        <v>10121</v>
+        <v>40127</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>95</v>
+        <v>611</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>97</v>
+        <v>612</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F174" s="5" t="s">
-        <v>99</v>
+        <v>24</v>
+      </c>
+      <c r="F174" s="5">
+        <v>40122</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>378</v>
+        <v>34</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>379</v>
+        <v>356</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>380</v>
+        <v>36</v>
       </c>
       <c r="F175" s="5">
-        <v>64020</v>
+        <v>20121</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>580</v>
+        <v>556</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>581</v>
+        <v>525</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F176" s="8" t="s">
-        <v>582</v>
+        <v>36</v>
+      </c>
+      <c r="F176" s="5">
+        <v>20154</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>410</v>
+        <v>526</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>34</v>
@@ -6367,21 +6484,21 @@
         <v>8</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>211</v>
+        <v>525</v>
       </c>
       <c r="E177" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F177" s="5">
-        <v>20121</v>
+        <v>20154</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>133</v>
+        <v>524</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>34</v>
@@ -6390,90 +6507,90 @@
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>134</v>
+        <v>525</v>
       </c>
       <c r="E178" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F178" s="5" t="s">
-        <v>135</v>
+      <c r="F178" s="5">
+        <v>20154</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F179" s="8" t="s">
-        <v>607</v>
+        <v>36</v>
+      </c>
+      <c r="F179" s="5">
+        <v>20154</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>257</v>
+        <v>515</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>258</v>
+        <v>29</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F180" s="5" t="s">
-        <v>58</v>
+        <v>30</v>
+      </c>
+      <c r="F180" s="5">
+        <v>39100</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>340</v>
+        <v>232</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>341</v>
+        <v>28</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>342</v>
+        <v>29</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="F181" s="5">
-        <v>37045</v>
+        <v>30</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>343</v>
+        <v>32</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>34</v>
@@ -6482,21 +6599,21 @@
         <v>8</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="E182" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>168</v>
+        <v>37</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>529</v>
+        <v>56</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>34</v>
@@ -6505,21 +6622,21 @@
         <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>167</v>
+        <v>57</v>
       </c>
       <c r="E183" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F183" s="5">
-        <v>20126</v>
+      <c r="F183" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>601</v>
+        <v>441</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>34</v>
@@ -6528,136 +6645,136 @@
         <v>8</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>602</v>
+        <v>442</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>36</v>
+        <v>443</v>
       </c>
       <c r="F184" s="5">
-        <v>20138</v>
+        <v>20038</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>609</v>
+        <v>426</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>610</v>
+        <v>236</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F185" s="5">
-        <v>20122</v>
+        <v>10121</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>594</v>
+        <v>95</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>394</v>
+        <v>97</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F186" s="5">
-        <v>20123</v>
+        <v>98</v>
+      </c>
+      <c r="F186" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>471</v>
+        <v>377</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>34</v>
+        <v>378</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>260</v>
+        <v>379</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>36</v>
+        <v>380</v>
       </c>
       <c r="F187" s="5">
-        <v>20135</v>
+        <v>64020</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>262</v>
+        <v>77</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>405</v>
+        <v>580</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>260</v>
+        <v>581</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F188" s="5">
-        <v>20135</v>
+        <v>10</v>
+      </c>
+      <c r="F188" s="8" t="s">
+        <v>582</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>262</v>
+        <v>11</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>204</v>
+        <v>410</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="F189" s="10" t="s">
-        <v>187</v>
+        <v>36</v>
+      </c>
+      <c r="F189" s="10">
+        <v>20121</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>319</v>
+        <v>38</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>453</v>
+        <v>133</v>
       </c>
       <c r="B190" s="9" t="s">
         <v>34</v>
@@ -6666,113 +6783,113 @@
         <v>8</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>454</v>
+        <v>134</v>
       </c>
       <c r="E190" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F190" s="10">
-        <v>20144</v>
+      <c r="F190" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>223</v>
+        <v>605</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>224</v>
+        <v>606</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F191" s="10" t="s">
-        <v>135</v>
+        <v>10</v>
+      </c>
+      <c r="F191" s="12" t="s">
+        <v>607</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>136</v>
+        <v>11</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>317</v>
+        <v>258</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="F192" s="10">
-        <v>40026</v>
+        <v>36</v>
+      </c>
+      <c r="F192" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>286</v>
+        <v>340</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>9</v>
+        <v>341</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F193" s="10" t="s">
-        <v>323</v>
+        <v>528</v>
+      </c>
+      <c r="F193" s="10">
+        <v>37045</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>11</v>
+        <v>343</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
-        <v>533</v>
+        <v>166</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C194" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>29</v>
+        <v>167</v>
       </c>
       <c r="E194" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F194" s="10">
-        <v>39100</v>
+        <v>36</v>
+      </c>
+      <c r="F194" s="10" t="s">
+        <v>168</v>
       </c>
       <c r="G194" s="9" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
-        <v>367</v>
+        <v>529</v>
       </c>
       <c r="B195" s="9" t="s">
         <v>34</v>
@@ -6781,90 +6898,90 @@
         <v>8</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>368</v>
+        <v>167</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F195" s="10">
-        <v>20123</v>
+        <v>20126</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
-        <v>287</v>
+        <v>601</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C196" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>321</v>
+        <v>602</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>322</v>
+        <v>36</v>
       </c>
       <c r="F196" s="10">
-        <v>12020</v>
+        <v>20138</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>307</v>
+        <v>262</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>39</v>
+        <v>609</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C197" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>41</v>
+        <v>610</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="F197" s="10" t="s">
-        <v>43</v>
+        <v>36</v>
+      </c>
+      <c r="F197" s="10">
+        <v>20122</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>421</v>
+        <v>594</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>422</v>
+        <v>34</v>
       </c>
       <c r="C198" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>423</v>
+        <v>394</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>424</v>
+        <v>36</v>
       </c>
       <c r="F198" s="10">
-        <v>28053</v>
+        <v>20123</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>172</v>
+        <v>471</v>
       </c>
       <c r="B199" s="9" t="s">
         <v>34</v>
@@ -6873,136 +6990,136 @@
         <v>8</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>169</v>
+        <v>260</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F199" s="10" t="s">
-        <v>171</v>
+        <v>36</v>
+      </c>
+      <c r="F199" s="10">
+        <v>20135</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>159</v>
+        <v>262</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A200" s="9" t="s">
-        <v>560</v>
-      </c>
-      <c r="B200" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C200" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D200" s="9" t="s">
-        <v>561</v>
-      </c>
-      <c r="E200" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F200" s="10">
-        <v>39100</v>
-      </c>
-      <c r="G200" s="9" t="s">
-        <v>32</v>
+      <c r="A200" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F200" s="7">
+        <v>20135</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A201" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="B201" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C201" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D201" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="E201" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F201" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="G201" s="9" t="s">
-        <v>26</v>
+      <c r="A201" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F201" s="7">
+        <v>20135</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
-        <v>207</v>
+        <v>405</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C202" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="F202" s="10" t="s">
-        <v>209</v>
+        <v>36</v>
+      </c>
+      <c r="F202" s="10">
+        <v>20135</v>
       </c>
       <c r="G202" s="9" t="s">
-        <v>73</v>
+        <v>262</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A203" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="B203" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C203" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D203" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="E203" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F203" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="G203" s="9" t="s">
-        <v>38</v>
+      <c r="A203" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F203" s="7">
+        <v>85100</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
-        <v>534</v>
+        <v>204</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="C204" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D204" s="9" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="E204" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F204" s="10">
-        <v>20121</v>
+        <v>186</v>
+      </c>
+      <c r="F204" s="10" t="s">
+        <v>187</v>
       </c>
       <c r="G204" s="9" t="s">
-        <v>38</v>
+        <v>319</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="9" t="s">
-        <v>578</v>
+        <v>453</v>
       </c>
       <c r="B205" s="9" t="s">
         <v>34</v>
@@ -7011,13 +7128,13 @@
         <v>8</v>
       </c>
       <c r="D205" s="9" t="s">
-        <v>579</v>
+        <v>454</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F205" s="10">
-        <v>20121</v>
+        <v>20144</v>
       </c>
       <c r="G205" s="9" t="s">
         <v>38</v>
@@ -7025,122 +7142,122 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="9" t="s">
-        <v>445</v>
+        <v>223</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="C206" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D206" s="9" t="s">
-        <v>447</v>
+        <v>224</v>
       </c>
       <c r="E206" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="F206" s="10">
-        <v>53048</v>
+        <v>36</v>
+      </c>
+      <c r="F206" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="G206" s="9" t="s">
-        <v>449</v>
+        <v>136</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
-        <v>516</v>
+        <v>285</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>509</v>
+        <v>22</v>
       </c>
       <c r="C207" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D207" s="9" t="s">
-        <v>517</v>
+        <v>317</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>518</v>
+        <v>318</v>
       </c>
       <c r="F207" s="10">
-        <v>35011</v>
+        <v>40026</v>
       </c>
       <c r="G207" s="9" t="s">
-        <v>505</v>
+        <v>26</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A208" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="B208" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C208" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D208" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="E208" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F208" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="G208" s="9" t="s">
-        <v>38</v>
+      <c r="A208" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="F208" s="7">
+        <v>20068</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="9" t="s">
-        <v>131</v>
+        <v>286</v>
       </c>
       <c r="B209" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C209" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D209" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="E209" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F209" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="G209" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A210" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="B210" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C209" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D209" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="E209" s="9" t="s">
+      <c r="C210" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D210" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E210" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F209" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G209" s="9" t="s">
+      <c r="F210" s="10">
+        <v>39100</v>
+      </c>
+      <c r="G210" s="9" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A210" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="B210" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C210" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D210" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="E210" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F210" s="7">
-        <v>20121</v>
-      </c>
-      <c r="G210" s="9" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="9" t="s">
-        <v>531</v>
+        <v>367</v>
       </c>
       <c r="B211" s="9" t="s">
         <v>34</v>
@@ -7149,13 +7266,13 @@
         <v>8</v>
       </c>
       <c r="D211" s="9" t="s">
-        <v>532</v>
+        <v>368</v>
       </c>
       <c r="E211" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F211" s="10">
-        <v>20121</v>
+        <v>20123</v>
       </c>
       <c r="G211" s="9" t="s">
         <v>38</v>
@@ -7163,168 +7280,168 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="9" t="s">
-        <v>21</v>
+        <v>287</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>22</v>
+        <v>308</v>
       </c>
       <c r="C212" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D212" s="9" t="s">
-        <v>23</v>
+        <v>321</v>
       </c>
       <c r="E212" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F212" s="10" t="s">
-        <v>25</v>
+        <v>322</v>
+      </c>
+      <c r="F212" s="10">
+        <v>12020</v>
       </c>
       <c r="G212" s="9" t="s">
-        <v>26</v>
+        <v>307</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A213" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="B213" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C213" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D213" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="E213" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F213" s="11" t="s">
-        <v>568</v>
-      </c>
-      <c r="G213" s="3" t="s">
-        <v>77</v>
+      <c r="A213" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B213" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C213" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D213" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E213" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F213" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G213" s="9" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="9" t="s">
-        <v>381</v>
+        <v>421</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>34</v>
+        <v>422</v>
       </c>
       <c r="C214" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D214" s="9" t="s">
-        <v>382</v>
+        <v>423</v>
       </c>
       <c r="E214" s="9" t="s">
-        <v>383</v>
+        <v>424</v>
       </c>
       <c r="F214" s="10">
-        <v>20089</v>
+        <v>28053</v>
       </c>
       <c r="G214" s="9" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="9" t="s">
-        <v>475</v>
+        <v>172</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C215" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D215" s="9" t="s">
-        <v>476</v>
+        <v>169</v>
       </c>
       <c r="E215" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F215" s="12" t="s">
-        <v>477</v>
+        <v>170</v>
+      </c>
+      <c r="F215" s="10" t="s">
+        <v>171</v>
       </c>
       <c r="G215" s="9" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="9" t="s">
-        <v>212</v>
+        <v>560</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C216" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D216" s="9" t="s">
-        <v>202</v>
+        <v>561</v>
       </c>
       <c r="E216" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F216" s="10" t="s">
-        <v>203</v>
+        <v>30</v>
+      </c>
+      <c r="F216" s="10">
+        <v>39100</v>
       </c>
       <c r="G216" s="9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="B217" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C217" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D217" s="9" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="E217" s="9" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F217" s="10" t="s">
-        <v>158</v>
+        <v>200</v>
       </c>
       <c r="G217" s="9" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="9" t="s">
-        <v>438</v>
+        <v>207</v>
       </c>
       <c r="B218" s="9" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C218" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D218" s="9" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="E218" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F218" s="10">
-        <v>20124</v>
+        <v>71</v>
+      </c>
+      <c r="F218" s="10" t="s">
+        <v>209</v>
       </c>
       <c r="G218" s="9" t="s">
-        <v>159</v>
+        <v>73</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="9" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="B219" s="9" t="s">
         <v>34</v>
@@ -7333,21 +7450,21 @@
         <v>8</v>
       </c>
       <c r="D219" s="9" t="s">
-        <v>230</v>
+        <v>177</v>
       </c>
       <c r="E219" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F219" s="10" t="s">
-        <v>231</v>
+        <v>58</v>
       </c>
       <c r="G219" s="9" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="9" t="s">
-        <v>256</v>
+        <v>534</v>
       </c>
       <c r="B220" s="9" t="s">
         <v>34</v>
@@ -7356,21 +7473,21 @@
         <v>8</v>
       </c>
       <c r="D220" s="9" t="s">
-        <v>230</v>
+        <v>177</v>
       </c>
       <c r="E220" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F220" s="10" t="s">
-        <v>231</v>
+      <c r="F220" s="10">
+        <v>20121</v>
       </c>
       <c r="G220" s="9" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="9" t="s">
-        <v>472</v>
+        <v>578</v>
       </c>
       <c r="B221" s="9" t="s">
         <v>34</v>
@@ -7379,67 +7496,67 @@
         <v>8</v>
       </c>
       <c r="D221" s="9" t="s">
-        <v>464</v>
+        <v>579</v>
       </c>
       <c r="E221" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F221" s="10">
-        <v>20129</v>
+        <v>20121</v>
       </c>
       <c r="G221" s="9" t="s">
-        <v>262</v>
+        <v>38</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="9" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>34</v>
+        <v>446</v>
       </c>
       <c r="C222" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D222" s="9" t="s">
-        <v>464</v>
+        <v>447</v>
       </c>
       <c r="E222" s="9" t="s">
-        <v>36</v>
+        <v>448</v>
       </c>
       <c r="F222" s="10">
-        <v>20129</v>
+        <v>53048</v>
       </c>
       <c r="G222" s="9" t="s">
-        <v>262</v>
+        <v>449</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="9" t="s">
-        <v>473</v>
+        <v>516</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>34</v>
+        <v>509</v>
       </c>
       <c r="C223" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D223" s="9" t="s">
-        <v>464</v>
+        <v>517</v>
       </c>
       <c r="E223" s="9" t="s">
-        <v>36</v>
+        <v>518</v>
       </c>
       <c r="F223" s="10">
-        <v>20129</v>
+        <v>35011</v>
       </c>
       <c r="G223" s="9" t="s">
-        <v>262</v>
+        <v>505</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="9" t="s">
-        <v>474</v>
+        <v>243</v>
       </c>
       <c r="B224" s="9" t="s">
         <v>34</v>
@@ -7448,82 +7565,82 @@
         <v>8</v>
       </c>
       <c r="D224" s="9" t="s">
-        <v>464</v>
+        <v>177</v>
       </c>
       <c r="E224" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F224" s="10">
-        <v>20129</v>
+      <c r="F224" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="G224" s="9" t="s">
-        <v>262</v>
+        <v>38</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="9" t="s">
-        <v>176</v>
+        <v>131</v>
       </c>
       <c r="B225" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C225" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D225" s="9" t="s">
-        <v>177</v>
+        <v>132</v>
       </c>
       <c r="E225" s="9" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F225" s="10" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="G225" s="9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A226" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="B226" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C226" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D226" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="E226" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="F226" s="10">
-        <v>40026</v>
-      </c>
-      <c r="G226" s="9" t="s">
-        <v>26</v>
+      <c r="A226" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F226" s="7">
+        <v>39100</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A227" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="B227" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C227" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D227" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="E227" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F227" s="10">
-        <v>20124</v>
+      <c r="A227" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F227" s="7">
+        <v>20121</v>
       </c>
       <c r="G227" s="9" t="s">
         <v>38</v>
@@ -7531,99 +7648,99 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="9" t="s">
-        <v>450</v>
+        <v>531</v>
       </c>
       <c r="B228" s="9" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="C228" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D228" s="9" t="s">
-        <v>451</v>
+        <v>532</v>
       </c>
       <c r="E228" s="9" t="s">
-        <v>452</v>
+        <v>36</v>
       </c>
       <c r="F228" s="10">
-        <v>12011</v>
+        <v>20121</v>
       </c>
       <c r="G228" s="9" t="s">
-        <v>307</v>
+        <v>38</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="9" t="s">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="B229" s="9" t="s">
-        <v>152</v>
+        <v>22</v>
       </c>
       <c r="C229" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D229" s="9" t="s">
-        <v>153</v>
+        <v>23</v>
       </c>
       <c r="E229" s="9" t="s">
-        <v>154</v>
+        <v>24</v>
       </c>
       <c r="F229" s="10" t="s">
-        <v>155</v>
+        <v>25</v>
       </c>
       <c r="G229" s="9" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A230" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="B230" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C230" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D230" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="E230" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F230" s="10">
-        <v>20123</v>
-      </c>
-      <c r="G230" s="9" t="s">
-        <v>38</v>
+      <c r="A230" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F230" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="9" t="s">
-        <v>491</v>
+        <v>381</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C231" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D231" s="9" t="s">
-        <v>492</v>
+        <v>382</v>
       </c>
       <c r="E231" s="9" t="s">
-        <v>19</v>
+        <v>383</v>
       </c>
       <c r="F231" s="10">
-        <v>90141</v>
+        <v>20089</v>
       </c>
       <c r="G231" s="9" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="9" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B232" s="9" t="s">
         <v>9</v>
@@ -7632,251 +7749,251 @@
         <v>8</v>
       </c>
       <c r="D232" s="9" t="s">
-        <v>388</v>
+        <v>476</v>
       </c>
       <c r="E232" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F232" s="12" t="s">
-        <v>390</v>
+        <v>477</v>
       </c>
       <c r="G232" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A233" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="B233" s="3" t="s">
-        <v>9</v>
+      <c r="A233" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="B233" s="9" t="s">
+        <v>22</v>
       </c>
       <c r="C233" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D233" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E233" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F233" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="G233" s="3" t="s">
-        <v>11</v>
+      <c r="D233" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="E233" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F233" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="G233" s="9" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="9" t="s">
-        <v>387</v>
+        <v>214</v>
       </c>
       <c r="B234" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C234" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D234" s="9" t="s">
-        <v>388</v>
+        <v>215</v>
       </c>
       <c r="E234" s="9" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F234" s="10" t="s">
-        <v>390</v>
+        <v>158</v>
       </c>
       <c r="G234" s="9" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="9" t="s">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="B235" s="9" t="s">
-        <v>264</v>
+        <v>34</v>
       </c>
       <c r="C235" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D235" s="9" t="s">
-        <v>466</v>
+        <v>215</v>
       </c>
       <c r="E235" s="9" t="s">
-        <v>467</v>
+        <v>36</v>
       </c>
       <c r="F235" s="10">
-        <v>38055</v>
+        <v>20124</v>
       </c>
       <c r="G235" s="9" t="s">
-        <v>268</v>
+        <v>159</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" s="3" t="s">
-        <v>572</v>
+        <v>635</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C236" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>134</v>
+        <v>636</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>36</v>
+        <v>148</v>
       </c>
       <c r="F236" s="7">
-        <v>20145</v>
+        <v>24050</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="9" t="s">
-        <v>427</v>
+        <v>229</v>
       </c>
       <c r="B237" s="9" t="s">
-        <v>103</v>
+        <v>34</v>
       </c>
       <c r="C237" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D237" s="9" t="s">
-        <v>428</v>
+        <v>230</v>
       </c>
       <c r="E237" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="F237" s="10">
-        <v>25010</v>
+        <v>36</v>
+      </c>
+      <c r="F237" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="G237" s="9" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A238" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="B238" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C238" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D238" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="E238" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F238" s="10">
-        <v>20123</v>
-      </c>
-      <c r="G238" s="9" t="s">
-        <v>38</v>
+      <c r="A238" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F238" s="7">
+        <v>20148</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" s="9" t="s">
-        <v>416</v>
+        <v>256</v>
       </c>
       <c r="B239" s="9" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="C239" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D239" s="9" t="s">
-        <v>417</v>
+        <v>230</v>
       </c>
       <c r="E239" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="F239" s="10">
-        <v>71016</v>
+        <v>36</v>
+      </c>
+      <c r="F239" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="G239" s="9" t="s">
-        <v>44</v>
+        <v>136</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="9" t="s">
-        <v>16</v>
+        <v>472</v>
       </c>
       <c r="B240" s="9" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C240" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D240" s="9" t="s">
-        <v>18</v>
+        <v>464</v>
       </c>
       <c r="E240" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F240" s="10" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="F240" s="10">
+        <v>20129</v>
       </c>
       <c r="G240" s="9" t="s">
-        <v>12</v>
+        <v>262</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" s="9" t="s">
-        <v>325</v>
+        <v>463</v>
       </c>
       <c r="B241" s="9" t="s">
-        <v>326</v>
+        <v>34</v>
       </c>
       <c r="C241" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D241" s="9" t="s">
-        <v>327</v>
+        <v>464</v>
       </c>
       <c r="E241" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="F241" s="10" t="s">
-        <v>329</v>
+        <v>36</v>
+      </c>
+      <c r="F241" s="10">
+        <v>20129</v>
       </c>
       <c r="G241" s="9" t="s">
-        <v>330</v>
+        <v>262</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A242" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="B242" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C242" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D242" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="E242" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F242" s="7">
-        <v>20122</v>
-      </c>
-      <c r="G242" s="3" t="s">
-        <v>38</v>
+      <c r="A242" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="B242" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C242" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D242" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="E242" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F242" s="10">
+        <v>20129</v>
+      </c>
+      <c r="G242" s="9" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" s="9" t="s">
-        <v>277</v>
+        <v>474</v>
       </c>
       <c r="B243" s="9" t="s">
         <v>34</v>
@@ -7885,21 +8002,21 @@
         <v>8</v>
       </c>
       <c r="D243" s="9" t="s">
-        <v>278</v>
+        <v>464</v>
       </c>
       <c r="E243" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F243" s="10" t="s">
-        <v>37</v>
+      <c r="F243" s="10">
+        <v>20129</v>
       </c>
       <c r="G243" s="9" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" s="9" t="s">
-        <v>478</v>
+        <v>176</v>
       </c>
       <c r="B244" s="9" t="s">
         <v>34</v>
@@ -7908,182 +8025,711 @@
         <v>8</v>
       </c>
       <c r="D244" s="9" t="s">
-        <v>479</v>
+        <v>177</v>
       </c>
       <c r="E244" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F244" s="10">
-        <v>20123</v>
+      <c r="F244" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="G244" s="9" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A245" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="B245" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C245" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D245" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="E245" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="F245" s="7">
-        <v>20094</v>
-      </c>
-      <c r="G245" s="3" t="s">
-        <v>38</v>
+      <c r="A245" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="B245" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C245" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D245" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="E245" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="F245" s="10">
+        <v>40026</v>
+      </c>
+      <c r="G245" s="9" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" s="9" t="s">
-        <v>396</v>
+        <v>288</v>
       </c>
       <c r="B246" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C246" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D246" s="9" t="s">
-        <v>217</v>
+        <v>324</v>
       </c>
       <c r="E246" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F246" s="10" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F246" s="10">
+        <v>20124</v>
       </c>
       <c r="G246" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" s="9" t="s">
-        <v>216</v>
+        <v>450</v>
       </c>
       <c r="B247" s="9" t="s">
-        <v>9</v>
+        <v>308</v>
       </c>
       <c r="C247" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D247" s="9" t="s">
-        <v>217</v>
+        <v>451</v>
       </c>
       <c r="E247" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F247" s="10" t="s">
-        <v>218</v>
+        <v>452</v>
+      </c>
+      <c r="F247" s="10">
+        <v>12011</v>
       </c>
       <c r="G247" s="9" t="s">
-        <v>11</v>
+        <v>307</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A248" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="B248" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C248" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D248" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="E248" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="F248" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G248" s="9" t="s">
-        <v>165</v>
+      <c r="A248" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F248" s="7">
+        <v>20121</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" s="9" t="s">
-        <v>434</v>
+        <v>151</v>
       </c>
       <c r="B249" s="9" t="s">
-        <v>9</v>
+        <v>152</v>
       </c>
       <c r="C249" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D249" s="9" t="s">
-        <v>217</v>
+        <v>153</v>
       </c>
       <c r="E249" s="9" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="F249" s="10" t="s">
-        <v>218</v>
+        <v>155</v>
       </c>
       <c r="G249" s="9" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" s="9" t="s">
-        <v>255</v>
+        <v>419</v>
       </c>
       <c r="B250" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C250" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D250" s="9" t="s">
-        <v>217</v>
+        <v>420</v>
       </c>
       <c r="E250" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F250" s="10" t="s">
-        <v>218</v>
+        <v>36</v>
+      </c>
+      <c r="F250" s="10">
+        <v>20123</v>
       </c>
       <c r="G250" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="B251" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C251" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D251" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="E251" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F251" s="10">
+        <v>90141</v>
+      </c>
+      <c r="G251" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A252" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="B252" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C252" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D252" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="E252" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F252" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="G252" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A253" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C253" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E253" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F253" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="G253" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A254" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C254" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E254" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F254" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="G254" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A255" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="B255" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C255" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D255" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="E255" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F255" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="G255" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A256" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="B256" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="C256" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D256" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="E256" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="F256" s="10">
+        <v>38055</v>
+      </c>
+      <c r="G256" s="9" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A257" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F257" s="7">
+        <v>20145</v>
+      </c>
+      <c r="G257" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A258" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="B258" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C258" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D258" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="E258" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="F258" s="10">
+        <v>25010</v>
+      </c>
+      <c r="G258" s="9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A259" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="B259" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C259" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D259" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="E259" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F259" s="10">
+        <v>20123</v>
+      </c>
+      <c r="G259" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A260" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="B260" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F260" s="7">
+        <v>20123</v>
+      </c>
+      <c r="G260" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A261" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="B261" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C261" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D261" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="E261" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="F261" s="10">
+        <v>71016</v>
+      </c>
+      <c r="G261" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A262" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B262" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C262" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D262" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E262" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F262" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G262" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A263" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C263" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D263" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="E263" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F263" s="7">
+        <v>20123</v>
+      </c>
+      <c r="G263" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A264" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="B264" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="C264" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D264" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E264" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="F264" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="G264" s="9" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A265" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="E265" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F265" s="7">
+        <v>20122</v>
+      </c>
+      <c r="G265" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A266" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="B266" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C266" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D266" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="E266" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F266" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G266" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A267" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="B267" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C267" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D267" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="E267" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F267" s="10">
+        <v>20123</v>
+      </c>
+      <c r="G267" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A268" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="E268" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="F268" s="7">
+        <v>20094</v>
+      </c>
+      <c r="G268" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A269" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="B269" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C269" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D269" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E269" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F269" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G269" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A270" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B270" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C270" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D270" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E270" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F270" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G270" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A271" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B271" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C271" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D271" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E271" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F271" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G271" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A272" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="B272" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C272" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D272" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E272" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F272" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G272" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A273" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B273" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C273" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D273" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E273" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F273" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G273" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A274" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B251" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C251" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D251" s="9" t="s">
+      <c r="B274" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C274" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D274" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E251" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F251" s="10" t="s">
+      <c r="E274" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F274" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G251" s="9" t="s">
+      <c r="G274" s="9" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G218" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G251">
+    <sortState ref="A2:G274">
       <sortCondition ref="A1:A218"/>
     </sortState>
   </autoFilter>
@@ -8096,23 +8742,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F040406D9EE34E48977C379A242BB45D" ma:contentTypeVersion="15" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="1ab2d492e43f6bec9a26aa4599c840e9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="877b7d34-4df7-40bf-9eb1-208952470e96" xmlns:ns4="05fc27dd-4454-4248-9c78-3d72b2b155c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebc604e5d4aadf5a992ba83f8d4fb519" ns3:_="" ns4:_="">
     <xsd:import namespace="877b7d34-4df7-40bf-9eb1-208952470e96"/>
@@ -8345,32 +8974,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBC6436E-C4E7-4E8D-94E8-64DAEC05792B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8387,4 +9008,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{18C4CF28-FFF8-4500-B8A9-D0C46F5ADB3D}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D82EC521-37F3-45CC-9AA9-4261C7006E89}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,9 +46,6 @@
     <t>Filiale di Riferimento</t>
   </si>
   <si>
-    <t>Cliente</t>
-  </si>
-  <si>
     <t>Prospect</t>
   </si>
   <si>
@@ -1988,6 +1985,9 @@
   </si>
   <si>
     <t>PIAZZA LINA BO BARDI 3</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -2450,6281 +2450,6281 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="F5" s="8" t="s">
         <v>587</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>588</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>503</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>504</v>
       </c>
       <c r="F6" s="5">
         <v>45100</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>402</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F7" s="5">
         <v>20123</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F8" s="5">
         <v>20123</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="F9" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="4" t="s">
         <v>261</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>503</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>504</v>
       </c>
       <c r="F11" s="5">
         <v>45100</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>512</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>513</v>
       </c>
       <c r="F12" s="5">
         <v>33050</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F14" s="5">
         <v>10121</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>237</v>
-      </c>
       <c r="G15" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>496</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>497</v>
       </c>
       <c r="F16" s="5">
         <v>10098</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="C17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="F17" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="G17" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>192</v>
-      </c>
       <c r="E18" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F18" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="E19" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="F19" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>180</v>
-      </c>
       <c r="G19" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="4" t="s">
+      <c r="F20" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>180</v>
-      </c>
       <c r="G20" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="4" t="s">
+      <c r="F21" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>180</v>
-      </c>
       <c r="G21" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="F22" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>180</v>
-      </c>
       <c r="G22" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="4" t="s">
+      <c r="F23" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>180</v>
-      </c>
       <c r="G23" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="F24" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>180</v>
-      </c>
       <c r="G24" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>627</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="C25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" s="4" t="s">
         <v>629</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>630</v>
       </c>
       <c r="F25" s="5">
         <v>36022</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>404</v>
-      </c>
       <c r="E26" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F26" s="5">
         <v>39100</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F27" s="5">
         <v>39100</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F28" s="5">
         <v>39100</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>400</v>
-      </c>
       <c r="E29" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F29" s="5">
         <v>20124</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="E30" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="4" t="s">
+      <c r="F30" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F31" s="5">
         <v>20123</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>350</v>
-      </c>
       <c r="E32" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F32" s="5">
         <v>20122</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B33" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="4" t="s">
+      <c r="E33" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="F33" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F33" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="G33" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="4" t="s">
+      <c r="E34" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>81</v>
       </c>
       <c r="F34" s="5">
         <v>10123</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="C35" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="4" t="s">
+      <c r="E35" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="F35" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="G35" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="4" t="s">
+      <c r="E36" s="4" t="s">
         <v>547</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>548</v>
       </c>
       <c r="F36" s="5">
         <v>33100</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D37" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="E37" s="4" t="s">
         <v>289</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>290</v>
       </c>
       <c r="F37" s="5">
         <v>39042</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F38" s="5">
         <v>20121</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>339</v>
-      </c>
       <c r="E39" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F39" s="5">
         <v>20121</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C40" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>35</v>
-      </c>
       <c r="E40" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F40" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="G40" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="E41" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="F41" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="C42" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="4" t="s">
+      <c r="E42" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="F42" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>120</v>
-      </c>
       <c r="G42" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="4" t="s">
+      <c r="E43" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="F43" s="5">
         <v>65125</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="4" t="s">
+      <c r="E44" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="F44" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="F44" s="5" t="s">
-        <v>120</v>
-      </c>
       <c r="G44" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="C45" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="4" t="s">
+      <c r="E45" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="F45" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F45" s="5" t="s">
-        <v>66</v>
-      </c>
       <c r="G45" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="C46" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" s="4" t="s">
+      <c r="E46" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="F46" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="G46" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>522</v>
-      </c>
       <c r="E47" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F47" s="5">
         <v>20033</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="C48" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="4" t="s">
+      <c r="E48" s="4" t="s">
         <v>293</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>294</v>
       </c>
       <c r="F48" s="5">
         <v>60035</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B49" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="4" t="s">
+      <c r="E49" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="F49" s="5">
         <v>39100</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B50" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C50" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="4" t="s">
+      <c r="E50" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="F50" s="5">
         <v>65125</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F51" s="5">
         <v>20124</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="B52" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>542</v>
-      </c>
       <c r="E52" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F52" s="5">
         <v>20121</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F53" s="5">
         <v>20121</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F54" s="5">
         <v>20121</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="B55" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>500</v>
-      </c>
       <c r="E55" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F55" s="5">
         <v>10143</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="B56" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="4" t="s">
+      <c r="E56" s="4" t="s">
         <v>618</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>619</v>
       </c>
       <c r="F56" s="5">
         <v>25038</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F57" s="5">
         <v>20123</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F58" s="5">
         <v>20123</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F59" s="5">
         <v>20123</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>270</v>
-      </c>
       <c r="E60" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F62" s="5">
         <v>20121</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B63" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="C63" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="4" t="s">
+      <c r="E63" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="E63" s="4" t="s">
+      <c r="F63" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="F63" s="5" t="s">
-        <v>142</v>
-      </c>
       <c r="G63" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B64" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D64" s="4" t="s">
+      <c r="E64" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F64" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="E64" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>127</v>
-      </c>
       <c r="G64" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F65" s="5">
         <v>90139</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F66" s="5">
         <v>20158</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="B67" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>226</v>
-      </c>
       <c r="E67" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F67" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F67" s="5" t="s">
+      <c r="G67" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B68" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="C68" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C68" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" s="4" t="s">
+      <c r="E68" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E68" s="4" t="s">
+      <c r="F68" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F68" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="G68" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="B69" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>584</v>
-      </c>
       <c r="E69" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F69" s="5">
         <v>38123</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="E70" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C70" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="F70" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="B71" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="C71" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="C71" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D71" s="4" t="s">
+      <c r="E71" s="4" t="s">
         <v>489</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>490</v>
       </c>
       <c r="F71" s="5">
         <v>26015</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B72" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="E72" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C72" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="E72" s="4" t="s">
+      <c r="F72" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="G72" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="E73" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="E73" s="4" t="s">
+      <c r="F73" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="G73" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D74" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="B74" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>593</v>
-      </c>
       <c r="E74" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F74" s="5">
         <v>20122</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="B75" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="4" t="s">
+      <c r="E75" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>302</v>
       </c>
       <c r="F75" s="5">
         <v>56025</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="E76" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C76" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D76" s="4" t="s">
+      <c r="F76" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="E76" s="4" t="s">
+      <c r="G76" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="B77" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>376</v>
-      </c>
       <c r="E77" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F77" s="5">
         <v>20121</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>7</v>
+        <v>654</v>
       </c>
       <c r="D78" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E78" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="E78" s="4" t="s">
-        <v>304</v>
       </c>
       <c r="F78" s="5">
         <v>24060</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F79" s="5">
         <v>20158</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F80" s="5">
         <v>20121</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D81" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F81" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E81" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F81" s="5" t="s">
+      <c r="G81" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="B82" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D82" s="4" t="s">
+      <c r="E82" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F82" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E82" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F82" s="5" t="s">
+      <c r="G82" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D83" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F83" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="E83" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>231</v>
-      </c>
       <c r="G83" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="B84" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>440</v>
-      </c>
       <c r="E84" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F84" s="5">
         <v>20122</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B85" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="C85" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="C85" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D85" s="4" t="s">
+      <c r="E85" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="E85" s="4" t="s">
+      <c r="F85" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="F85" s="5" t="s">
+      <c r="G85" s="4" t="s">
         <v>249</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D86" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="B86" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>252</v>
-      </c>
       <c r="E86" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B87" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="C87" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D87" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="C87" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D87" s="4" t="s">
+      <c r="E87" s="4" t="s">
         <v>364</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>365</v>
       </c>
       <c r="F87" s="5">
         <v>76123</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F88" s="5">
         <v>39100</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="B89" s="4" t="s">
         <v>551</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="C89" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="C89" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D89" s="4" t="s">
+      <c r="E89" s="4" t="s">
         <v>553</v>
       </c>
-      <c r="E89" s="4" t="s">
+      <c r="F89" s="8" t="s">
         <v>554</v>
       </c>
-      <c r="F89" s="8" t="s">
-        <v>555</v>
-      </c>
       <c r="G89" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D90" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="E90" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C90" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>649</v>
-      </c>
-      <c r="E90" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="F90" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="B91" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>392</v>
-      </c>
       <c r="E91" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F91" s="5">
         <v>70043</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="B92" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>220</v>
-      </c>
       <c r="E92" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F92" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F92" s="5" t="s">
+      <c r="G92" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B93" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D93" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C93" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D93" s="4" t="s">
+      <c r="E93" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E93" s="4" t="s">
+      <c r="F93" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F93" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="G93" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D94" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B94" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D94" s="4" t="s">
+      <c r="E94" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F94" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E94" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="G94" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D95" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B95" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>122</v>
-      </c>
       <c r="E95" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="B98" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="C98" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D98" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="C98" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D98" s="4" t="s">
+      <c r="E98" s="4" t="s">
         <v>373</v>
-      </c>
-      <c r="E98" s="4" t="s">
-        <v>374</v>
       </c>
       <c r="F98" s="5">
         <v>61121</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D99" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F99" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="E99" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>190</v>
-      </c>
       <c r="G99" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="E100" s="4" t="s">
         <v>506</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>507</v>
       </c>
       <c r="F100" s="5">
         <v>35010</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F101" s="5">
         <v>20123</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F102" s="5">
         <v>20122</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="B103" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="C103" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D103" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="C103" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D103" s="4" t="s">
+      <c r="E103" s="4" t="s">
         <v>353</v>
-      </c>
-      <c r="E103" s="4" t="s">
-        <v>354</v>
       </c>
       <c r="F103" s="5">
         <v>15033</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="B104" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="C104" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D104" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="C104" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D104" s="4" t="s">
+      <c r="E104" s="4" t="s">
         <v>353</v>
-      </c>
-      <c r="E104" s="4" t="s">
-        <v>354</v>
       </c>
       <c r="F104" s="5">
         <v>15033</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="B105" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="C105" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D105" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="C105" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D105" s="4" t="s">
+      <c r="E105" s="4" t="s">
         <v>353</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>354</v>
       </c>
       <c r="F105" s="5">
         <v>15033</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D106" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="B106" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>536</v>
-      </c>
       <c r="E106" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F106" s="5">
         <v>65127</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D107" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B107" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C107" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D107" s="4" t="s">
+      <c r="E107" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F107" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E107" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>61</v>
-      </c>
       <c r="G107" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D108" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="B108" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D108" s="4" t="s">
-        <v>337</v>
-      </c>
       <c r="E108" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F108" s="5">
         <v>10153</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F109" s="5">
         <v>10153</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D110" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="B110" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D110" s="4" t="s">
-        <v>574</v>
-      </c>
       <c r="E110" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F110" s="5">
         <v>20154</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B111" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="E111" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D111" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="E111" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="F111" s="5">
         <v>183</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D112" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B112" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>211</v>
-      </c>
       <c r="E112" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D113" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="B113" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>550</v>
-      </c>
       <c r="E113" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F113" s="5">
         <v>20154</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D114" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="B114" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>276</v>
-      </c>
       <c r="E114" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F114" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G114" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D115" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B115" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D115" s="4" t="s">
-        <v>129</v>
-      </c>
       <c r="E115" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F115" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F115" s="5" t="s">
+      <c r="G115" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="G115" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E116" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F116" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F116" s="5" t="s">
+      <c r="G116" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="G116" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D117" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="E117" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C117" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D117" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="E117" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="F117" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B118" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D118" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C118" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D118" s="4" t="s">
+      <c r="E118" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E118" s="4" t="s">
+      <c r="F118" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F118" s="5" t="s">
+      <c r="G118" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="G118" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D119" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="B119" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D119" s="4" t="s">
+      <c r="E119" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="E119" s="4" t="s">
+      <c r="F119" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="F119" s="5" t="s">
-        <v>241</v>
-      </c>
       <c r="G119" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D120" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="B120" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D120" s="4" t="s">
-        <v>599</v>
-      </c>
       <c r="E120" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F120" s="5">
         <v>20122</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="B121" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="C121" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D121" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="C121" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D121" s="4" t="s">
+      <c r="E121" s="4" t="s">
         <v>539</v>
-      </c>
-      <c r="E121" s="4" t="s">
-        <v>540</v>
       </c>
       <c r="F121" s="5">
         <v>34133</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F122" s="5">
         <v>39100</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D123" s="4" t="s">
         <v>651</v>
       </c>
-      <c r="B123" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>652</v>
-      </c>
       <c r="E123" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F123" s="5">
         <v>20121</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D124" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F124" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E124" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>61</v>
-      </c>
       <c r="G124" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F125" s="5">
         <v>20123</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D126" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F126" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E126" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F126" s="5" t="s">
-        <v>61</v>
-      </c>
       <c r="G126" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D127" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="B127" s="4" t="s">
+      <c r="E127" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C127" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>494</v>
-      </c>
-      <c r="E127" s="4" t="s">
+      <c r="F127" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="G127" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="F127" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="G127" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D128" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="B128" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>520</v>
-      </c>
       <c r="E128" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F128" s="5">
         <v>80121</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D129" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="B129" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D129" s="4" t="s">
+      <c r="E129" s="4" t="s">
         <v>407</v>
-      </c>
-      <c r="E129" s="4" t="s">
-        <v>408</v>
       </c>
       <c r="F129" s="5">
         <v>38121</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D130" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="B130" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D130" s="4" t="s">
-        <v>370</v>
-      </c>
       <c r="E130" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F130" s="5">
         <v>20123</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D131" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="B131" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D131" s="4" t="s">
-        <v>361</v>
-      </c>
       <c r="E131" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F131" s="5">
         <v>90139</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F132" s="5">
         <v>20123</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D133" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="B133" s="4" t="s">
+      <c r="E133" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C133" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="E133" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="F133" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B134" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D134" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="C134" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D134" s="4" t="s">
+      <c r="E134" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="E134" s="4" t="s">
-        <v>310</v>
       </c>
       <c r="F134" s="5">
         <v>12037</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D135" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B135" s="4" t="s">
+      <c r="E135" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C135" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D135" s="4" t="s">
+      <c r="F135" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E135" s="4" t="s">
+      <c r="G135" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="F135" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G135" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E136" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F136" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F136" s="5" t="s">
+      <c r="G136" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="G136" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D137" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B137" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D137" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="E137" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F137" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F137" s="5" t="s">
+      <c r="G137" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D138" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B138" s="4" t="s">
+      <c r="E138" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C138" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D138" s="4" t="s">
+      <c r="F138" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E138" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F138" s="5" t="s">
+      <c r="G138" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="G138" s="4" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D139" s="4" t="s">
         <v>653</v>
       </c>
-      <c r="B139" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D139" s="4" t="s">
-        <v>654</v>
-      </c>
       <c r="E139" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F139" s="5">
         <v>20124</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B140" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B140" s="4" t="s">
+      <c r="C140" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D140" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C140" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D140" s="4" t="s">
+      <c r="E140" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E140" s="4" t="s">
+      <c r="F140" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F140" s="5" t="s">
+      <c r="G140" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B141" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D141" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C141" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D141" s="4" t="s">
+      <c r="E141" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="E141" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="F141" s="5">
         <v>39100</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D142" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B142" s="4" t="s">
+      <c r="E142" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C142" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D142" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="E142" s="4" t="s">
+      <c r="F142" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="G142" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="G142" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D143" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="B143" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D143" s="4" t="s">
-        <v>591</v>
-      </c>
       <c r="E143" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F143" s="5">
         <v>20122</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D144" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B144" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D144" s="4" t="s">
+      <c r="E144" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F144" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="E144" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>190</v>
-      </c>
       <c r="G144" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="B145" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="B145" s="4" t="s">
+      <c r="C145" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D145" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="C145" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D145" s="4" t="s">
+      <c r="E145" s="4" t="s">
         <v>485</v>
-      </c>
-      <c r="E145" s="4" t="s">
-        <v>486</v>
       </c>
       <c r="F145" s="5">
         <v>66020</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B146" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D146" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="C146" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D146" s="4" t="s">
+      <c r="E146" s="4" t="s">
         <v>485</v>
-      </c>
-      <c r="E146" s="4" t="s">
-        <v>486</v>
       </c>
       <c r="F146" s="5">
         <v>66020</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D147" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="B147" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D147" s="4" t="s">
-        <v>577</v>
-      </c>
       <c r="E147" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F147" s="5">
         <v>20124</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D148" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="B148" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D148" s="4" t="s">
+      <c r="E148" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="E148" s="4" t="s">
-        <v>413</v>
       </c>
       <c r="F148" s="5">
         <v>37137</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D149" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="B149" s="4" t="s">
+      <c r="E149" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C149" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D149" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="E149" s="4" t="s">
+      <c r="F149" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="G149" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="F149" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="G149" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B150" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="B150" s="4" t="s">
+      <c r="C150" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D150" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="C150" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D150" s="4" t="s">
+      <c r="E150" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="E150" s="4" t="s">
-        <v>298</v>
       </c>
       <c r="F150" s="5">
         <v>56010</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D151" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="B151" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C151" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D151" s="4" t="s">
-        <v>604</v>
-      </c>
       <c r="E151" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F151" s="5">
         <v>20145</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D152" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="B152" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D152" s="4" t="s">
+      <c r="E152" s="4" t="s">
         <v>312</v>
-      </c>
-      <c r="E152" s="4" t="s">
-        <v>313</v>
       </c>
       <c r="F152" s="5">
         <v>40060</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D153" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="B153" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C153" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D153" s="4" t="s">
-        <v>385</v>
-      </c>
       <c r="E153" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F153" s="5">
         <v>20121</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B155" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E155" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C155" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D155" s="4" t="s">
+      <c r="F155" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="E155" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F155" s="5" t="s">
-        <v>180</v>
-      </c>
       <c r="G155" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F156" s="5">
         <v>20124</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F157" s="5">
         <v>20124</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D158" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="B158" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D158" s="4" t="s">
+      <c r="E158" s="4" t="s">
         <v>632</v>
-      </c>
-      <c r="E158" s="4" t="s">
-        <v>633</v>
       </c>
       <c r="F158" s="5">
         <v>39025</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B159" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B159" s="4" t="s">
+      <c r="C159" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D159" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C159" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D159" s="4" t="s">
+      <c r="E159" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E159" s="4" t="s">
+      <c r="F159" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F159" s="5" t="s">
+      <c r="G159" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="G159" s="4" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B160" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D160" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="C160" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D160" s="4" t="s">
+      <c r="E160" s="4" t="s">
         <v>315</v>
-      </c>
-      <c r="E160" s="4" t="s">
-        <v>316</v>
       </c>
       <c r="F160" s="5">
         <v>57021</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B161" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E161" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C161" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D161" s="4" t="s">
+      <c r="F161" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="E161" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F161" s="5" t="s">
-        <v>180</v>
-      </c>
       <c r="G161" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B162" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E162" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C162" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D162" s="4" t="s">
+      <c r="F162" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="E162" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F162" s="8" t="s">
-        <v>180</v>
-      </c>
       <c r="G162" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B163" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B163" s="4" t="s">
+      <c r="C163" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D163" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C163" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D163" s="4" t="s">
+      <c r="E163" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E163" s="4" t="s">
+      <c r="F163" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="F163" s="5" t="s">
+      <c r="G163" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="G163" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D164" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="B164" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C164" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D164" s="4" t="s">
+      <c r="E164" s="4" t="s">
         <v>347</v>
-      </c>
-      <c r="E164" s="4" t="s">
-        <v>348</v>
       </c>
       <c r="F164" s="5">
         <v>70124</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F165" s="5">
         <v>20158</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D166" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="B166" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C166" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D166" s="4" t="s">
-        <v>647</v>
-      </c>
       <c r="E166" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F166" s="5">
         <v>39100</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D167" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="B167" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="C167" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D167" s="4" t="s">
+      <c r="E167" s="4" t="s">
         <v>358</v>
-      </c>
-      <c r="E167" s="4" t="s">
-        <v>359</v>
       </c>
       <c r="F167" s="5">
         <v>12084</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D168" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="B168" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C168" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D168" s="4" t="s">
-        <v>195</v>
-      </c>
       <c r="E168" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D169" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="B169" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C169" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D169" s="4" t="s">
-        <v>228</v>
-      </c>
       <c r="E169" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F169" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F169" s="5" t="s">
+      <c r="G169" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="G169" s="4" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D170" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="B170" s="4" t="s">
+      <c r="E170" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C170" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D170" s="4" t="s">
+      <c r="F170" s="8" t="s">
         <v>458</v>
       </c>
-      <c r="E170" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F170" s="8" t="s">
-        <v>459</v>
-      </c>
       <c r="G170" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B171" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B171" s="4" t="s">
+      <c r="C171" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D171" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C171" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D171" s="4" t="s">
+      <c r="E171" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E171" s="4" t="s">
+      <c r="F171" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F171" s="5" t="s">
+      <c r="G171" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="G171" s="4" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D172" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="B172" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="C172" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D172" s="4" t="s">
+      <c r="E172" s="4" t="s">
         <v>432</v>
-      </c>
-      <c r="E172" s="4" t="s">
-        <v>433</v>
       </c>
       <c r="F172" s="5">
         <v>12100</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B173" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D173" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C173" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D173" s="4" t="s">
+      <c r="E173" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="E173" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="F173" s="5">
         <v>40127</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D174" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="B174" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D174" s="4" t="s">
-        <v>612</v>
-      </c>
       <c r="E174" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F174" s="5">
         <v>40122</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D175" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="B175" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C175" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D175" s="4" t="s">
-        <v>356</v>
-      </c>
       <c r="E175" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F175" s="5">
         <v>20121</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F176" s="5">
         <v>20154</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F177" s="5">
         <v>20154</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D178" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="B178" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C178" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D178" s="4" t="s">
-        <v>525</v>
-      </c>
       <c r="E178" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F178" s="5">
         <v>20154</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D179" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="B179" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C179" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D179" s="4" t="s">
-        <v>597</v>
-      </c>
       <c r="E179" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F179" s="5">
         <v>20154</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B180" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D180" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C180" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D180" s="4" t="s">
+      <c r="E180" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="E180" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="F180" s="5">
         <v>39100</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B181" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D181" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C181" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D181" s="4" t="s">
+      <c r="E181" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E181" s="4" t="s">
+      <c r="F181" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F181" s="5" t="s">
+      <c r="G181" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="G181" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D182" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B182" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C182" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D182" s="4" t="s">
-        <v>144</v>
-      </c>
       <c r="E182" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F182" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F182" s="5" t="s">
+      <c r="G182" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="G182" s="4" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D183" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B183" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C183" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D183" s="4" t="s">
+      <c r="E183" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F183" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E183" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F183" s="5" t="s">
-        <v>58</v>
-      </c>
       <c r="G183" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D184" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="B184" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C184" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D184" s="4" t="s">
+      <c r="E184" s="4" t="s">
         <v>442</v>
-      </c>
-      <c r="E184" s="4" t="s">
-        <v>443</v>
       </c>
       <c r="F184" s="5">
         <v>20038</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F185" s="5">
         <v>10121</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B186" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B186" s="4" t="s">
+      <c r="C186" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D186" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C186" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D186" s="4" t="s">
+      <c r="E186" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E186" s="4" t="s">
+      <c r="F186" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F186" s="5" t="s">
+      <c r="G186" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="G186" s="4" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="B187" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="B187" s="4" t="s">
+      <c r="C187" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D187" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="C187" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D187" s="4" t="s">
+      <c r="E187" s="4" t="s">
         <v>379</v>
-      </c>
-      <c r="E187" s="4" t="s">
-        <v>380</v>
       </c>
       <c r="F187" s="5">
         <v>64020</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D188" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="B188" s="4" t="s">
+      <c r="E188" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C188" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D188" s="4" t="s">
+      <c r="F188" s="8" t="s">
         <v>581</v>
       </c>
-      <c r="E188" s="4" t="s">
+      <c r="G188" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="F188" s="8" t="s">
-        <v>582</v>
-      </c>
-      <c r="G188" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>8</v>
+        <v>654</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F189" s="10">
         <v>20121</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B190" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D190" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B190" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C190" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D190" s="9" t="s">
+      <c r="E190" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F190" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="E190" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F190" s="10" t="s">
+      <c r="G190" s="9" t="s">
         <v>135</v>
-      </c>
-      <c r="G190" s="9" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="B191" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D191" s="9" t="s">
         <v>605</v>
       </c>
-      <c r="B191" s="9" t="s">
+      <c r="E191" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C191" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D191" s="9" t="s">
+      <c r="F191" s="12" t="s">
         <v>606</v>
       </c>
-      <c r="E191" s="9" t="s">
+      <c r="G191" s="9" t="s">
         <v>10</v>
-      </c>
-      <c r="F191" s="12" t="s">
-        <v>607</v>
-      </c>
-      <c r="G191" s="9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="B192" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D192" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="B192" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C192" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D192" s="9" t="s">
-        <v>258</v>
-      </c>
       <c r="E192" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F192" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="B193" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="B193" s="9" t="s">
+      <c r="C193" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D193" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="C193" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D193" s="9" t="s">
-        <v>342</v>
-      </c>
       <c r="E193" s="9" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F193" s="10">
         <v>37045</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B194" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D194" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="B194" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C194" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D194" s="9" t="s">
+      <c r="E194" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F194" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="E194" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F194" s="10" t="s">
-        <v>168</v>
-      </c>
       <c r="G194" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C195" s="9" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F195" s="10">
         <v>20126</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="B196" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D196" s="9" t="s">
         <v>601</v>
       </c>
-      <c r="B196" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C196" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D196" s="9" t="s">
-        <v>602</v>
-      </c>
       <c r="E196" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F196" s="10">
         <v>20138</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="B197" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D197" s="9" t="s">
         <v>609</v>
       </c>
-      <c r="B197" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C197" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D197" s="9" t="s">
-        <v>610</v>
-      </c>
       <c r="E197" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F197" s="10">
         <v>20122</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C198" s="9" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F198" s="10">
         <v>20123</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C199" s="9" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F199" s="10">
         <v>20135</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C200" s="3" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F200" s="7">
         <v>20135</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="3" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C201" s="3" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F201" s="7">
         <v>20135</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C202" s="9" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F202" s="10">
         <v>20135</v>
       </c>
       <c r="G202" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D203" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="B203" s="3" t="s">
+      <c r="E203" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="C203" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D203" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="E203" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="F203" s="7">
         <v>85100</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B204" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D204" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="B204" s="9" t="s">
+      <c r="E204" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="C204" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D204" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="E204" s="9" t="s">
+      <c r="F204" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="F204" s="10" t="s">
-        <v>187</v>
-      </c>
       <c r="G204" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="B205" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D205" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="B205" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C205" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D205" s="9" t="s">
-        <v>454</v>
-      </c>
       <c r="E205" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F205" s="10">
         <v>20144</v>
       </c>
       <c r="G205" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B206" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D206" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="B206" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C206" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D206" s="9" t="s">
-        <v>224</v>
-      </c>
       <c r="E206" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F206" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="G206" s="9" t="s">
         <v>135</v>
-      </c>
-      <c r="G206" s="9" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C207" s="9" t="s">
-        <v>7</v>
+        <v>21</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D207" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="E207" s="9" t="s">
         <v>317</v>
-      </c>
-      <c r="E207" s="9" t="s">
-        <v>318</v>
       </c>
       <c r="F207" s="10">
         <v>40026</v>
       </c>
       <c r="G207" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D208" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="B208" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C208" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D208" s="3" t="s">
+      <c r="E208" s="3" t="s">
         <v>638</v>
-      </c>
-      <c r="E208" s="3" t="s">
-        <v>639</v>
       </c>
       <c r="F208" s="7">
         <v>20068</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B209" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D209" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="E209" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C209" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D209" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="E209" s="9" t="s">
+      <c r="F209" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="G209" s="9" t="s">
         <v>10</v>
-      </c>
-      <c r="F209" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="G209" s="9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="9" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B210" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D210" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C210" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D210" s="9" t="s">
+      <c r="E210" s="9" t="s">
         <v>29</v>
-      </c>
-      <c r="E210" s="9" t="s">
-        <v>30</v>
       </c>
       <c r="F210" s="10">
         <v>39100</v>
       </c>
       <c r="G210" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="B211" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C211" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D211" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="B211" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C211" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D211" s="9" t="s">
-        <v>368</v>
-      </c>
       <c r="E211" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F211" s="10">
         <v>20123</v>
       </c>
       <c r="G211" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="C212" s="9" t="s">
-        <v>7</v>
+        <v>307</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D212" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="E212" s="9" t="s">
         <v>321</v>
-      </c>
-      <c r="E212" s="9" t="s">
-        <v>322</v>
       </c>
       <c r="F212" s="10">
         <v>12020</v>
       </c>
       <c r="G212" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B213" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B213" s="9" t="s">
+      <c r="C213" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D213" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C213" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D213" s="9" t="s">
+      <c r="E213" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E213" s="9" t="s">
+      <c r="F213" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F213" s="10" t="s">
+      <c r="G213" s="9" t="s">
         <v>43</v>
-      </c>
-      <c r="G213" s="9" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="B214" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="B214" s="9" t="s">
+      <c r="C214" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D214" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="C214" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D214" s="9" t="s">
+      <c r="E214" s="9" t="s">
         <v>423</v>
-      </c>
-      <c r="E214" s="9" t="s">
-        <v>424</v>
       </c>
       <c r="F214" s="10">
         <v>28053</v>
       </c>
       <c r="G214" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C215" s="9" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D215" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E215" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="E215" s="9" t="s">
+      <c r="F215" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="F215" s="10" t="s">
-        <v>171</v>
-      </c>
       <c r="G215" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="B216" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D216" s="9" t="s">
         <v>560</v>
       </c>
-      <c r="B216" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C216" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D216" s="9" t="s">
-        <v>561</v>
-      </c>
       <c r="E216" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F216" s="10">
         <v>39100</v>
       </c>
       <c r="G216" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="B217" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D217" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="B217" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C217" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D217" s="9" t="s">
+      <c r="E217" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F217" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E217" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F217" s="10" t="s">
-        <v>200</v>
-      </c>
       <c r="G217" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B218" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D218" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="B218" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C218" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D218" s="9" t="s">
+      <c r="E218" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F218" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="E218" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="F218" s="10" t="s">
-        <v>209</v>
-      </c>
       <c r="G218" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B219" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C219" s="9" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D219" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E219" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F219" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G219" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="9" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C220" s="9" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D220" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E220" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F220" s="10">
         <v>20121</v>
       </c>
       <c r="G220" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="B221" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D221" s="9" t="s">
         <v>578</v>
       </c>
-      <c r="B221" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C221" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D221" s="9" t="s">
-        <v>579</v>
-      </c>
       <c r="E221" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F221" s="10">
         <v>20121</v>
       </c>
       <c r="G221" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="B222" s="9" t="s">
         <v>445</v>
       </c>
-      <c r="B222" s="9" t="s">
+      <c r="C222" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D222" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="C222" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D222" s="9" t="s">
+      <c r="E222" s="9" t="s">
         <v>447</v>
-      </c>
-      <c r="E222" s="9" t="s">
-        <v>448</v>
       </c>
       <c r="F222" s="10">
         <v>53048</v>
       </c>
       <c r="G222" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="B223" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D223" s="9" t="s">
         <v>516</v>
       </c>
-      <c r="B223" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="C223" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D223" s="9" t="s">
+      <c r="E223" s="9" t="s">
         <v>517</v>
-      </c>
-      <c r="E223" s="9" t="s">
-        <v>518</v>
       </c>
       <c r="F223" s="10">
         <v>35011</v>
       </c>
       <c r="G223" s="9" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C224" s="9" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D224" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E224" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F224" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G224" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B225" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D225" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B225" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C225" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D225" s="9" t="s">
-        <v>132</v>
-      </c>
       <c r="E225" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F225" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F225" s="10" t="s">
+      <c r="G225" s="9" t="s">
         <v>31</v>
-      </c>
-      <c r="G225" s="9" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C226" s="3" t="s">
-        <v>8</v>
+        <v>27</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F226" s="7">
         <v>39100</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C227" s="3" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="C227" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F227" s="7">
         <v>20121</v>
       </c>
       <c r="G227" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="B228" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D228" s="9" t="s">
         <v>531</v>
       </c>
-      <c r="B228" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C228" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D228" s="9" t="s">
-        <v>532</v>
-      </c>
       <c r="E228" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F228" s="10">
         <v>20121</v>
       </c>
       <c r="G228" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B229" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B229" s="9" t="s">
+      <c r="C229" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D229" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C229" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D229" s="9" t="s">
+      <c r="E229" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E229" s="9" t="s">
+      <c r="F229" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F229" s="10" t="s">
+      <c r="G229" s="9" t="s">
         <v>25</v>
-      </c>
-      <c r="G229" s="9" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D230" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="B230" s="3" t="s">
+      <c r="E230" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C230" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D230" s="3" t="s">
+      <c r="F230" s="11" t="s">
         <v>567</v>
       </c>
-      <c r="E230" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F230" s="11" t="s">
-        <v>568</v>
-      </c>
       <c r="G230" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="B231" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C231" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D231" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="B231" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C231" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D231" s="9" t="s">
+      <c r="E231" s="9" t="s">
         <v>382</v>
-      </c>
-      <c r="E231" s="9" t="s">
-        <v>383</v>
       </c>
       <c r="F231" s="10">
         <v>20089</v>
       </c>
       <c r="G231" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="B232" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D232" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="B232" s="9" t="s">
+      <c r="E232" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C232" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D232" s="9" t="s">
+      <c r="F232" s="12" t="s">
         <v>476</v>
       </c>
-      <c r="E232" s="9" t="s">
+      <c r="G232" s="9" t="s">
         <v>10</v>
-      </c>
-      <c r="F232" s="12" t="s">
-        <v>477</v>
-      </c>
-      <c r="G232" s="9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B233" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C233" s="9" t="s">
-        <v>8</v>
+        <v>21</v>
+      </c>
+      <c r="C233" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D233" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="E233" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F233" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="E233" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F233" s="10" t="s">
-        <v>203</v>
-      </c>
       <c r="G233" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="B234" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D234" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="B234" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C234" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D234" s="9" t="s">
-        <v>215</v>
-      </c>
       <c r="E234" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F234" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="G234" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="G234" s="9" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B235" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C235" s="9" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D235" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E235" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F235" s="10">
         <v>20124</v>
       </c>
       <c r="G235" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D236" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="B236" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C236" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>636</v>
-      </c>
       <c r="E236" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F236" s="7">
         <v>24050</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B237" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D237" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="B237" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C237" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D237" s="9" t="s">
+      <c r="E237" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F237" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="E237" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F237" s="10" t="s">
-        <v>231</v>
-      </c>
       <c r="G237" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C238" s="3" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F238" s="7">
         <v>20148</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B239" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C239" s="9" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D239" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="E239" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F239" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="E239" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F239" s="10" t="s">
-        <v>231</v>
-      </c>
       <c r="G239" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B240" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C240" s="9" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="C240" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D240" s="9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E240" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F240" s="10">
         <v>20129</v>
       </c>
       <c r="G240" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="B241" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D241" s="9" t="s">
         <v>463</v>
       </c>
-      <c r="B241" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C241" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D241" s="9" t="s">
-        <v>464</v>
-      </c>
       <c r="E241" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F241" s="10">
         <v>20129</v>
       </c>
       <c r="G241" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" s="9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B242" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C242" s="9" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D242" s="9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E242" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F242" s="10">
         <v>20129</v>
       </c>
       <c r="G242" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B243" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C243" s="9" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D243" s="9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E243" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F243" s="10">
         <v>20129</v>
       </c>
       <c r="G243" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B244" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D244" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="B244" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C244" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D244" s="9" t="s">
-        <v>177</v>
-      </c>
       <c r="E244" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F244" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G244" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="B245" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C245" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D245" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="B245" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C245" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D245" s="9" t="s">
-        <v>332</v>
-      </c>
       <c r="E245" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F245" s="10">
         <v>40026</v>
       </c>
       <c r="G245" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B246" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C246" s="9" t="s">
-        <v>7</v>
+        <v>33</v>
+      </c>
+      <c r="C246" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D246" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E246" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F246" s="10">
         <v>20124</v>
       </c>
       <c r="G246" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="B247" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D247" s="9" t="s">
         <v>450</v>
       </c>
-      <c r="B247" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="C247" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D247" s="9" t="s">
+      <c r="E247" s="9" t="s">
         <v>451</v>
-      </c>
-      <c r="E247" s="9" t="s">
-        <v>452</v>
       </c>
       <c r="F247" s="10">
         <v>12011</v>
       </c>
       <c r="G247" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C248" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D248" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="B248" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C248" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D248" s="3" t="s">
-        <v>626</v>
-      </c>
       <c r="E248" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F248" s="7">
         <v>20121</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B249" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="B249" s="9" t="s">
+      <c r="C249" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D249" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="C249" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D249" s="9" t="s">
+      <c r="E249" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="E249" s="9" t="s">
+      <c r="F249" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="F249" s="10" t="s">
-        <v>155</v>
-      </c>
       <c r="G249" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="B250" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C250" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D250" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="B250" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C250" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D250" s="9" t="s">
-        <v>420</v>
-      </c>
       <c r="E250" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F250" s="10">
         <v>20123</v>
       </c>
       <c r="G250" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="B251" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C251" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D251" s="9" t="s">
         <v>491</v>
       </c>
-      <c r="B251" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C251" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D251" s="9" t="s">
-        <v>492</v>
-      </c>
       <c r="E251" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F251" s="10">
         <v>90141</v>
       </c>
       <c r="G251" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B252" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D252" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="E252" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C252" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D252" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="E252" s="9" t="s">
+      <c r="F252" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="G252" s="9" t="s">
         <v>10</v>
-      </c>
-      <c r="F252" s="12" t="s">
-        <v>390</v>
-      </c>
-      <c r="G252" s="9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B253" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="E253" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C253" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D253" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E253" s="3" t="s">
+      <c r="F253" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="G253" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="F253" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="G253" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B254" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="E254" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C254" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D254" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E254" s="3" t="s">
+      <c r="F254" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="G254" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="F254" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="G254" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="B255" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C255" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D255" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="B255" s="9" t="s">
+      <c r="E255" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C255" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D255" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="E255" s="9" t="s">
+      <c r="F255" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="G255" s="9" t="s">
         <v>10</v>
-      </c>
-      <c r="F255" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="G255" s="9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="B256" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D256" s="9" t="s">
         <v>465</v>
       </c>
-      <c r="B256" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="C256" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D256" s="9" t="s">
+      <c r="E256" s="9" t="s">
         <v>466</v>
-      </c>
-      <c r="E256" s="9" t="s">
-        <v>467</v>
       </c>
       <c r="F256" s="10">
         <v>38055</v>
       </c>
       <c r="G256" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C257" s="3" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F257" s="7">
         <v>20145</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="B258" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D258" s="9" t="s">
         <v>427</v>
       </c>
-      <c r="B258" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C258" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D258" s="9" t="s">
+      <c r="E258" s="9" t="s">
         <v>428</v>
-      </c>
-      <c r="E258" s="9" t="s">
-        <v>429</v>
       </c>
       <c r="F258" s="10">
         <v>25010</v>
       </c>
       <c r="G258" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="B259" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D259" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="B259" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C259" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D259" s="9" t="s">
-        <v>394</v>
-      </c>
       <c r="E259" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F259" s="10">
         <v>20123</v>
       </c>
       <c r="G259" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C260" s="3" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F260" s="7">
         <v>20123</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B261" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D261" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="B261" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C261" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D261" s="9" t="s">
+      <c r="E261" s="9" t="s">
         <v>417</v>
-      </c>
-      <c r="E261" s="9" t="s">
-        <v>418</v>
       </c>
       <c r="F261" s="10">
         <v>71016</v>
       </c>
       <c r="G261" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B262" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B262" s="9" t="s">
+      <c r="C262" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D262" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C262" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D262" s="9" t="s">
+      <c r="E262" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E262" s="9" t="s">
+      <c r="F262" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F262" s="10" t="s">
-        <v>20</v>
-      </c>
       <c r="G262" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C263" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D263" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="B263" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C263" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D263" s="3" t="s">
-        <v>641</v>
-      </c>
       <c r="E263" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F263" s="7">
         <v>20123</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="B264" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="B264" s="9" t="s">
+      <c r="C264" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D264" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="C264" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D264" s="9" t="s">
+      <c r="E264" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="E264" s="9" t="s">
+      <c r="F264" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="F264" s="10" t="s">
+      <c r="G264" s="9" t="s">
         <v>329</v>
-      </c>
-      <c r="G264" s="9" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C265" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D265" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="B265" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C265" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D265" s="3" t="s">
-        <v>563</v>
-      </c>
       <c r="E265" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F265" s="7">
         <v>20122</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="B266" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C266" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D266" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="B266" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C266" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D266" s="9" t="s">
-        <v>278</v>
-      </c>
       <c r="E266" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F266" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F266" s="10" t="s">
+      <c r="G266" s="9" t="s">
         <v>37</v>
-      </c>
-      <c r="G266" s="9" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="B267" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C267" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D267" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="B267" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C267" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D267" s="9" t="s">
-        <v>479</v>
-      </c>
       <c r="E267" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F267" s="10">
         <v>20123</v>
       </c>
       <c r="G267" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D268" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="B268" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C268" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D268" s="3" t="s">
+      <c r="E268" s="3" t="s">
         <v>570</v>
-      </c>
-      <c r="E268" s="3" t="s">
-        <v>571</v>
       </c>
       <c r="F268" s="7">
         <v>20094</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B269" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D269" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E269" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C269" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D269" s="9" t="s">
+      <c r="F269" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="E269" s="9" t="s">
+      <c r="G269" s="9" t="s">
         <v>10</v>
-      </c>
-      <c r="F269" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="G269" s="9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="B270" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D270" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="B270" s="9" t="s">
+      <c r="E270" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C270" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D270" s="9" t="s">
+      <c r="F270" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="E270" s="9" t="s">
+      <c r="G270" s="9" t="s">
         <v>10</v>
-      </c>
-      <c r="F270" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="G270" s="9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B271" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="B271" s="9" t="s">
+      <c r="C271" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D271" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="C271" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D271" s="9" t="s">
+      <c r="E271" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="E271" s="9" t="s">
+      <c r="F271" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="F271" s="10" t="s">
+      <c r="G271" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="G271" s="9" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" s="9" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B272" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D272" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E272" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C272" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D272" s="9" t="s">
+      <c r="F272" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="E272" s="9" t="s">
+      <c r="G272" s="9" t="s">
         <v>10</v>
-      </c>
-      <c r="F272" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="G272" s="9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B273" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C273" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D273" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E273" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C273" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D273" s="9" t="s">
+      <c r="F273" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="E273" s="9" t="s">
+      <c r="G273" s="9" t="s">
         <v>10</v>
-      </c>
-      <c r="F273" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="G273" s="9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B274" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D274" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B274" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C274" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D274" s="9" t="s">
-        <v>174</v>
-      </c>
       <c r="E274" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F274" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F274" s="10" t="s">
+      <c r="G274" s="9" t="s">
         <v>37</v>
-      </c>
-      <c r="G274" s="9" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -8742,6 +8742,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F040406D9EE34E48977C379A242BB45D" ma:contentTypeVersion="15" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="1ab2d492e43f6bec9a26aa4599c840e9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="877b7d34-4df7-40bf-9eb1-208952470e96" xmlns:ns4="05fc27dd-4454-4248-9c78-3d72b2b155c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebc604e5d4aadf5a992ba83f8d4fb519" ns3:_="" ns4:_="">
     <xsd:import namespace="877b7d34-4df7-40bf-9eb1-208952470e96"/>
@@ -8974,14 +8982,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -8992,6 +8992,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBC6436E-C4E7-4E8D-94E8-64DAEC05792B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9010,23 +9027,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
   <ds:schemaRefs>

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D82EC521-37F3-45CC-9AA9-4261C7006E89}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D2702A8C-B534-4FCC-949C-D2CA57ED4380}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="657">
   <si>
     <t>Nome account</t>
   </si>
@@ -1988,6 +1988,12 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>VOLT 9 SRL</t>
+  </si>
+  <si>
+    <t>VIA VINCENZO MONTI 11</t>
   </si>
 </sst>
 </file>
@@ -2412,7 +2418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G274"/>
+  <dimension ref="A1:G275"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -8544,77 +8550,77 @@
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A267" s="9" t="s">
+      <c r="A267" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C267" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D267" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="E267" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F267" s="7">
+        <v>20123</v>
+      </c>
+      <c r="G267" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A268" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="B267" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C267" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D267" s="9" t="s">
+      <c r="B268" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D268" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="E267" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F267" s="10">
+      <c r="E268" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F268" s="10">
         <v>20123</v>
       </c>
-      <c r="G267" s="9" t="s">
+      <c r="G268" s="9" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A268" s="3" t="s">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A269" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="B268" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C268" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D268" s="3" t="s">
+      <c r="B269" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D269" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="E268" s="3" t="s">
+      <c r="E269" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="F268" s="7">
+      <c r="F269" s="7">
         <v>20094</v>
       </c>
-      <c r="G268" s="3" t="s">
+      <c r="G269" s="3" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A269" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="B269" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C269" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D269" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="E269" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F269" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="G269" s="9" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" s="9" t="s">
-        <v>215</v>
+        <v>395</v>
       </c>
       <c r="B270" s="9" t="s">
         <v>8</v>
@@ -8637,53 +8643,53 @@
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" s="9" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="B271" s="9" t="s">
-        <v>160</v>
+        <v>8</v>
       </c>
       <c r="C271" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D271" s="9" t="s">
-        <v>161</v>
+        <v>216</v>
       </c>
       <c r="E271" s="9" t="s">
-        <v>162</v>
+        <v>9</v>
       </c>
       <c r="F271" s="10" t="s">
-        <v>163</v>
+        <v>217</v>
       </c>
       <c r="G271" s="9" t="s">
-        <v>164</v>
+        <v>10</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" s="9" t="s">
-        <v>433</v>
+        <v>159</v>
       </c>
       <c r="B272" s="9" t="s">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="C272" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D272" s="9" t="s">
-        <v>216</v>
+        <v>161</v>
       </c>
       <c r="E272" s="9" t="s">
-        <v>9</v>
+        <v>162</v>
       </c>
       <c r="F272" s="10" t="s">
-        <v>217</v>
+        <v>163</v>
       </c>
       <c r="G272" s="9" t="s">
-        <v>10</v>
+        <v>164</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" s="9" t="s">
-        <v>254</v>
+        <v>433</v>
       </c>
       <c r="B273" s="9" t="s">
         <v>8</v>
@@ -8706,30 +8712,53 @@
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="B274" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D274" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E274" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F274" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="G274" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A275" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B274" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C274" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D274" s="9" t="s">
+      <c r="B275" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C275" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="D275" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="E274" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F274" s="10" t="s">
+      <c r="E275" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F275" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="G274" s="9" t="s">
+      <c r="G275" s="9" t="s">
         <v>37</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G218" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G274">
+    <sortState ref="A2:G275">
       <sortCondition ref="A1:A218"/>
     </sortState>
   </autoFilter>
@@ -8742,11 +8771,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8983,27 +9013,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9028,9 +9048,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D2702A8C-B534-4FCC-949C-D2CA57ED4380}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{807EF6C9-DCBD-4903-A228-93ACA6334C46}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Report!$A$1:$G$218</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="658">
   <si>
     <t>Nome account</t>
   </si>
@@ -1994,6 +1994,9 @@
   </si>
   <si>
     <t>VIA VINCENZO MONTI 11</t>
+  </si>
+  <si>
+    <t>OPERATION ENERGY S.R.L.</t>
   </si>
 </sst>
 </file>
@@ -2418,7 +2421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G275"/>
+  <dimension ref="A1:G276"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -6458,7 +6461,7 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>555</v>
+        <v>657</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>33</v>
@@ -6467,21 +6470,21 @@
         <v>654</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>524</v>
+        <v>355</v>
       </c>
       <c r="E176" s="4" t="s">
         <v>35</v>
       </c>
       <c r="F176" s="5">
-        <v>20154</v>
+        <v>20121</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>158</v>
+        <v>37</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>525</v>
+        <v>555</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>33</v>
@@ -6504,7 +6507,7 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>33</v>
@@ -6527,7 +6530,7 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>595</v>
+        <v>523</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>33</v>
@@ -6536,7 +6539,7 @@
         <v>654</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>596</v>
+        <v>524</v>
       </c>
       <c r="E179" s="4" t="s">
         <v>35</v>
@@ -6550,30 +6553,30 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>514</v>
+        <v>595</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>28</v>
+        <v>596</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F180" s="5">
-        <v>39100</v>
+        <v>20154</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>231</v>
+        <v>514</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>27</v>
@@ -6587,8 +6590,8 @@
       <c r="E181" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F181" s="5" t="s">
-        <v>30</v>
+      <c r="F181" s="5">
+        <v>39100</v>
       </c>
       <c r="G181" s="4" t="s">
         <v>31</v>
@@ -6596,30 +6599,30 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>142</v>
+        <v>231</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>143</v>
+        <v>28</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>33</v>
@@ -6628,13 +6631,13 @@
         <v>654</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="E183" s="4" t="s">
         <v>35</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="G183" s="4" t="s">
         <v>37</v>
@@ -6642,7 +6645,7 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>440</v>
+        <v>55</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>33</v>
@@ -6651,136 +6654,136 @@
         <v>654</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>441</v>
+        <v>56</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="F184" s="5">
-        <v>20038</v>
+        <v>35</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>135</v>
+        <v>37</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>235</v>
+        <v>441</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>80</v>
+        <v>442</v>
       </c>
       <c r="F185" s="5">
-        <v>10121</v>
+        <v>20038</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>82</v>
+        <v>135</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>94</v>
+        <v>425</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>96</v>
+        <v>235</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F186" s="5" t="s">
-        <v>98</v>
+        <v>80</v>
+      </c>
+      <c r="F186" s="5">
+        <v>10121</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>376</v>
+        <v>94</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>377</v>
+        <v>95</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>378</v>
+        <v>96</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="F187" s="5">
-        <v>64020</v>
+        <v>97</v>
+      </c>
+      <c r="F187" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>579</v>
+        <v>376</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>8</v>
+        <v>377</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>580</v>
+        <v>378</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F188" s="8" t="s">
-        <v>581</v>
+        <v>379</v>
+      </c>
+      <c r="F188" s="5">
+        <v>64020</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>409</v>
+        <v>579</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>210</v>
+        <v>580</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F189" s="10">
-        <v>20121</v>
+        <v>9</v>
+      </c>
+      <c r="F189" s="12" t="s">
+        <v>581</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>132</v>
+        <v>409</v>
       </c>
       <c r="B190" s="9" t="s">
         <v>33</v>
@@ -6789,113 +6792,113 @@
         <v>654</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>133</v>
+        <v>210</v>
       </c>
       <c r="E190" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F190" s="10" t="s">
-        <v>134</v>
+      <c r="F190" s="10">
+        <v>20121</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>135</v>
+        <v>37</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>604</v>
+        <v>132</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>605</v>
+        <v>133</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F191" s="12" t="s">
-        <v>606</v>
+        <v>35</v>
+      </c>
+      <c r="F191" s="10" t="s">
+        <v>134</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>10</v>
+        <v>135</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>256</v>
+        <v>604</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>257</v>
+        <v>605</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F192" s="10" t="s">
-        <v>57</v>
+        <v>9</v>
+      </c>
+      <c r="F192" s="12" t="s">
+        <v>606</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>339</v>
+        <v>256</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>340</v>
+        <v>33</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>341</v>
+        <v>257</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="F193" s="10">
-        <v>37045</v>
+        <v>35</v>
+      </c>
+      <c r="F193" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>342</v>
+        <v>37</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
-        <v>165</v>
+        <v>339</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>33</v>
+        <v>340</v>
       </c>
       <c r="C194" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>166</v>
+        <v>341</v>
       </c>
       <c r="E194" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F194" s="10" t="s">
-        <v>167</v>
+        <v>527</v>
+      </c>
+      <c r="F194" s="10">
+        <v>37045</v>
       </c>
       <c r="G194" s="9" t="s">
-        <v>158</v>
+        <v>342</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
-        <v>528</v>
+        <v>165</v>
       </c>
       <c r="B195" s="9" t="s">
         <v>33</v>
@@ -6909,8 +6912,8 @@
       <c r="E195" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F195" s="10">
-        <v>20126</v>
+      <c r="F195" s="10" t="s">
+        <v>167</v>
       </c>
       <c r="G195" s="9" t="s">
         <v>158</v>
@@ -6918,7 +6921,7 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
-        <v>600</v>
+        <v>528</v>
       </c>
       <c r="B196" s="9" t="s">
         <v>33</v>
@@ -6927,21 +6930,21 @@
         <v>654</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>601</v>
+        <v>166</v>
       </c>
       <c r="E196" s="9" t="s">
         <v>35</v>
       </c>
       <c r="F196" s="10">
-        <v>20138</v>
+        <v>20126</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>261</v>
+        <v>158</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="B197" s="9" t="s">
         <v>33</v>
@@ -6950,21 +6953,21 @@
         <v>654</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="E197" s="9" t="s">
         <v>35</v>
       </c>
       <c r="F197" s="10">
-        <v>20122</v>
+        <v>20138</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>37</v>
+        <v>261</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>593</v>
+        <v>608</v>
       </c>
       <c r="B198" s="9" t="s">
         <v>33</v>
@@ -6973,13 +6976,13 @@
         <v>654</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>393</v>
+        <v>609</v>
       </c>
       <c r="E198" s="9" t="s">
         <v>35</v>
       </c>
       <c r="F198" s="10">
-        <v>20123</v>
+        <v>20122</v>
       </c>
       <c r="G198" s="9" t="s">
         <v>37</v>
@@ -6987,53 +6990,53 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="B199" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D199" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="E199" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F199" s="10">
+        <v>20123</v>
+      </c>
+      <c r="G199" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A200" s="9" t="s">
         <v>470</v>
       </c>
-      <c r="B199" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C199" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D199" s="9" t="s">
+      <c r="B200" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D200" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="E199" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F199" s="10">
+      <c r="E200" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F200" s="10">
         <v>20135</v>
       </c>
-      <c r="G199" s="9" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A200" s="3" t="s">
-        <v>621</v>
-      </c>
-      <c r="B200" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C200" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D200" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E200" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F200" s="7">
-        <v>20135</v>
-      </c>
-      <c r="G200" s="3" t="s">
+      <c r="G200" s="9" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="3" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>33</v>
@@ -7055,100 +7058,100 @@
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A202" s="9" t="s">
+      <c r="A202" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F202" s="7">
+        <v>20135</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A203" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B202" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C202" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D202" s="9" t="s">
+      <c r="B203" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D203" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="E202" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F202" s="10">
+      <c r="E203" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F203" s="10">
         <v>20135</v>
       </c>
-      <c r="G202" s="9" t="s">
+      <c r="G203" s="9" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A203" s="3" t="s">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A204" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="B203" s="3" t="s">
+      <c r="B204" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C203" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D203" s="3" t="s">
+      <c r="C204" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D204" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="E203" s="3" t="s">
+      <c r="E204" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="F203" s="7">
+      <c r="F204" s="7">
         <v>85100</v>
       </c>
-      <c r="G203" s="3" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A204" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="B204" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="C204" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D204" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="E204" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="F204" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="G204" s="9" t="s">
+      <c r="G204" s="3" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="9" t="s">
-        <v>452</v>
+        <v>203</v>
       </c>
       <c r="B205" s="9" t="s">
-        <v>33</v>
+        <v>184</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D205" s="9" t="s">
-        <v>453</v>
+        <v>204</v>
       </c>
       <c r="E205" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F205" s="10">
-        <v>20144</v>
+        <v>185</v>
+      </c>
+      <c r="F205" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="G205" s="9" t="s">
-        <v>37</v>
+        <v>318</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="9" t="s">
-        <v>222</v>
+        <v>452</v>
       </c>
       <c r="B206" s="9" t="s">
         <v>33</v>
@@ -7157,320 +7160,320 @@
         <v>654</v>
       </c>
       <c r="D206" s="9" t="s">
-        <v>223</v>
+        <v>453</v>
       </c>
       <c r="E206" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F206" s="10" t="s">
-        <v>134</v>
+      <c r="F206" s="10">
+        <v>20144</v>
       </c>
       <c r="G206" s="9" t="s">
-        <v>135</v>
+        <v>37</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B207" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D207" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="E207" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F207" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="G207" s="9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A208" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="B207" s="9" t="s">
+      <c r="B208" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C207" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D207" s="9" t="s">
+      <c r="C208" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D208" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="E207" s="9" t="s">
+      <c r="E208" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="F207" s="10">
+      <c r="F208" s="10">
         <v>40026</v>
       </c>
-      <c r="G207" s="9" t="s">
+      <c r="G208" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A208" s="3" t="s">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A209" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="B208" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C208" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D208" s="3" t="s">
+      <c r="B209" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D209" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="E208" s="3" t="s">
+      <c r="E209" s="3" t="s">
         <v>638</v>
       </c>
-      <c r="F208" s="7">
+      <c r="F209" s="7">
         <v>20068</v>
       </c>
-      <c r="G208" s="3" t="s">
+      <c r="G209" s="3" t="s">
         <v>261</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A209" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="B209" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C209" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D209" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="E209" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F209" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="G209" s="9" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="9" t="s">
-        <v>532</v>
+        <v>285</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D210" s="9" t="s">
-        <v>28</v>
+        <v>319</v>
       </c>
       <c r="E210" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F210" s="10">
-        <v>39100</v>
+        <v>9</v>
+      </c>
+      <c r="F210" s="10" t="s">
+        <v>322</v>
       </c>
       <c r="G210" s="9" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="9" t="s">
-        <v>366</v>
+        <v>532</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C211" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D211" s="9" t="s">
-        <v>367</v>
+        <v>28</v>
       </c>
       <c r="E211" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F211" s="10">
-        <v>20123</v>
+        <v>39100</v>
       </c>
       <c r="G211" s="9" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="9" t="s">
-        <v>286</v>
+        <v>366</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>307</v>
+        <v>33</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D212" s="9" t="s">
-        <v>320</v>
+        <v>367</v>
       </c>
       <c r="E212" s="9" t="s">
-        <v>321</v>
+        <v>35</v>
       </c>
       <c r="F212" s="10">
-        <v>12020</v>
+        <v>20123</v>
       </c>
       <c r="G212" s="9" t="s">
-        <v>306</v>
+        <v>37</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="9" t="s">
-        <v>38</v>
+        <v>286</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>39</v>
+        <v>307</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D213" s="9" t="s">
-        <v>40</v>
+        <v>320</v>
       </c>
       <c r="E213" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F213" s="10" t="s">
-        <v>42</v>
+        <v>321</v>
+      </c>
+      <c r="F213" s="10">
+        <v>12020</v>
       </c>
       <c r="G213" s="9" t="s">
-        <v>43</v>
+        <v>306</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="9" t="s">
-        <v>420</v>
+        <v>38</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>421</v>
+        <v>39</v>
       </c>
       <c r="C214" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D214" s="9" t="s">
-        <v>422</v>
+        <v>40</v>
       </c>
       <c r="E214" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="F214" s="10">
-        <v>28053</v>
+        <v>41</v>
+      </c>
+      <c r="F214" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="G214" s="9" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="9" t="s">
-        <v>171</v>
+        <v>420</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>33</v>
+        <v>421</v>
       </c>
       <c r="C215" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D215" s="9" t="s">
-        <v>168</v>
+        <v>422</v>
       </c>
       <c r="E215" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="F215" s="10" t="s">
-        <v>170</v>
+        <v>423</v>
+      </c>
+      <c r="F215" s="10">
+        <v>28053</v>
       </c>
       <c r="G215" s="9" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="9" t="s">
-        <v>559</v>
+        <v>171</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D216" s="9" t="s">
-        <v>560</v>
+        <v>168</v>
       </c>
       <c r="E216" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F216" s="10">
-        <v>39100</v>
+        <v>169</v>
+      </c>
+      <c r="F216" s="10" t="s">
+        <v>170</v>
       </c>
       <c r="G216" s="9" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
-        <v>197</v>
+        <v>559</v>
       </c>
       <c r="B217" s="9" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D217" s="9" t="s">
-        <v>198</v>
+        <v>560</v>
       </c>
       <c r="E217" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F217" s="10" t="s">
-        <v>199</v>
+        <v>29</v>
+      </c>
+      <c r="F217" s="10">
+        <v>39100</v>
       </c>
       <c r="G217" s="9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="9" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B218" s="9" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="C218" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D218" s="9" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E218" s="9" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="F218" s="10" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="G218" s="9" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="9" t="s">
-        <v>243</v>
+        <v>206</v>
       </c>
       <c r="B219" s="9" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="C219" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D219" s="9" t="s">
-        <v>176</v>
+        <v>207</v>
       </c>
       <c r="E219" s="9" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F219" s="10" t="s">
-        <v>57</v>
+        <v>208</v>
       </c>
       <c r="G219" s="9" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="9" t="s">
-        <v>533</v>
+        <v>243</v>
       </c>
       <c r="B220" s="9" t="s">
         <v>33</v>
@@ -7484,8 +7487,8 @@
       <c r="E220" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F220" s="10">
-        <v>20121</v>
+      <c r="F220" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="G220" s="9" t="s">
         <v>37</v>
@@ -7493,7 +7496,7 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="9" t="s">
-        <v>577</v>
+        <v>533</v>
       </c>
       <c r="B221" s="9" t="s">
         <v>33</v>
@@ -7502,7 +7505,7 @@
         <v>654</v>
       </c>
       <c r="D221" s="9" t="s">
-        <v>578</v>
+        <v>176</v>
       </c>
       <c r="E221" s="9" t="s">
         <v>35</v>
@@ -7516,159 +7519,159 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="9" t="s">
-        <v>444</v>
+        <v>577</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>445</v>
+        <v>33</v>
       </c>
       <c r="C222" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D222" s="9" t="s">
-        <v>446</v>
+        <v>578</v>
       </c>
       <c r="E222" s="9" t="s">
-        <v>447</v>
+        <v>35</v>
       </c>
       <c r="F222" s="10">
-        <v>53048</v>
+        <v>20121</v>
       </c>
       <c r="G222" s="9" t="s">
-        <v>448</v>
+        <v>37</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="9" t="s">
-        <v>515</v>
+        <v>444</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>508</v>
+        <v>445</v>
       </c>
       <c r="C223" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D223" s="9" t="s">
-        <v>516</v>
+        <v>446</v>
       </c>
       <c r="E223" s="9" t="s">
-        <v>517</v>
+        <v>447</v>
       </c>
       <c r="F223" s="10">
-        <v>35011</v>
+        <v>53048</v>
       </c>
       <c r="G223" s="9" t="s">
-        <v>504</v>
+        <v>448</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="9" t="s">
-        <v>242</v>
+        <v>515</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>33</v>
+        <v>508</v>
       </c>
       <c r="C224" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D224" s="9" t="s">
-        <v>176</v>
+        <v>516</v>
       </c>
       <c r="E224" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F224" s="10" t="s">
-        <v>57</v>
+        <v>517</v>
+      </c>
+      <c r="F224" s="10">
+        <v>35011</v>
       </c>
       <c r="G224" s="9" t="s">
-        <v>37</v>
+        <v>504</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="B225" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D225" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="E225" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F225" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G225" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A226" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B225" s="9" t="s">
+      <c r="B226" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C225" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D225" s="9" t="s">
+      <c r="C226" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D226" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="E225" s="9" t="s">
+      <c r="E226" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F225" s="10" t="s">
+      <c r="F226" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="G225" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A226" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C226" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D226" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E226" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F226" s="7">
-        <v>39100</v>
-      </c>
-      <c r="G226" s="3" t="s">
+      <c r="G226" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C227" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F227" s="7">
+        <v>39100</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A228" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="B227" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C227" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D227" s="3" t="s">
+      <c r="B228" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D228" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="E227" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F227" s="7">
-        <v>20121</v>
-      </c>
-      <c r="G227" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A228" s="9" t="s">
-        <v>530</v>
-      </c>
-      <c r="B228" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C228" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D228" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="E228" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F228" s="10">
+      <c r="E228" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F228" s="7">
         <v>20121</v>
       </c>
       <c r="G228" s="9" t="s">
@@ -7677,145 +7680,145 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="B229" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C229" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D229" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="E229" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F229" s="10">
+        <v>20121</v>
+      </c>
+      <c r="G229" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A230" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B229" s="9" t="s">
+      <c r="B230" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C229" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D229" s="9" t="s">
+      <c r="C230" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D230" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E229" s="9" t="s">
+      <c r="E230" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F229" s="10" t="s">
+      <c r="F230" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="G229" s="9" t="s">
+      <c r="G230" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A230" s="3" t="s">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A231" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="B230" s="3" t="s">
+      <c r="B231" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C230" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D230" s="3" t="s">
+      <c r="C231" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D231" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="E230" s="3" t="s">
+      <c r="E231" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F230" s="11" t="s">
+      <c r="F231" s="11" t="s">
         <v>567</v>
       </c>
-      <c r="G230" s="3" t="s">
+      <c r="G231" s="3" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A231" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="B231" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C231" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D231" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="E231" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="F231" s="10">
-        <v>20089</v>
-      </c>
-      <c r="G231" s="9" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="9" t="s">
-        <v>474</v>
+        <v>380</v>
       </c>
       <c r="B232" s="9" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D232" s="9" t="s">
-        <v>475</v>
+        <v>381</v>
       </c>
       <c r="E232" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F232" s="12" t="s">
-        <v>476</v>
+        <v>382</v>
+      </c>
+      <c r="F232" s="10">
+        <v>20089</v>
       </c>
       <c r="G232" s="9" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="9" t="s">
-        <v>211</v>
+        <v>474</v>
       </c>
       <c r="B233" s="9" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C233" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D233" s="9" t="s">
-        <v>201</v>
+        <v>475</v>
       </c>
       <c r="E233" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F233" s="10" t="s">
-        <v>202</v>
+        <v>9</v>
+      </c>
+      <c r="F233" s="12" t="s">
+        <v>476</v>
       </c>
       <c r="G233" s="9" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B234" s="9" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C234" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D234" s="9" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="E234" s="9" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F234" s="10" t="s">
-        <v>157</v>
+        <v>202</v>
       </c>
       <c r="G234" s="9" t="s">
-        <v>158</v>
+        <v>25</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="9" t="s">
-        <v>437</v>
+        <v>213</v>
       </c>
       <c r="B235" s="9" t="s">
         <v>33</v>
@@ -7829,108 +7832,108 @@
       <c r="E235" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F235" s="10">
-        <v>20124</v>
+      <c r="F235" s="10" t="s">
+        <v>157</v>
       </c>
       <c r="G235" s="9" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A236" s="3" t="s">
+      <c r="A236" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="B236" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D236" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E236" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F236" s="10">
+        <v>20124</v>
+      </c>
+      <c r="G236" s="9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A237" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="B236" s="3" t="s">
+      <c r="B237" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C236" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D236" s="3" t="s">
+      <c r="C237" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D237" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="E236" s="3" t="s">
+      <c r="E237" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F236" s="7">
+      <c r="F237" s="7">
         <v>24050</v>
       </c>
-      <c r="G236" s="3" t="s">
+      <c r="G237" s="3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A237" s="9" t="s">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A238" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="B237" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C237" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D237" s="9" t="s">
+      <c r="B238" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D238" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="E237" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F237" s="10" t="s">
+      <c r="E238" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F238" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="G237" s="9" t="s">
+      <c r="G238" s="9" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A238" s="3" t="s">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A239" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="B238" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C238" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D238" s="3" t="s">
+      <c r="B239" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D239" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E238" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F238" s="7">
+      <c r="E239" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F239" s="7">
         <v>20148</v>
       </c>
-      <c r="G238" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A239" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="B239" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C239" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D239" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="E239" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F239" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="G239" s="9" t="s">
+      <c r="G239" s="3" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="9" t="s">
-        <v>471</v>
+        <v>255</v>
       </c>
       <c r="B240" s="9" t="s">
         <v>33</v>
@@ -7939,21 +7942,21 @@
         <v>654</v>
       </c>
       <c r="D240" s="9" t="s">
-        <v>463</v>
+        <v>229</v>
       </c>
       <c r="E240" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F240" s="10">
-        <v>20129</v>
+      <c r="F240" s="10" t="s">
+        <v>230</v>
       </c>
       <c r="G240" s="9" t="s">
-        <v>261</v>
+        <v>135</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" s="9" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="B241" s="9" t="s">
         <v>33</v>
@@ -7976,7 +7979,7 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" s="9" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="B242" s="9" t="s">
         <v>33</v>
@@ -7999,7 +8002,7 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" s="9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B243" s="9" t="s">
         <v>33</v>
@@ -8022,7 +8025,7 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" s="9" t="s">
-        <v>175</v>
+        <v>473</v>
       </c>
       <c r="B244" s="9" t="s">
         <v>33</v>
@@ -8031,228 +8034,228 @@
         <v>654</v>
       </c>
       <c r="D244" s="9" t="s">
-        <v>176</v>
+        <v>463</v>
       </c>
       <c r="E244" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F244" s="10" t="s">
-        <v>57</v>
+      <c r="F244" s="10">
+        <v>20129</v>
       </c>
       <c r="G244" s="9" t="s">
-        <v>37</v>
+        <v>261</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" s="9" t="s">
-        <v>330</v>
+        <v>175</v>
       </c>
       <c r="B245" s="9" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C245" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D245" s="9" t="s">
-        <v>331</v>
+        <v>176</v>
       </c>
       <c r="E245" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="F245" s="10">
-        <v>40026</v>
+        <v>35</v>
+      </c>
+      <c r="F245" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="G245" s="9" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" s="9" t="s">
-        <v>287</v>
+        <v>330</v>
       </c>
       <c r="B246" s="9" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C246" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D246" s="9" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="E246" s="9" t="s">
-        <v>35</v>
+        <v>317</v>
       </c>
       <c r="F246" s="10">
-        <v>20124</v>
+        <v>40026</v>
       </c>
       <c r="G246" s="9" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="B247" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D247" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="E247" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F247" s="10">
+        <v>20124</v>
+      </c>
+      <c r="G247" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A248" s="9" t="s">
         <v>449</v>
       </c>
-      <c r="B247" s="9" t="s">
+      <c r="B248" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="C247" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D247" s="9" t="s">
+      <c r="C248" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D248" s="9" t="s">
         <v>450</v>
       </c>
-      <c r="E247" s="9" t="s">
+      <c r="E248" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="F247" s="10">
+      <c r="F248" s="10">
         <v>12011</v>
       </c>
-      <c r="G247" s="9" t="s">
+      <c r="G248" s="9" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A248" s="3" t="s">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A249" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="B248" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C248" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D248" s="3" t="s">
+      <c r="B249" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C249" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D249" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="E248" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F248" s="7">
+      <c r="E249" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F249" s="7">
         <v>20121</v>
       </c>
-      <c r="G248" s="3" t="s">
+      <c r="G249" s="3" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A249" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="B249" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="C249" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D249" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="E249" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="F249" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G249" s="9" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" s="9" t="s">
-        <v>418</v>
+        <v>150</v>
       </c>
       <c r="B250" s="9" t="s">
-        <v>33</v>
+        <v>151</v>
       </c>
       <c r="C250" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D250" s="9" t="s">
-        <v>419</v>
+        <v>152</v>
       </c>
       <c r="E250" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F250" s="10">
-        <v>20123</v>
+        <v>153</v>
+      </c>
+      <c r="F250" s="10" t="s">
+        <v>154</v>
       </c>
       <c r="G250" s="9" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" s="9" t="s">
-        <v>490</v>
+        <v>418</v>
       </c>
       <c r="B251" s="9" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C251" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D251" s="9" t="s">
-        <v>491</v>
+        <v>419</v>
       </c>
       <c r="E251" s="9" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F251" s="10">
-        <v>90141</v>
+        <v>20123</v>
       </c>
       <c r="G251" s="9" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="B252" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D252" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="E252" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F252" s="10">
+        <v>90141</v>
+      </c>
+      <c r="G252" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A253" s="9" t="s">
         <v>479</v>
       </c>
-      <c r="B252" s="9" t="s">
+      <c r="B253" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C252" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D252" s="9" t="s">
+      <c r="C253" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D253" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="E252" s="9" t="s">
+      <c r="E253" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F252" s="12" t="s">
+      <c r="F253" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="G252" s="9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A253" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="B253" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C253" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D253" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="E253" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F253" s="11" t="s">
-        <v>389</v>
-      </c>
-      <c r="G253" s="3" t="s">
+      <c r="G253" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" s="3" t="s">
-        <v>529</v>
+        <v>641</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>8</v>
@@ -8274,376 +8277,376 @@
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A255" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="B255" s="9" t="s">
+      <c r="A255" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="B255" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C255" s="4" t="s">
         <v>654</v>
       </c>
-      <c r="D255" s="9" t="s">
+      <c r="D255" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="E255" s="9" t="s">
+      <c r="E255" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F255" s="10" t="s">
+      <c r="F255" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="G255" s="9" t="s">
+      <c r="G255" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="B256" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D256" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="E256" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F256" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="G256" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A257" s="9" t="s">
         <v>464</v>
       </c>
-      <c r="B256" s="9" t="s">
+      <c r="B257" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="C256" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D256" s="9" t="s">
+      <c r="C257" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D257" s="9" t="s">
         <v>465</v>
       </c>
-      <c r="E256" s="9" t="s">
+      <c r="E257" s="9" t="s">
         <v>466</v>
       </c>
-      <c r="F256" s="10">
+      <c r="F257" s="10">
         <v>38055</v>
       </c>
-      <c r="G256" s="9" t="s">
+      <c r="G257" s="9" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A257" s="3" t="s">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A258" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="B257" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C257" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D257" s="3" t="s">
+      <c r="B258" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D258" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E257" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F257" s="7">
+      <c r="E258" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F258" s="7">
         <v>20145</v>
       </c>
-      <c r="G257" s="3" t="s">
+      <c r="G258" s="3" t="s">
         <v>135</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A258" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="B258" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C258" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D258" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="E258" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="F258" s="10">
-        <v>25010</v>
-      </c>
-      <c r="G258" s="9" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="B259" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D259" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="E259" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="F259" s="10">
+        <v>25010</v>
+      </c>
+      <c r="G259" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A260" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="B259" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C259" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D259" s="9" t="s">
+      <c r="B260" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D260" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="E259" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F259" s="10">
+      <c r="E260" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F260" s="10">
         <v>20123</v>
       </c>
-      <c r="G259" s="9" t="s">
+      <c r="G260" s="9" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A260" s="3" t="s">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A261" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="B260" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C260" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D260" s="3" t="s">
+      <c r="B261" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D261" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="E260" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F260" s="7">
+      <c r="E261" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F261" s="7">
         <v>20123</v>
       </c>
-      <c r="G260" s="3" t="s">
+      <c r="G261" s="3" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A261" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="B261" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C261" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D261" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="E261" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="F261" s="10">
-        <v>71016</v>
-      </c>
-      <c r="G261" s="9" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B262" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D262" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="E262" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="F262" s="10">
+        <v>71016</v>
+      </c>
+      <c r="G262" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A263" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B262" s="9" t="s">
+      <c r="B263" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C262" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D262" s="9" t="s">
+      <c r="C263" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D263" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E262" s="9" t="s">
+      <c r="E263" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F262" s="10" t="s">
+      <c r="F263" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G262" s="9" t="s">
+      <c r="G263" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A263" s="3" t="s">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A264" s="3" t="s">
         <v>639</v>
       </c>
-      <c r="B263" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C263" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D263" s="3" t="s">
+      <c r="B264" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C264" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D264" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="E263" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F263" s="7">
+      <c r="E264" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F264" s="7">
         <v>20123</v>
       </c>
-      <c r="G263" s="3" t="s">
+      <c r="G264" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A264" s="9" t="s">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A265" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="B264" s="9" t="s">
+      <c r="B265" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="C264" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D264" s="9" t="s">
+      <c r="C265" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D265" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="E264" s="9" t="s">
+      <c r="E265" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="F264" s="10" t="s">
+      <c r="F265" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="G264" s="9" t="s">
+      <c r="G265" s="9" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A265" s="3" t="s">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A266" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="B265" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C265" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D265" s="3" t="s">
+      <c r="B266" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C266" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D266" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="E265" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F265" s="7">
+      <c r="E266" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F266" s="7">
         <v>20122</v>
       </c>
-      <c r="G265" s="3" t="s">
+      <c r="G266" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A266" s="9" t="s">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A267" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="B266" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C266" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D266" s="9" t="s">
+      <c r="B267" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C267" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D267" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="E266" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F266" s="10" t="s">
+      <c r="E267" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F267" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="G266" s="9" t="s">
+      <c r="G267" s="9" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A267" s="3" t="s">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A268" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="B267" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C267" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D267" s="3" t="s">
+      <c r="B268" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D268" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="E267" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F267" s="7">
+      <c r="E268" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F268" s="7">
         <v>20123</v>
       </c>
-      <c r="G267" s="3" t="s">
+      <c r="G268" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A268" s="9" t="s">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A269" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="B268" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C268" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D268" s="9" t="s">
+      <c r="B269" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D269" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="E268" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F268" s="10">
+      <c r="E269" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F269" s="10">
         <v>20123</v>
       </c>
-      <c r="G268" s="9" t="s">
+      <c r="G269" s="9" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A269" s="3" t="s">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A270" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="B269" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C269" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D269" s="3" t="s">
+      <c r="B270" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D270" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="E269" s="3" t="s">
+      <c r="E270" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="F269" s="7">
+      <c r="F270" s="7">
         <v>20094</v>
       </c>
-      <c r="G269" s="3" t="s">
+      <c r="G270" s="3" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A270" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="B270" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C270" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D270" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="E270" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F270" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="G270" s="9" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" s="9" t="s">
-        <v>215</v>
+        <v>395</v>
       </c>
       <c r="B271" s="9" t="s">
         <v>8</v>
@@ -8666,53 +8669,53 @@
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" s="9" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="B272" s="9" t="s">
-        <v>160</v>
+        <v>8</v>
       </c>
       <c r="C272" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D272" s="9" t="s">
-        <v>161</v>
+        <v>216</v>
       </c>
       <c r="E272" s="9" t="s">
-        <v>162</v>
+        <v>9</v>
       </c>
       <c r="F272" s="10" t="s">
-        <v>163</v>
+        <v>217</v>
       </c>
       <c r="G272" s="9" t="s">
-        <v>164</v>
+        <v>10</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" s="9" t="s">
-        <v>433</v>
+        <v>159</v>
       </c>
       <c r="B273" s="9" t="s">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="C273" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D273" s="9" t="s">
-        <v>216</v>
+        <v>161</v>
       </c>
       <c r="E273" s="9" t="s">
-        <v>9</v>
+        <v>162</v>
       </c>
       <c r="F273" s="10" t="s">
-        <v>217</v>
+        <v>163</v>
       </c>
       <c r="G273" s="9" t="s">
-        <v>10</v>
+        <v>164</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" s="9" t="s">
-        <v>254</v>
+        <v>433</v>
       </c>
       <c r="B274" s="9" t="s">
         <v>8</v>
@@ -8735,30 +8738,53 @@
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="B275" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C275" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="D275" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E275" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F275" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="G275" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A276" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B275" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C275" s="9" t="s">
-        <v>654</v>
-      </c>
-      <c r="D275" s="9" t="s">
+      <c r="B276" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C276" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="D276" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="E275" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F275" s="10" t="s">
+      <c r="E276" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F276" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="G275" s="9" t="s">
+      <c r="G276" s="9" t="s">
         <v>37</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G218" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G275">
+    <sortState ref="A2:G276">
       <sortCondition ref="A1:A218"/>
     </sortState>
   </autoFilter>
@@ -8771,15 +8797,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F040406D9EE34E48977C379A242BB45D" ma:contentTypeVersion="15" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="1ab2d492e43f6bec9a26aa4599c840e9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="877b7d34-4df7-40bf-9eb1-208952470e96" xmlns:ns4="05fc27dd-4454-4248-9c78-3d72b2b155c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebc604e5d4aadf5a992ba83f8d4fb519" ns3:_="" ns4:_="">
     <xsd:import namespace="877b7d34-4df7-40bf-9eb1-208952470e96"/>
@@ -9012,6 +9029,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -9021,14 +9047,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBC6436E-C4E7-4E8D-94E8-64DAEC05792B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9047,18 +9065,26 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>

--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{807EF6C9-DCBD-4903-A228-93ACA6334C46}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{E476BC05-A230-47B0-B1D0-9E9524B23A2E}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="680">
   <si>
     <t>Nome account</t>
   </si>
@@ -46,9 +46,6 @@
     <t>Filiale di Riferimento</t>
   </si>
   <si>
-    <t>Prospect</t>
-  </si>
-  <si>
     <t>RM</t>
   </si>
   <si>
@@ -1997,6 +1994,75 @@
   </si>
   <si>
     <t>OPERATION ENERGY S.R.L.</t>
+  </si>
+  <si>
+    <t>EEC SOLAR 3 SRL</t>
+  </si>
+  <si>
+    <t>PIAZZALE ANNA CIABOTTI 8</t>
+  </si>
+  <si>
+    <t>S2SE TRE SRL</t>
+  </si>
+  <si>
+    <t>VIA DI SELVA CANDIDA 452</t>
+  </si>
+  <si>
+    <t>00166</t>
+  </si>
+  <si>
+    <t>EPSILON GEMINI SRL</t>
+  </si>
+  <si>
+    <t>SONNEDIX MAG SRL</t>
+  </si>
+  <si>
+    <t>PHOTOSOL ENERGIA ITALIA SRL</t>
+  </si>
+  <si>
+    <t>VIA SANTA MARIA SEGRETA 6</t>
+  </si>
+  <si>
+    <t>SOTTOCOLLE SRL</t>
+  </si>
+  <si>
+    <t>VIA AGOSTINO CAGGIOLI 2/C</t>
+  </si>
+  <si>
+    <t>PISOGNE</t>
+  </si>
+  <si>
+    <t>ACHEON SRL</t>
+  </si>
+  <si>
+    <t>VIA ANTONIO BERTOLONI 19</t>
+  </si>
+  <si>
+    <t>00197</t>
+  </si>
+  <si>
+    <t>SPD TRE SRL</t>
+  </si>
+  <si>
+    <t>FI</t>
+  </si>
+  <si>
+    <t>PIAZZALE DONATELLO 4</t>
+  </si>
+  <si>
+    <t>FIRENZE</t>
+  </si>
+  <si>
+    <t>IDROAGRI SOC AGRICOLA SRL</t>
+  </si>
+  <si>
+    <t>REGIONE BOSCHI 48</t>
+  </si>
+  <si>
+    <t>SEZZADIO</t>
+  </si>
+  <si>
+    <t>Genova</t>
   </si>
 </sst>
 </file>
@@ -2421,7 +2487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G276"/>
+  <dimension ref="A1:G285"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -2459,6332 +2525,6539 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="F5" s="8" t="s">
         <v>586</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>587</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>500</v>
+        <v>669</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>501</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>7</v>
+        <v>653</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>502</v>
+        <v>670</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="F6" s="5">
-        <v>45100</v>
+        <v>8</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>671</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>504</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>400</v>
+        <v>499</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>7</v>
+        <v>500</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>401</v>
+        <v>501</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>35</v>
+        <v>502</v>
       </c>
       <c r="F7" s="5">
-        <v>20123</v>
+        <v>45100</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>37</v>
+        <v>503</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>607</v>
+        <v>399</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F8" s="5">
         <v>20123</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>180</v>
+        <v>606</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>181</v>
+        <v>400</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>179</v>
+        <v>34</v>
+      </c>
+      <c r="F9" s="5">
+        <v>20123</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>258</v>
+        <v>179</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="C10" s="1" t="s">
+        <v>653</v>
+      </c>
       <c r="D10" s="4" t="s">
-        <v>259</v>
+        <v>180</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>260</v>
+        <v>178</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>261</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>614</v>
+        <v>257</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>502</v>
+        <v>258</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="F11" s="5">
-        <v>45100</v>
+        <v>34</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>259</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>504</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>509</v>
+        <v>613</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>7</v>
+        <v>500</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="F12" s="5">
-        <v>33050</v>
+        <v>45100</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>262</v>
+        <v>508</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>7</v>
+        <v>509</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>264</v>
+        <v>510</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>266</v>
+        <v>511</v>
+      </c>
+      <c r="F13" s="5">
+        <v>33050</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>267</v>
+        <v>512</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>599</v>
+        <v>261</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>7</v>
+        <v>262</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F14" s="5">
-        <v>10121</v>
+        <v>264</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>82</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>235</v>
-      </c>
       <c r="E15" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>236</v>
+        <v>79</v>
+      </c>
+      <c r="F15" s="5">
+        <v>10121</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>494</v>
+        <v>233</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>7</v>
+        <v>653</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>495</v>
+        <v>234</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>496</v>
-      </c>
-      <c r="F16" s="5">
-        <v>10098</v>
+        <v>79</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>44</v>
+        <v>493</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>7</v>
+        <v>77</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>46</v>
+        <v>494</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>48</v>
+        <v>495</v>
+      </c>
+      <c r="F17" s="5">
+        <v>10098</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>190</v>
+        <v>43</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>7</v>
+        <v>44</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>76</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="4" t="s">
+      <c r="F20" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>179</v>
-      </c>
       <c r="G20" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="4" t="s">
+      <c r="F21" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>179</v>
-      </c>
       <c r="G21" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>481</v>
+        <v>194</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="F22" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>179</v>
-      </c>
       <c r="G22" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>196</v>
+        <v>480</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="4" t="s">
+      <c r="F23" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>179</v>
-      </c>
       <c r="G23" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="F24" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>179</v>
-      </c>
       <c r="G24" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>626</v>
+        <v>181</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>627</v>
-      </c>
-      <c r="C25" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="C25" s="1" t="s">
+        <v>653</v>
+      </c>
       <c r="D25" s="4" t="s">
-        <v>628</v>
+        <v>177</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>629</v>
-      </c>
-      <c r="F25" s="5">
-        <v>36022</v>
+        <v>8</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>178</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>504</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>402</v>
+        <v>625</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>7</v>
+        <v>626</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>403</v>
+        <v>627</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>29</v>
+        <v>628</v>
       </c>
       <c r="F26" s="5">
-        <v>39100</v>
+        <v>36022</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>31</v>
+        <v>503</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>594</v>
+        <v>401</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>7</v>
+        <v>26</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F27" s="5">
         <v>39100</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>623</v>
+        <v>593</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>7</v>
+        <v>26</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F28" s="5">
         <v>39100</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>398</v>
+        <v>622</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>7</v>
+        <v>26</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F29" s="5">
-        <v>20124</v>
+        <v>39100</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>467</v>
+        <v>397</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>468</v>
+        <v>398</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>469</v>
+        <v>34</v>
+      </c>
+      <c r="F30" s="5">
+        <v>20124</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>10</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>435</v>
+        <v>466</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C31" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="C31" s="1" t="s">
+        <v>653</v>
+      </c>
       <c r="D31" s="4" t="s">
-        <v>304</v>
+        <v>467</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F31" s="5">
-        <v>20123</v>
+        <v>8</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>468</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>348</v>
+        <v>434</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>349</v>
+        <v>303</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F32" s="5">
-        <v>20122</v>
+        <v>20123</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>66</v>
+        <v>347</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>17</v>
+        <v>348</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>19</v>
+        <v>34</v>
+      </c>
+      <c r="F33" s="5">
+        <v>20122</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>397</v>
+        <v>65</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F34" s="5">
-        <v>10123</v>
+        <v>17</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="C35" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="4" t="s">
+      <c r="E35" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E35" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F35" s="5" t="s">
+      <c r="F35" s="5">
+        <v>10123</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>545</v>
+        <v>76</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>7</v>
+        <v>77</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>546</v>
+        <v>78</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>547</v>
-      </c>
-      <c r="F36" s="5">
-        <v>33100</v>
+        <v>79</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>80</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>513</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>278</v>
+        <v>544</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>7</v>
+        <v>509</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>288</v>
+        <v>545</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>289</v>
+        <v>546</v>
       </c>
       <c r="F37" s="5">
-        <v>39042</v>
+        <v>33100</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>31</v>
+        <v>512</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>522</v>
+        <v>277</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>7</v>
+        <v>26</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>338</v>
+        <v>287</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>35</v>
+        <v>288</v>
       </c>
       <c r="F38" s="5">
-        <v>20121</v>
+        <v>39042</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>338</v>
-      </c>
       <c r="E39" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F39" s="5">
         <v>20121</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>32</v>
+        <v>336</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>34</v>
+        <v>337</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F40" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F40" s="5">
+        <v>20121</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>220</v>
+        <v>31</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>221</v>
+        <v>33</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>179</v>
+        <v>35</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>115</v>
+        <v>219</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C42" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="C42" s="1" t="s">
+        <v>653</v>
+      </c>
       <c r="D42" s="4" t="s">
-        <v>117</v>
+        <v>220</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>118</v>
+        <v>8</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>526</v>
+        <v>114</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43" s="4" t="s">
+      <c r="E43" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="F43" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F43" s="5">
-        <v>65125</v>
-      </c>
       <c r="G43" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>253</v>
+        <v>525</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D44" s="4" t="s">
+      <c r="E44" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E44" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>119</v>
+      <c r="F44" s="5">
+        <v>65125</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>61</v>
+        <v>252</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>7</v>
+        <v>115</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>7</v>
+        <v>61</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>146</v>
+        <v>62</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>147</v>
+        <v>63</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>148</v>
+        <v>64</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>149</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>520</v>
+        <v>143</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>7</v>
+        <v>144</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>521</v>
+        <v>145</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F47" s="5">
-        <v>20033</v>
+        <v>146</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>147</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>290</v>
+        <v>519</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>292</v>
+        <v>520</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>293</v>
+        <v>34</v>
       </c>
       <c r="F48" s="5">
-        <v>60035</v>
+        <v>20033</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>649</v>
+        <v>289</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>7</v>
+        <v>290</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>28</v>
+        <v>291</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>29</v>
+        <v>292</v>
       </c>
       <c r="F49" s="5">
-        <v>39100</v>
+        <v>60035</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>31</v>
+        <v>163</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>584</v>
+        <v>648</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>7</v>
+        <v>26</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>117</v>
+        <v>27</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="F50" s="5">
-        <v>65125</v>
+        <v>39100</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>556</v>
+        <v>583</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>7</v>
+        <v>115</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>214</v>
+        <v>116</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="F51" s="5">
-        <v>20124</v>
+        <v>65125</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>158</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>541</v>
+        <v>213</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F52" s="5">
-        <v>20121</v>
+        <v>20124</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>37</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F53" s="5">
         <v>20121</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>558</v>
+        <v>541</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F54" s="5">
         <v>20121</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>498</v>
+        <v>557</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>7</v>
+        <v>653</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>499</v>
+        <v>540</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="F55" s="5">
-        <v>10143</v>
+        <v>20121</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>616</v>
+        <v>497</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>7</v>
+        <v>77</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>617</v>
+        <v>498</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>618</v>
+        <v>79</v>
       </c>
       <c r="F56" s="5">
-        <v>25038</v>
+        <v>10143</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>388</v>
+        <v>615</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>7</v>
+        <v>101</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>269</v>
+        <v>616</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>35</v>
+        <v>617</v>
       </c>
       <c r="F57" s="5">
-        <v>20123</v>
+        <v>25038</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>436</v>
+        <v>387</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F58" s="5">
         <v>20123</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>396</v>
+        <v>435</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F59" s="5">
         <v>20123</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>269</v>
-      </c>
       <c r="E60" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>60</v>
+        <v>34</v>
+      </c>
+      <c r="F60" s="5">
+        <v>20123</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>136</v>
+        <v>267</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>121</v>
+        <v>268</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>408</v>
+        <v>135</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F62" s="5">
-        <v>20121</v>
+        <v>34</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>137</v>
+        <v>407</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>141</v>
+        <v>34</v>
+      </c>
+      <c r="F63" s="5">
+        <v>20121</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>7</v>
+        <v>137</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>613</v>
+        <v>123</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D65" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="E65" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F65" s="5">
-        <v>90139</v>
-      </c>
       <c r="G65" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>443</v>
+        <v>612</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>188</v>
+        <v>124</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F66" s="5">
-        <v>20158</v>
+        <v>90139</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>224</v>
+        <v>442</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
+      </c>
+      <c r="F67" s="5">
+        <v>20158</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>31</v>
+        <v>157</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>83</v>
+        <v>223</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>7</v>
+        <v>26</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>85</v>
+        <v>224</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>582</v>
+        <v>82</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>7</v>
+        <v>83</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>583</v>
+        <v>84</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="F69" s="5">
-        <v>38123</v>
+        <v>85</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>267</v>
+        <v>42</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>543</v>
+        <v>581</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>7</v>
+        <v>262</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>544</v>
+        <v>582</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>179</v>
+        <v>406</v>
+      </c>
+      <c r="F70" s="5">
+        <v>38123</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>76</v>
+        <v>266</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>486</v>
+        <v>542</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>654</v>
+        <v>7</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>488</v>
+        <v>543</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="F71" s="5">
-        <v>26015</v>
+        <v>8</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>557</v>
+        <v>485</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>654</v>
+        <v>486</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>334</v>
+        <v>487</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>217</v>
+        <v>488</v>
+      </c>
+      <c r="F72" s="5">
+        <v>26015</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>10</v>
+        <v>105</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="E73" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="E73" s="4" t="s">
+      <c r="F73" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="G73" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>591</v>
+        <v>332</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>654</v>
+        <v>7</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>592</v>
+        <v>333</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F74" s="5">
-        <v>20122</v>
+        <v>8</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>299</v>
+        <v>590</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>300</v>
+        <v>591</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>301</v>
+        <v>34</v>
       </c>
       <c r="F75" s="5">
-        <v>56025</v>
+        <v>20122</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>298</v>
+        <v>36</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>270</v>
+        <v>298</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>654</v>
+        <v>294</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>272</v>
+        <v>300</v>
+      </c>
+      <c r="F76" s="5">
+        <v>56025</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>10</v>
+        <v>297</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>374</v>
+        <v>269</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>654</v>
+        <v>7</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>375</v>
+        <v>270</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F77" s="5">
-        <v>20121</v>
+        <v>8</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>279</v>
+        <v>373</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>302</v>
+        <v>374</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>303</v>
+        <v>34</v>
       </c>
       <c r="F78" s="5">
-        <v>24060</v>
+        <v>20121</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>149</v>
+        <v>36</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>615</v>
+        <v>278</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>654</v>
+        <v>144</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>188</v>
+        <v>301</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>35</v>
+        <v>302</v>
       </c>
       <c r="F79" s="5">
-        <v>20158</v>
+        <v>24060</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>480</v>
+        <v>614</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>257</v>
+        <v>187</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F80" s="5">
-        <v>20121</v>
+        <v>20158</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>37</v>
+        <v>157</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>174</v>
+        <v>479</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>156</v>
+        <v>256</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>157</v>
+        <v>34</v>
+      </c>
+      <c r="F81" s="5">
+        <v>20121</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>158</v>
+        <v>36</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B82" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D82" s="4" t="s">
+      <c r="E82" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F82" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="E82" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F82" s="5" t="s">
+      <c r="G82" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>252</v>
+        <v>154</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>229</v>
+        <v>155</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>230</v>
+        <v>156</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>438</v>
+        <v>657</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>654</v>
+        <v>290</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>439</v>
+        <v>658</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>35</v>
+        <v>292</v>
       </c>
       <c r="F84" s="5">
-        <v>20122</v>
+        <v>60035</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>37</v>
+        <v>163</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>247</v>
+        <v>34</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>249</v>
+        <v>134</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>250</v>
+        <v>437</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>251</v>
+        <v>438</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>236</v>
+        <v>34</v>
+      </c>
+      <c r="F86" s="5">
+        <v>20122</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>361</v>
+        <v>243</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>654</v>
+        <v>244</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>363</v>
+        <v>245</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="F87" s="5">
-        <v>76123</v>
+        <v>246</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>247</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>43</v>
+        <v>248</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>424</v>
+        <v>249</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>654</v>
+        <v>77</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F88" s="5">
-        <v>39100</v>
+        <v>79</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>550</v>
+        <v>360</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>654</v>
+        <v>361</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>552</v>
+        <v>362</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>553</v>
-      </c>
-      <c r="F89" s="8" t="s">
-        <v>554</v>
+        <v>363</v>
+      </c>
+      <c r="F89" s="5">
+        <v>76123</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>647</v>
+        <v>423</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>654</v>
+        <v>26</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>648</v>
+        <v>130</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F90" s="8" t="s">
-        <v>179</v>
+        <v>28</v>
+      </c>
+      <c r="F90" s="5">
+        <v>39100</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>390</v>
+        <v>549</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>654</v>
+        <v>550</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>391</v>
+        <v>551</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F91" s="5">
-        <v>70043</v>
+        <v>552</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>553</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>218</v>
+        <v>646</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>654</v>
+        <v>7</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>219</v>
+        <v>647</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>36</v>
+        <v>8</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>49</v>
+        <v>389</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>654</v>
+        <v>38</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>46</v>
+        <v>390</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>48</v>
+        <v>40</v>
+      </c>
+      <c r="F93" s="5">
+        <v>70043</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>50</v>
+        <v>217</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>51</v>
+        <v>218</v>
       </c>
       <c r="E94" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F94" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F94" s="5" t="s">
-        <v>52</v>
-      </c>
       <c r="G94" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>654</v>
+        <v>44</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>121</v>
+        <v>45</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>370</v>
+        <v>122</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>372</v>
+        <v>120</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="F98" s="5">
-        <v>61121</v>
+        <v>34</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>164</v>
+        <v>36</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>200</v>
+        <v>128</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>188</v>
+        <v>120</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>189</v>
+        <v>56</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>158</v>
+        <v>36</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>505</v>
+        <v>369</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>654</v>
+        <v>370</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>507</v>
+        <v>371</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>506</v>
+        <v>372</v>
       </c>
       <c r="F100" s="5">
-        <v>35010</v>
+        <v>61121</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>504</v>
+        <v>163</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>280</v>
+        <v>662</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>304</v>
+        <v>187</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F101" s="5">
-        <v>20123</v>
+        <v>20158</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>37</v>
+        <v>157</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>564</v>
+        <v>199</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>563</v>
+        <v>187</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F102" s="5">
-        <v>20122</v>
+        <v>34</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>37</v>
+        <v>157</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>350</v>
+        <v>504</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>654</v>
+        <v>507</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>352</v>
+        <v>506</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>353</v>
+        <v>505</v>
       </c>
       <c r="F103" s="5">
-        <v>15033</v>
+        <v>35010</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>82</v>
+        <v>503</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>350</v>
+        <v>279</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>352</v>
+        <v>303</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>353</v>
+        <v>34</v>
       </c>
       <c r="F104" s="5">
-        <v>15033</v>
+        <v>20123</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>350</v>
+        <v>563</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>352</v>
+        <v>562</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>353</v>
+        <v>34</v>
       </c>
       <c r="F105" s="5">
-        <v>15033</v>
+        <v>20122</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>534</v>
+        <v>349</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>654</v>
+        <v>350</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>535</v>
+        <v>351</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>118</v>
+        <v>352</v>
       </c>
       <c r="F106" s="5">
-        <v>65127</v>
+        <v>15033</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>58</v>
+        <v>349</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C107" s="4" t="s">
-        <v>654</v>
+        <v>350</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>59</v>
+        <v>351</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>60</v>
+        <v>352</v>
+      </c>
+      <c r="F107" s="5">
+        <v>15033</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>654</v>
+        <v>350</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="F108" s="5">
-        <v>10153</v>
+        <v>15033</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>429</v>
+        <v>533</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C109" s="4" t="s">
-        <v>654</v>
+        <v>115</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>336</v>
+        <v>534</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="F109" s="5">
-        <v>10153</v>
+        <v>65127</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>572</v>
+        <v>57</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>573</v>
+        <v>58</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F110" s="5">
-        <v>20154</v>
+        <v>34</v>
+      </c>
+      <c r="F110" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>158</v>
+        <v>36</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>281</v>
+        <v>334</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>654</v>
+        <v>77</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>305</v>
+        <v>335</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="F111" s="5">
-        <v>183</v>
+        <v>10153</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>306</v>
+        <v>81</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>209</v>
+        <v>428</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>654</v>
+        <v>77</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>210</v>
+        <v>335</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>57</v>
+        <v>79</v>
+      </c>
+      <c r="F112" s="5">
+        <v>10153</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>548</v>
+        <v>571</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>549</v>
+        <v>572</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F113" s="5">
         <v>20154</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>654</v>
+        <v>7</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>275</v>
+        <v>304</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>157</v>
+        <v>8</v>
+      </c>
+      <c r="F114" s="5">
+        <v>183</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>158</v>
+        <v>305</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>127</v>
+        <v>208</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>128</v>
+        <v>209</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>241</v>
+        <v>547</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>128</v>
+        <v>548</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F116" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
+      </c>
+      <c r="F116" s="5">
+        <v>20154</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>31</v>
+        <v>157</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>413</v>
+        <v>273</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>414</v>
+        <v>274</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>76</v>
+        <v>157</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>273</v>
+        <v>126</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>654</v>
+        <v>26</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D118" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E118" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E118" s="4" t="s">
+      <c r="F118" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F118" s="5" t="s">
+      <c r="G118" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="G118" s="4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>654</v>
+        <v>26</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>238</v>
+        <v>127</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>239</v>
+        <v>28</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>240</v>
+        <v>29</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>149</v>
+        <v>30</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>597</v>
+        <v>412</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>654</v>
+        <v>7</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>598</v>
+        <v>413</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F120" s="5">
-        <v>20122</v>
+        <v>8</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>178</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>536</v>
+        <v>272</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>537</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>654</v>
+        <v>26</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>538</v>
+        <v>27</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="F121" s="5">
-        <v>34133</v>
+        <v>28</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>513</v>
+        <v>30</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>434</v>
+        <v>236</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>654</v>
+        <v>144</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>128</v>
+        <v>237</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F122" s="5">
-        <v>39100</v>
+        <v>238</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>239</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>31</v>
+        <v>148</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>650</v>
+        <v>596</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>651</v>
+        <v>597</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F123" s="5">
-        <v>20121</v>
+        <v>20122</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>205</v>
+        <v>535</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>654</v>
+        <v>536</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>59</v>
+        <v>537</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>60</v>
+        <v>538</v>
+      </c>
+      <c r="F124" s="5">
+        <v>34133</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>37</v>
+        <v>512</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>365</v>
+        <v>433</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>654</v>
+        <v>26</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F125" s="5">
-        <v>20123</v>
+        <v>39100</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>100</v>
+        <v>649</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>59</v>
+        <v>650</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F126" s="5" t="s">
-        <v>60</v>
+        <v>34</v>
+      </c>
+      <c r="F126" s="5">
+        <v>20121</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>492</v>
+        <v>204</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>493</v>
+        <v>58</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F127" s="8" t="s">
-        <v>272</v>
+        <v>34</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>518</v>
+        <v>364</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>519</v>
+        <v>58</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="F128" s="5">
-        <v>80121</v>
+        <v>20123</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>405</v>
+        <v>99</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>406</v>
+        <v>58</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="F129" s="5">
-        <v>38121</v>
+        <v>34</v>
+      </c>
+      <c r="F129" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>267</v>
+        <v>36</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>368</v>
+        <v>491</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>654</v>
+        <v>7</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>369</v>
+        <v>492</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F130" s="5">
-        <v>20123</v>
+        <v>8</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>359</v>
+        <v>517</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>654</v>
+        <v>67</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>360</v>
+        <v>518</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="F131" s="5">
-        <v>90139</v>
+        <v>80121</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>344</v>
+        <v>404</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>654</v>
+        <v>262</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>194</v>
+        <v>405</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>35</v>
+        <v>406</v>
       </c>
       <c r="F132" s="5">
-        <v>20123</v>
+        <v>38121</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>37</v>
+        <v>266</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>454</v>
+        <v>367</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>455</v>
+        <v>368</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F133" s="8" t="s">
-        <v>179</v>
+        <v>34</v>
+      </c>
+      <c r="F133" s="5">
+        <v>20123</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>654</v>
+        <v>15</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>308</v>
+        <v>359</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>309</v>
+        <v>17</v>
       </c>
       <c r="F134" s="5">
-        <v>12037</v>
+        <v>90139</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>306</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>12</v>
+        <v>343</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>13</v>
+        <v>193</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F135" s="5" t="s">
-        <v>14</v>
+        <v>34</v>
+      </c>
+      <c r="F135" s="5">
+        <v>20123</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>122</v>
+        <v>453</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>654</v>
+        <v>7</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>54</v>
+        <v>454</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F136" s="5" t="s">
-        <v>30</v>
+        <v>8</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>53</v>
+        <v>281</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>654</v>
+        <v>306</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>54</v>
+        <v>307</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F137" s="5" t="s">
-        <v>30</v>
+        <v>308</v>
+      </c>
+      <c r="F137" s="5">
+        <v>12037</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>31</v>
+        <v>305</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="B138" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E138" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C138" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D138" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E138" s="4" t="s">
+      <c r="F138" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G138" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="G138" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>652</v>
+        <v>121</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>654</v>
+        <v>26</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>653</v>
+        <v>53</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F139" s="5">
-        <v>20124</v>
+        <v>28</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B140" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B140" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>654</v>
+      <c r="C140" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D140" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E140" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E140" s="4" t="s">
+      <c r="F140" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F140" s="5" t="s">
+      <c r="G140" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>497</v>
+        <v>72</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>654</v>
+        <v>7</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F141" s="5">
-        <v>39100</v>
+        <v>8</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>232</v>
+        <v>651</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>233</v>
+        <v>652</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>217</v>
+        <v>34</v>
+      </c>
+      <c r="F142" s="5">
+        <v>20124</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>10</v>
+        <v>157</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>589</v>
+        <v>676</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>654</v>
+        <v>350</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>590</v>
+        <v>677</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>35</v>
+        <v>678</v>
       </c>
       <c r="F143" s="5">
-        <v>20122</v>
+        <v>15079</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>37</v>
+        <v>679</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>187</v>
+        <v>25</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>654</v>
+        <v>26</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>188</v>
+        <v>27</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>189</v>
+        <v>29</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>654</v>
+        <v>26</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>484</v>
+        <v>27</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>485</v>
+        <v>28</v>
       </c>
       <c r="F145" s="5">
-        <v>66020</v>
+        <v>39100</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>620</v>
+        <v>231</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>654</v>
+        <v>7</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>484</v>
+        <v>232</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>485</v>
-      </c>
-      <c r="F146" s="5">
-        <v>66020</v>
+        <v>8</v>
+      </c>
+      <c r="F146" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>575</v>
+        <v>588</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>576</v>
+        <v>589</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F147" s="5">
-        <v>20124</v>
+        <v>20122</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>158</v>
+        <v>36</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>410</v>
+        <v>186</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>411</v>
+        <v>187</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="F148" s="5">
-        <v>37137</v>
+        <v>34</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>342</v>
+        <v>157</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>459</v>
+        <v>481</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C149" s="4" t="s">
-        <v>654</v>
+        <v>482</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F149" s="8" t="s">
-        <v>217</v>
+        <v>484</v>
+      </c>
+      <c r="F149" s="5">
+        <v>66020</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>10</v>
+        <v>75</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>294</v>
+        <v>619</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="C150" s="4" t="s">
-        <v>654</v>
+        <v>482</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>296</v>
+        <v>483</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>297</v>
+        <v>484</v>
       </c>
       <c r="F150" s="5">
-        <v>56010</v>
+        <v>66020</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>298</v>
+        <v>75</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>602</v>
+        <v>574</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C151" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>603</v>
+        <v>575</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F151" s="5">
-        <v>20145</v>
+        <v>20124</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>310</v>
+        <v>409</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>654</v>
+        <v>339</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>311</v>
+        <v>410</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>312</v>
+        <v>411</v>
       </c>
       <c r="F152" s="5">
-        <v>40060</v>
+        <v>37137</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>25</v>
+        <v>341</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>383</v>
+        <v>458</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C153" s="4" t="s">
-        <v>654</v>
+        <v>7</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>384</v>
+        <v>459</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F153" s="5">
-        <v>20121</v>
+        <v>8</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>216</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>385</v>
+        <v>293</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>654</v>
+        <v>294</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>384</v>
+        <v>295</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>57</v>
+        <v>296</v>
+      </c>
+      <c r="F154" s="5">
+        <v>56010</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>37</v>
+        <v>297</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>212</v>
+        <v>601</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C155" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>178</v>
+        <v>602</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F155" s="5" t="s">
-        <v>179</v>
+        <v>34</v>
+      </c>
+      <c r="F155" s="5">
+        <v>20145</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>76</v>
+        <v>134</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>574</v>
+        <v>309</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C156" s="4" t="s">
-        <v>654</v>
+        <v>20</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>191</v>
+        <v>310</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>35</v>
+        <v>311</v>
       </c>
       <c r="F156" s="5">
-        <v>20124</v>
+        <v>40060</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>158</v>
+        <v>24</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>588</v>
+        <v>382</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C157" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>191</v>
+        <v>383</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F157" s="5">
-        <v>20124</v>
+        <v>20121</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>158</v>
+        <v>36</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>630</v>
+        <v>384</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>631</v>
+        <v>383</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="F158" s="5">
-        <v>39025</v>
+        <v>34</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>67</v>
+        <v>211</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C159" s="4" t="s">
-        <v>654</v>
+        <v>7</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>69</v>
+        <v>177</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>71</v>
+        <v>178</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>283</v>
+        <v>573</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>314</v>
+        <v>190</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>315</v>
+        <v>34</v>
       </c>
       <c r="F160" s="5">
-        <v>57021</v>
+        <v>20124</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>298</v>
+        <v>157</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>183</v>
+        <v>587</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C161" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F161" s="5" t="s">
-        <v>179</v>
+        <v>34</v>
+      </c>
+      <c r="F161" s="5">
+        <v>20124</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>76</v>
+        <v>157</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>461</v>
+        <v>629</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>654</v>
+        <v>26</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>178</v>
+        <v>630</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F162" s="8" t="s">
-        <v>179</v>
+        <v>631</v>
+      </c>
+      <c r="F162" s="5">
+        <v>39025</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C163" s="4" t="s">
-        <v>654</v>
+        <v>67</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>345</v>
+        <v>282</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C164" s="4" t="s">
-        <v>654</v>
+        <v>312</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>346</v>
+        <v>313</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>347</v>
+        <v>314</v>
       </c>
       <c r="F164" s="5">
-        <v>70124</v>
+        <v>57021</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>43</v>
+        <v>297</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>332</v>
+        <v>182</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C165" s="4" t="s">
-        <v>654</v>
+        <v>7</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F165" s="5">
-        <v>20158</v>
+        <v>8</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>178</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>158</v>
+        <v>75</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>645</v>
+        <v>460</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C166" s="4" t="s">
-        <v>654</v>
+        <v>7</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>646</v>
+        <v>177</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F166" s="5">
-        <v>39100</v>
+        <v>8</v>
+      </c>
+      <c r="F166" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>356</v>
+        <v>87</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="C167" s="4" t="s">
-        <v>654</v>
+        <v>88</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>357</v>
+        <v>89</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="F167" s="5">
-        <v>12084</v>
+        <v>90</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>306</v>
+        <v>92</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>193</v>
+        <v>344</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C168" s="4" t="s">
-        <v>654</v>
+        <v>38</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>194</v>
+        <v>345</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>60</v>
+        <v>346</v>
+      </c>
+      <c r="F168" s="5">
+        <v>70124</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>226</v>
+        <v>331</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C169" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
+      </c>
+      <c r="F169" s="5">
+        <v>20158</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>37</v>
+        <v>157</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>456</v>
+        <v>644</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C170" s="4" t="s">
-        <v>654</v>
+        <v>26</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>457</v>
+        <v>645</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F170" s="8" t="s">
-        <v>458</v>
+        <v>28</v>
+      </c>
+      <c r="F170" s="5">
+        <v>39100</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>107</v>
+        <v>355</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C171" s="4" t="s">
-        <v>654</v>
+        <v>306</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>109</v>
+        <v>356</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="F171" s="5" t="s">
-        <v>111</v>
+        <v>357</v>
+      </c>
+      <c r="F171" s="5">
+        <v>12084</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>112</v>
+        <v>305</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>430</v>
+        <v>192</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="C172" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>431</v>
+        <v>193</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="F172" s="5">
-        <v>12100</v>
+        <v>34</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>306</v>
+        <v>36</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>394</v>
+        <v>225</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C173" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>22</v>
+        <v>226</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F173" s="5">
-        <v>40127</v>
+        <v>34</v>
+      </c>
+      <c r="F173" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>610</v>
+        <v>455</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>654</v>
+        <v>7</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>611</v>
+        <v>456</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F174" s="5">
-        <v>40122</v>
+        <v>8</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>457</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>354</v>
+        <v>106</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C175" s="4" t="s">
-        <v>654</v>
+        <v>107</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>355</v>
+        <v>108</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F175" s="5">
-        <v>20121</v>
+        <v>109</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>37</v>
+        <v>111</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>657</v>
+        <v>429</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C176" s="4" t="s">
-        <v>654</v>
+        <v>306</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>355</v>
+        <v>430</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>35</v>
+        <v>431</v>
       </c>
       <c r="F176" s="5">
-        <v>20121</v>
+        <v>12100</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>37</v>
+        <v>305</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>555</v>
+        <v>393</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C177" s="4" t="s">
-        <v>654</v>
+        <v>20</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>524</v>
+        <v>21</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F177" s="5">
-        <v>20154</v>
+        <v>40127</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>158</v>
+        <v>24</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>525</v>
+        <v>609</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C178" s="4" t="s">
-        <v>654</v>
+        <v>20</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>524</v>
+        <v>610</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F178" s="5">
-        <v>20154</v>
+        <v>40122</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>158</v>
+        <v>24</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>523</v>
+        <v>353</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C179" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>524</v>
+        <v>354</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F179" s="5">
-        <v>20154</v>
+        <v>20121</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>158</v>
+        <v>36</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>595</v>
+        <v>656</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C180" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>596</v>
+        <v>354</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F180" s="5">
-        <v>20154</v>
+        <v>20121</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>158</v>
+        <v>36</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>514</v>
+        <v>554</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C181" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>28</v>
+        <v>523</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F181" s="5">
-        <v>39100</v>
+        <v>20154</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>31</v>
+        <v>157</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>231</v>
+        <v>524</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C182" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>28</v>
+        <v>523</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
+      </c>
+      <c r="F182" s="5">
+        <v>20154</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>31</v>
+        <v>157</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>142</v>
+        <v>522</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C183" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>143</v>
+        <v>523</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F183" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
+      </c>
+      <c r="F183" s="5">
+        <v>20154</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>37</v>
+        <v>157</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>55</v>
+        <v>594</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C184" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>56</v>
+        <v>595</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F184" s="5" t="s">
-        <v>57</v>
+        <v>34</v>
+      </c>
+      <c r="F184" s="5">
+        <v>20154</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>37</v>
+        <v>157</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>440</v>
+        <v>513</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C185" s="4" t="s">
-        <v>654</v>
+        <v>26</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>441</v>
+        <v>27</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>442</v>
+        <v>28</v>
       </c>
       <c r="F185" s="5">
-        <v>20038</v>
+        <v>39100</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>135</v>
+        <v>30</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>425</v>
+        <v>230</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C186" s="4" t="s">
-        <v>654</v>
+        <v>26</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>235</v>
+        <v>27</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F186" s="5">
-        <v>10121</v>
+        <v>28</v>
+      </c>
+      <c r="F186" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C187" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>376</v>
+        <v>664</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="C188" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>378</v>
+        <v>665</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>379</v>
+        <v>34</v>
       </c>
       <c r="F188" s="5">
-        <v>64020</v>
+        <v>20123</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>579</v>
+        <v>54</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C189" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>580</v>
+        <v>55</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F189" s="12" t="s">
-        <v>581</v>
+        <v>34</v>
+      </c>
+      <c r="F189" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>409</v>
+        <v>439</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C190" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>210</v>
+        <v>440</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>35</v>
+        <v>441</v>
       </c>
       <c r="F190" s="10">
-        <v>20121</v>
+        <v>20038</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>132</v>
+        <v>424</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C191" s="4" t="s">
-        <v>654</v>
+        <v>77</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>133</v>
+        <v>234</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F191" s="10" t="s">
-        <v>134</v>
+        <v>79</v>
+      </c>
+      <c r="F191" s="10">
+        <v>10121</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>604</v>
+        <v>93</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C192" s="4" t="s">
-        <v>654</v>
+        <v>94</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>605</v>
+        <v>95</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F192" s="12" t="s">
-        <v>606</v>
+        <v>96</v>
+      </c>
+      <c r="F192" s="10" t="s">
+        <v>97</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>10</v>
+        <v>98</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
-        <v>256</v>
+        <v>375</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C193" s="4" t="s">
-        <v>654</v>
+        <v>376</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>257</v>
+        <v>377</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F193" s="10" t="s">
-        <v>57</v>
+        <v>378</v>
+      </c>
+      <c r="F193" s="10">
+        <v>64020</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
-        <v>339</v>
+        <v>578</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="C194" s="4" t="s">
-        <v>654</v>
+        <v>7</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>341</v>
+        <v>579</v>
       </c>
       <c r="E194" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="F194" s="10">
-        <v>37045</v>
+        <v>8</v>
+      </c>
+      <c r="F194" s="12" t="s">
+        <v>580</v>
       </c>
       <c r="G194" s="9" t="s">
-        <v>342</v>
+        <v>9</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
-        <v>165</v>
+        <v>408</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C195" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>166</v>
+        <v>209</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F195" s="10" t="s">
-        <v>167</v>
+        <v>34</v>
+      </c>
+      <c r="F195" s="10">
+        <v>20121</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>158</v>
+        <v>36</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
-        <v>528</v>
+        <v>131</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C196" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F196" s="10">
-        <v>20126</v>
+        <v>34</v>
+      </c>
+      <c r="F196" s="10" t="s">
+        <v>133</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C197" s="4" t="s">
-        <v>654</v>
+        <v>7</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F197" s="10">
-        <v>20138</v>
+        <v>8</v>
+      </c>
+      <c r="F197" s="12" t="s">
+        <v>605</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>608</v>
+        <v>255</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C198" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>609</v>
+        <v>256</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F198" s="10">
-        <v>20122</v>
+        <v>34</v>
+      </c>
+      <c r="F198" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>593</v>
+        <v>338</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C199" s="4" t="s">
-        <v>654</v>
+        <v>339</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>393</v>
+        <v>340</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>35</v>
+        <v>526</v>
       </c>
       <c r="F199" s="10">
-        <v>20123</v>
+        <v>37045</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>37</v>
+        <v>341</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
-        <v>470</v>
+        <v>164</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C200" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
       <c r="E200" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F200" s="10">
-        <v>20135</v>
+        <v>34</v>
+      </c>
+      <c r="F200" s="10" t="s">
+        <v>166</v>
       </c>
       <c r="G200" s="9" t="s">
-        <v>261</v>
+        <v>157</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A201" s="3" t="s">
-        <v>621</v>
-      </c>
-      <c r="B201" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C201" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D201" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E201" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F201" s="7">
-        <v>20135</v>
-      </c>
-      <c r="G201" s="3" t="s">
-        <v>261</v>
+      <c r="A201" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="B201" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D201" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="E201" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F201" s="10">
+        <v>20126</v>
+      </c>
+      <c r="G201" s="9" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A202" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="B202" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C202" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D202" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E202" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F202" s="7">
-        <v>20135</v>
-      </c>
-      <c r="G202" s="3" t="s">
-        <v>261</v>
+      <c r="A202" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="B202" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D202" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="E202" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F202" s="10">
+        <v>20138</v>
+      </c>
+      <c r="G202" s="9" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="9" t="s">
-        <v>404</v>
+        <v>607</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C203" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D203" s="9" t="s">
-        <v>259</v>
+        <v>608</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F203" s="10">
-        <v>20135</v>
+        <v>20122</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>261</v>
+        <v>36</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A204" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="B204" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C204" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D204" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="E204" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F204" s="7">
-        <v>85100</v>
-      </c>
-      <c r="G204" s="3" t="s">
-        <v>318</v>
+      <c r="A204" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="B204" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D204" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="E204" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F204" s="10">
+        <v>20123</v>
+      </c>
+      <c r="G204" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="9" t="s">
-        <v>203</v>
+        <v>469</v>
       </c>
       <c r="B205" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="C205" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D205" s="9" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="E205" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="F205" s="10" t="s">
-        <v>186</v>
+        <v>34</v>
+      </c>
+      <c r="F205" s="10">
+        <v>20135</v>
       </c>
       <c r="G205" s="9" t="s">
-        <v>318</v>
+        <v>260</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A206" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="B206" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C206" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D206" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="E206" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F206" s="10">
-        <v>20144</v>
-      </c>
-      <c r="G206" s="9" t="s">
-        <v>37</v>
+      <c r="A206" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F206" s="7">
+        <v>20135</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A207" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="B207" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C207" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D207" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="E207" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F207" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="G207" s="9" t="s">
-        <v>135</v>
+      <c r="A207" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F207" s="7">
+        <v>20135</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="9" t="s">
-        <v>284</v>
+        <v>403</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C208" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D208" s="9" t="s">
-        <v>316</v>
+        <v>258</v>
       </c>
       <c r="E208" s="9" t="s">
-        <v>317</v>
+        <v>34</v>
       </c>
       <c r="F208" s="10">
-        <v>40026</v>
+        <v>20135</v>
       </c>
       <c r="G208" s="9" t="s">
-        <v>25</v>
+        <v>260</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="3" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C209" s="4" t="s">
-        <v>654</v>
+        <v>183</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>638</v>
+        <v>184</v>
       </c>
       <c r="F209" s="7">
-        <v>20068</v>
+        <v>85100</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>261</v>
+        <v>317</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="9" t="s">
-        <v>285</v>
+        <v>202</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C210" s="4" t="s">
-        <v>654</v>
+        <v>183</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D210" s="9" t="s">
-        <v>319</v>
+        <v>203</v>
       </c>
       <c r="E210" s="9" t="s">
-        <v>9</v>
+        <v>184</v>
       </c>
       <c r="F210" s="10" t="s">
-        <v>322</v>
+        <v>185</v>
       </c>
       <c r="G210" s="9" t="s">
-        <v>10</v>
+        <v>317</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="9" t="s">
-        <v>532</v>
+        <v>451</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C211" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D211" s="9" t="s">
-        <v>28</v>
+        <v>452</v>
       </c>
       <c r="E211" s="9" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F211" s="10">
-        <v>39100</v>
+        <v>20144</v>
       </c>
       <c r="G211" s="9" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="9" t="s">
-        <v>366</v>
+        <v>221</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C212" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D212" s="9" t="s">
-        <v>367</v>
+        <v>222</v>
       </c>
       <c r="E212" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F212" s="10">
-        <v>20123</v>
+        <v>34</v>
+      </c>
+      <c r="F212" s="10" t="s">
+        <v>133</v>
       </c>
       <c r="G212" s="9" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="C213" s="4" t="s">
-        <v>654</v>
+        <v>20</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D213" s="9" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E213" s="9" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="F213" s="10">
-        <v>12020</v>
+        <v>40026</v>
       </c>
       <c r="G213" s="9" t="s">
-        <v>306</v>
+        <v>24</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A214" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B214" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C214" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D214" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E214" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F214" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G214" s="9" t="s">
-        <v>43</v>
+      <c r="A214" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="F214" s="7">
+        <v>20068</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="9" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="C215" s="4" t="s">
-        <v>654</v>
+        <v>7</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D215" s="9" t="s">
-        <v>422</v>
+        <v>318</v>
       </c>
       <c r="E215" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="F215" s="10">
-        <v>28053</v>
+        <v>8</v>
+      </c>
+      <c r="F215" s="10" t="s">
+        <v>321</v>
       </c>
       <c r="G215" s="9" t="s">
-        <v>135</v>
+        <v>9</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A216" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="B216" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C216" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D216" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E216" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="F216" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="G216" s="9" t="s">
-        <v>158</v>
+      <c r="A216" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F216" s="11" t="s">
+        <v>661</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
-        <v>559</v>
+        <v>531</v>
       </c>
       <c r="B217" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D217" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C217" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D217" s="9" t="s">
-        <v>560</v>
-      </c>
       <c r="E217" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F217" s="10">
         <v>39100</v>
       </c>
       <c r="G217" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="9" t="s">
-        <v>197</v>
+        <v>365</v>
       </c>
       <c r="B218" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C218" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D218" s="9" t="s">
-        <v>198</v>
+        <v>366</v>
       </c>
       <c r="E218" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F218" s="10" t="s">
-        <v>199</v>
+        <v>34</v>
+      </c>
+      <c r="F218" s="10">
+        <v>20123</v>
       </c>
       <c r="G218" s="9" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="9" t="s">
-        <v>206</v>
+        <v>285</v>
       </c>
       <c r="B219" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C219" s="4" t="s">
-        <v>654</v>
+        <v>306</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D219" s="9" t="s">
-        <v>207</v>
+        <v>319</v>
       </c>
       <c r="E219" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F219" s="10" t="s">
-        <v>208</v>
+        <v>320</v>
+      </c>
+      <c r="F219" s="10">
+        <v>12020</v>
       </c>
       <c r="G219" s="9" t="s">
-        <v>72</v>
+        <v>305</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="9" t="s">
-        <v>243</v>
+        <v>37</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C220" s="4" t="s">
-        <v>654</v>
+        <v>38</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D220" s="9" t="s">
-        <v>176</v>
+        <v>39</v>
       </c>
       <c r="E220" s="9" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F220" s="10" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="G220" s="9" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="9" t="s">
-        <v>533</v>
+        <v>419</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C221" s="4" t="s">
-        <v>654</v>
+        <v>420</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D221" s="9" t="s">
-        <v>176</v>
+        <v>421</v>
       </c>
       <c r="E221" s="9" t="s">
-        <v>35</v>
+        <v>422</v>
       </c>
       <c r="F221" s="10">
-        <v>20121</v>
+        <v>28053</v>
       </c>
       <c r="G221" s="9" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="9" t="s">
-        <v>577</v>
+        <v>170</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C222" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D222" s="9" t="s">
-        <v>578</v>
+        <v>167</v>
       </c>
       <c r="E222" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F222" s="10">
-        <v>20121</v>
+        <v>168</v>
+      </c>
+      <c r="F222" s="10" t="s">
+        <v>169</v>
       </c>
       <c r="G222" s="9" t="s">
-        <v>37</v>
+        <v>157</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="9" t="s">
-        <v>444</v>
+        <v>558</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="C223" s="4" t="s">
-        <v>654</v>
+        <v>26</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D223" s="9" t="s">
-        <v>446</v>
+        <v>559</v>
       </c>
       <c r="E223" s="9" t="s">
-        <v>447</v>
+        <v>28</v>
       </c>
       <c r="F223" s="10">
-        <v>53048</v>
+        <v>39100</v>
       </c>
       <c r="G223" s="9" t="s">
-        <v>448</v>
+        <v>30</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="9" t="s">
-        <v>515</v>
+        <v>196</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>508</v>
-      </c>
-      <c r="C224" s="4" t="s">
-        <v>654</v>
+        <v>20</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D224" s="9" t="s">
-        <v>516</v>
+        <v>197</v>
       </c>
       <c r="E224" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="F224" s="10">
-        <v>35011</v>
+        <v>22</v>
+      </c>
+      <c r="F224" s="10" t="s">
+        <v>198</v>
       </c>
       <c r="G224" s="9" t="s">
-        <v>504</v>
+        <v>24</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="9" t="s">
-        <v>242</v>
+        <v>205</v>
       </c>
       <c r="B225" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C225" s="4" t="s">
-        <v>654</v>
+        <v>67</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D225" s="9" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="E225" s="9" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="F225" s="10" t="s">
-        <v>57</v>
+        <v>207</v>
       </c>
       <c r="G225" s="9" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="9" t="s">
-        <v>130</v>
+        <v>242</v>
       </c>
       <c r="B226" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C226" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D226" s="9" t="s">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="E226" s="9" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F226" s="10" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="G226" s="9" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A227" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="B227" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C227" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D227" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E227" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F227" s="7">
-        <v>39100</v>
-      </c>
-      <c r="G227" s="3" t="s">
-        <v>31</v>
+      <c r="A227" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="B227" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D227" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E227" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F227" s="10">
+        <v>20121</v>
+      </c>
+      <c r="G227" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A228" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="B228" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C228" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D228" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="E228" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F228" s="7">
+      <c r="A228" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="B228" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D228" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="E228" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F228" s="10">
         <v>20121</v>
       </c>
       <c r="G228" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="9" t="s">
-        <v>530</v>
+        <v>443</v>
       </c>
       <c r="B229" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C229" s="4" t="s">
-        <v>654</v>
+        <v>444</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D229" s="9" t="s">
-        <v>531</v>
+        <v>445</v>
       </c>
       <c r="E229" s="9" t="s">
-        <v>35</v>
+        <v>446</v>
       </c>
       <c r="F229" s="10">
-        <v>20121</v>
+        <v>53048</v>
       </c>
       <c r="G229" s="9" t="s">
-        <v>37</v>
+        <v>447</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="9" t="s">
-        <v>20</v>
+        <v>514</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C230" s="4" t="s">
-        <v>654</v>
+        <v>507</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D230" s="9" t="s">
-        <v>22</v>
+        <v>515</v>
       </c>
       <c r="E230" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F230" s="10" t="s">
-        <v>24</v>
+        <v>516</v>
+      </c>
+      <c r="F230" s="10">
+        <v>35011</v>
       </c>
       <c r="G230" s="9" t="s">
-        <v>25</v>
+        <v>503</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A231" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="B231" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C231" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D231" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="E231" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F231" s="11" t="s">
-        <v>567</v>
-      </c>
-      <c r="G231" s="3" t="s">
-        <v>76</v>
+      <c r="A231" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="B231" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D231" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E231" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F231" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G231" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="9" t="s">
-        <v>380</v>
+        <v>129</v>
       </c>
       <c r="B232" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C232" s="4" t="s">
-        <v>654</v>
+        <v>26</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D232" s="9" t="s">
-        <v>381</v>
+        <v>130</v>
       </c>
       <c r="E232" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="F232" s="10">
-        <v>20089</v>
+        <v>28</v>
+      </c>
+      <c r="F232" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="G232" s="9" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A233" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="B233" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C233" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D233" s="9" t="s">
-        <v>475</v>
-      </c>
-      <c r="E233" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F233" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="G233" s="9" t="s">
-        <v>10</v>
+      <c r="A233" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F233" s="7">
+        <v>39100</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A234" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="B234" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C234" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D234" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="E234" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F234" s="10" t="s">
-        <v>202</v>
+      <c r="A234" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F234" s="7">
+        <v>20121</v>
       </c>
       <c r="G234" s="9" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="9" t="s">
-        <v>213</v>
+        <v>529</v>
       </c>
       <c r="B235" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C235" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D235" s="9" t="s">
-        <v>214</v>
+        <v>530</v>
       </c>
       <c r="E235" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F235" s="10" t="s">
-        <v>157</v>
+        <v>34</v>
+      </c>
+      <c r="F235" s="10">
+        <v>20121</v>
       </c>
       <c r="G235" s="9" t="s">
-        <v>158</v>
+        <v>36</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" s="9" t="s">
-        <v>437</v>
+        <v>19</v>
       </c>
       <c r="B236" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C236" s="4" t="s">
-        <v>654</v>
+        <v>20</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D236" s="9" t="s">
-        <v>214</v>
+        <v>21</v>
       </c>
       <c r="E236" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F236" s="10">
-        <v>20124</v>
+        <v>22</v>
+      </c>
+      <c r="F236" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="G236" s="9" t="s">
-        <v>158</v>
+        <v>24</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="3" t="s">
-        <v>634</v>
+        <v>564</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C237" s="4" t="s">
-        <v>654</v>
+        <v>7</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>635</v>
+        <v>565</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F237" s="7">
-        <v>24050</v>
+        <v>8</v>
+      </c>
+      <c r="F237" s="11" t="s">
+        <v>566</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="9" t="s">
-        <v>228</v>
+        <v>379</v>
       </c>
       <c r="B238" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C238" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D238" s="9" t="s">
-        <v>229</v>
+        <v>380</v>
       </c>
       <c r="E238" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F238" s="10" t="s">
-        <v>230</v>
+        <v>381</v>
+      </c>
+      <c r="F238" s="10">
+        <v>20089</v>
       </c>
       <c r="G238" s="9" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A239" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="B239" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C239" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D239" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E239" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F239" s="7">
-        <v>20148</v>
-      </c>
-      <c r="G239" s="3" t="s">
-        <v>135</v>
+      <c r="A239" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="B239" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D239" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="E239" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F239" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="G239" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="9" t="s">
-        <v>255</v>
+        <v>210</v>
       </c>
       <c r="B240" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C240" s="4" t="s">
-        <v>654</v>
+        <v>20</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D240" s="9" t="s">
-        <v>229</v>
+        <v>200</v>
       </c>
       <c r="E240" s="9" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F240" s="10" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="G240" s="9" t="s">
-        <v>135</v>
+        <v>24</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" s="9" t="s">
-        <v>471</v>
+        <v>212</v>
       </c>
       <c r="B241" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C241" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D241" s="9" t="s">
-        <v>463</v>
+        <v>213</v>
       </c>
       <c r="E241" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F241" s="10">
-        <v>20129</v>
+        <v>34</v>
+      </c>
+      <c r="F241" s="10" t="s">
+        <v>156</v>
       </c>
       <c r="G241" s="9" t="s">
-        <v>261</v>
+        <v>157</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A242" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="B242" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C242" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D242" s="9" t="s">
-        <v>463</v>
-      </c>
-      <c r="E242" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F242" s="10">
-        <v>20129</v>
-      </c>
-      <c r="G242" s="9" t="s">
-        <v>261</v>
+      <c r="A242" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E242" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F242" s="7">
+        <v>20124</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" s="9" t="s">
-        <v>472</v>
+        <v>436</v>
       </c>
       <c r="B243" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C243" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D243" s="9" t="s">
-        <v>463</v>
+        <v>213</v>
       </c>
       <c r="E243" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F243" s="10">
-        <v>20129</v>
+        <v>20124</v>
       </c>
       <c r="G243" s="9" t="s">
-        <v>261</v>
+        <v>157</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A244" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="B244" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C244" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D244" s="9" t="s">
-        <v>463</v>
-      </c>
-      <c r="E244" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F244" s="10">
-        <v>20129</v>
-      </c>
-      <c r="G244" s="9" t="s">
-        <v>261</v>
+      <c r="A244" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="E244" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F244" s="7">
+        <v>24050</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" s="9" t="s">
-        <v>175</v>
+        <v>227</v>
       </c>
       <c r="B245" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C245" s="4" t="s">
-        <v>654</v>
+        <v>32</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D245" s="9" t="s">
-        <v>176</v>
+        <v>228</v>
       </c>
       <c r="E245" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F245" s="10" t="s">
-        <v>57</v>
+        <v>229</v>
       </c>
       <c r="G245" s="9" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A246" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="B246" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C246" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D246" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="E246" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="F246" s="10">
-        <v>40026</v>
-      </c>
-      <c r="G246" s="9" t="s">
-        <v>25</v>
+      <c r="A246" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F246" s="7">
+        <v>20148</v>
+      </c>
+      <c r="G246" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" s="9" t="s">
-        <v>287</v>
+        <v>254</v>
       </c>
       <c r="B247" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C247" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D247" s="9" t="s">
-        <v>323</v>
+        <v>228</v>
       </c>
       <c r="E247" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F247" s="10">
-        <v>20124</v>
+        <v>34</v>
+      </c>
+      <c r="F247" s="10" t="s">
+        <v>229</v>
       </c>
       <c r="G247" s="9" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A248" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="B248" s="9" t="s">
-        <v>307</v>
+      <c r="A248" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D248" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="E248" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="F248" s="10">
-        <v>12011</v>
-      </c>
-      <c r="G248" s="9" t="s">
-        <v>306</v>
+        <v>653</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="F248" s="7">
+        <v>25055</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" s="3" t="s">
-        <v>624</v>
+        <v>672</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>33</v>
+        <v>673</v>
       </c>
       <c r="C249" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>625</v>
+        <v>674</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>35</v>
+        <v>675</v>
       </c>
       <c r="F249" s="7">
-        <v>20121</v>
+        <v>50132</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>37</v>
+        <v>447</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" s="9" t="s">
-        <v>150</v>
+        <v>470</v>
       </c>
       <c r="B250" s="9" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D250" s="9" t="s">
-        <v>152</v>
+        <v>462</v>
       </c>
       <c r="E250" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="F250" s="10" t="s">
-        <v>154</v>
+        <v>34</v>
+      </c>
+      <c r="F250" s="10">
+        <v>20129</v>
       </c>
       <c r="G250" s="9" t="s">
-        <v>43</v>
+        <v>260</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" s="9" t="s">
-        <v>418</v>
+        <v>461</v>
       </c>
       <c r="B251" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D251" s="9" t="s">
-        <v>419</v>
+        <v>462</v>
       </c>
       <c r="E251" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F251" s="10">
-        <v>20123</v>
+        <v>20129</v>
       </c>
       <c r="G251" s="9" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" s="9" t="s">
-        <v>490</v>
+        <v>471</v>
       </c>
       <c r="B252" s="9" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D252" s="9" t="s">
-        <v>491</v>
+        <v>462</v>
       </c>
       <c r="E252" s="9" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F252" s="10">
-        <v>90141</v>
+        <v>20129</v>
       </c>
       <c r="G252" s="9" t="s">
-        <v>11</v>
+        <v>260</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" s="9" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="B253" s="9" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C253" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D253" s="9" t="s">
-        <v>387</v>
+        <v>462</v>
       </c>
       <c r="E253" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F253" s="12" t="s">
-        <v>389</v>
+        <v>34</v>
+      </c>
+      <c r="F253" s="10">
+        <v>20129</v>
       </c>
       <c r="G253" s="9" t="s">
-        <v>10</v>
+        <v>260</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A254" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="B254" s="3" t="s">
-        <v>8</v>
+      <c r="A254" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B254" s="9" t="s">
+        <v>32</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D254" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="E254" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F254" s="11" t="s">
-        <v>389</v>
-      </c>
-      <c r="G254" s="3" t="s">
-        <v>10</v>
+        <v>653</v>
+      </c>
+      <c r="D254" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E254" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F254" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G254" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A255" s="3" t="s">
-        <v>529</v>
-      </c>
-      <c r="B255" s="3" t="s">
-        <v>8</v>
+      <c r="A255" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="B255" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="C255" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D255" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="E255" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F255" s="11" t="s">
-        <v>389</v>
-      </c>
-      <c r="G255" s="3" t="s">
-        <v>10</v>
+        <v>653</v>
+      </c>
+      <c r="D255" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="E255" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="F255" s="10">
+        <v>40026</v>
+      </c>
+      <c r="G255" s="9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" s="9" t="s">
-        <v>386</v>
+        <v>286</v>
       </c>
       <c r="B256" s="9" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D256" s="9" t="s">
-        <v>387</v>
+        <v>322</v>
       </c>
       <c r="E256" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F256" s="10" t="s">
-        <v>389</v>
+        <v>34</v>
+      </c>
+      <c r="F256" s="10">
+        <v>20124</v>
       </c>
       <c r="G256" s="9" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" s="9" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="B257" s="9" t="s">
-        <v>263</v>
+        <v>306</v>
       </c>
       <c r="C257" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D257" s="9" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="E257" s="9" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="F257" s="10">
-        <v>38055</v>
+        <v>12011</v>
       </c>
       <c r="G257" s="9" t="s">
-        <v>267</v>
+        <v>305</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" s="3" t="s">
-        <v>571</v>
+        <v>623</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>133</v>
+        <v>624</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F258" s="7">
-        <v>20145</v>
+        <v>20121</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" s="9" t="s">
-        <v>426</v>
+        <v>149</v>
       </c>
       <c r="B259" s="9" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="C259" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D259" s="9" t="s">
-        <v>427</v>
+        <v>151</v>
       </c>
       <c r="E259" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="F259" s="10">
-        <v>25010</v>
+        <v>152</v>
+      </c>
+      <c r="F259" s="10" t="s">
+        <v>153</v>
       </c>
       <c r="G259" s="9" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" s="9" t="s">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="B260" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D260" s="9" t="s">
-        <v>393</v>
+        <v>418</v>
       </c>
       <c r="E260" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F260" s="10">
         <v>20123</v>
       </c>
       <c r="G260" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A261" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="B261" s="3" t="s">
-        <v>33</v>
+      <c r="A261" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="B261" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="C261" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D261" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="E261" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F261" s="7">
-        <v>20123</v>
-      </c>
-      <c r="G261" s="3" t="s">
-        <v>37</v>
+        <v>653</v>
+      </c>
+      <c r="D261" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="E261" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F261" s="10">
+        <v>90141</v>
+      </c>
+      <c r="G261" s="9" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" s="9" t="s">
-        <v>415</v>
+        <v>478</v>
       </c>
       <c r="B262" s="9" t="s">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D262" s="9" t="s">
-        <v>416</v>
+        <v>386</v>
       </c>
       <c r="E262" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="F262" s="10">
-        <v>71016</v>
+        <v>8</v>
+      </c>
+      <c r="F262" s="12" t="s">
+        <v>388</v>
       </c>
       <c r="G262" s="9" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A263" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B263" s="9" t="s">
-        <v>16</v>
+      <c r="A263" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="C263" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D263" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E263" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F263" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G263" s="9" t="s">
-        <v>11</v>
+        <v>653</v>
+      </c>
+      <c r="D263" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="E263" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F263" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="G263" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" s="3" t="s">
-        <v>639</v>
+        <v>528</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>640</v>
+        <v>386</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F264" s="7">
-        <v>20123</v>
+        <v>8</v>
+      </c>
+      <c r="F264" s="11" t="s">
+        <v>388</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" s="9" t="s">
-        <v>324</v>
+        <v>385</v>
       </c>
       <c r="B265" s="9" t="s">
-        <v>325</v>
+        <v>7</v>
       </c>
       <c r="C265" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D265" s="9" t="s">
-        <v>326</v>
+        <v>386</v>
       </c>
       <c r="E265" s="9" t="s">
-        <v>327</v>
+        <v>8</v>
       </c>
       <c r="F265" s="10" t="s">
-        <v>328</v>
+        <v>388</v>
       </c>
       <c r="G265" s="9" t="s">
-        <v>329</v>
+        <v>9</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A266" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="B266" s="3" t="s">
-        <v>33</v>
+      <c r="A266" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="B266" s="9" t="s">
+        <v>262</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D266" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="E266" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F266" s="7">
-        <v>20122</v>
-      </c>
-      <c r="G266" s="3" t="s">
-        <v>37</v>
+        <v>653</v>
+      </c>
+      <c r="D266" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="E266" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="F266" s="10">
+        <v>38055</v>
+      </c>
+      <c r="G266" s="9" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A267" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="B267" s="9" t="s">
-        <v>33</v>
+      <c r="A267" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="C267" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D267" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="E267" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F267" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G267" s="9" t="s">
-        <v>37</v>
+        <v>653</v>
+      </c>
+      <c r="D267" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E267" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F267" s="7">
+        <v>20145</v>
+      </c>
+      <c r="G267" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A268" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="B268" s="3" t="s">
-        <v>33</v>
+      <c r="A268" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="B268" s="9" t="s">
+        <v>101</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D268" s="3" t="s">
-        <v>656</v>
-      </c>
-      <c r="E268" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F268" s="7">
-        <v>20123</v>
-      </c>
-      <c r="G268" s="3" t="s">
-        <v>37</v>
+        <v>653</v>
+      </c>
+      <c r="D268" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="E268" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="F268" s="10">
+        <v>25010</v>
+      </c>
+      <c r="G268" s="9" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" s="9" t="s">
-        <v>477</v>
+        <v>391</v>
       </c>
       <c r="B269" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C269" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D269" s="9" t="s">
-        <v>478</v>
+        <v>392</v>
       </c>
       <c r="E269" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F269" s="10">
         <v>20123</v>
       </c>
       <c r="G269" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" s="3" t="s">
-        <v>568</v>
+        <v>618</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>569</v>
+        <v>392</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>570</v>
+        <v>34</v>
       </c>
       <c r="F270" s="7">
-        <v>20094</v>
+        <v>20123</v>
       </c>
       <c r="G270" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" s="9" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="B271" s="9" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="C271" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D271" s="9" t="s">
-        <v>216</v>
+        <v>415</v>
       </c>
       <c r="E271" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F271" s="10" t="s">
-        <v>217</v>
+        <v>416</v>
+      </c>
+      <c r="F271" s="10">
+        <v>71016</v>
       </c>
       <c r="G271" s="9" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" s="9" t="s">
-        <v>215</v>
+        <v>14</v>
       </c>
       <c r="B272" s="9" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D272" s="9" t="s">
-        <v>216</v>
+        <v>16</v>
       </c>
       <c r="E272" s="9" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F272" s="10" t="s">
-        <v>217</v>
+        <v>18</v>
       </c>
       <c r="G272" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A273" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B273" s="9" t="s">
-        <v>160</v>
+      <c r="A273" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="B273" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="C273" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D273" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="E273" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="F273" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="G273" s="9" t="s">
-        <v>164</v>
+        <v>653</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="E273" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F273" s="7">
+        <v>20123</v>
+      </c>
+      <c r="G273" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" s="9" t="s">
-        <v>433</v>
+        <v>323</v>
       </c>
       <c r="B274" s="9" t="s">
-        <v>8</v>
+        <v>324</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D274" s="9" t="s">
-        <v>216</v>
+        <v>325</v>
       </c>
       <c r="E274" s="9" t="s">
-        <v>9</v>
+        <v>326</v>
       </c>
       <c r="F274" s="10" t="s">
-        <v>217</v>
+        <v>327</v>
       </c>
       <c r="G274" s="9" t="s">
-        <v>10</v>
+        <v>328</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A275" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="B275" s="9" t="s">
-        <v>8</v>
+      <c r="A275" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="C275" s="9" t="s">
-        <v>654</v>
-      </c>
-      <c r="D275" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="E275" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F275" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="G275" s="9" t="s">
-        <v>10</v>
+        <v>653</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="E275" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F275" s="7">
+        <v>20122</v>
+      </c>
+      <c r="G275" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="B276" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C276" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D276" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="E276" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F276" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G276" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A277" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C277" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D277" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="E277" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F277" s="7">
+        <v>20123</v>
+      </c>
+      <c r="G277" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A278" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="B278" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C278" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D278" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="E278" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F278" s="10">
+        <v>20123</v>
+      </c>
+      <c r="G278" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A279" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="B279" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C279" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="E279" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="F279" s="7">
+        <v>20094</v>
+      </c>
+      <c r="G279" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A280" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="B280" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C280" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D280" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="E280" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F280" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="G280" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A281" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B281" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C281" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D281" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="E281" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F281" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="G281" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A282" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B282" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C282" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D282" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E282" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F282" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="G282" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A283" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="B283" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C283" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D283" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="E283" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F283" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="G283" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A284" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="B284" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C284" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D284" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="E284" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F284" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="G284" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A285" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="B285" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C285" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D285" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B276" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C276" s="9" t="s">
-        <v>654</v>
-      </c>
-      <c r="D276" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="E276" s="9" t="s">
+      <c r="E285" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F285" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F276" s="10" t="s">
+      <c r="G285" s="9" t="s">
         <v>36</v>
-      </c>
-      <c r="G276" s="9" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G218" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G276">
+    <sortState ref="A2:G285">
       <sortCondition ref="A1:A218"/>
     </sortState>
   </autoFilter>
@@ -9076,16 +9349,16 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
     <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{E476BC05-A230-47B0-B1D0-9E9524B23A2E}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{3A2F71C2-38D5-4D3E-8211-48ED79184602}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1852" uniqueCount="683">
   <si>
     <t>Nome account</t>
   </si>
@@ -2063,6 +2063,15 @@
   </si>
   <si>
     <t>Genova</t>
+  </si>
+  <si>
+    <t>DS ITALIA 34 SRL</t>
+  </si>
+  <si>
+    <t>PV ITALY 1 SRL</t>
+  </si>
+  <si>
+    <t>VELINO SOLAR ITALY SRL</t>
   </si>
 </sst>
 </file>
@@ -2487,7 +2496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G285"/>
+  <dimension ref="A1:G288"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -4158,12 +4167,12 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>556</v>
+        <v>680</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D73" s="4" t="s">
@@ -4172,7 +4181,7 @@
       <c r="E73" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F73" s="8" t="s">
+      <c r="F73" s="5" t="s">
         <v>216</v>
       </c>
       <c r="G73" s="4" t="s">
@@ -4181,7 +4190,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>332</v>
+        <v>556</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>7</v>
@@ -4195,7 +4204,7 @@
       <c r="E74" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F74" s="5" t="s">
+      <c r="F74" s="8" t="s">
         <v>216</v>
       </c>
       <c r="G74" s="4" t="s">
@@ -4204,145 +4213,145 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>590</v>
+        <v>332</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>591</v>
+        <v>333</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F75" s="5">
-        <v>20122</v>
+        <v>8</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>298</v>
+        <v>590</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>294</v>
+        <v>32</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>299</v>
+        <v>591</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>300</v>
+        <v>34</v>
       </c>
       <c r="F76" s="5">
-        <v>56025</v>
+        <v>20122</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>297</v>
+        <v>36</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>7</v>
+        <v>294</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>270</v>
+        <v>299</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>271</v>
+        <v>300</v>
+      </c>
+      <c r="F77" s="5">
+        <v>56025</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>9</v>
+        <v>297</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>373</v>
+        <v>269</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>374</v>
+        <v>270</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F78" s="5">
-        <v>20121</v>
+        <v>8</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>278</v>
+        <v>373</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>301</v>
+        <v>374</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>302</v>
+        <v>34</v>
       </c>
       <c r="F79" s="5">
-        <v>24060</v>
+        <v>20121</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>614</v>
+        <v>278</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>187</v>
+        <v>301</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>34</v>
+        <v>302</v>
       </c>
       <c r="F80" s="5">
-        <v>20158</v>
+        <v>24060</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>479</v>
+        <v>614</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>32</v>
@@ -4351,21 +4360,21 @@
         <v>653</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>256</v>
+        <v>187</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F81" s="5">
-        <v>20121</v>
+        <v>20158</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>173</v>
+        <v>479</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>32</v>
@@ -4374,21 +4383,21 @@
         <v>653</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>155</v>
+        <v>256</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F82" s="5" t="s">
-        <v>156</v>
+      <c r="F82" s="5">
+        <v>20121</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>32</v>
@@ -4411,53 +4420,53 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>657</v>
+        <v>154</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>290</v>
+        <v>32</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>658</v>
+        <v>155</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="F84" s="5">
-        <v>60035</v>
+        <v>34</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>156</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>251</v>
+        <v>657</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>32</v>
+        <v>290</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>228</v>
+        <v>658</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>229</v>
+        <v>292</v>
+      </c>
+      <c r="F85" s="5">
+        <v>60035</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>437</v>
+        <v>251</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>32</v>
@@ -4466,151 +4475,151 @@
         <v>653</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>438</v>
+        <v>228</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F86" s="5">
-        <v>20122</v>
+      <c r="F86" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>36</v>
+        <v>134</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>243</v>
+        <v>437</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>244</v>
+        <v>32</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>245</v>
+        <v>438</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>247</v>
+        <v>34</v>
+      </c>
+      <c r="F87" s="5">
+        <v>20122</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>248</v>
+        <v>36</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>81</v>
+        <v>248</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>360</v>
+        <v>249</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>361</v>
+        <v>77</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>362</v>
+        <v>250</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="F89" s="5">
-        <v>76123</v>
+        <v>79</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>423</v>
+        <v>360</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>26</v>
+        <v>361</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>130</v>
+        <v>362</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>28</v>
+        <v>363</v>
       </c>
       <c r="F90" s="5">
-        <v>39100</v>
+        <v>76123</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>549</v>
+        <v>423</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>550</v>
+        <v>26</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>551</v>
+        <v>130</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="F91" s="8" t="s">
-        <v>553</v>
+        <v>28</v>
+      </c>
+      <c r="F91" s="5">
+        <v>39100</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>646</v>
+        <v>549</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>7</v>
+        <v>550</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>647</v>
+        <v>551</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>8</v>
+        <v>552</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>178</v>
+        <v>553</v>
       </c>
       <c r="G92" s="4" t="s">
         <v>75</v>
@@ -4618,99 +4627,99 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>389</v>
+        <v>646</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>390</v>
+        <v>647</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F93" s="5">
-        <v>70043</v>
+        <v>8</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>217</v>
+        <v>389</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>218</v>
+        <v>390</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
+      </c>
+      <c r="F94" s="5">
+        <v>70043</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>48</v>
+        <v>217</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>45</v>
+        <v>218</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>32</v>
@@ -4719,13 +4728,13 @@
         <v>653</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G97" s="4" t="s">
         <v>36</v>
@@ -4733,7 +4742,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>32</v>
@@ -4756,7 +4765,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>32</v>
@@ -4779,53 +4788,53 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>369</v>
+        <v>128</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>370</v>
+        <v>32</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>371</v>
+        <v>120</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="F100" s="5">
-        <v>61121</v>
+        <v>34</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>163</v>
+        <v>36</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>662</v>
+        <v>369</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>32</v>
+        <v>370</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>187</v>
+        <v>371</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>34</v>
+        <v>372</v>
       </c>
       <c r="F101" s="5">
-        <v>20158</v>
+        <v>61121</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>199</v>
+        <v>662</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>32</v>
@@ -4839,8 +4848,8 @@
       <c r="E102" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F102" s="5" t="s">
-        <v>188</v>
+      <c r="F102" s="5">
+        <v>20158</v>
       </c>
       <c r="G102" s="4" t="s">
         <v>157</v>
@@ -4848,53 +4857,53 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>504</v>
+        <v>199</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>507</v>
+        <v>32</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>506</v>
+        <v>187</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="F103" s="5">
-        <v>35010</v>
+        <v>34</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>503</v>
+        <v>157</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>279</v>
+        <v>504</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>32</v>
+        <v>507</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>303</v>
+        <v>506</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>34</v>
+        <v>505</v>
       </c>
       <c r="F104" s="5">
-        <v>20123</v>
+        <v>35010</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>36</v>
+        <v>503</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>563</v>
+        <v>279</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>32</v>
@@ -4903,13 +4912,13 @@
         <v>653</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>562</v>
+        <v>303</v>
       </c>
       <c r="E105" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F105" s="5">
-        <v>20122</v>
+        <v>20123</v>
       </c>
       <c r="G105" s="4" t="s">
         <v>36</v>
@@ -4917,25 +4926,25 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>349</v>
+        <v>563</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>350</v>
+        <v>32</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>351</v>
+        <v>562</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="F106" s="5">
-        <v>15033</v>
+        <v>20122</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
@@ -4986,76 +4995,76 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>533</v>
+        <v>349</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>115</v>
+        <v>350</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>534</v>
+        <v>351</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>117</v>
+        <v>352</v>
       </c>
       <c r="F109" s="5">
-        <v>65127</v>
+        <v>15033</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>57</v>
+        <v>533</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>58</v>
+        <v>534</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F110" s="5" t="s">
-        <v>59</v>
+        <v>117</v>
+      </c>
+      <c r="F110" s="5">
+        <v>65127</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>334</v>
+        <v>57</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>335</v>
+        <v>58</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F111" s="5">
-        <v>10153</v>
+        <v>34</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>428</v>
+        <v>334</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>77</v>
@@ -5078,76 +5087,76 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>571</v>
+        <v>428</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>572</v>
+        <v>335</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="F113" s="5">
-        <v>20154</v>
+        <v>10153</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>280</v>
+        <v>571</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>304</v>
+        <v>572</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F114" s="5">
-        <v>183</v>
+        <v>20154</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>305</v>
+        <v>157</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>208</v>
+        <v>280</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>209</v>
+        <v>304</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F115" s="5" t="s">
-        <v>56</v>
+        <v>8</v>
+      </c>
+      <c r="F115" s="5">
+        <v>183</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>36</v>
+        <v>305</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>547</v>
+        <v>208</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>32</v>
@@ -5156,21 +5165,21 @@
         <v>653</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>548</v>
+        <v>209</v>
       </c>
       <c r="E116" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F116" s="5">
-        <v>20154</v>
+      <c r="F116" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>273</v>
+        <v>547</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>32</v>
@@ -5179,13 +5188,13 @@
         <v>653</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>274</v>
+        <v>548</v>
       </c>
       <c r="E117" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F117" s="5" t="s">
-        <v>156</v>
+      <c r="F117" s="5">
+        <v>20154</v>
       </c>
       <c r="G117" s="4" t="s">
         <v>157</v>
@@ -5193,30 +5202,30 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>126</v>
+        <v>273</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>127</v>
+        <v>274</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>29</v>
+        <v>156</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>240</v>
+        <v>126</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>26</v>
@@ -5239,168 +5248,168 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>412</v>
+        <v>240</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>413</v>
+        <v>127</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>178</v>
+        <v>29</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>272</v>
+        <v>412</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>27</v>
+        <v>413</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>29</v>
+        <v>178</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>144</v>
+        <v>26</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>237</v>
+        <v>27</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>238</v>
+        <v>28</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>239</v>
+        <v>29</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>148</v>
+        <v>30</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>596</v>
+        <v>236</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>597</v>
+        <v>237</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F123" s="5">
-        <v>20122</v>
+        <v>238</v>
+      </c>
+      <c r="F123" s="5" t="s">
+        <v>239</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>36</v>
+        <v>148</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>535</v>
+        <v>596</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>536</v>
+        <v>32</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>537</v>
+        <v>597</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>538</v>
+        <v>34</v>
       </c>
       <c r="F124" s="5">
-        <v>34133</v>
+        <v>20122</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>512</v>
+        <v>36</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>433</v>
+        <v>535</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>26</v>
+        <v>536</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>127</v>
+        <v>537</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>28</v>
+        <v>538</v>
       </c>
       <c r="F125" s="5">
-        <v>39100</v>
+        <v>34133</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>30</v>
+        <v>512</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>649</v>
+        <v>433</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>650</v>
+        <v>127</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F126" s="5">
-        <v>20121</v>
+        <v>39100</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>204</v>
+        <v>649</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>32</v>
@@ -5409,13 +5418,13 @@
         <v>653</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>58</v>
+        <v>650</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F127" s="5" t="s">
-        <v>59</v>
+      <c r="F127" s="5">
+        <v>20121</v>
       </c>
       <c r="G127" s="4" t="s">
         <v>36</v>
@@ -5423,7 +5432,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>364</v>
+        <v>204</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>32</v>
@@ -5437,8 +5446,8 @@
       <c r="E128" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F128" s="5">
-        <v>20123</v>
+      <c r="F128" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G128" s="4" t="s">
         <v>36</v>
@@ -5446,7 +5455,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>99</v>
+        <v>364</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>32</v>
@@ -5460,8 +5469,8 @@
       <c r="E129" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F129" s="5" t="s">
-        <v>59</v>
+      <c r="F129" s="5">
+        <v>20123</v>
       </c>
       <c r="G129" s="4" t="s">
         <v>36</v>
@@ -5469,237 +5478,237 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>491</v>
+        <v>99</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>492</v>
+        <v>58</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F130" s="8" t="s">
-        <v>271</v>
+        <v>34</v>
+      </c>
+      <c r="F130" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>518</v>
+        <v>492</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F131" s="5">
-        <v>80121</v>
+        <v>8</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>404</v>
+        <v>517</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>262</v>
+        <v>67</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>405</v>
+        <v>518</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>406</v>
+        <v>69</v>
       </c>
       <c r="F132" s="5">
-        <v>38121</v>
+        <v>80121</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>266</v>
+        <v>71</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>367</v>
+        <v>404</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>32</v>
+        <v>262</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>34</v>
+        <v>406</v>
       </c>
       <c r="F133" s="5">
-        <v>20123</v>
+        <v>38121</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>36</v>
+        <v>266</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F134" s="5">
-        <v>90139</v>
+        <v>20123</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>193</v>
+        <v>359</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F135" s="5">
-        <v>20123</v>
+        <v>90139</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>453</v>
+        <v>343</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>454</v>
+        <v>193</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F136" s="8" t="s">
-        <v>178</v>
+        <v>34</v>
+      </c>
+      <c r="F136" s="5">
+        <v>20123</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>281</v>
+        <v>453</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>306</v>
+        <v>7</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>307</v>
+        <v>454</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="F137" s="5">
-        <v>12037</v>
+        <v>8</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>305</v>
+        <v>75</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>11</v>
+        <v>281</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>7</v>
+        <v>306</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>12</v>
+        <v>307</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>13</v>
+        <v>308</v>
+      </c>
+      <c r="F138" s="5">
+        <v>12037</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>9</v>
+        <v>305</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>121</v>
+        <v>11</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="B140" s="4" t="s">
         <v>26</v>
@@ -5722,99 +5731,99 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>651</v>
+        <v>72</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>652</v>
+        <v>73</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F142" s="5">
-        <v>20124</v>
+        <v>8</v>
+      </c>
+      <c r="F142" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>676</v>
+        <v>651</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>350</v>
+        <v>32</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>677</v>
+        <v>652</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>678</v>
+        <v>34</v>
       </c>
       <c r="F143" s="5">
-        <v>15079</v>
+        <v>20124</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>679</v>
+        <v>157</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>25</v>
+        <v>676</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>26</v>
+        <v>350</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>27</v>
+        <v>677</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>29</v>
+        <v>678</v>
+      </c>
+      <c r="F144" s="5">
+        <v>15079</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>30</v>
+        <v>679</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>496</v>
+        <v>25</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>26</v>
@@ -5828,8 +5837,8 @@
       <c r="E145" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F145" s="5">
-        <v>39100</v>
+      <c r="F145" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G145" s="4" t="s">
         <v>30</v>
@@ -5837,53 +5846,53 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>231</v>
+        <v>496</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>232</v>
+        <v>27</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>216</v>
+        <v>28</v>
+      </c>
+      <c r="F146" s="5">
+        <v>39100</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>588</v>
+        <v>231</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>589</v>
+        <v>232</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F147" s="5">
-        <v>20122</v>
+        <v>8</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>186</v>
+        <v>588</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>32</v>
@@ -5892,44 +5901,44 @@
         <v>653</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>187</v>
+        <v>589</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F148" s="5" t="s">
-        <v>188</v>
+      <c r="F148" s="5">
+        <v>20122</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>481</v>
+        <v>186</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>482</v>
+        <v>32</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>483</v>
+        <v>187</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="F149" s="5">
-        <v>66020</v>
+        <v>34</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>75</v>
+        <v>157</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>619</v>
+        <v>481</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>482</v>
@@ -5952,168 +5961,168 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>574</v>
+        <v>619</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>32</v>
+        <v>482</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>575</v>
+        <v>483</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>34</v>
+        <v>484</v>
       </c>
       <c r="F151" s="5">
-        <v>20124</v>
+        <v>66020</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>409</v>
+        <v>574</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>339</v>
+        <v>32</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>410</v>
+        <v>575</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="F152" s="5">
-        <v>37137</v>
+        <v>20124</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>341</v>
+        <v>157</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>458</v>
+        <v>409</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>7</v>
+        <v>339</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>459</v>
+        <v>410</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F153" s="8" t="s">
-        <v>216</v>
+        <v>411</v>
+      </c>
+      <c r="F153" s="5">
+        <v>37137</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>9</v>
+        <v>341</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>293</v>
+        <v>458</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>294</v>
+        <v>7</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>295</v>
+        <v>459</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="F154" s="5">
-        <v>56010</v>
+        <v>8</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>216</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>297</v>
+        <v>9</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>601</v>
+        <v>293</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>32</v>
+        <v>294</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>602</v>
+        <v>295</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="F155" s="5">
-        <v>20145</v>
+        <v>56010</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>134</v>
+        <v>297</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>309</v>
+        <v>601</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>310</v>
+        <v>602</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>311</v>
+        <v>34</v>
       </c>
       <c r="F156" s="5">
-        <v>40060</v>
+        <v>20145</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>382</v>
+        <v>309</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>383</v>
+        <v>310</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>34</v>
+        <v>311</v>
       </c>
       <c r="F157" s="5">
-        <v>20121</v>
+        <v>40060</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>32</v>
@@ -6127,8 +6136,8 @@
       <c r="E158" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F158" s="5" t="s">
-        <v>56</v>
+      <c r="F158" s="5">
+        <v>20121</v>
       </c>
       <c r="G158" s="4" t="s">
         <v>36</v>
@@ -6136,53 +6145,53 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>211</v>
+        <v>384</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>177</v>
+        <v>383</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>178</v>
+        <v>56</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>573</v>
+        <v>211</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F160" s="5">
-        <v>20124</v>
+        <v>8</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>178</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>32</v>
@@ -6205,99 +6214,99 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>629</v>
+        <v>587</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>630</v>
+        <v>190</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>631</v>
+        <v>34</v>
       </c>
       <c r="F162" s="5">
-        <v>39025</v>
+        <v>20124</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>66</v>
+        <v>629</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>68</v>
+        <v>630</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>70</v>
+        <v>631</v>
+      </c>
+      <c r="F163" s="5">
+        <v>39025</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>282</v>
+        <v>66</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>312</v>
+        <v>67</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>313</v>
+        <v>68</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="F164" s="5">
-        <v>57021</v>
+        <v>69</v>
+      </c>
+      <c r="F164" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>297</v>
+        <v>71</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>182</v>
+        <v>282</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>7</v>
+        <v>312</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>177</v>
+        <v>313</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F165" s="5" t="s">
-        <v>178</v>
+        <v>314</v>
+      </c>
+      <c r="F165" s="5">
+        <v>57021</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>75</v>
+        <v>297</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>460</v>
+        <v>182</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>7</v>
@@ -6311,7 +6320,7 @@
       <c r="E166" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F166" s="8" t="s">
+      <c r="F166" s="5" t="s">
         <v>178</v>
       </c>
       <c r="G166" s="4" t="s">
@@ -6320,145 +6329,145 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>87</v>
+        <v>460</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>89</v>
+        <v>177</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>91</v>
+        <v>8</v>
+      </c>
+      <c r="F167" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>344</v>
+        <v>87</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>345</v>
+        <v>89</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="F168" s="5">
-        <v>70124</v>
+        <v>90</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>187</v>
+        <v>345</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>34</v>
+        <v>346</v>
       </c>
       <c r="F169" s="5">
-        <v>20158</v>
+        <v>70124</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>157</v>
+        <v>42</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>644</v>
+        <v>331</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>645</v>
+        <v>187</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F170" s="5">
-        <v>39100</v>
+        <v>20158</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>355</v>
+        <v>644</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>306</v>
+        <v>26</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>356</v>
+        <v>645</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>357</v>
+        <v>28</v>
       </c>
       <c r="F171" s="5">
-        <v>12084</v>
+        <v>39100</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>305</v>
+        <v>30</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>192</v>
+        <v>355</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>32</v>
+        <v>306</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>193</v>
+        <v>356</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F172" s="5" t="s">
-        <v>59</v>
+        <v>357</v>
+      </c>
+      <c r="F172" s="5">
+        <v>12084</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>36</v>
+        <v>305</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>32</v>
@@ -6467,13 +6476,13 @@
         <v>653</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
       <c r="E173" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="G173" s="4" t="s">
         <v>36</v>
@@ -6481,99 +6490,99 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>455</v>
+        <v>225</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>456</v>
+        <v>226</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F174" s="8" t="s">
-        <v>457</v>
+        <v>34</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>106</v>
+        <v>455</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>107</v>
+        <v>7</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>108</v>
+        <v>456</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F175" s="5" t="s">
-        <v>110</v>
+        <v>8</v>
+      </c>
+      <c r="F175" s="8" t="s">
+        <v>457</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>429</v>
+        <v>106</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>306</v>
+        <v>107</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>430</v>
+        <v>108</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="F176" s="5">
-        <v>12100</v>
+        <v>109</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>305</v>
+        <v>111</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>393</v>
+        <v>429</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>20</v>
+        <v>306</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>21</v>
+        <v>430</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>22</v>
+        <v>431</v>
       </c>
       <c r="F177" s="5">
-        <v>40127</v>
+        <v>12100</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>24</v>
+        <v>305</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>609</v>
+        <v>393</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>20</v>
@@ -6582,13 +6591,13 @@
         <v>653</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>610</v>
+        <v>21</v>
       </c>
       <c r="E178" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F178" s="5">
-        <v>40122</v>
+        <v>40127</v>
       </c>
       <c r="G178" s="4" t="s">
         <v>24</v>
@@ -6596,30 +6605,30 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>353</v>
+        <v>609</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>354</v>
+        <v>610</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F179" s="5">
-        <v>20121</v>
+        <v>40122</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>656</v>
+        <v>353</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>32</v>
@@ -6642,7 +6651,7 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>554</v>
+        <v>656</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>32</v>
@@ -6651,21 +6660,21 @@
         <v>653</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>523</v>
+        <v>354</v>
       </c>
       <c r="E181" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F181" s="5">
-        <v>20154</v>
+        <v>20121</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>32</v>
@@ -6688,7 +6697,7 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>32</v>
@@ -6711,7 +6720,7 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>594</v>
+        <v>522</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>32</v>
@@ -6720,7 +6729,7 @@
         <v>653</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>595</v>
+        <v>523</v>
       </c>
       <c r="E184" s="4" t="s">
         <v>34</v>
@@ -6734,30 +6743,30 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>513</v>
+        <v>594</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>27</v>
+        <v>595</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F185" s="5">
-        <v>39100</v>
+        <v>20154</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>230</v>
+        <v>513</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>26</v>
@@ -6771,8 +6780,8 @@
       <c r="E186" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F186" s="5" t="s">
-        <v>29</v>
+      <c r="F186" s="5">
+        <v>39100</v>
       </c>
       <c r="G186" s="4" t="s">
         <v>30</v>
@@ -6780,30 +6789,30 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>141</v>
+        <v>230</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>142</v>
+        <v>27</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>664</v>
+        <v>141</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>32</v>
@@ -6812,13 +6821,13 @@
         <v>653</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>665</v>
+        <v>142</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F188" s="5">
-        <v>20123</v>
+      <c r="F188" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="G188" s="4" t="s">
         <v>36</v>
@@ -6826,7 +6835,7 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>54</v>
+        <v>664</v>
       </c>
       <c r="B189" s="9" t="s">
         <v>32</v>
@@ -6835,13 +6844,13 @@
         <v>653</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>55</v>
+        <v>665</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F189" s="10" t="s">
-        <v>56</v>
+      <c r="F189" s="10">
+        <v>20123</v>
       </c>
       <c r="G189" s="9" t="s">
         <v>36</v>
@@ -6849,7 +6858,7 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>439</v>
+        <v>54</v>
       </c>
       <c r="B190" s="9" t="s">
         <v>32</v>
@@ -6858,182 +6867,182 @@
         <v>653</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>440</v>
+        <v>55</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="F190" s="10">
-        <v>20038</v>
+        <v>34</v>
+      </c>
+      <c r="F190" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="G190" s="9" t="s">
-        <v>134</v>
+        <v>36</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>234</v>
+        <v>440</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>79</v>
+        <v>441</v>
       </c>
       <c r="F191" s="10">
-        <v>10121</v>
+        <v>20038</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>81</v>
+        <v>134</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>93</v>
+        <v>424</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>95</v>
+        <v>234</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F192" s="10" t="s">
-        <v>97</v>
+        <v>79</v>
+      </c>
+      <c r="F192" s="10">
+        <v>10121</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A193" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="B193" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D193" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="E193" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="F193" s="10">
-        <v>64020</v>
-      </c>
-      <c r="G193" s="9" t="s">
-        <v>75</v>
+      <c r="A193" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F193" s="7">
+        <v>20124</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
-        <v>578</v>
+        <v>93</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>7</v>
+        <v>94</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>579</v>
+        <v>95</v>
       </c>
       <c r="E194" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F194" s="12" t="s">
-        <v>580</v>
+        <v>96</v>
+      </c>
+      <c r="F194" s="10" t="s">
+        <v>97</v>
       </c>
       <c r="G194" s="9" t="s">
-        <v>9</v>
+        <v>98</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
-        <v>408</v>
+        <v>375</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>32</v>
+        <v>376</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>209</v>
+        <v>377</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>34</v>
+        <v>378</v>
       </c>
       <c r="F195" s="10">
-        <v>20121</v>
+        <v>64020</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
-        <v>131</v>
+        <v>578</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>132</v>
+        <v>579</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F196" s="10" t="s">
-        <v>133</v>
+        <v>8</v>
+      </c>
+      <c r="F196" s="12" t="s">
+        <v>580</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>134</v>
+        <v>9</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>603</v>
+        <v>408</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>604</v>
+        <v>209</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F197" s="12" t="s">
-        <v>605</v>
+        <v>34</v>
+      </c>
+      <c r="F197" s="10">
+        <v>20121</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>255</v>
+        <v>131</v>
       </c>
       <c r="B198" s="9" t="s">
         <v>32</v>
@@ -7042,44 +7051,44 @@
         <v>653</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>256</v>
+        <v>132</v>
       </c>
       <c r="E198" s="9" t="s">
         <v>34</v>
       </c>
       <c r="F198" s="10" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>36</v>
+        <v>134</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>338</v>
+        <v>603</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>339</v>
+        <v>7</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>340</v>
+        <v>604</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="F199" s="10">
-        <v>37045</v>
+        <v>8</v>
+      </c>
+      <c r="F199" s="12" t="s">
+        <v>605</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>341</v>
+        <v>9</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
-        <v>164</v>
+        <v>255</v>
       </c>
       <c r="B200" s="9" t="s">
         <v>32</v>
@@ -7088,44 +7097,44 @@
         <v>653</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>165</v>
+        <v>256</v>
       </c>
       <c r="E200" s="9" t="s">
         <v>34</v>
       </c>
       <c r="F200" s="10" t="s">
-        <v>166</v>
+        <v>56</v>
       </c>
       <c r="G200" s="9" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="9" t="s">
-        <v>527</v>
+        <v>338</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>32</v>
+        <v>339</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D201" s="9" t="s">
-        <v>165</v>
+        <v>340</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>34</v>
+        <v>526</v>
       </c>
       <c r="F201" s="10">
-        <v>20126</v>
+        <v>37045</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>157</v>
+        <v>341</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
-        <v>599</v>
+        <v>164</v>
       </c>
       <c r="B202" s="9" t="s">
         <v>32</v>
@@ -7134,21 +7143,21 @@
         <v>653</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>600</v>
+        <v>165</v>
       </c>
       <c r="E202" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F202" s="10">
-        <v>20138</v>
+      <c r="F202" s="10" t="s">
+        <v>166</v>
       </c>
       <c r="G202" s="9" t="s">
-        <v>260</v>
+        <v>157</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="9" t="s">
-        <v>607</v>
+        <v>527</v>
       </c>
       <c r="B203" s="9" t="s">
         <v>32</v>
@@ -7157,21 +7166,21 @@
         <v>653</v>
       </c>
       <c r="D203" s="9" t="s">
-        <v>608</v>
+        <v>165</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>34</v>
       </c>
       <c r="F203" s="10">
-        <v>20122</v>
+        <v>20126</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="B204" s="9" t="s">
         <v>32</v>
@@ -7180,550 +7189,550 @@
         <v>653</v>
       </c>
       <c r="D204" s="9" t="s">
-        <v>392</v>
+        <v>600</v>
       </c>
       <c r="E204" s="9" t="s">
         <v>34</v>
       </c>
       <c r="F204" s="10">
-        <v>20123</v>
+        <v>20138</v>
       </c>
       <c r="G204" s="9" t="s">
-        <v>36</v>
+        <v>260</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="B205" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D205" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="E205" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F205" s="10">
+        <v>20122</v>
+      </c>
+      <c r="G205" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A206" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="B206" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D206" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="E206" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F206" s="10">
+        <v>20123</v>
+      </c>
+      <c r="G206" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A207" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="B205" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C205" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D205" s="9" t="s">
+      <c r="B207" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D207" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="E205" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F205" s="10">
+      <c r="E207" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F207" s="10">
         <v>20135</v>
       </c>
-      <c r="G205" s="9" t="s">
+      <c r="G207" s="9" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A206" s="3" t="s">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A208" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="B206" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D206" s="3" t="s">
+      <c r="B208" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D208" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="E206" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F206" s="7">
+      <c r="E208" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F208" s="7">
         <v>20135</v>
       </c>
-      <c r="G206" s="3" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A207" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="B207" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D207" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="E207" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F207" s="7">
-        <v>20135</v>
-      </c>
-      <c r="G207" s="3" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A208" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="B208" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D208" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="E208" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F208" s="10">
-        <v>20135</v>
-      </c>
-      <c r="G208" s="9" t="s">
+      <c r="G208" s="3" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="3" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>183</v>
+        <v>32</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>643</v>
+        <v>258</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>184</v>
+        <v>34</v>
       </c>
       <c r="F209" s="7">
-        <v>85100</v>
+        <v>20135</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>317</v>
+        <v>260</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="9" t="s">
-        <v>202</v>
+        <v>403</v>
       </c>
       <c r="B210" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D210" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="E210" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F210" s="10">
+        <v>20135</v>
+      </c>
+      <c r="G210" s="9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A211" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="B211" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C210" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D210" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="E210" s="9" t="s">
+      <c r="C211" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="E211" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="F210" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="G210" s="9" t="s">
+      <c r="F211" s="7">
+        <v>85100</v>
+      </c>
+      <c r="G211" s="3" t="s">
         <v>317</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A211" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="B211" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D211" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="E211" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F211" s="10">
-        <v>20144</v>
-      </c>
-      <c r="G211" s="9" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="9" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>32</v>
+        <v>183</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D212" s="9" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="E212" s="9" t="s">
-        <v>34</v>
+        <v>184</v>
       </c>
       <c r="F212" s="10" t="s">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="G212" s="9" t="s">
-        <v>134</v>
+        <v>317</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="9" t="s">
-        <v>283</v>
+        <v>451</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D213" s="9" t="s">
-        <v>315</v>
+        <v>452</v>
       </c>
       <c r="E213" s="9" t="s">
-        <v>316</v>
+        <v>34</v>
       </c>
       <c r="F213" s="10">
-        <v>40026</v>
+        <v>20144</v>
       </c>
       <c r="G213" s="9" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A214" s="3" t="s">
-        <v>635</v>
-      </c>
-      <c r="B214" s="3" t="s">
+      <c r="A214" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="B214" s="9" t="s">
         <v>32</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="D214" s="3" t="s">
-        <v>636</v>
-      </c>
-      <c r="E214" s="3" t="s">
-        <v>637</v>
-      </c>
-      <c r="F214" s="7">
-        <v>20068</v>
-      </c>
-      <c r="G214" s="3" t="s">
-        <v>260</v>
+      <c r="D214" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="E214" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F214" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="G214" s="9" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D215" s="9" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E215" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F215" s="10" t="s">
-        <v>321</v>
+        <v>316</v>
+      </c>
+      <c r="F215" s="10">
+        <v>40026</v>
       </c>
       <c r="G215" s="9" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="3" t="s">
-        <v>659</v>
+        <v>635</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>660</v>
+        <v>636</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F216" s="11" t="s">
-        <v>661</v>
+        <v>637</v>
+      </c>
+      <c r="F216" s="7">
+        <v>20068</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>9</v>
+        <v>260</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
-        <v>531</v>
+        <v>284</v>
       </c>
       <c r="B217" s="9" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D217" s="9" t="s">
-        <v>27</v>
+        <v>318</v>
       </c>
       <c r="E217" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F217" s="10">
-        <v>39100</v>
+        <v>8</v>
+      </c>
+      <c r="F217" s="10" t="s">
+        <v>321</v>
       </c>
       <c r="G217" s="9" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A218" s="9" t="s">
-        <v>365</v>
-      </c>
-      <c r="B218" s="9" t="s">
-        <v>32</v>
+      <c r="A218" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="D218" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="E218" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F218" s="10">
-        <v>20123</v>
-      </c>
-      <c r="G218" s="9" t="s">
-        <v>36</v>
+      <c r="D218" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F218" s="11" t="s">
+        <v>661</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="9" t="s">
-        <v>285</v>
+        <v>531</v>
       </c>
       <c r="B219" s="9" t="s">
-        <v>306</v>
+        <v>26</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D219" s="9" t="s">
-        <v>319</v>
+        <v>27</v>
       </c>
       <c r="E219" s="9" t="s">
-        <v>320</v>
+        <v>28</v>
       </c>
       <c r="F219" s="10">
-        <v>12020</v>
+        <v>39100</v>
       </c>
       <c r="G219" s="9" t="s">
-        <v>305</v>
+        <v>30</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="9" t="s">
-        <v>37</v>
+        <v>365</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D220" s="9" t="s">
-        <v>39</v>
+        <v>366</v>
       </c>
       <c r="E220" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F220" s="10" t="s">
-        <v>41</v>
+        <v>34</v>
+      </c>
+      <c r="F220" s="10">
+        <v>20123</v>
       </c>
       <c r="G220" s="9" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="9" t="s">
-        <v>419</v>
+        <v>285</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>420</v>
+        <v>306</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D221" s="9" t="s">
-        <v>421</v>
+        <v>319</v>
       </c>
       <c r="E221" s="9" t="s">
-        <v>422</v>
+        <v>320</v>
       </c>
       <c r="F221" s="10">
-        <v>28053</v>
+        <v>12020</v>
       </c>
       <c r="G221" s="9" t="s">
-        <v>134</v>
+        <v>305</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="9" t="s">
-        <v>170</v>
+        <v>37</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D222" s="9" t="s">
-        <v>167</v>
+        <v>39</v>
       </c>
       <c r="E222" s="9" t="s">
-        <v>168</v>
+        <v>40</v>
       </c>
       <c r="F222" s="10" t="s">
-        <v>169</v>
+        <v>41</v>
       </c>
       <c r="G222" s="9" t="s">
-        <v>157</v>
+        <v>42</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="9" t="s">
-        <v>558</v>
+        <v>419</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>26</v>
+        <v>420</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D223" s="9" t="s">
-        <v>559</v>
+        <v>421</v>
       </c>
       <c r="E223" s="9" t="s">
-        <v>28</v>
+        <v>422</v>
       </c>
       <c r="F223" s="10">
-        <v>39100</v>
+        <v>28053</v>
       </c>
       <c r="G223" s="9" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="9" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D224" s="9" t="s">
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="E224" s="9" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="F224" s="10" t="s">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="G224" s="9" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="9" t="s">
-        <v>205</v>
+        <v>558</v>
       </c>
       <c r="B225" s="9" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D225" s="9" t="s">
-        <v>206</v>
+        <v>559</v>
       </c>
       <c r="E225" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F225" s="10" t="s">
-        <v>207</v>
+        <v>28</v>
+      </c>
+      <c r="F225" s="10">
+        <v>39100</v>
       </c>
       <c r="G225" s="9" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="9" t="s">
-        <v>242</v>
+        <v>196</v>
       </c>
       <c r="B226" s="9" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D226" s="9" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="E226" s="9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F226" s="10" t="s">
-        <v>56</v>
+        <v>198</v>
       </c>
       <c r="G226" s="9" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="9" t="s">
-        <v>532</v>
+        <v>205</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D227" s="9" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="E227" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F227" s="10">
-        <v>20121</v>
+        <v>69</v>
+      </c>
+      <c r="F227" s="10" t="s">
+        <v>207</v>
       </c>
       <c r="G227" s="9" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="9" t="s">
-        <v>576</v>
+        <v>242</v>
       </c>
       <c r="B228" s="9" t="s">
         <v>32</v>
@@ -7732,13 +7741,13 @@
         <v>653</v>
       </c>
       <c r="D228" s="9" t="s">
-        <v>577</v>
+        <v>175</v>
       </c>
       <c r="E228" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F228" s="10">
-        <v>20121</v>
+      <c r="F228" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="G228" s="9" t="s">
         <v>36</v>
@@ -7746,329 +7755,329 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="9" t="s">
-        <v>443</v>
+        <v>532</v>
       </c>
       <c r="B229" s="9" t="s">
-        <v>444</v>
+        <v>32</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D229" s="9" t="s">
-        <v>445</v>
+        <v>175</v>
       </c>
       <c r="E229" s="9" t="s">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="F229" s="10">
-        <v>53048</v>
+        <v>20121</v>
       </c>
       <c r="G229" s="9" t="s">
-        <v>447</v>
+        <v>36</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="9" t="s">
-        <v>514</v>
+        <v>576</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>507</v>
+        <v>32</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D230" s="9" t="s">
-        <v>515</v>
+        <v>577</v>
       </c>
       <c r="E230" s="9" t="s">
-        <v>516</v>
+        <v>34</v>
       </c>
       <c r="F230" s="10">
-        <v>35011</v>
+        <v>20121</v>
       </c>
       <c r="G230" s="9" t="s">
-        <v>503</v>
+        <v>36</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="9" t="s">
-        <v>241</v>
+        <v>443</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>32</v>
+        <v>444</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D231" s="9" t="s">
-        <v>175</v>
+        <v>445</v>
       </c>
       <c r="E231" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F231" s="10" t="s">
-        <v>56</v>
+        <v>446</v>
+      </c>
+      <c r="F231" s="10">
+        <v>53048</v>
       </c>
       <c r="G231" s="9" t="s">
-        <v>36</v>
+        <v>447</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="B232" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D232" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="E232" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="F232" s="10">
+        <v>35011</v>
+      </c>
+      <c r="G232" s="9" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A233" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="B233" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D233" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E233" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F233" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G233" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A234" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B232" s="9" t="s">
+      <c r="B234" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C232" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D232" s="9" t="s">
+      <c r="C234" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D234" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="E232" s="9" t="s">
+      <c r="E234" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F232" s="10" t="s">
+      <c r="F234" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G232" s="9" t="s">
+      <c r="G234" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A233" s="3" t="s">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A235" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="B233" s="3" t="s">
+      <c r="B235" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C233" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D233" s="3" t="s">
+      <c r="C235" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D235" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E233" s="3" t="s">
+      <c r="E235" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F233" s="7">
+      <c r="F235" s="7">
         <v>39100</v>
       </c>
-      <c r="G233" s="3" t="s">
+      <c r="G235" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A234" s="3" t="s">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A236" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="B234" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D234" s="3" t="s">
+      <c r="B236" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D236" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="E234" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F234" s="7">
+      <c r="E236" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F236" s="7">
         <v>20121</v>
       </c>
-      <c r="G234" s="9" t="s">
+      <c r="G236" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A235" s="9" t="s">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A237" s="9" t="s">
         <v>529</v>
       </c>
-      <c r="B235" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D235" s="9" t="s">
+      <c r="B237" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D237" s="9" t="s">
         <v>530</v>
       </c>
-      <c r="E235" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F235" s="10">
+      <c r="E237" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F237" s="10">
         <v>20121</v>
       </c>
-      <c r="G235" s="9" t="s">
+      <c r="G237" s="9" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A236" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B236" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C236" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D236" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E236" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F236" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G236" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A237" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="B237" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C237" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D237" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="E237" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F237" s="11" t="s">
-        <v>566</v>
-      </c>
-      <c r="G237" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="9" t="s">
-        <v>379</v>
+        <v>19</v>
       </c>
       <c r="B238" s="9" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D238" s="9" t="s">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="E238" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="F238" s="10">
-        <v>20089</v>
+        <v>22</v>
+      </c>
+      <c r="F238" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="G238" s="9" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A239" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="B239" s="9" t="s">
+      <c r="A239" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="B239" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="D239" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="E239" s="9" t="s">
+      <c r="D239" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="E239" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F239" s="12" t="s">
-        <v>475</v>
-      </c>
-      <c r="G239" s="9" t="s">
-        <v>9</v>
+      <c r="F239" s="11" t="s">
+        <v>566</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="9" t="s">
-        <v>210</v>
+        <v>379</v>
       </c>
       <c r="B240" s="9" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D240" s="9" t="s">
-        <v>200</v>
+        <v>380</v>
       </c>
       <c r="E240" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F240" s="10" t="s">
-        <v>201</v>
+        <v>381</v>
+      </c>
+      <c r="F240" s="10">
+        <v>20089</v>
       </c>
       <c r="G240" s="9" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" s="9" t="s">
-        <v>212</v>
+        <v>473</v>
       </c>
       <c r="B241" s="9" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D241" s="9" t="s">
-        <v>213</v>
+        <v>474</v>
       </c>
       <c r="E241" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F241" s="10" t="s">
-        <v>156</v>
+        <v>8</v>
+      </c>
+      <c r="F241" s="12" t="s">
+        <v>475</v>
       </c>
       <c r="G241" s="9" t="s">
-        <v>157</v>
+        <v>9</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A242" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="B242" s="3" t="s">
-        <v>32</v>
+      <c r="A242" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B242" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="D242" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E242" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F242" s="7">
-        <v>20124</v>
-      </c>
-      <c r="G242" s="3" t="s">
-        <v>157</v>
+      <c r="D242" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="E242" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F242" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="G242" s="9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" s="9" t="s">
-        <v>436</v>
+        <v>212</v>
       </c>
       <c r="B243" s="9" t="s">
         <v>32</v>
@@ -8082,8 +8091,8 @@
       <c r="E243" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F243" s="10">
-        <v>20124</v>
+      <c r="F243" s="10" t="s">
+        <v>156</v>
       </c>
       <c r="G243" s="9" t="s">
         <v>157</v>
@@ -8091,30 +8100,30 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" s="3" t="s">
-        <v>633</v>
+        <v>663</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>634</v>
+        <v>213</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="F244" s="7">
-        <v>24050</v>
+        <v>20124</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" s="9" t="s">
-        <v>227</v>
+        <v>436</v>
       </c>
       <c r="B245" s="9" t="s">
         <v>32</v>
@@ -8123,49 +8132,49 @@
         <v>653</v>
       </c>
       <c r="D245" s="9" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="E245" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F245" s="10" t="s">
-        <v>229</v>
+      <c r="F245" s="10">
+        <v>20124</v>
       </c>
       <c r="G245" s="9" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" s="3" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>228</v>
+        <v>634</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="F246" s="7">
-        <v>20148</v>
+        <v>24050</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" s="9" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="B247" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C247" s="4" t="s">
+      <c r="C247" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D247" s="9" t="s">
@@ -8183,99 +8192,99 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F248" s="7">
+        <v>20148</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A249" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="B249" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C249" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D249" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="E249" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F249" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="G249" s="9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A250" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="B248" s="3" t="s">
+      <c r="B250" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C248" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D248" s="3" t="s">
+      <c r="C250" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D250" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="E248" s="3" t="s">
+      <c r="E250" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="F248" s="7">
+      <c r="F250" s="7">
         <v>25055</v>
       </c>
-      <c r="G248" s="3" t="s">
+      <c r="G250" s="3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A249" s="3" t="s">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A251" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="B249" s="3" t="s">
+      <c r="B251" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="C249" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D249" s="3" t="s">
+      <c r="C251" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D251" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="E249" s="3" t="s">
+      <c r="E251" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="F249" s="7">
+      <c r="F251" s="7">
         <v>50132</v>
       </c>
-      <c r="G249" s="3" t="s">
+      <c r="G251" s="3" t="s">
         <v>447</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A250" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="B250" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C250" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D250" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="E250" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F250" s="10">
-        <v>20129</v>
-      </c>
-      <c r="G250" s="9" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A251" s="9" t="s">
-        <v>461</v>
-      </c>
-      <c r="B251" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C251" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D251" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="E251" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F251" s="10">
-        <v>20129</v>
-      </c>
-      <c r="G251" s="9" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" s="9" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B252" s="9" t="s">
         <v>32</v>
@@ -8298,7 +8307,7 @@
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" s="9" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="B253" s="9" t="s">
         <v>32</v>
@@ -8321,7 +8330,7 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" s="9" t="s">
-        <v>174</v>
+        <v>471</v>
       </c>
       <c r="B254" s="9" t="s">
         <v>32</v>
@@ -8330,44 +8339,44 @@
         <v>653</v>
       </c>
       <c r="D254" s="9" t="s">
-        <v>175</v>
+        <v>462</v>
       </c>
       <c r="E254" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F254" s="10" t="s">
-        <v>56</v>
+      <c r="F254" s="10">
+        <v>20129</v>
       </c>
       <c r="G254" s="9" t="s">
-        <v>36</v>
+        <v>260</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" s="9" t="s">
-        <v>329</v>
+        <v>472</v>
       </c>
       <c r="B255" s="9" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C255" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D255" s="9" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="E255" s="9" t="s">
-        <v>316</v>
+        <v>34</v>
       </c>
       <c r="F255" s="10">
-        <v>40026</v>
+        <v>20129</v>
       </c>
       <c r="G255" s="9" t="s">
-        <v>24</v>
+        <v>260</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" s="9" t="s">
-        <v>286</v>
+        <v>174</v>
       </c>
       <c r="B256" s="9" t="s">
         <v>32</v>
@@ -8376,13 +8385,13 @@
         <v>653</v>
       </c>
       <c r="D256" s="9" t="s">
-        <v>322</v>
+        <v>175</v>
       </c>
       <c r="E256" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F256" s="10">
-        <v>20124</v>
+      <c r="F256" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="G256" s="9" t="s">
         <v>36</v>
@@ -8390,421 +8399,421 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" s="9" t="s">
-        <v>448</v>
+        <v>329</v>
       </c>
       <c r="B257" s="9" t="s">
-        <v>306</v>
+        <v>20</v>
       </c>
       <c r="C257" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D257" s="9" t="s">
-        <v>449</v>
+        <v>330</v>
       </c>
       <c r="E257" s="9" t="s">
-        <v>450</v>
+        <v>316</v>
       </c>
       <c r="F257" s="10">
-        <v>12011</v>
+        <v>40026</v>
       </c>
       <c r="G257" s="9" t="s">
-        <v>305</v>
+        <v>24</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A258" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="B258" s="3" t="s">
+      <c r="A258" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="B258" s="9" t="s">
         <v>32</v>
       </c>
       <c r="C258" s="4" t="s">
         <v>653</v>
       </c>
-      <c r="D258" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="E258" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F258" s="7">
-        <v>20121</v>
-      </c>
-      <c r="G258" s="3" t="s">
+      <c r="D258" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="E258" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F258" s="10">
+        <v>20124</v>
+      </c>
+      <c r="G258" s="9" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" s="9" t="s">
-        <v>149</v>
+        <v>448</v>
       </c>
       <c r="B259" s="9" t="s">
-        <v>150</v>
+        <v>306</v>
       </c>
       <c r="C259" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D259" s="9" t="s">
-        <v>151</v>
+        <v>449</v>
       </c>
       <c r="E259" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F259" s="10" t="s">
-        <v>153</v>
+        <v>450</v>
+      </c>
+      <c r="F259" s="10">
+        <v>12011</v>
       </c>
       <c r="G259" s="9" t="s">
-        <v>42</v>
+        <v>305</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A260" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="B260" s="9" t="s">
+      <c r="A260" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="B260" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C260" s="4" t="s">
         <v>653</v>
       </c>
-      <c r="D260" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="E260" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F260" s="10">
-        <v>20123</v>
-      </c>
-      <c r="G260" s="9" t="s">
+      <c r="D260" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F260" s="7">
+        <v>20121</v>
+      </c>
+      <c r="G260" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" s="9" t="s">
-        <v>489</v>
+        <v>149</v>
       </c>
       <c r="B261" s="9" t="s">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="C261" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D261" s="9" t="s">
-        <v>490</v>
+        <v>151</v>
       </c>
       <c r="E261" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F261" s="10">
-        <v>90141</v>
+        <v>152</v>
+      </c>
+      <c r="F261" s="10" t="s">
+        <v>153</v>
       </c>
       <c r="G261" s="9" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="B262" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D262" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="E262" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F262" s="10">
+        <v>20123</v>
+      </c>
+      <c r="G262" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A263" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="B263" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C263" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D263" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="E263" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F263" s="10">
+        <v>90141</v>
+      </c>
+      <c r="G263" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A264" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="B262" s="9" t="s">
+      <c r="B264" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C262" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D262" s="9" t="s">
+      <c r="C264" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D264" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="E262" s="9" t="s">
+      <c r="E264" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F262" s="12" t="s">
+      <c r="F264" s="12" t="s">
         <v>388</v>
       </c>
-      <c r="G262" s="9" t="s">
+      <c r="G264" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A263" s="3" t="s">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A265" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="B263" s="3" t="s">
+      <c r="B265" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C263" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D263" s="3" t="s">
+      <c r="C265" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D265" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="E263" s="3" t="s">
+      <c r="E265" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F263" s="11" t="s">
+      <c r="F265" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="G263" s="3" t="s">
+      <c r="G265" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A264" s="3" t="s">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A266" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="B264" s="3" t="s">
+      <c r="B266" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C264" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D264" s="3" t="s">
+      <c r="C266" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D266" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="E264" s="3" t="s">
+      <c r="E266" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F264" s="11" t="s">
+      <c r="F266" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="G264" s="3" t="s">
+      <c r="G266" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A265" s="9" t="s">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A267" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="B265" s="9" t="s">
+      <c r="B267" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C265" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D265" s="9" t="s">
+      <c r="C267" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D267" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="E265" s="9" t="s">
+      <c r="E267" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F265" s="10" t="s">
+      <c r="F267" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="G265" s="9" t="s">
+      <c r="G267" s="9" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A266" s="9" t="s">
-        <v>463</v>
-      </c>
-      <c r="B266" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="C266" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D266" s="9" t="s">
-        <v>464</v>
-      </c>
-      <c r="E266" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="F266" s="10">
-        <v>38055</v>
-      </c>
-      <c r="G266" s="9" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A267" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="B267" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C267" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D267" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E267" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F267" s="7">
-        <v>20145</v>
-      </c>
-      <c r="G267" s="3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="B268" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D268" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="E268" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="F268" s="10">
+        <v>38055</v>
+      </c>
+      <c r="G268" s="9" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A269" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E269" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F269" s="7">
+        <v>20145</v>
+      </c>
+      <c r="G269" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A270" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="B268" s="9" t="s">
+      <c r="B270" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C268" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D268" s="9" t="s">
+      <c r="C270" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D270" s="9" t="s">
         <v>426</v>
       </c>
-      <c r="E268" s="9" t="s">
+      <c r="E270" s="9" t="s">
         <v>427</v>
       </c>
-      <c r="F268" s="10">
+      <c r="F270" s="10">
         <v>25010</v>
       </c>
-      <c r="G268" s="9" t="s">
+      <c r="G270" s="9" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A269" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="B269" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C269" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D269" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="E269" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F269" s="10">
-        <v>20123</v>
-      </c>
-      <c r="G269" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A270" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="B270" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C270" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D270" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="E270" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F270" s="7">
-        <v>20123</v>
-      </c>
-      <c r="G270" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="B271" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C271" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D271" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="E271" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F271" s="10">
+        <v>20123</v>
+      </c>
+      <c r="G271" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A272" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D272" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E272" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F272" s="7">
+        <v>20123</v>
+      </c>
+      <c r="G272" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A273" s="9" t="s">
         <v>414</v>
       </c>
-      <c r="B271" s="9" t="s">
+      <c r="B273" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C271" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D271" s="9" t="s">
+      <c r="C273" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D273" s="9" t="s">
         <v>415</v>
       </c>
-      <c r="E271" s="9" t="s">
+      <c r="E273" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="F271" s="10">
+      <c r="F273" s="10">
         <v>71016</v>
       </c>
-      <c r="G271" s="9" t="s">
+      <c r="G273" s="9" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A272" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B272" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C272" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D272" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E272" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F272" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G272" s="9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A273" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="B273" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C273" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D273" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="E273" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F273" s="7">
-        <v>20123</v>
-      </c>
-      <c r="G273" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" s="9" t="s">
-        <v>323</v>
+        <v>14</v>
       </c>
       <c r="B274" s="9" t="s">
-        <v>324</v>
+        <v>15</v>
       </c>
       <c r="C274" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D274" s="9" t="s">
-        <v>325</v>
+        <v>16</v>
       </c>
       <c r="E274" s="9" t="s">
-        <v>326</v>
+        <v>17</v>
       </c>
       <c r="F274" s="10" t="s">
-        <v>327</v>
+        <v>18</v>
       </c>
       <c r="G274" s="9" t="s">
-        <v>328</v>
+        <v>10</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" s="3" t="s">
-        <v>560</v>
+        <v>638</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>32</v>
@@ -8813,182 +8822,182 @@
         <v>653</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>561</v>
+        <v>639</v>
       </c>
       <c r="E275" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F275" s="7">
-        <v>20122</v>
+        <v>20123</v>
       </c>
       <c r="G275" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A276" s="9" t="s">
+      <c r="A276" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C276" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E276" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F276" s="7">
+        <v>20145</v>
+      </c>
+      <c r="G276" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A277" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="B277" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="C277" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D277" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="E277" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="F277" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="G277" s="9" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A278" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="B278" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C278" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="E278" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F278" s="7">
+        <v>20122</v>
+      </c>
+      <c r="G278" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A279" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="B276" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C276" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D276" s="9" t="s">
+      <c r="B279" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C279" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D279" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="E276" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F276" s="10" t="s">
+      <c r="E279" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F279" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="G276" s="9" t="s">
+      <c r="G279" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A277" s="3" t="s">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A280" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="B277" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C277" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D277" s="3" t="s">
+      <c r="B280" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C280" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D280" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="E277" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F277" s="7">
+      <c r="E280" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F280" s="7">
         <v>20123</v>
       </c>
-      <c r="G277" s="3" t="s">
+      <c r="G280" s="3" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A278" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="B278" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C278" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D278" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="E278" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F278" s="10">
-        <v>20123</v>
-      </c>
-      <c r="G278" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A279" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="B279" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C279" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D279" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="E279" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F279" s="7">
-        <v>20094</v>
-      </c>
-      <c r="G279" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A280" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="B280" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C280" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D280" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="E280" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F280" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="G280" s="9" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" s="9" t="s">
-        <v>214</v>
+        <v>476</v>
       </c>
       <c r="B281" s="9" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C281" s="9" t="s">
         <v>653</v>
       </c>
       <c r="D281" s="9" t="s">
-        <v>215</v>
+        <v>477</v>
       </c>
       <c r="E281" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F281" s="10" t="s">
-        <v>216</v>
+        <v>34</v>
+      </c>
+      <c r="F281" s="10">
+        <v>20123</v>
       </c>
       <c r="G281" s="9" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A282" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="B282" s="9" t="s">
-        <v>159</v>
+      <c r="A282" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="B282" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="C282" s="9" t="s">
         <v>653</v>
       </c>
-      <c r="D282" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="E282" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="F282" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="G282" s="9" t="s">
-        <v>163</v>
+      <c r="D282" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="E282" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="F282" s="7">
+        <v>20094</v>
+      </c>
+      <c r="G282" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" s="9" t="s">
-        <v>432</v>
+        <v>394</v>
       </c>
       <c r="B283" s="9" t="s">
         <v>7</v>
@@ -9011,7 +9020,7 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" s="9" t="s">
-        <v>253</v>
+        <v>214</v>
       </c>
       <c r="B284" s="9" t="s">
         <v>7</v>
@@ -9034,30 +9043,99 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B285" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C285" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D285" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E285" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F285" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="G285" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A286" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="B286" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C286" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D286" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="E286" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F286" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="G286" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A287" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="B287" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C287" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D287" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="E287" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F287" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="G287" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A288" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="B285" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C285" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D285" s="9" t="s">
+      <c r="B288" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C288" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D288" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="E285" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F285" s="10" t="s">
+      <c r="E288" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F288" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="G285" s="9" t="s">
+      <c r="G288" s="9" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G218" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G285">
+    <sortState ref="A2:G288">
       <sortCondition ref="A1:A218"/>
     </sortState>
   </autoFilter>
@@ -9070,6 +9148,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F040406D9EE34E48977C379A242BB45D" ma:contentTypeVersion="15" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="1ab2d492e43f6bec9a26aa4599c840e9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="877b7d34-4df7-40bf-9eb1-208952470e96" xmlns:ns4="05fc27dd-4454-4248-9c78-3d72b2b155c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebc604e5d4aadf5a992ba83f8d4fb519" ns3:_="" ns4:_="">
     <xsd:import namespace="877b7d34-4df7-40bf-9eb1-208952470e96"/>
@@ -9302,24 +9397,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBC6436E-C4E7-4E8D-94E8-64DAEC05792B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9336,29 +9439,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{3A2F71C2-38D5-4D3E-8211-48ED79184602}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{35A2E496-1210-4BA4-9F9C-3D5DBEB59194}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1852" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1858" uniqueCount="684">
   <si>
     <t>Nome account</t>
   </si>
@@ -2072,6 +2072,9 @@
   </si>
   <si>
     <t>VELINO SOLAR ITALY SRL</t>
+  </si>
+  <si>
+    <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
   </si>
 </sst>
 </file>
@@ -2496,7 +2499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G288"/>
+  <dimension ref="A1:G289"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -3546,168 +3549,168 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>60</v>
+        <v>683</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C46" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>64</v>
+        <v>117</v>
+      </c>
+      <c r="F46" s="5">
+        <v>65125</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>143</v>
+        <v>60</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>144</v>
+        <v>61</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>148</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>519</v>
+        <v>143</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>520</v>
+        <v>145</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F48" s="5">
-        <v>20033</v>
+        <v>146</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>147</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>289</v>
+        <v>519</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>290</v>
+        <v>32</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>291</v>
+        <v>520</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>292</v>
+        <v>34</v>
       </c>
       <c r="F49" s="5">
-        <v>60035</v>
+        <v>20033</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>648</v>
+        <v>289</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>26</v>
+        <v>290</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>27</v>
+        <v>291</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>28</v>
+        <v>292</v>
       </c>
       <c r="F50" s="5">
-        <v>39100</v>
+        <v>60035</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>30</v>
+        <v>163</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>583</v>
+        <v>648</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>115</v>
+        <v>26</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>116</v>
+        <v>27</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>117</v>
+        <v>28</v>
       </c>
       <c r="F51" s="5">
-        <v>65125</v>
+        <v>39100</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>555</v>
+        <v>583</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>213</v>
+        <v>116</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="F52" s="5">
-        <v>20124</v>
+        <v>65125</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>539</v>
+        <v>555</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>32</v>
@@ -3716,21 +3719,21 @@
         <v>653</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>540</v>
+        <v>213</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F53" s="5">
-        <v>20121</v>
+        <v>20124</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>32</v>
@@ -3753,7 +3756,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>32</v>
@@ -3776,76 +3779,76 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>497</v>
+        <v>557</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>498</v>
+        <v>540</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="F56" s="5">
-        <v>10143</v>
+        <v>20121</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>615</v>
+        <v>497</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>616</v>
+        <v>498</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>617</v>
+        <v>79</v>
       </c>
       <c r="F57" s="5">
-        <v>25038</v>
+        <v>10143</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>387</v>
+        <v>615</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>268</v>
+        <v>616</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>34</v>
+        <v>617</v>
       </c>
       <c r="F58" s="5">
-        <v>20123</v>
+        <v>25038</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>36</v>
+        <v>105</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>435</v>
+        <v>387</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>32</v>
@@ -3868,7 +3871,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>395</v>
+        <v>435</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>32</v>
@@ -3891,7 +3894,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>267</v>
+        <v>395</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>32</v>
@@ -3905,8 +3908,8 @@
       <c r="E61" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F61" s="5" t="s">
-        <v>59</v>
+      <c r="F61" s="5">
+        <v>20123</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>36</v>
@@ -3914,7 +3917,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>135</v>
+        <v>267</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>32</v>
@@ -3923,13 +3926,13 @@
         <v>653</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>120</v>
+        <v>268</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>36</v>
@@ -3937,7 +3940,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>407</v>
+        <v>135</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>32</v>
@@ -3951,8 +3954,8 @@
       <c r="E63" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F63" s="5">
-        <v>20121</v>
+      <c r="F63" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>36</v>
@@ -3960,53 +3963,53 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>136</v>
+        <v>407</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>140</v>
+        <v>34</v>
+      </c>
+      <c r="F64" s="5">
+        <v>20121</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>612</v>
+        <v>123</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>15</v>
@@ -4020,8 +4023,8 @@
       <c r="E66" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F66" s="5">
-        <v>90139</v>
+      <c r="F66" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>10</v>
@@ -4029,173 +4032,173 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>442</v>
+        <v>612</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>187</v>
+        <v>124</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F67" s="5">
-        <v>20158</v>
+        <v>90139</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>157</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>223</v>
+        <v>442</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>29</v>
+        <v>34</v>
+      </c>
+      <c r="F68" s="5">
+        <v>20158</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>84</v>
+        <v>224</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>581</v>
+        <v>82</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>262</v>
+        <v>83</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>582</v>
+        <v>84</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="F70" s="5">
-        <v>38123</v>
+        <v>85</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>266</v>
+        <v>42</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>542</v>
+        <v>581</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>7</v>
+        <v>262</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>543</v>
+        <v>582</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>178</v>
+        <v>406</v>
+      </c>
+      <c r="F71" s="5">
+        <v>38123</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>75</v>
+        <v>266</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>485</v>
+        <v>542</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>486</v>
+        <v>7</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>487</v>
+        <v>543</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="F72" s="5">
-        <v>26015</v>
+        <v>8</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>680</v>
+        <v>485</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C73" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>333</v>
+        <v>487</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>216</v>
+        <v>488</v>
+      </c>
+      <c r="F73" s="5">
+        <v>26015</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>9</v>
+        <v>105</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>556</v>
+        <v>680</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D74" s="4" t="s">
@@ -4204,7 +4207,7 @@
       <c r="E74" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F74" s="8" t="s">
+      <c r="F74" s="5" t="s">
         <v>216</v>
       </c>
       <c r="G74" s="4" t="s">
@@ -4213,7 +4216,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>332</v>
+        <v>556</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>7</v>
@@ -4227,7 +4230,7 @@
       <c r="E75" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="F75" s="8" t="s">
         <v>216</v>
       </c>
       <c r="G75" s="4" t="s">
@@ -4236,145 +4239,145 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>590</v>
+        <v>332</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>591</v>
+        <v>333</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F76" s="5">
-        <v>20122</v>
+        <v>8</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>298</v>
+        <v>590</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>294</v>
+        <v>32</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>299</v>
+        <v>591</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>300</v>
+        <v>34</v>
       </c>
       <c r="F77" s="5">
-        <v>56025</v>
+        <v>20122</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>297</v>
+        <v>36</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>7</v>
+        <v>294</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>270</v>
+        <v>299</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>271</v>
+        <v>300</v>
+      </c>
+      <c r="F78" s="5">
+        <v>56025</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>9</v>
+        <v>297</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>373</v>
+        <v>269</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>374</v>
+        <v>270</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F79" s="5">
-        <v>20121</v>
+        <v>8</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>278</v>
+        <v>373</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>301</v>
+        <v>374</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>302</v>
+        <v>34</v>
       </c>
       <c r="F80" s="5">
-        <v>24060</v>
+        <v>20121</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>614</v>
+        <v>278</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>187</v>
+        <v>301</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>34</v>
+        <v>302</v>
       </c>
       <c r="F81" s="5">
-        <v>20158</v>
+        <v>24060</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>479</v>
+        <v>614</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>32</v>
@@ -4383,21 +4386,21 @@
         <v>653</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>256</v>
+        <v>187</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F82" s="5">
-        <v>20121</v>
+        <v>20158</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>173</v>
+        <v>479</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>32</v>
@@ -4406,21 +4409,21 @@
         <v>653</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>155</v>
+        <v>256</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F83" s="5" t="s">
-        <v>156</v>
+      <c r="F83" s="5">
+        <v>20121</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>32</v>
@@ -4443,53 +4446,53 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>657</v>
+        <v>154</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>290</v>
+        <v>32</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>658</v>
+        <v>155</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="F85" s="5">
-        <v>60035</v>
+        <v>34</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>156</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>251</v>
+        <v>657</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>32</v>
+        <v>290</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>228</v>
+        <v>658</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>229</v>
+        <v>292</v>
+      </c>
+      <c r="F86" s="5">
+        <v>60035</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>437</v>
+        <v>251</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>32</v>
@@ -4498,151 +4501,151 @@
         <v>653</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>438</v>
+        <v>228</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F87" s="5">
-        <v>20122</v>
+      <c r="F87" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>36</v>
+        <v>134</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>243</v>
+        <v>437</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>244</v>
+        <v>32</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>245</v>
+        <v>438</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>247</v>
+        <v>34</v>
+      </c>
+      <c r="F88" s="5">
+        <v>20122</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>248</v>
+        <v>36</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>81</v>
+        <v>248</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>360</v>
+        <v>249</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>361</v>
+        <v>77</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>362</v>
+        <v>250</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="F90" s="5">
-        <v>76123</v>
+        <v>79</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>423</v>
+        <v>360</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>26</v>
+        <v>361</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>130</v>
+        <v>362</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>28</v>
+        <v>363</v>
       </c>
       <c r="F91" s="5">
-        <v>39100</v>
+        <v>76123</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>549</v>
+        <v>423</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>550</v>
+        <v>26</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>551</v>
+        <v>130</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="F92" s="8" t="s">
-        <v>553</v>
+        <v>28</v>
+      </c>
+      <c r="F92" s="5">
+        <v>39100</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>646</v>
+        <v>549</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>7</v>
+        <v>550</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>647</v>
+        <v>551</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>8</v>
+        <v>552</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>178</v>
+        <v>553</v>
       </c>
       <c r="G93" s="4" t="s">
         <v>75</v>
@@ -4650,99 +4653,99 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>389</v>
+        <v>646</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>390</v>
+        <v>647</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F94" s="5">
-        <v>70043</v>
+        <v>8</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>217</v>
+        <v>389</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>218</v>
+        <v>390</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
+      </c>
+      <c r="F95" s="5">
+        <v>70043</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>48</v>
+        <v>217</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>45</v>
+        <v>218</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>32</v>
@@ -4751,13 +4754,13 @@
         <v>653</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G98" s="4" t="s">
         <v>36</v>
@@ -4765,7 +4768,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>32</v>
@@ -4788,7 +4791,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>32</v>
@@ -4811,53 +4814,53 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>369</v>
+        <v>128</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>370</v>
+        <v>32</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>371</v>
+        <v>120</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="F101" s="5">
-        <v>61121</v>
+        <v>34</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>163</v>
+        <v>36</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>662</v>
+        <v>369</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>32</v>
+        <v>370</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>187</v>
+        <v>371</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>34</v>
+        <v>372</v>
       </c>
       <c r="F102" s="5">
-        <v>20158</v>
+        <v>61121</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>199</v>
+        <v>662</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>32</v>
@@ -4871,8 +4874,8 @@
       <c r="E103" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F103" s="5" t="s">
-        <v>188</v>
+      <c r="F103" s="5">
+        <v>20158</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>157</v>
@@ -4880,53 +4883,53 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>504</v>
+        <v>199</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>507</v>
+        <v>32</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>506</v>
+        <v>187</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="F104" s="5">
-        <v>35010</v>
+        <v>34</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>503</v>
+        <v>157</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>279</v>
+        <v>504</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>32</v>
+        <v>507</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>303</v>
+        <v>506</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>34</v>
+        <v>505</v>
       </c>
       <c r="F105" s="5">
-        <v>20123</v>
+        <v>35010</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>36</v>
+        <v>503</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>563</v>
+        <v>279</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>32</v>
@@ -4935,13 +4938,13 @@
         <v>653</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>562</v>
+        <v>303</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F106" s="5">
-        <v>20122</v>
+        <v>20123</v>
       </c>
       <c r="G106" s="4" t="s">
         <v>36</v>
@@ -4949,25 +4952,25 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>349</v>
+        <v>563</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>350</v>
+        <v>32</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>351</v>
+        <v>562</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="F107" s="5">
-        <v>15033</v>
+        <v>20122</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
@@ -5018,76 +5021,76 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>533</v>
+        <v>349</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>115</v>
+        <v>350</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>534</v>
+        <v>351</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>117</v>
+        <v>352</v>
       </c>
       <c r="F110" s="5">
-        <v>65127</v>
+        <v>15033</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>57</v>
+        <v>533</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>58</v>
+        <v>534</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F111" s="5" t="s">
-        <v>59</v>
+        <v>117</v>
+      </c>
+      <c r="F111" s="5">
+        <v>65127</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>334</v>
+        <v>57</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>335</v>
+        <v>58</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F112" s="5">
-        <v>10153</v>
+        <v>34</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>428</v>
+        <v>334</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>77</v>
@@ -5110,76 +5113,76 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>571</v>
+        <v>428</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>572</v>
+        <v>335</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="F114" s="5">
-        <v>20154</v>
+        <v>10153</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>280</v>
+        <v>571</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>304</v>
+        <v>572</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F115" s="5">
-        <v>183</v>
+        <v>20154</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>305</v>
+        <v>157</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>208</v>
+        <v>280</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>209</v>
+        <v>304</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F116" s="5" t="s">
-        <v>56</v>
+        <v>8</v>
+      </c>
+      <c r="F116" s="5">
+        <v>183</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>36</v>
+        <v>305</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>547</v>
+        <v>208</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>32</v>
@@ -5188,21 +5191,21 @@
         <v>653</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>548</v>
+        <v>209</v>
       </c>
       <c r="E117" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F117" s="5">
-        <v>20154</v>
+      <c r="F117" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>273</v>
+        <v>547</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>32</v>
@@ -5211,13 +5214,13 @@
         <v>653</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>274</v>
+        <v>548</v>
       </c>
       <c r="E118" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F118" s="5" t="s">
-        <v>156</v>
+      <c r="F118" s="5">
+        <v>20154</v>
       </c>
       <c r="G118" s="4" t="s">
         <v>157</v>
@@ -5225,30 +5228,30 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>126</v>
+        <v>273</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>127</v>
+        <v>274</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>29</v>
+        <v>156</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>240</v>
+        <v>126</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>26</v>
@@ -5271,168 +5274,168 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>412</v>
+        <v>240</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>413</v>
+        <v>127</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>178</v>
+        <v>29</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>272</v>
+        <v>412</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>27</v>
+        <v>413</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>29</v>
+        <v>178</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>144</v>
+        <v>26</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>237</v>
+        <v>27</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>238</v>
+        <v>28</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>239</v>
+        <v>29</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>148</v>
+        <v>30</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>596</v>
+        <v>236</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>597</v>
+        <v>237</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F124" s="5">
-        <v>20122</v>
+        <v>238</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>239</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>36</v>
+        <v>148</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>535</v>
+        <v>596</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>536</v>
+        <v>32</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>537</v>
+        <v>597</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>538</v>
+        <v>34</v>
       </c>
       <c r="F125" s="5">
-        <v>34133</v>
+        <v>20122</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>512</v>
+        <v>36</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>433</v>
+        <v>535</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>26</v>
+        <v>536</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>127</v>
+        <v>537</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>28</v>
+        <v>538</v>
       </c>
       <c r="F126" s="5">
-        <v>39100</v>
+        <v>34133</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>30</v>
+        <v>512</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>649</v>
+        <v>433</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>650</v>
+        <v>127</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F127" s="5">
-        <v>20121</v>
+        <v>39100</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>204</v>
+        <v>649</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>32</v>
@@ -5441,13 +5444,13 @@
         <v>653</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>58</v>
+        <v>650</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F128" s="5" t="s">
-        <v>59</v>
+      <c r="F128" s="5">
+        <v>20121</v>
       </c>
       <c r="G128" s="4" t="s">
         <v>36</v>
@@ -5455,7 +5458,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>364</v>
+        <v>204</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>32</v>
@@ -5469,8 +5472,8 @@
       <c r="E129" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F129" s="5">
-        <v>20123</v>
+      <c r="F129" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G129" s="4" t="s">
         <v>36</v>
@@ -5478,7 +5481,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>99</v>
+        <v>364</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>32</v>
@@ -5492,8 +5495,8 @@
       <c r="E130" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F130" s="5" t="s">
-        <v>59</v>
+      <c r="F130" s="5">
+        <v>20123</v>
       </c>
       <c r="G130" s="4" t="s">
         <v>36</v>
@@ -5501,237 +5504,237 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>491</v>
+        <v>99</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>492</v>
+        <v>58</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F131" s="8" t="s">
-        <v>271</v>
+        <v>34</v>
+      </c>
+      <c r="F131" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>518</v>
+        <v>492</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F132" s="5">
-        <v>80121</v>
+        <v>8</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>404</v>
+        <v>517</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>262</v>
+        <v>67</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>405</v>
+        <v>518</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>406</v>
+        <v>69</v>
       </c>
       <c r="F133" s="5">
-        <v>38121</v>
+        <v>80121</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>266</v>
+        <v>71</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>367</v>
+        <v>404</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>32</v>
+        <v>262</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>34</v>
+        <v>406</v>
       </c>
       <c r="F134" s="5">
-        <v>20123</v>
+        <v>38121</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>36</v>
+        <v>266</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F135" s="5">
-        <v>90139</v>
+        <v>20123</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>193</v>
+        <v>359</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F136" s="5">
-        <v>20123</v>
+        <v>90139</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>453</v>
+        <v>343</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>454</v>
+        <v>193</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F137" s="8" t="s">
-        <v>178</v>
+        <v>34</v>
+      </c>
+      <c r="F137" s="5">
+        <v>20123</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>281</v>
+        <v>453</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>306</v>
+        <v>7</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>307</v>
+        <v>454</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="F138" s="5">
-        <v>12037</v>
+        <v>8</v>
+      </c>
+      <c r="F138" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>305</v>
+        <v>75</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>11</v>
+        <v>281</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>7</v>
+        <v>306</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>12</v>
+        <v>307</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F139" s="5" t="s">
-        <v>13</v>
+        <v>308</v>
+      </c>
+      <c r="F139" s="5">
+        <v>12037</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>9</v>
+        <v>305</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>121</v>
+        <v>11</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>26</v>
@@ -5754,99 +5757,99 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>651</v>
+        <v>72</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>652</v>
+        <v>73</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F143" s="5">
-        <v>20124</v>
+        <v>8</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>676</v>
+        <v>651</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>350</v>
+        <v>32</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>677</v>
+        <v>652</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>678</v>
+        <v>34</v>
       </c>
       <c r="F144" s="5">
-        <v>15079</v>
+        <v>20124</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>679</v>
+        <v>157</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>25</v>
+        <v>676</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>26</v>
+        <v>350</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>27</v>
+        <v>677</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>29</v>
+        <v>678</v>
+      </c>
+      <c r="F145" s="5">
+        <v>15079</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>30</v>
+        <v>679</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>496</v>
+        <v>25</v>
       </c>
       <c r="B146" s="4" t="s">
         <v>26</v>
@@ -5860,8 +5863,8 @@
       <c r="E146" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F146" s="5">
-        <v>39100</v>
+      <c r="F146" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G146" s="4" t="s">
         <v>30</v>
@@ -5869,53 +5872,53 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>231</v>
+        <v>496</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>232</v>
+        <v>27</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>216</v>
+        <v>28</v>
+      </c>
+      <c r="F147" s="5">
+        <v>39100</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>588</v>
+        <v>231</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>589</v>
+        <v>232</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F148" s="5">
-        <v>20122</v>
+        <v>8</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>186</v>
+        <v>588</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>32</v>
@@ -5924,44 +5927,44 @@
         <v>653</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>187</v>
+        <v>589</v>
       </c>
       <c r="E149" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F149" s="5" t="s">
-        <v>188</v>
+      <c r="F149" s="5">
+        <v>20122</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>481</v>
+        <v>186</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>482</v>
+        <v>32</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>483</v>
+        <v>187</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="F150" s="5">
-        <v>66020</v>
+        <v>34</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>75</v>
+        <v>157</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>619</v>
+        <v>481</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>482</v>
@@ -5984,168 +5987,168 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>574</v>
+        <v>619</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>32</v>
+        <v>482</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>575</v>
+        <v>483</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>34</v>
+        <v>484</v>
       </c>
       <c r="F152" s="5">
-        <v>20124</v>
+        <v>66020</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>409</v>
+        <v>574</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>339</v>
+        <v>32</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>410</v>
+        <v>575</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="F153" s="5">
-        <v>37137</v>
+        <v>20124</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>341</v>
+        <v>157</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>458</v>
+        <v>409</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>7</v>
+        <v>339</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>459</v>
+        <v>410</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F154" s="8" t="s">
-        <v>216</v>
+        <v>411</v>
+      </c>
+      <c r="F154" s="5">
+        <v>37137</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>9</v>
+        <v>341</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>293</v>
+        <v>458</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>294</v>
+        <v>7</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>295</v>
+        <v>459</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="F155" s="5">
-        <v>56010</v>
+        <v>8</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>216</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>297</v>
+        <v>9</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>601</v>
+        <v>293</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>32</v>
+        <v>294</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>602</v>
+        <v>295</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="F156" s="5">
-        <v>20145</v>
+        <v>56010</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>134</v>
+        <v>297</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>309</v>
+        <v>601</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>310</v>
+        <v>602</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>311</v>
+        <v>34</v>
       </c>
       <c r="F157" s="5">
-        <v>40060</v>
+        <v>20145</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>382</v>
+        <v>309</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>383</v>
+        <v>310</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>34</v>
+        <v>311</v>
       </c>
       <c r="F158" s="5">
-        <v>20121</v>
+        <v>40060</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B159" s="4" t="s">
         <v>32</v>
@@ -6159,8 +6162,8 @@
       <c r="E159" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F159" s="5" t="s">
-        <v>56</v>
+      <c r="F159" s="5">
+        <v>20121</v>
       </c>
       <c r="G159" s="4" t="s">
         <v>36</v>
@@ -6168,53 +6171,53 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>211</v>
+        <v>384</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>177</v>
+        <v>383</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>178</v>
+        <v>56</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>573</v>
+        <v>211</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F161" s="5">
-        <v>20124</v>
+        <v>8</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>178</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>32</v>
@@ -6237,99 +6240,99 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>629</v>
+        <v>587</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>630</v>
+        <v>190</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>631</v>
+        <v>34</v>
       </c>
       <c r="F163" s="5">
-        <v>39025</v>
+        <v>20124</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>66</v>
+        <v>629</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>68</v>
+        <v>630</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F164" s="5" t="s">
-        <v>70</v>
+        <v>631</v>
+      </c>
+      <c r="F164" s="5">
+        <v>39025</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>282</v>
+        <v>66</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>312</v>
+        <v>67</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>313</v>
+        <v>68</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="F165" s="5">
-        <v>57021</v>
+        <v>69</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>297</v>
+        <v>71</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>182</v>
+        <v>282</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>7</v>
+        <v>312</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>177</v>
+        <v>313</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>178</v>
+        <v>314</v>
+      </c>
+      <c r="F166" s="5">
+        <v>57021</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>75</v>
+        <v>297</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>460</v>
+        <v>182</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>7</v>
@@ -6343,7 +6346,7 @@
       <c r="E167" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F167" s="8" t="s">
+      <c r="F167" s="5" t="s">
         <v>178</v>
       </c>
       <c r="G167" s="4" t="s">
@@ -6352,145 +6355,145 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>87</v>
+        <v>460</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>89</v>
+        <v>177</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>91</v>
+        <v>8</v>
+      </c>
+      <c r="F168" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>344</v>
+        <v>87</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>345</v>
+        <v>89</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="F169" s="5">
-        <v>70124</v>
+        <v>90</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>187</v>
+        <v>345</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>34</v>
+        <v>346</v>
       </c>
       <c r="F170" s="5">
-        <v>20158</v>
+        <v>70124</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>157</v>
+        <v>42</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>644</v>
+        <v>331</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>645</v>
+        <v>187</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F171" s="5">
-        <v>39100</v>
+        <v>20158</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>355</v>
+        <v>644</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>306</v>
+        <v>26</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>356</v>
+        <v>645</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>357</v>
+        <v>28</v>
       </c>
       <c r="F172" s="5">
-        <v>12084</v>
+        <v>39100</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>305</v>
+        <v>30</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>192</v>
+        <v>355</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>32</v>
+        <v>306</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>193</v>
+        <v>356</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>59</v>
+        <v>357</v>
+      </c>
+      <c r="F173" s="5">
+        <v>12084</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>36</v>
+        <v>305</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>32</v>
@@ -6499,13 +6502,13 @@
         <v>653</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
       <c r="E174" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="G174" s="4" t="s">
         <v>36</v>
@@ -6513,99 +6516,99 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>455</v>
+        <v>225</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>456</v>
+        <v>226</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F175" s="8" t="s">
-        <v>457</v>
+        <v>34</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>106</v>
+        <v>455</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>107</v>
+        <v>7</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>108</v>
+        <v>456</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>110</v>
+        <v>8</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>457</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>429</v>
+        <v>106</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>306</v>
+        <v>107</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>430</v>
+        <v>108</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="F177" s="5">
-        <v>12100</v>
+        <v>109</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>305</v>
+        <v>111</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>393</v>
+        <v>429</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>20</v>
+        <v>306</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>21</v>
+        <v>430</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>22</v>
+        <v>431</v>
       </c>
       <c r="F178" s="5">
-        <v>40127</v>
+        <v>12100</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>24</v>
+        <v>305</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>609</v>
+        <v>393</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>20</v>
@@ -6614,13 +6617,13 @@
         <v>653</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>610</v>
+        <v>21</v>
       </c>
       <c r="E179" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F179" s="5">
-        <v>40122</v>
+        <v>40127</v>
       </c>
       <c r="G179" s="4" t="s">
         <v>24</v>
@@ -6628,30 +6631,30 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>353</v>
+        <v>609</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>354</v>
+        <v>610</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F180" s="5">
-        <v>20121</v>
+        <v>40122</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>656</v>
+        <v>353</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>32</v>
@@ -6674,7 +6677,7 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>554</v>
+        <v>656</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>32</v>
@@ -6683,21 +6686,21 @@
         <v>653</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>523</v>
+        <v>354</v>
       </c>
       <c r="E182" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F182" s="5">
-        <v>20154</v>
+        <v>20121</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>32</v>
@@ -6720,7 +6723,7 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>32</v>
@@ -6743,7 +6746,7 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>594</v>
+        <v>522</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>32</v>
@@ -6752,7 +6755,7 @@
         <v>653</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>595</v>
+        <v>523</v>
       </c>
       <c r="E185" s="4" t="s">
         <v>34</v>
@@ -6766,30 +6769,30 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>513</v>
+        <v>594</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>27</v>
+        <v>595</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F186" s="5">
-        <v>39100</v>
+        <v>20154</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>230</v>
+        <v>513</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>26</v>
@@ -6803,8 +6806,8 @@
       <c r="E187" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F187" s="5" t="s">
-        <v>29</v>
+      <c r="F187" s="5">
+        <v>39100</v>
       </c>
       <c r="G187" s="4" t="s">
         <v>30</v>
@@ -6812,30 +6815,30 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>141</v>
+        <v>230</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>142</v>
+        <v>27</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>664</v>
+        <v>141</v>
       </c>
       <c r="B189" s="9" t="s">
         <v>32</v>
@@ -6844,13 +6847,13 @@
         <v>653</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>665</v>
+        <v>142</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F189" s="10">
-        <v>20123</v>
+      <c r="F189" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="G189" s="9" t="s">
         <v>36</v>
@@ -6858,7 +6861,7 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>54</v>
+        <v>664</v>
       </c>
       <c r="B190" s="9" t="s">
         <v>32</v>
@@ -6867,13 +6870,13 @@
         <v>653</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>55</v>
+        <v>665</v>
       </c>
       <c r="E190" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F190" s="10" t="s">
-        <v>56</v>
+      <c r="F190" s="10">
+        <v>20123</v>
       </c>
       <c r="G190" s="9" t="s">
         <v>36</v>
@@ -6881,7 +6884,7 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>439</v>
+        <v>54</v>
       </c>
       <c r="B191" s="9" t="s">
         <v>32</v>
@@ -6890,159 +6893,159 @@
         <v>653</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>440</v>
+        <v>55</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="F191" s="10">
-        <v>20038</v>
+        <v>34</v>
+      </c>
+      <c r="F191" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>134</v>
+        <v>36</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="B192" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D192" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="E192" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="F192" s="10">
+        <v>20038</v>
+      </c>
+      <c r="G192" s="9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A193" s="9" t="s">
         <v>424</v>
       </c>
-      <c r="B192" s="9" t="s">
+      <c r="B193" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C192" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D192" s="9" t="s">
+      <c r="C193" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D193" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="E192" s="9" t="s">
+      <c r="E193" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F192" s="10">
+      <c r="F193" s="10">
         <v>10121</v>
       </c>
-      <c r="G192" s="9" t="s">
+      <c r="G193" s="9" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A193" s="3" t="s">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A194" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="B193" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C193" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D193" s="3" t="s">
+      <c r="B194" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D194" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="E193" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F193" s="7">
+      <c r="E194" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F194" s="7">
         <v>20124</v>
       </c>
-      <c r="G193" s="3" t="s">
+      <c r="G194" s="3" t="s">
         <v>157</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A194" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B194" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D194" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E194" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F194" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="G194" s="9" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
-        <v>375</v>
+        <v>93</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>376</v>
+        <v>94</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>377</v>
+        <v>95</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="F195" s="10">
-        <v>64020</v>
+        <v>96</v>
+      </c>
+      <c r="F195" s="10" t="s">
+        <v>97</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
-        <v>578</v>
+        <v>375</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>7</v>
+        <v>376</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>579</v>
+        <v>377</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F196" s="12" t="s">
-        <v>580</v>
+        <v>378</v>
+      </c>
+      <c r="F196" s="10">
+        <v>64020</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>408</v>
+        <v>578</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>209</v>
+        <v>579</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F197" s="10">
-        <v>20121</v>
+        <v>8</v>
+      </c>
+      <c r="F197" s="12" t="s">
+        <v>580</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>131</v>
+        <v>408</v>
       </c>
       <c r="B198" s="9" t="s">
         <v>32</v>
@@ -7051,113 +7054,113 @@
         <v>653</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>132</v>
+        <v>209</v>
       </c>
       <c r="E198" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F198" s="10" t="s">
-        <v>133</v>
+      <c r="F198" s="10">
+        <v>20121</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>134</v>
+        <v>36</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>603</v>
+        <v>131</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>604</v>
+        <v>132</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F199" s="12" t="s">
-        <v>605</v>
+        <v>34</v>
+      </c>
+      <c r="F199" s="10" t="s">
+        <v>133</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
-        <v>255</v>
+        <v>603</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>256</v>
+        <v>604</v>
       </c>
       <c r="E200" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F200" s="10" t="s">
-        <v>56</v>
+        <v>8</v>
+      </c>
+      <c r="F200" s="12" t="s">
+        <v>605</v>
       </c>
       <c r="G200" s="9" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="9" t="s">
-        <v>338</v>
+        <v>255</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>339</v>
+        <v>32</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D201" s="9" t="s">
-        <v>340</v>
+        <v>256</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="F201" s="10">
-        <v>37045</v>
+        <v>34</v>
+      </c>
+      <c r="F201" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>341</v>
+        <v>36</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
-        <v>164</v>
+        <v>338</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>32</v>
+        <v>339</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>165</v>
+        <v>340</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F202" s="10" t="s">
-        <v>166</v>
+        <v>526</v>
+      </c>
+      <c r="F202" s="10">
+        <v>37045</v>
       </c>
       <c r="G202" s="9" t="s">
-        <v>157</v>
+        <v>341</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="9" t="s">
-        <v>527</v>
+        <v>164</v>
       </c>
       <c r="B203" s="9" t="s">
         <v>32</v>
@@ -7171,8 +7174,8 @@
       <c r="E203" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F203" s="10">
-        <v>20126</v>
+      <c r="F203" s="10" t="s">
+        <v>166</v>
       </c>
       <c r="G203" s="9" t="s">
         <v>157</v>
@@ -7180,7 +7183,7 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
-        <v>599</v>
+        <v>527</v>
       </c>
       <c r="B204" s="9" t="s">
         <v>32</v>
@@ -7189,21 +7192,21 @@
         <v>653</v>
       </c>
       <c r="D204" s="9" t="s">
-        <v>600</v>
+        <v>165</v>
       </c>
       <c r="E204" s="9" t="s">
         <v>34</v>
       </c>
       <c r="F204" s="10">
-        <v>20138</v>
+        <v>20126</v>
       </c>
       <c r="G204" s="9" t="s">
-        <v>260</v>
+        <v>157</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="9" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="B205" s="9" t="s">
         <v>32</v>
@@ -7212,21 +7215,21 @@
         <v>653</v>
       </c>
       <c r="D205" s="9" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>34</v>
       </c>
       <c r="F205" s="10">
-        <v>20122</v>
+        <v>20138</v>
       </c>
       <c r="G205" s="9" t="s">
-        <v>36</v>
+        <v>260</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="9" t="s">
-        <v>592</v>
+        <v>607</v>
       </c>
       <c r="B206" s="9" t="s">
         <v>32</v>
@@ -7235,13 +7238,13 @@
         <v>653</v>
       </c>
       <c r="D206" s="9" t="s">
-        <v>392</v>
+        <v>608</v>
       </c>
       <c r="E206" s="9" t="s">
         <v>34</v>
       </c>
       <c r="F206" s="10">
-        <v>20123</v>
+        <v>20122</v>
       </c>
       <c r="G206" s="9" t="s">
         <v>36</v>
@@ -7249,53 +7252,53 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="B207" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D207" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="E207" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F207" s="10">
+        <v>20123</v>
+      </c>
+      <c r="G207" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A208" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="B207" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D207" s="9" t="s">
+      <c r="B208" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D208" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="E207" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F207" s="10">
+      <c r="E208" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F208" s="10">
         <v>20135</v>
       </c>
-      <c r="G207" s="9" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A208" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="B208" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D208" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="E208" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F208" s="7">
-        <v>20135</v>
-      </c>
-      <c r="G208" s="3" t="s">
+      <c r="G208" s="9" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="3" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>32</v>
@@ -7317,100 +7320,100 @@
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A210" s="9" t="s">
+      <c r="A210" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F210" s="7">
+        <v>20135</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A211" s="9" t="s">
         <v>403</v>
       </c>
-      <c r="B210" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D210" s="9" t="s">
+      <c r="B211" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D211" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="E210" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F210" s="10">
+      <c r="E211" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F211" s="10">
         <v>20135</v>
       </c>
-      <c r="G210" s="9" t="s">
+      <c r="G211" s="9" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A211" s="3" t="s">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A212" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="B211" s="3" t="s">
+      <c r="B212" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C211" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D211" s="3" t="s">
+      <c r="C212" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D212" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="E211" s="3" t="s">
+      <c r="E212" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="F211" s="7">
+      <c r="F212" s="7">
         <v>85100</v>
       </c>
-      <c r="G211" s="3" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A212" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="B212" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D212" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="E212" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="F212" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="G212" s="9" t="s">
+      <c r="G212" s="3" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="9" t="s">
-        <v>451</v>
+        <v>202</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>32</v>
+        <v>183</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D213" s="9" t="s">
-        <v>452</v>
+        <v>203</v>
       </c>
       <c r="E213" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F213" s="10">
-        <v>20144</v>
+        <v>184</v>
+      </c>
+      <c r="F213" s="10" t="s">
+        <v>185</v>
       </c>
       <c r="G213" s="9" t="s">
-        <v>36</v>
+        <v>317</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="9" t="s">
-        <v>221</v>
+        <v>451</v>
       </c>
       <c r="B214" s="9" t="s">
         <v>32</v>
@@ -7419,343 +7422,343 @@
         <v>653</v>
       </c>
       <c r="D214" s="9" t="s">
-        <v>222</v>
+        <v>452</v>
       </c>
       <c r="E214" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F214" s="10" t="s">
-        <v>133</v>
+      <c r="F214" s="10">
+        <v>20144</v>
       </c>
       <c r="G214" s="9" t="s">
-        <v>134</v>
+        <v>36</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="B215" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D215" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="E215" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F215" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="G215" s="9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A216" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="B215" s="9" t="s">
+      <c r="B216" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C215" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D215" s="9" t="s">
+      <c r="C216" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D216" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="E215" s="9" t="s">
+      <c r="E216" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="F215" s="10">
+      <c r="F216" s="10">
         <v>40026</v>
       </c>
-      <c r="G215" s="9" t="s">
+      <c r="G216" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A216" s="3" t="s">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A217" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="B216" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D216" s="3" t="s">
+      <c r="B217" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D217" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="E216" s="3" t="s">
+      <c r="E217" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="F216" s="7">
+      <c r="F217" s="7">
         <v>20068</v>
       </c>
-      <c r="G216" s="3" t="s">
+      <c r="G217" s="3" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A217" s="9" t="s">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A218" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="B217" s="9" t="s">
+      <c r="B218" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C217" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D217" s="9" t="s">
+      <c r="C218" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D218" s="9" t="s">
         <v>318</v>
       </c>
-      <c r="E217" s="9" t="s">
+      <c r="E218" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F217" s="10" t="s">
+      <c r="F218" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="G217" s="9" t="s">
+      <c r="G218" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A218" s="3" t="s">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A219" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="B218" s="3" t="s">
+      <c r="B219" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C218" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D218" s="3" t="s">
+      <c r="C219" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D219" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="E218" s="3" t="s">
+      <c r="E219" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F218" s="11" t="s">
+      <c r="F219" s="11" t="s">
         <v>661</v>
       </c>
-      <c r="G218" s="3" t="s">
+      <c r="G219" s="3" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A219" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="B219" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D219" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E219" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F219" s="10">
-        <v>39100</v>
-      </c>
-      <c r="G219" s="9" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="9" t="s">
-        <v>365</v>
+        <v>531</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D220" s="9" t="s">
-        <v>366</v>
+        <v>27</v>
       </c>
       <c r="E220" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F220" s="10">
-        <v>20123</v>
+        <v>39100</v>
       </c>
       <c r="G220" s="9" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="9" t="s">
-        <v>285</v>
+        <v>365</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>306</v>
+        <v>32</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D221" s="9" t="s">
-        <v>319</v>
+        <v>366</v>
       </c>
       <c r="E221" s="9" t="s">
-        <v>320</v>
+        <v>34</v>
       </c>
       <c r="F221" s="10">
-        <v>12020</v>
+        <v>20123</v>
       </c>
       <c r="G221" s="9" t="s">
-        <v>305</v>
+        <v>36</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="9" t="s">
-        <v>37</v>
+        <v>285</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>38</v>
+        <v>306</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D222" s="9" t="s">
-        <v>39</v>
+        <v>319</v>
       </c>
       <c r="E222" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F222" s="10" t="s">
-        <v>41</v>
+        <v>320</v>
+      </c>
+      <c r="F222" s="10">
+        <v>12020</v>
       </c>
       <c r="G222" s="9" t="s">
-        <v>42</v>
+        <v>305</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="9" t="s">
-        <v>419</v>
+        <v>37</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>420</v>
+        <v>38</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D223" s="9" t="s">
-        <v>421</v>
+        <v>39</v>
       </c>
       <c r="E223" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="F223" s="10">
-        <v>28053</v>
+        <v>40</v>
+      </c>
+      <c r="F223" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="G223" s="9" t="s">
-        <v>134</v>
+        <v>42</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="9" t="s">
-        <v>170</v>
+        <v>419</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>32</v>
+        <v>420</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D224" s="9" t="s">
-        <v>167</v>
+        <v>421</v>
       </c>
       <c r="E224" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="F224" s="10" t="s">
-        <v>169</v>
+        <v>422</v>
+      </c>
+      <c r="F224" s="10">
+        <v>28053</v>
       </c>
       <c r="G224" s="9" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="9" t="s">
-        <v>558</v>
+        <v>170</v>
       </c>
       <c r="B225" s="9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D225" s="9" t="s">
-        <v>559</v>
+        <v>167</v>
       </c>
       <c r="E225" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F225" s="10">
-        <v>39100</v>
+        <v>168</v>
+      </c>
+      <c r="F225" s="10" t="s">
+        <v>169</v>
       </c>
       <c r="G225" s="9" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="9" t="s">
-        <v>196</v>
+        <v>558</v>
       </c>
       <c r="B226" s="9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D226" s="9" t="s">
-        <v>197</v>
+        <v>559</v>
       </c>
       <c r="E226" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F226" s="10" t="s">
-        <v>198</v>
+        <v>28</v>
+      </c>
+      <c r="F226" s="10">
+        <v>39100</v>
       </c>
       <c r="G226" s="9" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="9" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D227" s="9" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="E227" s="9" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="F227" s="10" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="G227" s="9" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="9" t="s">
-        <v>242</v>
+        <v>205</v>
       </c>
       <c r="B228" s="9" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D228" s="9" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="E228" s="9" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="F228" s="10" t="s">
-        <v>56</v>
+        <v>207</v>
       </c>
       <c r="G228" s="9" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="9" t="s">
-        <v>532</v>
+        <v>242</v>
       </c>
       <c r="B229" s="9" t="s">
         <v>32</v>
@@ -7769,8 +7772,8 @@
       <c r="E229" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F229" s="10">
-        <v>20121</v>
+      <c r="F229" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="G229" s="9" t="s">
         <v>36</v>
@@ -7778,7 +7781,7 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="9" t="s">
-        <v>576</v>
+        <v>532</v>
       </c>
       <c r="B230" s="9" t="s">
         <v>32</v>
@@ -7787,7 +7790,7 @@
         <v>653</v>
       </c>
       <c r="D230" s="9" t="s">
-        <v>577</v>
+        <v>175</v>
       </c>
       <c r="E230" s="9" t="s">
         <v>34</v>
@@ -7801,159 +7804,159 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="9" t="s">
-        <v>443</v>
+        <v>576</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>444</v>
+        <v>32</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D231" s="9" t="s">
-        <v>445</v>
+        <v>577</v>
       </c>
       <c r="E231" s="9" t="s">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="F231" s="10">
-        <v>53048</v>
+        <v>20121</v>
       </c>
       <c r="G231" s="9" t="s">
-        <v>447</v>
+        <v>36</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="9" t="s">
-        <v>514</v>
+        <v>443</v>
       </c>
       <c r="B232" s="9" t="s">
-        <v>507</v>
+        <v>444</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D232" s="9" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
       <c r="E232" s="9" t="s">
-        <v>516</v>
+        <v>446</v>
       </c>
       <c r="F232" s="10">
-        <v>35011</v>
+        <v>53048</v>
       </c>
       <c r="G232" s="9" t="s">
-        <v>503</v>
+        <v>447</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="9" t="s">
-        <v>241</v>
+        <v>514</v>
       </c>
       <c r="B233" s="9" t="s">
-        <v>32</v>
+        <v>507</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D233" s="9" t="s">
-        <v>175</v>
+        <v>515</v>
       </c>
       <c r="E233" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F233" s="10" t="s">
-        <v>56</v>
+        <v>516</v>
+      </c>
+      <c r="F233" s="10">
+        <v>35011</v>
       </c>
       <c r="G233" s="9" t="s">
-        <v>36</v>
+        <v>503</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="B234" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D234" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E234" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F234" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G234" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A235" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B234" s="9" t="s">
+      <c r="B235" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C234" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D234" s="9" t="s">
+      <c r="C235" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D235" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="E234" s="9" t="s">
+      <c r="E235" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F234" s="10" t="s">
+      <c r="F235" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G234" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A235" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="B235" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D235" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E235" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F235" s="7">
-        <v>39100</v>
-      </c>
-      <c r="G235" s="3" t="s">
+      <c r="G235" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F236" s="7">
+        <v>39100</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A237" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="B236" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C236" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D236" s="3" t="s">
+      <c r="B237" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D237" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="E236" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F236" s="7">
-        <v>20121</v>
-      </c>
-      <c r="G236" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A237" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="B237" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C237" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D237" s="9" t="s">
-        <v>530</v>
-      </c>
-      <c r="E237" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F237" s="10">
+      <c r="E237" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F237" s="7">
         <v>20121</v>
       </c>
       <c r="G237" s="9" t="s">
@@ -7962,352 +7965,352 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="B238" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D238" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="E238" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F238" s="10">
+        <v>20121</v>
+      </c>
+      <c r="G238" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A239" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B238" s="9" t="s">
+      <c r="B239" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C238" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D238" s="9" t="s">
+      <c r="C239" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D239" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E238" s="9" t="s">
+      <c r="E239" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F238" s="10" t="s">
+      <c r="F239" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G238" s="9" t="s">
+      <c r="G239" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A239" s="3" t="s">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A240" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="B239" s="3" t="s">
+      <c r="B240" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C239" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D239" s="3" t="s">
+      <c r="C240" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D240" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="E239" s="3" t="s">
+      <c r="E240" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F239" s="11" t="s">
+      <c r="F240" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="G239" s="3" t="s">
+      <c r="G240" s="3" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A240" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="B240" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C240" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D240" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="E240" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="F240" s="10">
-        <v>20089</v>
-      </c>
-      <c r="G240" s="9" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" s="9" t="s">
-        <v>473</v>
+        <v>379</v>
       </c>
       <c r="B241" s="9" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D241" s="9" t="s">
-        <v>474</v>
+        <v>380</v>
       </c>
       <c r="E241" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F241" s="12" t="s">
-        <v>475</v>
+        <v>381</v>
+      </c>
+      <c r="F241" s="10">
+        <v>20089</v>
       </c>
       <c r="G241" s="9" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" s="9" t="s">
-        <v>210</v>
+        <v>473</v>
       </c>
       <c r="B242" s="9" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D242" s="9" t="s">
-        <v>200</v>
+        <v>474</v>
       </c>
       <c r="E242" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F242" s="10" t="s">
-        <v>201</v>
+        <v>8</v>
+      </c>
+      <c r="F242" s="12" t="s">
+        <v>475</v>
       </c>
       <c r="G242" s="9" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B243" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D243" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="E243" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F243" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="G243" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A244" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B243" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C243" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D243" s="9" t="s">
+      <c r="B244" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D244" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="E243" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F243" s="10" t="s">
+      <c r="E244" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F244" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="G243" s="9" t="s">
+      <c r="G244" s="9" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A244" s="3" t="s">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A245" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="B244" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C244" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D244" s="3" t="s">
+      <c r="B245" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D245" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="E244" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F244" s="7">
+      <c r="E245" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F245" s="7">
         <v>20124</v>
       </c>
-      <c r="G244" s="3" t="s">
+      <c r="G245" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A245" s="9" t="s">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A246" s="9" t="s">
         <v>436</v>
       </c>
-      <c r="B245" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C245" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D245" s="9" t="s">
+      <c r="B246" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D246" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="E245" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F245" s="10">
+      <c r="E246" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F246" s="10">
         <v>20124</v>
       </c>
-      <c r="G245" s="9" t="s">
+      <c r="G246" s="9" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A246" s="3" t="s">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A247" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="B246" s="3" t="s">
+      <c r="B247" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C246" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D246" s="3" t="s">
+      <c r="C247" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D247" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="E246" s="3" t="s">
+      <c r="E247" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F246" s="7">
+      <c r="F247" s="7">
         <v>24050</v>
       </c>
-      <c r="G246" s="3" t="s">
+      <c r="G247" s="3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A247" s="9" t="s">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A248" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="B247" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C247" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D247" s="9" t="s">
+      <c r="B248" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D248" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="E247" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F247" s="10" t="s">
+      <c r="E248" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F248" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="G247" s="9" t="s">
+      <c r="G248" s="9" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A248" s="3" t="s">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A249" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="B248" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C248" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D248" s="3" t="s">
+      <c r="B249" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D249" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="E248" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F248" s="7">
+      <c r="E249" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F249" s="7">
         <v>20148</v>
       </c>
-      <c r="G248" s="3" t="s">
+      <c r="G249" s="3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A249" s="9" t="s">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A250" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="B249" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C249" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D249" s="9" t="s">
+      <c r="B250" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C250" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D250" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="E249" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F249" s="10" t="s">
+      <c r="E250" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F250" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="G249" s="9" t="s">
+      <c r="G250" s="9" t="s">
         <v>134</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A250" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="B250" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C250" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D250" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="E250" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="F250" s="7">
-        <v>25055</v>
-      </c>
-      <c r="G250" s="3" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C251" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="E251" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="F251" s="7">
+        <v>25055</v>
+      </c>
+      <c r="G251" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A252" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="B251" s="3" t="s">
+      <c r="B252" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="C251" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D251" s="3" t="s">
+      <c r="C252" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D252" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="E251" s="3" t="s">
+      <c r="E252" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="F251" s="7">
+      <c r="F252" s="7">
         <v>50132</v>
       </c>
-      <c r="G251" s="3" t="s">
+      <c r="G252" s="3" t="s">
         <v>447</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A252" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="B252" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C252" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D252" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="E252" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F252" s="10">
-        <v>20129</v>
-      </c>
-      <c r="G252" s="9" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" s="9" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="B253" s="9" t="s">
         <v>32</v>
@@ -8330,7 +8333,7 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" s="9" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="B254" s="9" t="s">
         <v>32</v>
@@ -8353,7 +8356,7 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" s="9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B255" s="9" t="s">
         <v>32</v>
@@ -8376,7 +8379,7 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" s="9" t="s">
-        <v>174</v>
+        <v>472</v>
       </c>
       <c r="B256" s="9" t="s">
         <v>32</v>
@@ -8385,228 +8388,228 @@
         <v>653</v>
       </c>
       <c r="D256" s="9" t="s">
-        <v>175</v>
+        <v>462</v>
       </c>
       <c r="E256" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F256" s="10" t="s">
-        <v>56</v>
+      <c r="F256" s="10">
+        <v>20129</v>
       </c>
       <c r="G256" s="9" t="s">
-        <v>36</v>
+        <v>260</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" s="9" t="s">
-        <v>329</v>
+        <v>174</v>
       </c>
       <c r="B257" s="9" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C257" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D257" s="9" t="s">
-        <v>330</v>
+        <v>175</v>
       </c>
       <c r="E257" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="F257" s="10">
-        <v>40026</v>
+        <v>34</v>
+      </c>
+      <c r="F257" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="G257" s="9" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" s="9" t="s">
-        <v>286</v>
+        <v>329</v>
       </c>
       <c r="B258" s="9" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C258" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D258" s="9" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="E258" s="9" t="s">
-        <v>34</v>
+        <v>316</v>
       </c>
       <c r="F258" s="10">
-        <v>20124</v>
+        <v>40026</v>
       </c>
       <c r="G258" s="9" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="B259" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D259" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="E259" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F259" s="10">
+        <v>20124</v>
+      </c>
+      <c r="G259" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A260" s="9" t="s">
         <v>448</v>
       </c>
-      <c r="B259" s="9" t="s">
+      <c r="B260" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="C259" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D259" s="9" t="s">
+      <c r="C260" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D260" s="9" t="s">
         <v>449</v>
       </c>
-      <c r="E259" s="9" t="s">
+      <c r="E260" s="9" t="s">
         <v>450</v>
       </c>
-      <c r="F259" s="10">
+      <c r="F260" s="10">
         <v>12011</v>
       </c>
-      <c r="G259" s="9" t="s">
+      <c r="G260" s="9" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A260" s="3" t="s">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A261" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="B260" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C260" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D260" s="3" t="s">
+      <c r="B261" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D261" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="E260" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F260" s="7">
+      <c r="E261" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F261" s="7">
         <v>20121</v>
       </c>
-      <c r="G260" s="3" t="s">
+      <c r="G261" s="3" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A261" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="B261" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="C261" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D261" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E261" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F261" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="G261" s="9" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" s="9" t="s">
-        <v>417</v>
+        <v>149</v>
       </c>
       <c r="B262" s="9" t="s">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="C262" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D262" s="9" t="s">
-        <v>418</v>
+        <v>151</v>
       </c>
       <c r="E262" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F262" s="10">
-        <v>20123</v>
+        <v>152</v>
+      </c>
+      <c r="F262" s="10" t="s">
+        <v>153</v>
       </c>
       <c r="G262" s="9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" s="9" t="s">
-        <v>489</v>
+        <v>417</v>
       </c>
       <c r="B263" s="9" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C263" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D263" s="9" t="s">
-        <v>490</v>
+        <v>418</v>
       </c>
       <c r="E263" s="9" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F263" s="10">
-        <v>90141</v>
+        <v>20123</v>
       </c>
       <c r="G263" s="9" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="B264" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C264" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D264" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="E264" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F264" s="10">
+        <v>90141</v>
+      </c>
+      <c r="G264" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A265" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="B264" s="9" t="s">
+      <c r="B265" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C264" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D264" s="9" t="s">
+      <c r="C265" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D265" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="E264" s="9" t="s">
+      <c r="E265" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F264" s="12" t="s">
+      <c r="F265" s="12" t="s">
         <v>388</v>
       </c>
-      <c r="G264" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A265" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="B265" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C265" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D265" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="E265" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F265" s="11" t="s">
-        <v>388</v>
-      </c>
-      <c r="G265" s="3" t="s">
+      <c r="G265" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" s="3" t="s">
-        <v>528</v>
+        <v>640</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>7</v>
@@ -8628,399 +8631,399 @@
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A267" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="B267" s="9" t="s">
+      <c r="A267" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="B267" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C267" s="4" t="s">
         <v>653</v>
       </c>
-      <c r="D267" s="9" t="s">
+      <c r="D267" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="E267" s="9" t="s">
+      <c r="E267" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F267" s="10" t="s">
+      <c r="F267" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="G267" s="9" t="s">
+      <c r="G267" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="B268" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D268" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="E268" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F268" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="G268" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A269" s="9" t="s">
         <v>463</v>
       </c>
-      <c r="B268" s="9" t="s">
+      <c r="B269" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="C268" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D268" s="9" t="s">
+      <c r="C269" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D269" s="9" t="s">
         <v>464</v>
       </c>
-      <c r="E268" s="9" t="s">
+      <c r="E269" s="9" t="s">
         <v>465</v>
       </c>
-      <c r="F268" s="10">
+      <c r="F269" s="10">
         <v>38055</v>
       </c>
-      <c r="G268" s="9" t="s">
+      <c r="G269" s="9" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A269" s="3" t="s">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A270" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="B269" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C269" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D269" s="3" t="s">
+      <c r="B270" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D270" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E269" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F269" s="7">
+      <c r="E270" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F270" s="7">
         <v>20145</v>
       </c>
-      <c r="G269" s="3" t="s">
+      <c r="G270" s="3" t="s">
         <v>134</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A270" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="B270" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C270" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D270" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="E270" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="F270" s="10">
-        <v>25010</v>
-      </c>
-      <c r="G270" s="9" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="B271" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C271" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D271" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="E271" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="F271" s="10">
+        <v>25010</v>
+      </c>
+      <c r="G271" s="9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A272" s="9" t="s">
         <v>391</v>
       </c>
-      <c r="B271" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C271" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D271" s="9" t="s">
+      <c r="B272" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D272" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="E271" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F271" s="10">
+      <c r="E272" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F272" s="10">
         <v>20123</v>
       </c>
-      <c r="G271" s="9" t="s">
+      <c r="G272" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A272" s="3" t="s">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A273" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="B272" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C272" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D272" s="3" t="s">
+      <c r="B273" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C273" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D273" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="E272" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F272" s="7">
+      <c r="E273" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F273" s="7">
         <v>20123</v>
       </c>
-      <c r="G272" s="3" t="s">
+      <c r="G273" s="3" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A273" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="B273" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C273" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D273" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="E273" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="F273" s="10">
-        <v>71016</v>
-      </c>
-      <c r="G273" s="9" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="B274" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D274" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="E274" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="F274" s="10">
+        <v>71016</v>
+      </c>
+      <c r="G274" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A275" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B274" s="9" t="s">
+      <c r="B275" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C274" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D274" s="9" t="s">
+      <c r="C275" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D275" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E274" s="9" t="s">
+      <c r="E275" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F274" s="10" t="s">
+      <c r="F275" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G274" s="9" t="s">
+      <c r="G275" s="9" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A275" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="B275" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C275" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D275" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="E275" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F275" s="7">
-        <v>20123</v>
-      </c>
-      <c r="G275" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C276" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="E276" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F276" s="7">
+        <v>20123</v>
+      </c>
+      <c r="G276" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A277" s="3" t="s">
         <v>682</v>
       </c>
-      <c r="B276" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C276" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="D276" s="3" t="s">
+      <c r="B277" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C277" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D277" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="E276" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F276" s="7">
+      <c r="E277" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F277" s="7">
         <v>20145</v>
       </c>
-      <c r="G276" s="3" t="s">
+      <c r="G277" s="3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A277" s="9" t="s">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A278" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="B277" s="9" t="s">
+      <c r="B278" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C277" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D277" s="9" t="s">
+      <c r="C278" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D278" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="E277" s="9" t="s">
+      <c r="E278" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="F277" s="10" t="s">
+      <c r="F278" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="G277" s="9" t="s">
+      <c r="G278" s="9" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A278" s="3" t="s">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A279" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="B278" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C278" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D278" s="3" t="s">
+      <c r="B279" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C279" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D279" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="E278" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F278" s="7">
+      <c r="E279" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F279" s="7">
         <v>20122</v>
       </c>
-      <c r="G278" s="3" t="s">
+      <c r="G279" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A279" s="9" t="s">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A280" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="B279" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C279" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D279" s="9" t="s">
+      <c r="B280" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C280" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D280" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="E279" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F279" s="10" t="s">
+      <c r="E280" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F280" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="G279" s="9" t="s">
+      <c r="G280" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A280" s="3" t="s">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A281" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="B280" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C280" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D280" s="3" t="s">
+      <c r="B281" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C281" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D281" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="E280" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F280" s="7">
+      <c r="E281" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F281" s="7">
         <v>20123</v>
       </c>
-      <c r="G280" s="3" t="s">
+      <c r="G281" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A281" s="9" t="s">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A282" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="B281" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C281" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D281" s="9" t="s">
+      <c r="B282" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C282" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D282" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="E281" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F281" s="10">
+      <c r="E282" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F282" s="10">
         <v>20123</v>
       </c>
-      <c r="G281" s="9" t="s">
+      <c r="G282" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A282" s="3" t="s">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A283" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="B282" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C282" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D282" s="3" t="s">
+      <c r="B283" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C283" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D283" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="E282" s="3" t="s">
+      <c r="E283" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F282" s="7">
+      <c r="F283" s="7">
         <v>20094</v>
       </c>
-      <c r="G282" s="3" t="s">
+      <c r="G283" s="3" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A283" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="B283" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C283" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D283" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="E283" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F283" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="G283" s="9" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" s="9" t="s">
-        <v>214</v>
+        <v>394</v>
       </c>
       <c r="B284" s="9" t="s">
         <v>7</v>
@@ -9043,53 +9046,53 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" s="9" t="s">
-        <v>158</v>
+        <v>214</v>
       </c>
       <c r="B285" s="9" t="s">
-        <v>159</v>
+        <v>7</v>
       </c>
       <c r="C285" s="9" t="s">
         <v>653</v>
       </c>
       <c r="D285" s="9" t="s">
-        <v>160</v>
+        <v>215</v>
       </c>
       <c r="E285" s="9" t="s">
-        <v>161</v>
+        <v>8</v>
       </c>
       <c r="F285" s="10" t="s">
-        <v>162</v>
+        <v>216</v>
       </c>
       <c r="G285" s="9" t="s">
-        <v>163</v>
+        <v>9</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286" s="9" t="s">
-        <v>432</v>
+        <v>158</v>
       </c>
       <c r="B286" s="9" t="s">
-        <v>7</v>
+        <v>159</v>
       </c>
       <c r="C286" s="9" t="s">
         <v>653</v>
       </c>
       <c r="D286" s="9" t="s">
-        <v>215</v>
+        <v>160</v>
       </c>
       <c r="E286" s="9" t="s">
-        <v>8</v>
+        <v>161</v>
       </c>
       <c r="F286" s="10" t="s">
-        <v>216</v>
+        <v>162</v>
       </c>
       <c r="G286" s="9" t="s">
-        <v>9</v>
+        <v>163</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287" s="9" t="s">
-        <v>253</v>
+        <v>432</v>
       </c>
       <c r="B287" s="9" t="s">
         <v>7</v>
@@ -9112,30 +9115,53 @@
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="B288" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C288" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D288" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="E288" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F288" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="G288" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A289" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="B288" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C288" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D288" s="9" t="s">
+      <c r="B289" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C289" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D289" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="E288" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F288" s="10" t="s">
+      <c r="E289" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F289" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="G288" s="9" t="s">
+      <c r="G289" s="9" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G218" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G288">
+    <sortState ref="A2:G289">
       <sortCondition ref="A1:A218"/>
     </sortState>
   </autoFilter>
@@ -9148,23 +9174,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F040406D9EE34E48977C379A242BB45D" ma:contentTypeVersion="15" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="1ab2d492e43f6bec9a26aa4599c840e9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="877b7d34-4df7-40bf-9eb1-208952470e96" xmlns:ns4="05fc27dd-4454-4248-9c78-3d72b2b155c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebc604e5d4aadf5a992ba83f8d4fb519" ns3:_="" ns4:_="">
     <xsd:import namespace="877b7d34-4df7-40bf-9eb1-208952470e96"/>
@@ -9397,32 +9406,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBC6436E-C4E7-4E8D-94E8-64DAEC05792B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9439,4 +9440,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{35A2E496-1210-4BA4-9F9C-3D5DBEB59194}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{006EA0E2-4EE9-4B4F-8989-9D92DF729528}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1858" uniqueCount="684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1864" uniqueCount="685">
   <si>
     <t>Nome account</t>
   </si>
@@ -2075,6 +2075,9 @@
   </si>
   <si>
     <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
+  </si>
+  <si>
+    <t>INE NARDO' SRL</t>
   </si>
 </sst>
 </file>
@@ -2499,7 +2502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G289"/>
+  <dimension ref="A1:G290"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -5895,53 +5898,53 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>231</v>
+        <v>684</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C148" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C148" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>232</v>
+        <v>27</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>216</v>
+        <v>28</v>
+      </c>
+      <c r="F148" s="5">
+        <v>39100</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>588</v>
+        <v>231</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>589</v>
+        <v>232</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F149" s="5">
-        <v>20122</v>
+        <v>8</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>186</v>
+        <v>588</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>32</v>
@@ -5950,44 +5953,44 @@
         <v>653</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>187</v>
+        <v>589</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F150" s="5" t="s">
-        <v>188</v>
+      <c r="F150" s="5">
+        <v>20122</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>481</v>
+        <v>186</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>482</v>
+        <v>32</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>483</v>
+        <v>187</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="F151" s="5">
-        <v>66020</v>
+        <v>34</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>75</v>
+        <v>157</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>619</v>
+        <v>481</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>482</v>
@@ -6010,168 +6013,168 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>574</v>
+        <v>619</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>32</v>
+        <v>482</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>575</v>
+        <v>483</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>34</v>
+        <v>484</v>
       </c>
       <c r="F153" s="5">
-        <v>20124</v>
+        <v>66020</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>409</v>
+        <v>574</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>339</v>
+        <v>32</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>410</v>
+        <v>575</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="F154" s="5">
-        <v>37137</v>
+        <v>20124</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>341</v>
+        <v>157</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>458</v>
+        <v>409</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>7</v>
+        <v>339</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>459</v>
+        <v>410</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F155" s="8" t="s">
-        <v>216</v>
+        <v>411</v>
+      </c>
+      <c r="F155" s="5">
+        <v>37137</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>9</v>
+        <v>341</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>293</v>
+        <v>458</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>294</v>
+        <v>7</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>295</v>
+        <v>459</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="F156" s="5">
-        <v>56010</v>
+        <v>8</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>216</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>297</v>
+        <v>9</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>601</v>
+        <v>293</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>32</v>
+        <v>294</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>602</v>
+        <v>295</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="F157" s="5">
-        <v>20145</v>
+        <v>56010</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>134</v>
+        <v>297</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>309</v>
+        <v>601</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>310</v>
+        <v>602</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>311</v>
+        <v>34</v>
       </c>
       <c r="F158" s="5">
-        <v>40060</v>
+        <v>20145</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>382</v>
+        <v>309</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>383</v>
+        <v>310</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>34</v>
+        <v>311</v>
       </c>
       <c r="F159" s="5">
-        <v>20121</v>
+        <v>40060</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>32</v>
@@ -6185,8 +6188,8 @@
       <c r="E160" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F160" s="5" t="s">
-        <v>56</v>
+      <c r="F160" s="5">
+        <v>20121</v>
       </c>
       <c r="G160" s="4" t="s">
         <v>36</v>
@@ -6194,53 +6197,53 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>211</v>
+        <v>384</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>177</v>
+        <v>383</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>178</v>
+        <v>56</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>573</v>
+        <v>211</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F162" s="5">
-        <v>20124</v>
+        <v>8</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>178</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>32</v>
@@ -6263,99 +6266,99 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>629</v>
+        <v>587</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>630</v>
+        <v>190</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>631</v>
+        <v>34</v>
       </c>
       <c r="F164" s="5">
-        <v>39025</v>
+        <v>20124</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>66</v>
+        <v>629</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>68</v>
+        <v>630</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F165" s="5" t="s">
-        <v>70</v>
+        <v>631</v>
+      </c>
+      <c r="F165" s="5">
+        <v>39025</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>282</v>
+        <v>66</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>312</v>
+        <v>67</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>313</v>
+        <v>68</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="F166" s="5">
-        <v>57021</v>
+        <v>69</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>297</v>
+        <v>71</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>182</v>
+        <v>282</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>7</v>
+        <v>312</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>177</v>
+        <v>313</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>178</v>
+        <v>314</v>
+      </c>
+      <c r="F167" s="5">
+        <v>57021</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>75</v>
+        <v>297</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>460</v>
+        <v>182</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>7</v>
@@ -6369,7 +6372,7 @@
       <c r="E168" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F168" s="8" t="s">
+      <c r="F168" s="5" t="s">
         <v>178</v>
       </c>
       <c r="G168" s="4" t="s">
@@ -6378,145 +6381,145 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>87</v>
+        <v>460</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>89</v>
+        <v>177</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>91</v>
+        <v>8</v>
+      </c>
+      <c r="F169" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>344</v>
+        <v>87</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>345</v>
+        <v>89</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="F170" s="5">
-        <v>70124</v>
+        <v>90</v>
+      </c>
+      <c r="F170" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>187</v>
+        <v>345</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>34</v>
+        <v>346</v>
       </c>
       <c r="F171" s="5">
-        <v>20158</v>
+        <v>70124</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>157</v>
+        <v>42</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>644</v>
+        <v>331</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>645</v>
+        <v>187</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F172" s="5">
-        <v>39100</v>
+        <v>20158</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>355</v>
+        <v>644</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>306</v>
+        <v>26</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>356</v>
+        <v>645</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>357</v>
+        <v>28</v>
       </c>
       <c r="F173" s="5">
-        <v>12084</v>
+        <v>39100</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>305</v>
+        <v>30</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>192</v>
+        <v>355</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>32</v>
+        <v>306</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>193</v>
+        <v>356</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F174" s="5" t="s">
-        <v>59</v>
+        <v>357</v>
+      </c>
+      <c r="F174" s="5">
+        <v>12084</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>36</v>
+        <v>305</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>32</v>
@@ -6525,13 +6528,13 @@
         <v>653</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
       <c r="E175" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="G175" s="4" t="s">
         <v>36</v>
@@ -6539,99 +6542,99 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>455</v>
+        <v>225</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>456</v>
+        <v>226</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F176" s="8" t="s">
-        <v>457</v>
+        <v>34</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>106</v>
+        <v>455</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>107</v>
+        <v>7</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>108</v>
+        <v>456</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F177" s="5" t="s">
-        <v>110</v>
+        <v>8</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>457</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>429</v>
+        <v>106</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>306</v>
+        <v>107</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>430</v>
+        <v>108</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="F178" s="5">
-        <v>12100</v>
+        <v>109</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>305</v>
+        <v>111</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>393</v>
+        <v>429</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>20</v>
+        <v>306</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>21</v>
+        <v>430</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>22</v>
+        <v>431</v>
       </c>
       <c r="F179" s="5">
-        <v>40127</v>
+        <v>12100</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>24</v>
+        <v>305</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>609</v>
+        <v>393</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>20</v>
@@ -6640,13 +6643,13 @@
         <v>653</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>610</v>
+        <v>21</v>
       </c>
       <c r="E180" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F180" s="5">
-        <v>40122</v>
+        <v>40127</v>
       </c>
       <c r="G180" s="4" t="s">
         <v>24</v>
@@ -6654,30 +6657,30 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>353</v>
+        <v>609</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>354</v>
+        <v>610</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F181" s="5">
-        <v>20121</v>
+        <v>40122</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>656</v>
+        <v>353</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>32</v>
@@ -6700,7 +6703,7 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>554</v>
+        <v>656</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>32</v>
@@ -6709,21 +6712,21 @@
         <v>653</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>523</v>
+        <v>354</v>
       </c>
       <c r="E183" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F183" s="5">
-        <v>20154</v>
+        <v>20121</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>32</v>
@@ -6746,7 +6749,7 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>32</v>
@@ -6769,7 +6772,7 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>594</v>
+        <v>522</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>32</v>
@@ -6778,7 +6781,7 @@
         <v>653</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>595</v>
+        <v>523</v>
       </c>
       <c r="E186" s="4" t="s">
         <v>34</v>
@@ -6792,30 +6795,30 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>513</v>
+        <v>594</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>27</v>
+        <v>595</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F187" s="5">
-        <v>39100</v>
+        <v>20154</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>230</v>
+        <v>513</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>26</v>
@@ -6829,8 +6832,8 @@
       <c r="E188" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F188" s="5" t="s">
-        <v>29</v>
+      <c r="F188" s="5">
+        <v>39100</v>
       </c>
       <c r="G188" s="4" t="s">
         <v>30</v>
@@ -6838,30 +6841,30 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>141</v>
+        <v>230</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>142</v>
+        <v>27</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F189" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>664</v>
+        <v>141</v>
       </c>
       <c r="B190" s="9" t="s">
         <v>32</v>
@@ -6870,13 +6873,13 @@
         <v>653</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>665</v>
+        <v>142</v>
       </c>
       <c r="E190" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F190" s="10">
-        <v>20123</v>
+      <c r="F190" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="G190" s="9" t="s">
         <v>36</v>
@@ -6884,7 +6887,7 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>54</v>
+        <v>664</v>
       </c>
       <c r="B191" s="9" t="s">
         <v>32</v>
@@ -6893,13 +6896,13 @@
         <v>653</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>55</v>
+        <v>665</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F191" s="10" t="s">
-        <v>56</v>
+      <c r="F191" s="10">
+        <v>20123</v>
       </c>
       <c r="G191" s="9" t="s">
         <v>36</v>
@@ -6907,7 +6910,7 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>439</v>
+        <v>54</v>
       </c>
       <c r="B192" s="9" t="s">
         <v>32</v>
@@ -6916,159 +6919,159 @@
         <v>653</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>440</v>
+        <v>55</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="F192" s="10">
-        <v>20038</v>
+        <v>34</v>
+      </c>
+      <c r="F192" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>134</v>
+        <v>36</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="B193" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D193" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="E193" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="F193" s="10">
+        <v>20038</v>
+      </c>
+      <c r="G193" s="9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A194" s="9" t="s">
         <v>424</v>
       </c>
-      <c r="B193" s="9" t="s">
+      <c r="B194" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C193" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D193" s="9" t="s">
+      <c r="C194" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D194" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="E193" s="9" t="s">
+      <c r="E194" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F193" s="10">
+      <c r="F194" s="10">
         <v>10121</v>
       </c>
-      <c r="G193" s="9" t="s">
+      <c r="G194" s="9" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A194" s="3" t="s">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A195" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="B194" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C194" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D194" s="3" t="s">
+      <c r="B195" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D195" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="E194" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F194" s="7">
+      <c r="E195" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F195" s="7">
         <v>20124</v>
       </c>
-      <c r="G194" s="3" t="s">
+      <c r="G195" s="3" t="s">
         <v>157</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A195" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B195" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D195" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E195" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F195" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="G195" s="9" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
-        <v>375</v>
+        <v>93</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>376</v>
+        <v>94</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>377</v>
+        <v>95</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="F196" s="10">
-        <v>64020</v>
+        <v>96</v>
+      </c>
+      <c r="F196" s="10" t="s">
+        <v>97</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
-        <v>578</v>
+        <v>375</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>7</v>
+        <v>376</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>579</v>
+        <v>377</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F197" s="12" t="s">
-        <v>580</v>
+        <v>378</v>
+      </c>
+      <c r="F197" s="10">
+        <v>64020</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
-        <v>408</v>
+        <v>578</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>209</v>
+        <v>579</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F198" s="10">
-        <v>20121</v>
+        <v>8</v>
+      </c>
+      <c r="F198" s="12" t="s">
+        <v>580</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
-        <v>131</v>
+        <v>408</v>
       </c>
       <c r="B199" s="9" t="s">
         <v>32</v>
@@ -7077,113 +7080,113 @@
         <v>653</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>132</v>
+        <v>209</v>
       </c>
       <c r="E199" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F199" s="10" t="s">
-        <v>133</v>
+      <c r="F199" s="10">
+        <v>20121</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>134</v>
+        <v>36</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
-        <v>603</v>
+        <v>131</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>604</v>
+        <v>132</v>
       </c>
       <c r="E200" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F200" s="12" t="s">
-        <v>605</v>
+        <v>34</v>
+      </c>
+      <c r="F200" s="10" t="s">
+        <v>133</v>
       </c>
       <c r="G200" s="9" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="9" t="s">
-        <v>255</v>
+        <v>603</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D201" s="9" t="s">
-        <v>256</v>
+        <v>604</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F201" s="10" t="s">
-        <v>56</v>
+        <v>8</v>
+      </c>
+      <c r="F201" s="12" t="s">
+        <v>605</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
-        <v>338</v>
+        <v>255</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>339</v>
+        <v>32</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>340</v>
+        <v>256</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="F202" s="10">
-        <v>37045</v>
+        <v>34</v>
+      </c>
+      <c r="F202" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="G202" s="9" t="s">
-        <v>341</v>
+        <v>36</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="9" t="s">
-        <v>164</v>
+        <v>338</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>32</v>
+        <v>339</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D203" s="9" t="s">
-        <v>165</v>
+        <v>340</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F203" s="10" t="s">
-        <v>166</v>
+        <v>526</v>
+      </c>
+      <c r="F203" s="10">
+        <v>37045</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>157</v>
+        <v>341</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
-        <v>527</v>
+        <v>164</v>
       </c>
       <c r="B204" s="9" t="s">
         <v>32</v>
@@ -7197,8 +7200,8 @@
       <c r="E204" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F204" s="10">
-        <v>20126</v>
+      <c r="F204" s="10" t="s">
+        <v>166</v>
       </c>
       <c r="G204" s="9" t="s">
         <v>157</v>
@@ -7206,7 +7209,7 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="9" t="s">
-        <v>599</v>
+        <v>527</v>
       </c>
       <c r="B205" s="9" t="s">
         <v>32</v>
@@ -7215,21 +7218,21 @@
         <v>653</v>
       </c>
       <c r="D205" s="9" t="s">
-        <v>600</v>
+        <v>165</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>34</v>
       </c>
       <c r="F205" s="10">
-        <v>20138</v>
+        <v>20126</v>
       </c>
       <c r="G205" s="9" t="s">
-        <v>260</v>
+        <v>157</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="9" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="B206" s="9" t="s">
         <v>32</v>
@@ -7238,21 +7241,21 @@
         <v>653</v>
       </c>
       <c r="D206" s="9" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="E206" s="9" t="s">
         <v>34</v>
       </c>
       <c r="F206" s="10">
-        <v>20122</v>
+        <v>20138</v>
       </c>
       <c r="G206" s="9" t="s">
-        <v>36</v>
+        <v>260</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
-        <v>592</v>
+        <v>607</v>
       </c>
       <c r="B207" s="9" t="s">
         <v>32</v>
@@ -7261,13 +7264,13 @@
         <v>653</v>
       </c>
       <c r="D207" s="9" t="s">
-        <v>392</v>
+        <v>608</v>
       </c>
       <c r="E207" s="9" t="s">
         <v>34</v>
       </c>
       <c r="F207" s="10">
-        <v>20123</v>
+        <v>20122</v>
       </c>
       <c r="G207" s="9" t="s">
         <v>36</v>
@@ -7275,53 +7278,53 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="B208" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D208" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="E208" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F208" s="10">
+        <v>20123</v>
+      </c>
+      <c r="G208" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A209" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="B208" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D208" s="9" t="s">
+      <c r="B209" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D209" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="E208" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F208" s="10">
+      <c r="E209" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F209" s="10">
         <v>20135</v>
       </c>
-      <c r="G208" s="9" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A209" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="B209" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D209" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="E209" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F209" s="7">
-        <v>20135</v>
-      </c>
-      <c r="G209" s="3" t="s">
+      <c r="G209" s="9" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="3" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>32</v>
@@ -7343,100 +7346,100 @@
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A211" s="9" t="s">
+      <c r="A211" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F211" s="7">
+        <v>20135</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A212" s="9" t="s">
         <v>403</v>
       </c>
-      <c r="B211" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D211" s="9" t="s">
+      <c r="B212" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D212" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="E211" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F211" s="10">
+      <c r="E212" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F212" s="10">
         <v>20135</v>
       </c>
-      <c r="G211" s="9" t="s">
+      <c r="G212" s="9" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A212" s="3" t="s">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A213" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="B212" s="3" t="s">
+      <c r="B213" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C212" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D212" s="3" t="s">
+      <c r="C213" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D213" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="E212" s="3" t="s">
+      <c r="E213" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="F212" s="7">
+      <c r="F213" s="7">
         <v>85100</v>
       </c>
-      <c r="G212" s="3" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A213" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="B213" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D213" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="E213" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="F213" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="G213" s="9" t="s">
+      <c r="G213" s="3" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="9" t="s">
-        <v>451</v>
+        <v>202</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>32</v>
+        <v>183</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D214" s="9" t="s">
-        <v>452</v>
+        <v>203</v>
       </c>
       <c r="E214" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F214" s="10">
-        <v>20144</v>
+        <v>184</v>
+      </c>
+      <c r="F214" s="10" t="s">
+        <v>185</v>
       </c>
       <c r="G214" s="9" t="s">
-        <v>36</v>
+        <v>317</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="9" t="s">
-        <v>221</v>
+        <v>451</v>
       </c>
       <c r="B215" s="9" t="s">
         <v>32</v>
@@ -7445,343 +7448,343 @@
         <v>653</v>
       </c>
       <c r="D215" s="9" t="s">
-        <v>222</v>
+        <v>452</v>
       </c>
       <c r="E215" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F215" s="10" t="s">
-        <v>133</v>
+      <c r="F215" s="10">
+        <v>20144</v>
       </c>
       <c r="G215" s="9" t="s">
-        <v>134</v>
+        <v>36</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="B216" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D216" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="E216" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F216" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="G216" s="9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A217" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="B216" s="9" t="s">
+      <c r="B217" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C216" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D216" s="9" t="s">
+      <c r="C217" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D217" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="E216" s="9" t="s">
+      <c r="E217" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="F216" s="10">
+      <c r="F217" s="10">
         <v>40026</v>
       </c>
-      <c r="G216" s="9" t="s">
+      <c r="G217" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A217" s="3" t="s">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A218" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="B217" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D217" s="3" t="s">
+      <c r="B218" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D218" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="E217" s="3" t="s">
+      <c r="E218" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="F217" s="7">
+      <c r="F218" s="7">
         <v>20068</v>
       </c>
-      <c r="G217" s="3" t="s">
+      <c r="G218" s="3" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A218" s="9" t="s">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A219" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="B218" s="9" t="s">
+      <c r="B219" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C218" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D218" s="9" t="s">
+      <c r="C219" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D219" s="9" t="s">
         <v>318</v>
       </c>
-      <c r="E218" s="9" t="s">
+      <c r="E219" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F218" s="10" t="s">
+      <c r="F219" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="G218" s="9" t="s">
+      <c r="G219" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A219" s="3" t="s">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A220" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="B219" s="3" t="s">
+      <c r="B220" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C219" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D219" s="3" t="s">
+      <c r="C220" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D220" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="E219" s="3" t="s">
+      <c r="E220" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F219" s="11" t="s">
+      <c r="F220" s="11" t="s">
         <v>661</v>
       </c>
-      <c r="G219" s="3" t="s">
+      <c r="G220" s="3" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A220" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="B220" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D220" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E220" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F220" s="10">
-        <v>39100</v>
-      </c>
-      <c r="G220" s="9" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="9" t="s">
-        <v>365</v>
+        <v>531</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D221" s="9" t="s">
-        <v>366</v>
+        <v>27</v>
       </c>
       <c r="E221" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F221" s="10">
-        <v>20123</v>
+        <v>39100</v>
       </c>
       <c r="G221" s="9" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="9" t="s">
-        <v>285</v>
+        <v>365</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>306</v>
+        <v>32</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D222" s="9" t="s">
-        <v>319</v>
+        <v>366</v>
       </c>
       <c r="E222" s="9" t="s">
-        <v>320</v>
+        <v>34</v>
       </c>
       <c r="F222" s="10">
-        <v>12020</v>
+        <v>20123</v>
       </c>
       <c r="G222" s="9" t="s">
-        <v>305</v>
+        <v>36</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="9" t="s">
-        <v>37</v>
+        <v>285</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>38</v>
+        <v>306</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D223" s="9" t="s">
-        <v>39</v>
+        <v>319</v>
       </c>
       <c r="E223" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F223" s="10" t="s">
-        <v>41</v>
+        <v>320</v>
+      </c>
+      <c r="F223" s="10">
+        <v>12020</v>
       </c>
       <c r="G223" s="9" t="s">
-        <v>42</v>
+        <v>305</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="9" t="s">
-        <v>419</v>
+        <v>37</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>420</v>
+        <v>38</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D224" s="9" t="s">
-        <v>421</v>
+        <v>39</v>
       </c>
       <c r="E224" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="F224" s="10">
-        <v>28053</v>
+        <v>40</v>
+      </c>
+      <c r="F224" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="G224" s="9" t="s">
-        <v>134</v>
+        <v>42</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="9" t="s">
-        <v>170</v>
+        <v>419</v>
       </c>
       <c r="B225" s="9" t="s">
-        <v>32</v>
+        <v>420</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D225" s="9" t="s">
-        <v>167</v>
+        <v>421</v>
       </c>
       <c r="E225" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="F225" s="10" t="s">
-        <v>169</v>
+        <v>422</v>
+      </c>
+      <c r="F225" s="10">
+        <v>28053</v>
       </c>
       <c r="G225" s="9" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="9" t="s">
-        <v>558</v>
+        <v>170</v>
       </c>
       <c r="B226" s="9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D226" s="9" t="s">
-        <v>559</v>
+        <v>167</v>
       </c>
       <c r="E226" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F226" s="10">
-        <v>39100</v>
+        <v>168</v>
+      </c>
+      <c r="F226" s="10" t="s">
+        <v>169</v>
       </c>
       <c r="G226" s="9" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="9" t="s">
-        <v>196</v>
+        <v>558</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D227" s="9" t="s">
-        <v>197</v>
+        <v>559</v>
       </c>
       <c r="E227" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F227" s="10" t="s">
-        <v>198</v>
+        <v>28</v>
+      </c>
+      <c r="F227" s="10">
+        <v>39100</v>
       </c>
       <c r="G227" s="9" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="9" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="B228" s="9" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D228" s="9" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="E228" s="9" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="F228" s="10" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="G228" s="9" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="9" t="s">
-        <v>242</v>
+        <v>205</v>
       </c>
       <c r="B229" s="9" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D229" s="9" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="E229" s="9" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="F229" s="10" t="s">
-        <v>56</v>
+        <v>207</v>
       </c>
       <c r="G229" s="9" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="9" t="s">
-        <v>532</v>
+        <v>242</v>
       </c>
       <c r="B230" s="9" t="s">
         <v>32</v>
@@ -7795,8 +7798,8 @@
       <c r="E230" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F230" s="10">
-        <v>20121</v>
+      <c r="F230" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="G230" s="9" t="s">
         <v>36</v>
@@ -7804,7 +7807,7 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="9" t="s">
-        <v>576</v>
+        <v>532</v>
       </c>
       <c r="B231" s="9" t="s">
         <v>32</v>
@@ -7813,7 +7816,7 @@
         <v>653</v>
       </c>
       <c r="D231" s="9" t="s">
-        <v>577</v>
+        <v>175</v>
       </c>
       <c r="E231" s="9" t="s">
         <v>34</v>
@@ -7827,159 +7830,159 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="9" t="s">
-        <v>443</v>
+        <v>576</v>
       </c>
       <c r="B232" s="9" t="s">
-        <v>444</v>
+        <v>32</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D232" s="9" t="s">
-        <v>445</v>
+        <v>577</v>
       </c>
       <c r="E232" s="9" t="s">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="F232" s="10">
-        <v>53048</v>
+        <v>20121</v>
       </c>
       <c r="G232" s="9" t="s">
-        <v>447</v>
+        <v>36</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="9" t="s">
-        <v>514</v>
+        <v>443</v>
       </c>
       <c r="B233" s="9" t="s">
-        <v>507</v>
+        <v>444</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D233" s="9" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
       <c r="E233" s="9" t="s">
-        <v>516</v>
+        <v>446</v>
       </c>
       <c r="F233" s="10">
-        <v>35011</v>
+        <v>53048</v>
       </c>
       <c r="G233" s="9" t="s">
-        <v>503</v>
+        <v>447</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="9" t="s">
-        <v>241</v>
+        <v>514</v>
       </c>
       <c r="B234" s="9" t="s">
-        <v>32</v>
+        <v>507</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D234" s="9" t="s">
-        <v>175</v>
+        <v>515</v>
       </c>
       <c r="E234" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F234" s="10" t="s">
-        <v>56</v>
+        <v>516</v>
+      </c>
+      <c r="F234" s="10">
+        <v>35011</v>
       </c>
       <c r="G234" s="9" t="s">
-        <v>36</v>
+        <v>503</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="B235" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D235" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E235" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F235" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G235" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A236" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B235" s="9" t="s">
+      <c r="B236" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C235" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D235" s="9" t="s">
+      <c r="C236" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D236" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="E235" s="9" t="s">
+      <c r="E236" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F235" s="10" t="s">
+      <c r="F236" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G235" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A236" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="B236" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C236" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E236" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F236" s="7">
-        <v>39100</v>
-      </c>
-      <c r="G236" s="3" t="s">
+      <c r="G236" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F237" s="7">
+        <v>39100</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A238" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="B237" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C237" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D237" s="3" t="s">
+      <c r="B238" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D238" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="E237" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F237" s="7">
-        <v>20121</v>
-      </c>
-      <c r="G237" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A238" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="B238" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C238" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D238" s="9" t="s">
-        <v>530</v>
-      </c>
-      <c r="E238" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F238" s="10">
+      <c r="E238" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F238" s="7">
         <v>20121</v>
       </c>
       <c r="G238" s="9" t="s">
@@ -7988,352 +7991,352 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="B239" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D239" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="E239" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F239" s="10">
+        <v>20121</v>
+      </c>
+      <c r="G239" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A240" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B239" s="9" t="s">
+      <c r="B240" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C239" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D239" s="9" t="s">
+      <c r="C240" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D240" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E239" s="9" t="s">
+      <c r="E240" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F239" s="10" t="s">
+      <c r="F240" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G239" s="9" t="s">
+      <c r="G240" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A240" s="3" t="s">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A241" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="B240" s="3" t="s">
+      <c r="B241" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C240" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D240" s="3" t="s">
+      <c r="C241" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D241" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="E240" s="3" t="s">
+      <c r="E241" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F240" s="11" t="s">
+      <c r="F241" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="G240" s="3" t="s">
+      <c r="G241" s="3" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A241" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="B241" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C241" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D241" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="E241" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="F241" s="10">
-        <v>20089</v>
-      </c>
-      <c r="G241" s="9" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" s="9" t="s">
-        <v>473</v>
+        <v>379</v>
       </c>
       <c r="B242" s="9" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D242" s="9" t="s">
-        <v>474</v>
+        <v>380</v>
       </c>
       <c r="E242" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F242" s="12" t="s">
-        <v>475</v>
+        <v>381</v>
+      </c>
+      <c r="F242" s="10">
+        <v>20089</v>
       </c>
       <c r="G242" s="9" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" s="9" t="s">
-        <v>210</v>
+        <v>473</v>
       </c>
       <c r="B243" s="9" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D243" s="9" t="s">
-        <v>200</v>
+        <v>474</v>
       </c>
       <c r="E243" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F243" s="10" t="s">
-        <v>201</v>
+        <v>8</v>
+      </c>
+      <c r="F243" s="12" t="s">
+        <v>475</v>
       </c>
       <c r="G243" s="9" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B244" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D244" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="E244" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F244" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="G244" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A245" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B244" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C244" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D244" s="9" t="s">
+      <c r="B245" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D245" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="E244" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F244" s="10" t="s">
+      <c r="E245" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F245" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="G244" s="9" t="s">
+      <c r="G245" s="9" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A245" s="3" t="s">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A246" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="B245" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C245" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D245" s="3" t="s">
+      <c r="B246" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D246" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="E245" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F245" s="7">
+      <c r="E246" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F246" s="7">
         <v>20124</v>
       </c>
-      <c r="G245" s="3" t="s">
+      <c r="G246" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A246" s="9" t="s">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A247" s="9" t="s">
         <v>436</v>
       </c>
-      <c r="B246" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C246" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D246" s="9" t="s">
+      <c r="B247" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D247" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="E246" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F246" s="10">
+      <c r="E247" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F247" s="10">
         <v>20124</v>
       </c>
-      <c r="G246" s="9" t="s">
+      <c r="G247" s="9" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A247" s="3" t="s">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A248" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="B247" s="3" t="s">
+      <c r="B248" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C247" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D247" s="3" t="s">
+      <c r="C248" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D248" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="E247" s="3" t="s">
+      <c r="E248" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F247" s="7">
+      <c r="F248" s="7">
         <v>24050</v>
       </c>
-      <c r="G247" s="3" t="s">
+      <c r="G248" s="3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A248" s="9" t="s">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A249" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="B248" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C248" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D248" s="9" t="s">
+      <c r="B249" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D249" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="E248" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F248" s="10" t="s">
+      <c r="E249" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F249" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="G248" s="9" t="s">
+      <c r="G249" s="9" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A249" s="3" t="s">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A250" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="B249" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C249" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D249" s="3" t="s">
+      <c r="B250" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D250" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="E249" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F249" s="7">
+      <c r="E250" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F250" s="7">
         <v>20148</v>
       </c>
-      <c r="G249" s="3" t="s">
+      <c r="G250" s="3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A250" s="9" t="s">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A251" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="B250" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C250" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D250" s="9" t="s">
+      <c r="B251" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C251" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D251" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="E250" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F250" s="10" t="s">
+      <c r="E251" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F251" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="G250" s="9" t="s">
+      <c r="G251" s="9" t="s">
         <v>134</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A251" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="B251" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C251" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D251" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="E251" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="F251" s="7">
-        <v>25055</v>
-      </c>
-      <c r="G251" s="3" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="E252" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="F252" s="7">
+        <v>25055</v>
+      </c>
+      <c r="G252" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A253" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="B252" s="3" t="s">
+      <c r="B253" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="C252" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D252" s="3" t="s">
+      <c r="C253" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D253" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="E252" s="3" t="s">
+      <c r="E253" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="F252" s="7">
+      <c r="F253" s="7">
         <v>50132</v>
       </c>
-      <c r="G252" s="3" t="s">
+      <c r="G253" s="3" t="s">
         <v>447</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A253" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="B253" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C253" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D253" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="E253" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F253" s="10">
-        <v>20129</v>
-      </c>
-      <c r="G253" s="9" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" s="9" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="B254" s="9" t="s">
         <v>32</v>
@@ -8356,7 +8359,7 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" s="9" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="B255" s="9" t="s">
         <v>32</v>
@@ -8379,7 +8382,7 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" s="9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B256" s="9" t="s">
         <v>32</v>
@@ -8402,7 +8405,7 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" s="9" t="s">
-        <v>174</v>
+        <v>472</v>
       </c>
       <c r="B257" s="9" t="s">
         <v>32</v>
@@ -8411,228 +8414,228 @@
         <v>653</v>
       </c>
       <c r="D257" s="9" t="s">
-        <v>175</v>
+        <v>462</v>
       </c>
       <c r="E257" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F257" s="10" t="s">
-        <v>56</v>
+      <c r="F257" s="10">
+        <v>20129</v>
       </c>
       <c r="G257" s="9" t="s">
-        <v>36</v>
+        <v>260</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" s="9" t="s">
-        <v>329</v>
+        <v>174</v>
       </c>
       <c r="B258" s="9" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C258" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D258" s="9" t="s">
-        <v>330</v>
+        <v>175</v>
       </c>
       <c r="E258" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="F258" s="10">
-        <v>40026</v>
+        <v>34</v>
+      </c>
+      <c r="F258" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="G258" s="9" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" s="9" t="s">
-        <v>286</v>
+        <v>329</v>
       </c>
       <c r="B259" s="9" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C259" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D259" s="9" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="E259" s="9" t="s">
-        <v>34</v>
+        <v>316</v>
       </c>
       <c r="F259" s="10">
-        <v>20124</v>
+        <v>40026</v>
       </c>
       <c r="G259" s="9" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="B260" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D260" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="E260" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F260" s="10">
+        <v>20124</v>
+      </c>
+      <c r="G260" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A261" s="9" t="s">
         <v>448</v>
       </c>
-      <c r="B260" s="9" t="s">
+      <c r="B261" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="C260" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D260" s="9" t="s">
+      <c r="C261" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D261" s="9" t="s">
         <v>449</v>
       </c>
-      <c r="E260" s="9" t="s">
+      <c r="E261" s="9" t="s">
         <v>450</v>
       </c>
-      <c r="F260" s="10">
+      <c r="F261" s="10">
         <v>12011</v>
       </c>
-      <c r="G260" s="9" t="s">
+      <c r="G261" s="9" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A261" s="3" t="s">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A262" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="B261" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C261" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D261" s="3" t="s">
+      <c r="B262" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D262" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="E261" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F261" s="7">
+      <c r="E262" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F262" s="7">
         <v>20121</v>
       </c>
-      <c r="G261" s="3" t="s">
+      <c r="G262" s="3" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A262" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="B262" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="C262" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D262" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E262" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F262" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="G262" s="9" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" s="9" t="s">
-        <v>417</v>
+        <v>149</v>
       </c>
       <c r="B263" s="9" t="s">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="C263" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D263" s="9" t="s">
-        <v>418</v>
+        <v>151</v>
       </c>
       <c r="E263" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F263" s="10">
-        <v>20123</v>
+        <v>152</v>
+      </c>
+      <c r="F263" s="10" t="s">
+        <v>153</v>
       </c>
       <c r="G263" s="9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" s="9" t="s">
-        <v>489</v>
+        <v>417</v>
       </c>
       <c r="B264" s="9" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C264" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D264" s="9" t="s">
-        <v>490</v>
+        <v>418</v>
       </c>
       <c r="E264" s="9" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F264" s="10">
-        <v>90141</v>
+        <v>20123</v>
       </c>
       <c r="G264" s="9" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="B265" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C265" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D265" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="E265" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F265" s="10">
+        <v>90141</v>
+      </c>
+      <c r="G265" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A266" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="B265" s="9" t="s">
+      <c r="B266" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C265" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D265" s="9" t="s">
+      <c r="C266" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D266" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="E265" s="9" t="s">
+      <c r="E266" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F265" s="12" t="s">
+      <c r="F266" s="12" t="s">
         <v>388</v>
       </c>
-      <c r="G265" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A266" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="B266" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C266" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D266" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="E266" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F266" s="11" t="s">
-        <v>388</v>
-      </c>
-      <c r="G266" s="3" t="s">
+      <c r="G266" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" s="3" t="s">
-        <v>528</v>
+        <v>640</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>7</v>
@@ -8654,399 +8657,399 @@
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A268" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="B268" s="9" t="s">
+      <c r="A268" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="B268" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C268" s="4" t="s">
         <v>653</v>
       </c>
-      <c r="D268" s="9" t="s">
+      <c r="D268" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="E268" s="9" t="s">
+      <c r="E268" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F268" s="10" t="s">
+      <c r="F268" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="G268" s="9" t="s">
+      <c r="G268" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="B269" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D269" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="E269" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F269" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="G269" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A270" s="9" t="s">
         <v>463</v>
       </c>
-      <c r="B269" s="9" t="s">
+      <c r="B270" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="C269" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D269" s="9" t="s">
+      <c r="C270" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D270" s="9" t="s">
         <v>464</v>
       </c>
-      <c r="E269" s="9" t="s">
+      <c r="E270" s="9" t="s">
         <v>465</v>
       </c>
-      <c r="F269" s="10">
+      <c r="F270" s="10">
         <v>38055</v>
       </c>
-      <c r="G269" s="9" t="s">
+      <c r="G270" s="9" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A270" s="3" t="s">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A271" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="B270" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C270" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D270" s="3" t="s">
+      <c r="B271" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C271" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D271" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E270" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F270" s="7">
+      <c r="E271" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F271" s="7">
         <v>20145</v>
       </c>
-      <c r="G270" s="3" t="s">
+      <c r="G271" s="3" t="s">
         <v>134</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A271" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="B271" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C271" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D271" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="E271" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="F271" s="10">
-        <v>25010</v>
-      </c>
-      <c r="G271" s="9" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="B272" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D272" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="E272" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="F272" s="10">
+        <v>25010</v>
+      </c>
+      <c r="G272" s="9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A273" s="9" t="s">
         <v>391</v>
       </c>
-      <c r="B272" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C272" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D272" s="9" t="s">
+      <c r="B273" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C273" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D273" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="E272" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F272" s="10">
+      <c r="E273" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F273" s="10">
         <v>20123</v>
       </c>
-      <c r="G272" s="9" t="s">
+      <c r="G273" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A273" s="3" t="s">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A274" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="B273" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C273" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D273" s="3" t="s">
+      <c r="B274" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D274" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="E273" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F273" s="7">
+      <c r="E274" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F274" s="7">
         <v>20123</v>
       </c>
-      <c r="G273" s="3" t="s">
+      <c r="G274" s="3" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A274" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="B274" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C274" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D274" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="E274" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="F274" s="10">
-        <v>71016</v>
-      </c>
-      <c r="G274" s="9" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="B275" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C275" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D275" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="E275" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="F275" s="10">
+        <v>71016</v>
+      </c>
+      <c r="G275" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A276" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B275" s="9" t="s">
+      <c r="B276" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C275" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D275" s="9" t="s">
+      <c r="C276" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D276" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E275" s="9" t="s">
+      <c r="E276" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F275" s="10" t="s">
+      <c r="F276" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G275" s="9" t="s">
+      <c r="G276" s="9" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A276" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="B276" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C276" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D276" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="E276" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F276" s="7">
-        <v>20123</v>
-      </c>
-      <c r="G276" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C277" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D277" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="E277" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F277" s="7">
+        <v>20123</v>
+      </c>
+      <c r="G277" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A278" s="3" t="s">
         <v>682</v>
       </c>
-      <c r="B277" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C277" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="D277" s="3" t="s">
+      <c r="B278" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C278" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D278" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="E277" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F277" s="7">
+      <c r="E278" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F278" s="7">
         <v>20145</v>
       </c>
-      <c r="G277" s="3" t="s">
+      <c r="G278" s="3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A278" s="9" t="s">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A279" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="B278" s="9" t="s">
+      <c r="B279" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C278" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D278" s="9" t="s">
+      <c r="C279" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D279" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="E278" s="9" t="s">
+      <c r="E279" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="F278" s="10" t="s">
+      <c r="F279" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="G278" s="9" t="s">
+      <c r="G279" s="9" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A279" s="3" t="s">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A280" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="B279" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C279" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D279" s="3" t="s">
+      <c r="B280" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C280" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D280" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="E279" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F279" s="7">
+      <c r="E280" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F280" s="7">
         <v>20122</v>
       </c>
-      <c r="G279" s="3" t="s">
+      <c r="G280" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A280" s="9" t="s">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A281" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="B280" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C280" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D280" s="9" t="s">
+      <c r="B281" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C281" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D281" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="E280" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F280" s="10" t="s">
+      <c r="E281" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F281" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="G280" s="9" t="s">
+      <c r="G281" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A281" s="3" t="s">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A282" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="B281" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C281" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D281" s="3" t="s">
+      <c r="B282" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C282" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D282" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="E281" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F281" s="7">
+      <c r="E282" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F282" s="7">
         <v>20123</v>
       </c>
-      <c r="G281" s="3" t="s">
+      <c r="G282" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A282" s="9" t="s">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A283" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="B282" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C282" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D282" s="9" t="s">
+      <c r="B283" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C283" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D283" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="E282" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F282" s="10">
+      <c r="E283" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F283" s="10">
         <v>20123</v>
       </c>
-      <c r="G282" s="9" t="s">
+      <c r="G283" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A283" s="3" t="s">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A284" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="B283" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C283" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D283" s="3" t="s">
+      <c r="B284" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C284" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D284" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="E283" s="3" t="s">
+      <c r="E284" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F283" s="7">
+      <c r="F284" s="7">
         <v>20094</v>
       </c>
-      <c r="G283" s="3" t="s">
+      <c r="G284" s="3" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A284" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="B284" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C284" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D284" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="E284" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F284" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="G284" s="9" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" s="9" t="s">
-        <v>214</v>
+        <v>394</v>
       </c>
       <c r="B285" s="9" t="s">
         <v>7</v>
@@ -9069,53 +9072,53 @@
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286" s="9" t="s">
-        <v>158</v>
+        <v>214</v>
       </c>
       <c r="B286" s="9" t="s">
-        <v>159</v>
+        <v>7</v>
       </c>
       <c r="C286" s="9" t="s">
         <v>653</v>
       </c>
       <c r="D286" s="9" t="s">
-        <v>160</v>
+        <v>215</v>
       </c>
       <c r="E286" s="9" t="s">
-        <v>161</v>
+        <v>8</v>
       </c>
       <c r="F286" s="10" t="s">
-        <v>162</v>
+        <v>216</v>
       </c>
       <c r="G286" s="9" t="s">
-        <v>163</v>
+        <v>9</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287" s="9" t="s">
-        <v>432</v>
+        <v>158</v>
       </c>
       <c r="B287" s="9" t="s">
-        <v>7</v>
+        <v>159</v>
       </c>
       <c r="C287" s="9" t="s">
         <v>653</v>
       </c>
       <c r="D287" s="9" t="s">
-        <v>215</v>
+        <v>160</v>
       </c>
       <c r="E287" s="9" t="s">
-        <v>8</v>
+        <v>161</v>
       </c>
       <c r="F287" s="10" t="s">
-        <v>216</v>
+        <v>162</v>
       </c>
       <c r="G287" s="9" t="s">
-        <v>9</v>
+        <v>163</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288" s="9" t="s">
-        <v>253</v>
+        <v>432</v>
       </c>
       <c r="B288" s="9" t="s">
         <v>7</v>
@@ -9138,30 +9141,53 @@
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="B289" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C289" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D289" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="E289" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F289" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="G289" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A290" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="B289" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C289" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D289" s="9" t="s">
+      <c r="B290" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C290" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D290" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="E289" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F289" s="10" t="s">
+      <c r="E290" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F290" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="G289" s="9" t="s">
+      <c r="G290" s="9" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G218" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G289">
+    <sortState ref="A2:G290">
       <sortCondition ref="A1:A218"/>
     </sortState>
   </autoFilter>
@@ -9174,6 +9200,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F040406D9EE34E48977C379A242BB45D" ma:contentTypeVersion="15" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="1ab2d492e43f6bec9a26aa4599c840e9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="877b7d34-4df7-40bf-9eb1-208952470e96" xmlns:ns4="05fc27dd-4454-4248-9c78-3d72b2b155c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebc604e5d4aadf5a992ba83f8d4fb519" ns3:_="" ns4:_="">
     <xsd:import namespace="877b7d34-4df7-40bf-9eb1-208952470e96"/>
@@ -9406,24 +9449,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBC6436E-C4E7-4E8D-94E8-64DAEC05792B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9440,29 +9491,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anzillotti\OneDrive - CGT Edilizia S.p.a\Documenti\GitHub\pv_echarts\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgtedilizia-my.sharepoint.com/personal/emanuele_anzilotti_alayanrentals_it/Documents/Documenti/GitHub/pv_echarts/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{006EA0E2-4EE9-4B4F-8989-9D92DF729528}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B84DC042-1AB5-4E1E-967B-CC220D01D2F5}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1864" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="689">
   <si>
     <t>Nome account</t>
   </si>
@@ -2078,6 +2078,18 @@
   </si>
   <si>
     <t>INE NARDO' SRL</t>
+  </si>
+  <si>
+    <t>CR RINNOVABILI 4 SRL</t>
+  </si>
+  <si>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>VIA NAZIONALE SNC</t>
+  </si>
+  <si>
+    <t>CUTRO</t>
   </si>
 </sst>
 </file>
@@ -2158,9 +2170,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2178,14 +2190,11 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2205,10 +2214,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2246,7 +2259,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2352,7 +2365,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2494,7 +2507,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2502,7 +2515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G290"/>
+  <dimension ref="A1:G291"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -3943,30 +3956,30 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>135</v>
+        <v>685</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C63" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="C63" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>120</v>
+        <v>687</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>56</v>
+        <v>688</v>
+      </c>
+      <c r="F63" s="5">
+        <v>88842</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>407</v>
+        <v>135</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>32</v>
@@ -3980,8 +3993,8 @@
       <c r="E64" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F64" s="5">
-        <v>20121</v>
+      <c r="F64" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>36</v>
@@ -3989,53 +4002,53 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>136</v>
+        <v>407</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>140</v>
+        <v>34</v>
+      </c>
+      <c r="F65" s="5">
+        <v>20121</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>612</v>
+        <v>123</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>15</v>
@@ -4049,8 +4062,8 @@
       <c r="E67" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F67" s="5">
-        <v>90139</v>
+      <c r="F67" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>10</v>
@@ -4058,173 +4071,173 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>442</v>
+        <v>612</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>187</v>
+        <v>124</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F68" s="5">
-        <v>20158</v>
+        <v>90139</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>157</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>223</v>
+        <v>442</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>29</v>
+        <v>34</v>
+      </c>
+      <c r="F69" s="5">
+        <v>20158</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>84</v>
+        <v>224</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>581</v>
+        <v>82</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>262</v>
+        <v>83</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>582</v>
+        <v>84</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="F71" s="5">
-        <v>38123</v>
+        <v>85</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>266</v>
+        <v>42</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>542</v>
+        <v>581</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>7</v>
+        <v>262</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>543</v>
+        <v>582</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>178</v>
+        <v>406</v>
+      </c>
+      <c r="F72" s="5">
+        <v>38123</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>75</v>
+        <v>266</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>485</v>
+        <v>542</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>486</v>
+        <v>7</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>487</v>
+        <v>543</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="F73" s="5">
-        <v>26015</v>
+        <v>8</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>680</v>
+        <v>485</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C74" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>333</v>
+        <v>487</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>216</v>
+        <v>488</v>
+      </c>
+      <c r="F74" s="5">
+        <v>26015</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>9</v>
+        <v>105</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>556</v>
+        <v>680</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D75" s="4" t="s">
@@ -4233,7 +4246,7 @@
       <c r="E75" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F75" s="8" t="s">
+      <c r="F75" s="5" t="s">
         <v>216</v>
       </c>
       <c r="G75" s="4" t="s">
@@ -4242,7 +4255,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>332</v>
+        <v>556</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>7</v>
@@ -4256,7 +4269,7 @@
       <c r="E76" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F76" s="5" t="s">
+      <c r="F76" s="8" t="s">
         <v>216</v>
       </c>
       <c r="G76" s="4" t="s">
@@ -4265,145 +4278,145 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>590</v>
+        <v>332</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>591</v>
+        <v>333</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F77" s="5">
-        <v>20122</v>
+        <v>8</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>298</v>
+        <v>590</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>294</v>
+        <v>32</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>299</v>
+        <v>591</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>300</v>
+        <v>34</v>
       </c>
       <c r="F78" s="5">
-        <v>56025</v>
+        <v>20122</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>297</v>
+        <v>36</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>7</v>
+        <v>294</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>270</v>
+        <v>299</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>271</v>
+        <v>300</v>
+      </c>
+      <c r="F79" s="5">
+        <v>56025</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>9</v>
+        <v>297</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>373</v>
+        <v>269</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>374</v>
+        <v>270</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F80" s="5">
-        <v>20121</v>
+        <v>8</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>278</v>
+        <v>373</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>301</v>
+        <v>374</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>302</v>
+        <v>34</v>
       </c>
       <c r="F81" s="5">
-        <v>24060</v>
+        <v>20121</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>614</v>
+        <v>278</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>187</v>
+        <v>301</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>34</v>
+        <v>302</v>
       </c>
       <c r="F82" s="5">
-        <v>20158</v>
+        <v>24060</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>479</v>
+        <v>614</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>32</v>
@@ -4412,21 +4425,21 @@
         <v>653</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>256</v>
+        <v>187</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F83" s="5">
-        <v>20121</v>
+        <v>20158</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>173</v>
+        <v>479</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>32</v>
@@ -4435,21 +4448,21 @@
         <v>653</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>155</v>
+        <v>256</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F84" s="5" t="s">
-        <v>156</v>
+      <c r="F84" s="5">
+        <v>20121</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>32</v>
@@ -4472,53 +4485,53 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>657</v>
+        <v>154</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>290</v>
+        <v>32</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>658</v>
+        <v>155</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="F86" s="5">
-        <v>60035</v>
+        <v>34</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>156</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>251</v>
+        <v>657</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>32</v>
+        <v>290</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>228</v>
+        <v>658</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>229</v>
+        <v>292</v>
+      </c>
+      <c r="F87" s="5">
+        <v>60035</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>437</v>
+        <v>251</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>32</v>
@@ -4527,151 +4540,151 @@
         <v>653</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>438</v>
+        <v>228</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F88" s="5">
-        <v>20122</v>
+      <c r="F88" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>36</v>
+        <v>134</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>243</v>
+        <v>437</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>244</v>
+        <v>32</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>245</v>
+        <v>438</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>247</v>
+        <v>34</v>
+      </c>
+      <c r="F89" s="5">
+        <v>20122</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>248</v>
+        <v>36</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>81</v>
+        <v>248</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>360</v>
+        <v>249</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>361</v>
+        <v>77</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>362</v>
+        <v>250</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="F91" s="5">
-        <v>76123</v>
+        <v>79</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>423</v>
+        <v>360</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>26</v>
+        <v>361</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>130</v>
+        <v>362</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>28</v>
+        <v>363</v>
       </c>
       <c r="F92" s="5">
-        <v>39100</v>
+        <v>76123</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>549</v>
+        <v>423</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>550</v>
+        <v>26</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>551</v>
+        <v>130</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="F93" s="8" t="s">
-        <v>553</v>
+        <v>28</v>
+      </c>
+      <c r="F93" s="5">
+        <v>39100</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>646</v>
+        <v>549</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>7</v>
+        <v>550</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>647</v>
+        <v>551</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>8</v>
+        <v>552</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>178</v>
+        <v>553</v>
       </c>
       <c r="G94" s="4" t="s">
         <v>75</v>
@@ -4679,99 +4692,99 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>389</v>
+        <v>646</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>390</v>
+        <v>647</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F95" s="5">
-        <v>70043</v>
+        <v>8</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>217</v>
+        <v>389</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>218</v>
+        <v>390</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
+      </c>
+      <c r="F96" s="5">
+        <v>70043</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>48</v>
+        <v>217</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>45</v>
+        <v>218</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>32</v>
@@ -4780,13 +4793,13 @@
         <v>653</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G99" s="4" t="s">
         <v>36</v>
@@ -4794,7 +4807,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>32</v>
@@ -4817,7 +4830,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>32</v>
@@ -4840,53 +4853,53 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>369</v>
+        <v>128</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>370</v>
+        <v>32</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>371</v>
+        <v>120</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="F102" s="5">
-        <v>61121</v>
+        <v>34</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>163</v>
+        <v>36</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>662</v>
+        <v>369</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>32</v>
+        <v>370</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>187</v>
+        <v>371</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>34</v>
+        <v>372</v>
       </c>
       <c r="F103" s="5">
-        <v>20158</v>
+        <v>61121</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>199</v>
+        <v>662</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>32</v>
@@ -4900,8 +4913,8 @@
       <c r="E104" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F104" s="5" t="s">
-        <v>188</v>
+      <c r="F104" s="5">
+        <v>20158</v>
       </c>
       <c r="G104" s="4" t="s">
         <v>157</v>
@@ -4909,53 +4922,53 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>504</v>
+        <v>199</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>507</v>
+        <v>32</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>506</v>
+        <v>187</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="F105" s="5">
-        <v>35010</v>
+        <v>34</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>503</v>
+        <v>157</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>279</v>
+        <v>504</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>32</v>
+        <v>507</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>303</v>
+        <v>506</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>34</v>
+        <v>505</v>
       </c>
       <c r="F106" s="5">
-        <v>20123</v>
+        <v>35010</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>36</v>
+        <v>503</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>563</v>
+        <v>279</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>32</v>
@@ -4964,13 +4977,13 @@
         <v>653</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>562</v>
+        <v>303</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F107" s="5">
-        <v>20122</v>
+        <v>20123</v>
       </c>
       <c r="G107" s="4" t="s">
         <v>36</v>
@@ -4978,25 +4991,25 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>349</v>
+        <v>563</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>350</v>
+        <v>32</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>351</v>
+        <v>562</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="F108" s="5">
-        <v>15033</v>
+        <v>20122</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
@@ -5047,76 +5060,76 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>533</v>
+        <v>349</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>115</v>
+        <v>350</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>534</v>
+        <v>351</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>117</v>
+        <v>352</v>
       </c>
       <c r="F111" s="5">
-        <v>65127</v>
+        <v>15033</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>57</v>
+        <v>533</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>58</v>
+        <v>534</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>59</v>
+        <v>117</v>
+      </c>
+      <c r="F112" s="5">
+        <v>65127</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>334</v>
+        <v>57</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>335</v>
+        <v>58</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F113" s="5">
-        <v>10153</v>
+        <v>34</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>428</v>
+        <v>334</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>77</v>
@@ -5139,76 +5152,76 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>571</v>
+        <v>428</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>572</v>
+        <v>335</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="F115" s="5">
-        <v>20154</v>
+        <v>10153</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>280</v>
+        <v>571</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>304</v>
+        <v>572</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F116" s="5">
-        <v>183</v>
+        <v>20154</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>305</v>
+        <v>157</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>208</v>
+        <v>280</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>209</v>
+        <v>304</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F117" s="5" t="s">
-        <v>56</v>
+        <v>8</v>
+      </c>
+      <c r="F117" s="5">
+        <v>183</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>36</v>
+        <v>305</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>547</v>
+        <v>208</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>32</v>
@@ -5217,21 +5230,21 @@
         <v>653</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>548</v>
+        <v>209</v>
       </c>
       <c r="E118" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F118" s="5">
-        <v>20154</v>
+      <c r="F118" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>273</v>
+        <v>547</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>32</v>
@@ -5240,13 +5253,13 @@
         <v>653</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>274</v>
+        <v>548</v>
       </c>
       <c r="E119" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F119" s="5" t="s">
-        <v>156</v>
+      <c r="F119" s="5">
+        <v>20154</v>
       </c>
       <c r="G119" s="4" t="s">
         <v>157</v>
@@ -5254,30 +5267,30 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>126</v>
+        <v>273</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>127</v>
+        <v>274</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>29</v>
+        <v>156</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>240</v>
+        <v>126</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>26</v>
@@ -5300,168 +5313,168 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>412</v>
+        <v>240</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>413</v>
+        <v>127</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>178</v>
+        <v>29</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>272</v>
+        <v>412</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>27</v>
+        <v>413</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>29</v>
+        <v>178</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>144</v>
+        <v>26</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>237</v>
+        <v>27</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>238</v>
+        <v>28</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>239</v>
+        <v>29</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>148</v>
+        <v>30</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>596</v>
+        <v>236</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>597</v>
+        <v>237</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F125" s="5">
-        <v>20122</v>
+        <v>238</v>
+      </c>
+      <c r="F125" s="5" t="s">
+        <v>239</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>36</v>
+        <v>148</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>535</v>
+        <v>596</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>536</v>
+        <v>32</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>537</v>
+        <v>597</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>538</v>
+        <v>34</v>
       </c>
       <c r="F126" s="5">
-        <v>34133</v>
+        <v>20122</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>512</v>
+        <v>36</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>433</v>
+        <v>535</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>26</v>
+        <v>536</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>127</v>
+        <v>537</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>28</v>
+        <v>538</v>
       </c>
       <c r="F127" s="5">
-        <v>39100</v>
+        <v>34133</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>30</v>
+        <v>512</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>649</v>
+        <v>433</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>650</v>
+        <v>127</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F128" s="5">
-        <v>20121</v>
+        <v>39100</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>204</v>
+        <v>649</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>32</v>
@@ -5470,13 +5483,13 @@
         <v>653</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>58</v>
+        <v>650</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F129" s="5" t="s">
-        <v>59</v>
+      <c r="F129" s="5">
+        <v>20121</v>
       </c>
       <c r="G129" s="4" t="s">
         <v>36</v>
@@ -5484,7 +5497,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>364</v>
+        <v>204</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>32</v>
@@ -5498,8 +5511,8 @@
       <c r="E130" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F130" s="5">
-        <v>20123</v>
+      <c r="F130" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G130" s="4" t="s">
         <v>36</v>
@@ -5507,7 +5520,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>99</v>
+        <v>364</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>32</v>
@@ -5521,8 +5534,8 @@
       <c r="E131" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F131" s="5" t="s">
-        <v>59</v>
+      <c r="F131" s="5">
+        <v>20123</v>
       </c>
       <c r="G131" s="4" t="s">
         <v>36</v>
@@ -5530,237 +5543,237 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>491</v>
+        <v>99</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>492</v>
+        <v>58</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F132" s="8" t="s">
-        <v>271</v>
+        <v>34</v>
+      </c>
+      <c r="F132" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>518</v>
+        <v>492</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F133" s="5">
-        <v>80121</v>
+        <v>8</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>404</v>
+        <v>517</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>262</v>
+        <v>67</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>405</v>
+        <v>518</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>406</v>
+        <v>69</v>
       </c>
       <c r="F134" s="5">
-        <v>38121</v>
+        <v>80121</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>266</v>
+        <v>71</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>367</v>
+        <v>404</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>32</v>
+        <v>262</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>34</v>
+        <v>406</v>
       </c>
       <c r="F135" s="5">
-        <v>20123</v>
+        <v>38121</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>36</v>
+        <v>266</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F136" s="5">
-        <v>90139</v>
+        <v>20123</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>193</v>
+        <v>359</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F137" s="5">
-        <v>20123</v>
+        <v>90139</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>453</v>
+        <v>343</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>454</v>
+        <v>193</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F138" s="8" t="s">
-        <v>178</v>
+        <v>34</v>
+      </c>
+      <c r="F138" s="5">
+        <v>20123</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>281</v>
+        <v>453</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>306</v>
+        <v>7</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>307</v>
+        <v>454</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="F139" s="5">
-        <v>12037</v>
+        <v>8</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>305</v>
+        <v>75</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>11</v>
+        <v>281</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>7</v>
+        <v>306</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>12</v>
+        <v>307</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>13</v>
+        <v>308</v>
+      </c>
+      <c r="F140" s="5">
+        <v>12037</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>9</v>
+        <v>305</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>121</v>
+        <v>11</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>26</v>
@@ -5783,99 +5796,99 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>651</v>
+        <v>72</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>652</v>
+        <v>73</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F144" s="5">
-        <v>20124</v>
+        <v>8</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>676</v>
+        <v>651</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>350</v>
+        <v>32</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>677</v>
+        <v>652</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>678</v>
+        <v>34</v>
       </c>
       <c r="F145" s="5">
-        <v>15079</v>
+        <v>20124</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>679</v>
+        <v>157</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>25</v>
+        <v>676</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>26</v>
+        <v>350</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>27</v>
+        <v>677</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>29</v>
+        <v>678</v>
+      </c>
+      <c r="F146" s="5">
+        <v>15079</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>30</v>
+        <v>679</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>496</v>
+        <v>25</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>26</v>
@@ -5889,8 +5902,8 @@
       <c r="E147" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F147" s="5">
-        <v>39100</v>
+      <c r="F147" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G147" s="4" t="s">
         <v>30</v>
@@ -5898,12 +5911,12 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>684</v>
+        <v>496</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C148" s="4" t="s">
+      <c r="C148" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D148" s="4" t="s">
@@ -5921,53 +5934,53 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>231</v>
+        <v>684</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C149" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C149" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>232</v>
+        <v>27</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>216</v>
+        <v>28</v>
+      </c>
+      <c r="F149" s="5">
+        <v>39100</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>588</v>
+        <v>231</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>589</v>
+        <v>232</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F150" s="5">
-        <v>20122</v>
+        <v>8</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>186</v>
+        <v>588</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>32</v>
@@ -5976,44 +5989,44 @@
         <v>653</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>187</v>
+        <v>589</v>
       </c>
       <c r="E151" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F151" s="5" t="s">
-        <v>188</v>
+      <c r="F151" s="5">
+        <v>20122</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>481</v>
+        <v>186</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>482</v>
+        <v>32</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>483</v>
+        <v>187</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="F152" s="5">
-        <v>66020</v>
+        <v>34</v>
+      </c>
+      <c r="F152" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>75</v>
+        <v>157</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>619</v>
+        <v>481</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>482</v>
@@ -6036,168 +6049,168 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>574</v>
+        <v>619</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>32</v>
+        <v>482</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>575</v>
+        <v>483</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>34</v>
+        <v>484</v>
       </c>
       <c r="F154" s="5">
-        <v>20124</v>
+        <v>66020</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>409</v>
+        <v>574</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>339</v>
+        <v>32</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>410</v>
+        <v>575</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="F155" s="5">
-        <v>37137</v>
+        <v>20124</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>341</v>
+        <v>157</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>458</v>
+        <v>409</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>7</v>
+        <v>339</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>459</v>
+        <v>410</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F156" s="8" t="s">
-        <v>216</v>
+        <v>411</v>
+      </c>
+      <c r="F156" s="5">
+        <v>37137</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>9</v>
+        <v>341</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>293</v>
+        <v>458</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>294</v>
+        <v>7</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>295</v>
+        <v>459</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="F157" s="5">
-        <v>56010</v>
+        <v>8</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>216</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>297</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>601</v>
+        <v>293</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>32</v>
+        <v>294</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>602</v>
+        <v>295</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="F158" s="5">
-        <v>20145</v>
+        <v>56010</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>134</v>
+        <v>297</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>309</v>
+        <v>601</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>310</v>
+        <v>602</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>311</v>
+        <v>34</v>
       </c>
       <c r="F159" s="5">
-        <v>40060</v>
+        <v>20145</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>382</v>
+        <v>309</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>383</v>
+        <v>310</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>34</v>
+        <v>311</v>
       </c>
       <c r="F160" s="5">
-        <v>20121</v>
+        <v>40060</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>32</v>
@@ -6211,8 +6224,8 @@
       <c r="E161" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F161" s="5" t="s">
-        <v>56</v>
+      <c r="F161" s="5">
+        <v>20121</v>
       </c>
       <c r="G161" s="4" t="s">
         <v>36</v>
@@ -6220,53 +6233,53 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>211</v>
+        <v>384</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>177</v>
+        <v>383</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>178</v>
+        <v>56</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>573</v>
+        <v>211</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F163" s="5">
-        <v>20124</v>
+        <v>8</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>178</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>32</v>
@@ -6289,99 +6302,99 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>629</v>
+        <v>587</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>630</v>
+        <v>190</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>631</v>
+        <v>34</v>
       </c>
       <c r="F165" s="5">
-        <v>39025</v>
+        <v>20124</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>66</v>
+        <v>629</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>68</v>
+        <v>630</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>70</v>
+        <v>631</v>
+      </c>
+      <c r="F166" s="5">
+        <v>39025</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>282</v>
+        <v>66</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>312</v>
+        <v>67</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>313</v>
+        <v>68</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="F167" s="5">
-        <v>57021</v>
+        <v>69</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>297</v>
+        <v>71</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>182</v>
+        <v>282</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>7</v>
+        <v>312</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>177</v>
+        <v>313</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>178</v>
+        <v>314</v>
+      </c>
+      <c r="F168" s="5">
+        <v>57021</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>75</v>
+        <v>297</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>460</v>
+        <v>182</v>
       </c>
       <c r="B169" s="4" t="s">
         <v>7</v>
@@ -6395,7 +6408,7 @@
       <c r="E169" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F169" s="8" t="s">
+      <c r="F169" s="5" t="s">
         <v>178</v>
       </c>
       <c r="G169" s="4" t="s">
@@ -6404,145 +6417,145 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>87</v>
+        <v>460</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>89</v>
+        <v>177</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F170" s="5" t="s">
-        <v>91</v>
+        <v>8</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>344</v>
+        <v>87</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>345</v>
+        <v>89</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="F171" s="5">
-        <v>70124</v>
+        <v>90</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>187</v>
+        <v>345</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>34</v>
+        <v>346</v>
       </c>
       <c r="F172" s="5">
-        <v>20158</v>
+        <v>70124</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>157</v>
+        <v>42</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>644</v>
+        <v>331</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>645</v>
+        <v>187</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F173" s="5">
-        <v>39100</v>
+        <v>20158</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>355</v>
+        <v>644</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>306</v>
+        <v>26</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>356</v>
+        <v>645</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>357</v>
+        <v>28</v>
       </c>
       <c r="F174" s="5">
-        <v>12084</v>
+        <v>39100</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>305</v>
+        <v>30</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>192</v>
+        <v>355</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>32</v>
+        <v>306</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>193</v>
+        <v>356</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F175" s="5" t="s">
-        <v>59</v>
+        <v>357</v>
+      </c>
+      <c r="F175" s="5">
+        <v>12084</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>36</v>
+        <v>305</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>32</v>
@@ -6551,13 +6564,13 @@
         <v>653</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
       <c r="E176" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="G176" s="4" t="s">
         <v>36</v>
@@ -6565,99 +6578,99 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>455</v>
+        <v>225</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>456</v>
+        <v>226</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F177" s="8" t="s">
-        <v>457</v>
+        <v>34</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>106</v>
+        <v>455</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>107</v>
+        <v>7</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>108</v>
+        <v>456</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F178" s="5" t="s">
-        <v>110</v>
+        <v>8</v>
+      </c>
+      <c r="F178" s="8" t="s">
+        <v>457</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>429</v>
+        <v>106</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>306</v>
+        <v>107</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>430</v>
+        <v>108</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="F179" s="5">
-        <v>12100</v>
+        <v>109</v>
+      </c>
+      <c r="F179" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>305</v>
+        <v>111</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>393</v>
+        <v>429</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>20</v>
+        <v>306</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>21</v>
+        <v>430</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>22</v>
+        <v>431</v>
       </c>
       <c r="F180" s="5">
-        <v>40127</v>
+        <v>12100</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>24</v>
+        <v>305</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>609</v>
+        <v>393</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>20</v>
@@ -6666,13 +6679,13 @@
         <v>653</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>610</v>
+        <v>21</v>
       </c>
       <c r="E181" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F181" s="5">
-        <v>40122</v>
+        <v>40127</v>
       </c>
       <c r="G181" s="4" t="s">
         <v>24</v>
@@ -6680,30 +6693,30 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>353</v>
+        <v>609</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>354</v>
+        <v>610</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F182" s="5">
-        <v>20121</v>
+        <v>40122</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>656</v>
+        <v>353</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>32</v>
@@ -6726,7 +6739,7 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>554</v>
+        <v>656</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>32</v>
@@ -6735,21 +6748,21 @@
         <v>653</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>523</v>
+        <v>354</v>
       </c>
       <c r="E184" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F184" s="5">
-        <v>20154</v>
+        <v>20121</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>32</v>
@@ -6772,7 +6785,7 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>32</v>
@@ -6795,7 +6808,7 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>594</v>
+        <v>522</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>32</v>
@@ -6804,7 +6817,7 @@
         <v>653</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>595</v>
+        <v>523</v>
       </c>
       <c r="E187" s="4" t="s">
         <v>34</v>
@@ -6818,513 +6831,513 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="E188" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F188" s="5">
+        <v>20154</v>
+      </c>
+      <c r="G188" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A189" s="10" t="s">
         <v>513</v>
       </c>
-      <c r="B188" s="4" t="s">
+      <c r="B189" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C188" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D188" s="4" t="s">
+      <c r="C189" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D189" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E188" s="4" t="s">
+      <c r="E189" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F188" s="5">
+      <c r="F189" s="11">
         <v>39100</v>
       </c>
-      <c r="G188" s="4" t="s">
+      <c r="G189" s="10" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A189" s="9" t="s">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A190" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B189" s="9" t="s">
+      <c r="B190" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C189" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D189" s="9" t="s">
+      <c r="C190" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D190" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E189" s="9" t="s">
+      <c r="E190" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F189" s="10" t="s">
+      <c r="F190" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G189" s="9" t="s">
+      <c r="G190" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A190" s="9" t="s">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A191" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B190" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D190" s="9" t="s">
+      <c r="B191" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D191" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E190" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F190" s="10" t="s">
+      <c r="E191" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F191" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G190" s="9" t="s">
+      <c r="G191" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A191" s="9" t="s">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A192" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="B191" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D191" s="9" t="s">
+      <c r="B192" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D192" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="E191" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F191" s="10">
+      <c r="E192" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F192" s="7">
         <v>20123</v>
       </c>
-      <c r="G191" s="9" t="s">
+      <c r="G192" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A192" s="9" t="s">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A193" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B192" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D192" s="9" t="s">
+      <c r="B193" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D193" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E192" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F192" s="10" t="s">
+      <c r="E193" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F193" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G192" s="9" t="s">
+      <c r="G193" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A193" s="9" t="s">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A194" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="B193" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D193" s="9" t="s">
+      <c r="B194" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D194" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="E193" s="9" t="s">
+      <c r="E194" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="F193" s="10">
+      <c r="F194" s="7">
         <v>20038</v>
       </c>
-      <c r="G193" s="9" t="s">
+      <c r="G194" s="3" t="s">
         <v>134</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A194" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="B194" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D194" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="E194" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="F194" s="10">
-        <v>10121</v>
-      </c>
-      <c r="G194" s="9" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F195" s="7">
+        <v>10121</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A196" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="B195" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C195" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D195" s="3" t="s">
+      <c r="B196" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D196" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="E195" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F195" s="7">
+      <c r="E196" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F196" s="7">
         <v>20124</v>
       </c>
-      <c r="G195" s="3" t="s">
+      <c r="G196" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A196" s="9" t="s">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A197" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B196" s="9" t="s">
+      <c r="B197" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C196" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D196" s="9" t="s">
+      <c r="C197" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D197" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E196" s="9" t="s">
+      <c r="E197" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F196" s="10" t="s">
+      <c r="F197" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G196" s="9" t="s">
+      <c r="G197" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A197" s="9" t="s">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A198" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="B197" s="9" t="s">
+      <c r="B198" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="C197" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D197" s="9" t="s">
+      <c r="C198" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D198" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="E197" s="9" t="s">
+      <c r="E198" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="F197" s="10">
+      <c r="F198" s="7">
         <v>64020</v>
       </c>
-      <c r="G197" s="9" t="s">
+      <c r="G198" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A198" s="9" t="s">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A199" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="B198" s="9" t="s">
+      <c r="B199" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C198" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D198" s="9" t="s">
+      <c r="C199" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D199" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="E198" s="9" t="s">
+      <c r="E199" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F198" s="12" t="s">
+      <c r="F199" s="9" t="s">
         <v>580</v>
       </c>
-      <c r="G198" s="9" t="s">
+      <c r="G199" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A199" s="9" t="s">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A200" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="B199" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D199" s="9" t="s">
+      <c r="B200" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D200" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E199" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F199" s="10">
+      <c r="E200" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F200" s="7">
         <v>20121</v>
       </c>
-      <c r="G199" s="9" t="s">
+      <c r="G200" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A200" s="9" t="s">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A201" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B200" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D200" s="9" t="s">
+      <c r="B201" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D201" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E200" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F200" s="10" t="s">
+      <c r="E201" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F201" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="G200" s="9" t="s">
+      <c r="G201" s="3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A201" s="9" t="s">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A202" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="B201" s="9" t="s">
+      <c r="B202" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C201" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D201" s="9" t="s">
+      <c r="C202" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D202" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="E201" s="9" t="s">
+      <c r="E202" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F201" s="12" t="s">
+      <c r="F202" s="9" t="s">
         <v>605</v>
       </c>
-      <c r="G201" s="9" t="s">
+      <c r="G202" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A202" s="9" t="s">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A203" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B202" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C202" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D202" s="9" t="s">
+      <c r="B203" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D203" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="E202" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F202" s="10" t="s">
+      <c r="E203" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F203" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G202" s="9" t="s">
+      <c r="G203" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A203" s="9" t="s">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A204" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="B203" s="9" t="s">
+      <c r="B204" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="C203" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D203" s="9" t="s">
+      <c r="C204" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D204" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="E203" s="9" t="s">
+      <c r="E204" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="F203" s="10">
+      <c r="F204" s="7">
         <v>37045</v>
       </c>
-      <c r="G203" s="9" t="s">
+      <c r="G204" s="3" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A204" s="9" t="s">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A205" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B204" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D204" s="9" t="s">
+      <c r="B205" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D205" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E204" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F204" s="10" t="s">
+      <c r="E205" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F205" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="G204" s="9" t="s">
+      <c r="G205" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A205" s="9" t="s">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A206" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="B205" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C205" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D205" s="9" t="s">
+      <c r="B206" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D206" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E205" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F205" s="10">
+      <c r="E206" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F206" s="7">
         <v>20126</v>
       </c>
-      <c r="G205" s="9" t="s">
+      <c r="G206" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A206" s="9" t="s">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A207" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="B206" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D206" s="9" t="s">
+      <c r="B207" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D207" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="E206" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F206" s="10">
+      <c r="E207" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F207" s="7">
         <v>20138</v>
       </c>
-      <c r="G206" s="9" t="s">
+      <c r="G207" s="3" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A207" s="9" t="s">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A208" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="B207" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D207" s="9" t="s">
+      <c r="B208" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D208" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="E207" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F207" s="10">
+      <c r="E208" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F208" s="7">
         <v>20122</v>
       </c>
-      <c r="G207" s="9" t="s">
+      <c r="G208" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A208" s="9" t="s">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A209" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="B208" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D208" s="9" t="s">
+      <c r="B209" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D209" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="E208" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F208" s="10">
+      <c r="E209" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F209" s="7">
         <v>20123</v>
       </c>
-      <c r="G208" s="9" t="s">
+      <c r="G209" s="3" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A209" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="B209" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D209" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="E209" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F209" s="10">
-        <v>20135</v>
-      </c>
-      <c r="G209" s="9" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="3" t="s">
-        <v>620</v>
+        <v>469</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>32</v>
@@ -7347,7 +7360,7 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="3" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>32</v>
@@ -7369,192 +7382,192 @@
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A212" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="B212" s="9" t="s">
+      <c r="A212" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="B212" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="D212" s="9" t="s">
+      <c r="D212" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="E212" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F212" s="10">
+      <c r="E212" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F212" s="7">
         <v>20135</v>
       </c>
-      <c r="G212" s="9" t="s">
+      <c r="G212" s="3" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F213" s="7">
+        <v>20135</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A214" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="B213" s="3" t="s">
+      <c r="B214" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C213" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D213" s="3" t="s">
+      <c r="C214" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D214" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="E213" s="3" t="s">
+      <c r="E214" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="F213" s="7">
+      <c r="F214" s="7">
         <v>85100</v>
       </c>
-      <c r="G213" s="3" t="s">
+      <c r="G214" s="3" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A214" s="9" t="s">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A215" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B214" s="9" t="s">
+      <c r="B215" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C214" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D214" s="9" t="s">
+      <c r="C215" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D215" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E214" s="9" t="s">
+      <c r="E215" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="F214" s="10" t="s">
+      <c r="F215" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="G214" s="9" t="s">
+      <c r="G215" s="3" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A215" s="9" t="s">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A216" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="B215" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D215" s="9" t="s">
+      <c r="B216" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D216" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="E215" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F215" s="10">
+      <c r="E216" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F216" s="7">
         <v>20144</v>
       </c>
-      <c r="G215" s="9" t="s">
+      <c r="G216" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A216" s="9" t="s">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A217" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B216" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D216" s="9" t="s">
+      <c r="B217" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D217" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="E216" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F216" s="10" t="s">
+      <c r="E217" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F217" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="G216" s="9" t="s">
+      <c r="G217" s="3" t="s">
         <v>134</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A217" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="B217" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D217" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="E217" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="F217" s="10">
-        <v>40026</v>
-      </c>
-      <c r="G217" s="9" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="F218" s="7">
+        <v>40026</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A219" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="B218" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D218" s="3" t="s">
+      <c r="B219" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D219" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="E218" s="3" t="s">
+      <c r="E219" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="F218" s="7">
+      <c r="F219" s="7">
         <v>20068</v>
       </c>
-      <c r="G218" s="3" t="s">
+      <c r="G219" s="3" t="s">
         <v>260</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A219" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="B219" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D219" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="E219" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F219" s="10" t="s">
-        <v>321</v>
-      </c>
-      <c r="G219" s="9" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="3" t="s">
-        <v>659</v>
+        <v>284</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>7</v>
@@ -7563,389 +7576,389 @@
         <v>653</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>660</v>
+        <v>318</v>
       </c>
       <c r="E220" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F220" s="11" t="s">
-        <v>661</v>
+      <c r="F220" s="7" t="s">
+        <v>321</v>
       </c>
       <c r="G220" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A221" s="9" t="s">
+      <c r="A221" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F221" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A222" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="B221" s="9" t="s">
+      <c r="B222" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C221" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D221" s="9" t="s">
+      <c r="C222" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D222" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E221" s="9" t="s">
+      <c r="E222" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F221" s="10">
+      <c r="F222" s="7">
         <v>39100</v>
       </c>
-      <c r="G221" s="9" t="s">
+      <c r="G222" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A222" s="9" t="s">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A223" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B222" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D222" s="9" t="s">
+      <c r="B223" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D223" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="E222" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F222" s="10">
+      <c r="E223" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F223" s="7">
         <v>20123</v>
       </c>
-      <c r="G222" s="9" t="s">
+      <c r="G223" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A223" s="9" t="s">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A224" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="B223" s="9" t="s">
+      <c r="B224" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C223" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D223" s="9" t="s">
+      <c r="C224" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D224" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="E223" s="9" t="s">
+      <c r="E224" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="F223" s="10">
+      <c r="F224" s="7">
         <v>12020</v>
       </c>
-      <c r="G223" s="9" t="s">
+      <c r="G224" s="3" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A224" s="9" t="s">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A225" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B224" s="9" t="s">
+      <c r="B225" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C224" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D224" s="9" t="s">
+      <c r="C225" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D225" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E224" s="9" t="s">
+      <c r="E225" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F224" s="10" t="s">
+      <c r="F225" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G224" s="9" t="s">
+      <c r="G225" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A225" s="9" t="s">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A226" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="B225" s="9" t="s">
+      <c r="B226" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="C225" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D225" s="9" t="s">
+      <c r="C226" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D226" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="E225" s="9" t="s">
+      <c r="E226" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="F225" s="10">
+      <c r="F226" s="7">
         <v>28053</v>
       </c>
-      <c r="G225" s="9" t="s">
+      <c r="G226" s="3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A226" s="9" t="s">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A227" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B226" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C226" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D226" s="9" t="s">
+      <c r="B227" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D227" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E226" s="9" t="s">
+      <c r="E227" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="F226" s="10" t="s">
+      <c r="F227" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="G226" s="9" t="s">
+      <c r="G227" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A227" s="9" t="s">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A228" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="B227" s="9" t="s">
+      <c r="B228" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C227" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D227" s="9" t="s">
+      <c r="C228" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D228" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="E227" s="9" t="s">
+      <c r="E228" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F227" s="10">
+      <c r="F228" s="7">
         <v>39100</v>
       </c>
-      <c r="G227" s="9" t="s">
+      <c r="G228" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A228" s="9" t="s">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A229" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B228" s="9" t="s">
+      <c r="B229" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C228" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D228" s="9" t="s">
+      <c r="C229" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D229" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="E228" s="9" t="s">
+      <c r="E229" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F228" s="10" t="s">
+      <c r="F229" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="G228" s="9" t="s">
+      <c r="G229" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A229" s="9" t="s">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A230" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B229" s="9" t="s">
+      <c r="B230" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C229" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D229" s="9" t="s">
+      <c r="C230" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D230" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="E229" s="9" t="s">
+      <c r="E230" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F229" s="10" t="s">
+      <c r="F230" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="G229" s="9" t="s">
+      <c r="G230" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A230" s="9" t="s">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A231" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B230" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C230" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D230" s="9" t="s">
+      <c r="B231" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D231" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E230" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F230" s="10" t="s">
+      <c r="E231" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F231" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G230" s="9" t="s">
+      <c r="G231" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A231" s="9" t="s">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A232" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="B231" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C231" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D231" s="9" t="s">
+      <c r="B232" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D232" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E231" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F231" s="10">
+      <c r="E232" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F232" s="7">
         <v>20121</v>
       </c>
-      <c r="G231" s="9" t="s">
+      <c r="G232" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A232" s="9" t="s">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A233" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="B232" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C232" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D232" s="9" t="s">
+      <c r="B233" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D233" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="E232" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F232" s="10">
+      <c r="E233" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F233" s="7">
         <v>20121</v>
       </c>
-      <c r="G232" s="9" t="s">
+      <c r="G233" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A233" s="9" t="s">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A234" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="B233" s="9" t="s">
+      <c r="B234" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="C233" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D233" s="9" t="s">
+      <c r="C234" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D234" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="E233" s="9" t="s">
+      <c r="E234" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="F233" s="10">
+      <c r="F234" s="7">
         <v>53048</v>
       </c>
-      <c r="G233" s="9" t="s">
+      <c r="G234" s="3" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A234" s="9" t="s">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A235" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="B234" s="9" t="s">
+      <c r="B235" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="C234" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D234" s="9" t="s">
+      <c r="C235" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D235" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="E234" s="9" t="s">
+      <c r="E235" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="F234" s="10">
+      <c r="F235" s="7">
         <v>35011</v>
       </c>
-      <c r="G234" s="9" t="s">
+      <c r="G235" s="3" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A235" s="9" t="s">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A236" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B235" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D235" s="9" t="s">
+      <c r="B236" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D236" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E235" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F235" s="10" t="s">
+      <c r="E236" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F236" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G235" s="9" t="s">
+      <c r="G236" s="3" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A236" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="B236" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C236" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D236" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E236" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F236" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G236" s="9" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="3" t="s">
-        <v>641</v>
+        <v>129</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>26</v>
@@ -7959,8 +7972,8 @@
       <c r="E237" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F237" s="7">
-        <v>39100</v>
+      <c r="F237" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="G237" s="3" t="s">
         <v>30</v>
@@ -7968,191 +7981,191 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F238" s="7">
+        <v>39100</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A239" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="B238" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C238" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D238" s="3" t="s">
+      <c r="B239" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D239" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="E238" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F238" s="7">
+      <c r="E239" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F239" s="7">
         <v>20121</v>
       </c>
-      <c r="G238" s="9" t="s">
+      <c r="G239" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A239" s="9" t="s">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A240" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="B239" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C239" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D239" s="9" t="s">
+      <c r="B240" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D240" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="E239" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F239" s="10">
+      <c r="E240" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F240" s="7">
         <v>20121</v>
       </c>
-      <c r="G239" s="9" t="s">
+      <c r="G240" s="3" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A240" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B240" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C240" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D240" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E240" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F240" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G240" s="9" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F241" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A242" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="B241" s="3" t="s">
+      <c r="B242" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C241" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D241" s="3" t="s">
+      <c r="C242" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D242" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="E241" s="3" t="s">
+      <c r="E242" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F241" s="11" t="s">
+      <c r="F242" s="9" t="s">
         <v>566</v>
       </c>
-      <c r="G241" s="3" t="s">
+      <c r="G242" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A242" s="9" t="s">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A243" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="B242" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C242" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D242" s="9" t="s">
+      <c r="B243" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D243" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="E242" s="9" t="s">
+      <c r="E243" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="F242" s="10">
+      <c r="F243" s="7">
         <v>20089</v>
       </c>
-      <c r="G242" s="9" t="s">
+      <c r="G243" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A243" s="9" t="s">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A244" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="B243" s="9" t="s">
+      <c r="B244" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C243" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D243" s="9" t="s">
+      <c r="C244" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D244" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="E243" s="9" t="s">
+      <c r="E244" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F243" s="12" t="s">
+      <c r="F244" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="G243" s="9" t="s">
+      <c r="G244" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A244" s="9" t="s">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A245" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B244" s="9" t="s">
+      <c r="B245" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C244" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D244" s="9" t="s">
+      <c r="C245" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D245" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="E244" s="9" t="s">
+      <c r="E245" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F244" s="10" t="s">
+      <c r="F245" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="G244" s="9" t="s">
+      <c r="G245" s="3" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A245" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="B245" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C245" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D245" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="E245" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F245" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="G245" s="9" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" s="3" t="s">
-        <v>663</v>
+        <v>212</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>32</v>
@@ -8166,85 +8179,85 @@
       <c r="E246" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F246" s="7">
-        <v>20124</v>
+      <c r="F246" s="7" t="s">
+        <v>156</v>
       </c>
       <c r="G246" s="3" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A247" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="B247" s="9" t="s">
+      <c r="A247" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="B247" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="D247" s="9" t="s">
+      <c r="D247" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="E247" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F247" s="10">
+      <c r="E247" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F247" s="7">
         <v>20124</v>
       </c>
-      <c r="G247" s="9" t="s">
+      <c r="G247" s="3" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F248" s="7">
+        <v>20124</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A249" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="B248" s="3" t="s">
+      <c r="B249" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C248" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D248" s="3" t="s">
+      <c r="C249" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D249" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="E248" s="3" t="s">
+      <c r="E249" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F248" s="7">
+      <c r="F249" s="7">
         <v>24050</v>
       </c>
-      <c r="G248" s="3" t="s">
+      <c r="G249" s="3" t="s">
         <v>148</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A249" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="B249" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C249" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D249" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="E249" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F249" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="G249" s="9" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" s="3" t="s">
-        <v>621</v>
+        <v>227</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>32</v>
@@ -8258,384 +8271,384 @@
       <c r="E250" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F250" s="7">
-        <v>20148</v>
+      <c r="F250" s="7" t="s">
+        <v>229</v>
       </c>
       <c r="G250" s="3" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A251" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="B251" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C251" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D251" s="9" t="s">
+      <c r="A251" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D251" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="E251" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F251" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="G251" s="9" t="s">
+      <c r="E251" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F251" s="7">
+        <v>20148</v>
+      </c>
+      <c r="G251" s="3" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" s="3" t="s">
-        <v>666</v>
+        <v>254</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>101</v>
+        <v>32</v>
       </c>
       <c r="C252" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>667</v>
+        <v>228</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="F252" s="7">
-        <v>25055</v>
+        <v>34</v>
+      </c>
+      <c r="F252" s="7" t="s">
+        <v>229</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="E253" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="F253" s="7">
+        <v>25055</v>
+      </c>
+      <c r="G253" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A254" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="B253" s="3" t="s">
+      <c r="B254" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="C253" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D253" s="3" t="s">
+      <c r="C254" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D254" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="E253" s="3" t="s">
+      <c r="E254" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="F253" s="7">
+      <c r="F254" s="7">
         <v>50132</v>
       </c>
-      <c r="G253" s="3" t="s">
+      <c r="G254" s="3" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A254" s="9" t="s">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A255" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="B254" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C254" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D254" s="9" t="s">
+      <c r="B255" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C255" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D255" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="E254" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F254" s="10">
+      <c r="E255" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F255" s="7">
         <v>20129</v>
       </c>
-      <c r="G254" s="9" t="s">
+      <c r="G255" s="3" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A255" s="9" t="s">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A256" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="B255" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C255" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D255" s="9" t="s">
+      <c r="B256" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D256" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="E255" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F255" s="10">
+      <c r="E256" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F256" s="7">
         <v>20129</v>
       </c>
-      <c r="G255" s="9" t="s">
+      <c r="G256" s="3" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A256" s="9" t="s">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A257" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="B256" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C256" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D256" s="9" t="s">
+      <c r="B257" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D257" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="E256" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F256" s="10">
+      <c r="E257" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F257" s="7">
         <v>20129</v>
       </c>
-      <c r="G256" s="9" t="s">
+      <c r="G257" s="3" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A257" s="9" t="s">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A258" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="B257" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C257" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D257" s="9" t="s">
+      <c r="B258" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D258" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="E257" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F257" s="10">
+      <c r="E258" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F258" s="7">
         <v>20129</v>
       </c>
-      <c r="G257" s="9" t="s">
+      <c r="G258" s="3" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A258" s="9" t="s">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A259" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B258" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C258" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D258" s="9" t="s">
+      <c r="B259" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D259" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E258" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F258" s="10" t="s">
+      <c r="E259" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F259" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G258" s="9" t="s">
+      <c r="G259" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A259" s="9" t="s">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A260" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="B259" s="9" t="s">
+      <c r="B260" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C259" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D259" s="9" t="s">
+      <c r="C260" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D260" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="E259" s="9" t="s">
+      <c r="E260" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="F259" s="10">
+      <c r="F260" s="7">
         <v>40026</v>
       </c>
-      <c r="G259" s="9" t="s">
+      <c r="G260" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A260" s="9" t="s">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A261" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B260" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C260" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D260" s="9" t="s">
+      <c r="B261" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D261" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="E260" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F260" s="10">
+      <c r="E261" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F261" s="7">
         <v>20124</v>
       </c>
-      <c r="G260" s="9" t="s">
+      <c r="G261" s="3" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A261" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="B261" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="C261" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D261" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="E261" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="F261" s="10">
-        <v>12011</v>
-      </c>
-      <c r="G261" s="9" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D262" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="E262" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="F262" s="7">
+        <v>12011</v>
+      </c>
+      <c r="G262" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A263" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="B262" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C262" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D262" s="3" t="s">
+      <c r="B263" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C263" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D263" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="E262" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F262" s="7">
+      <c r="E263" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F263" s="7">
         <v>20121</v>
       </c>
-      <c r="G262" s="3" t="s">
+      <c r="G263" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A263" s="9" t="s">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A264" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B263" s="9" t="s">
+      <c r="B264" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C263" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D263" s="9" t="s">
+      <c r="C264" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D264" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E263" s="9" t="s">
+      <c r="E264" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="F263" s="10" t="s">
+      <c r="F264" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="G263" s="9" t="s">
+      <c r="G264" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A264" s="9" t="s">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A265" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="B264" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C264" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D264" s="9" t="s">
+      <c r="B265" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C265" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D265" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="E264" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F264" s="10">
+      <c r="E265" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F265" s="7">
         <v>20123</v>
       </c>
-      <c r="G264" s="9" t="s">
+      <c r="G265" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A265" s="9" t="s">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A266" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="B265" s="9" t="s">
+      <c r="B266" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C265" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D265" s="9" t="s">
+      <c r="C266" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D266" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="E265" s="9" t="s">
+      <c r="E266" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F265" s="10">
+      <c r="F266" s="7">
         <v>90141</v>
       </c>
-      <c r="G265" s="9" t="s">
+      <c r="G266" s="3" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A266" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="B266" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C266" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D266" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="E266" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F266" s="12" t="s">
-        <v>388</v>
-      </c>
-      <c r="G266" s="9" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" s="3" t="s">
-        <v>640</v>
+        <v>478</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>7</v>
@@ -8649,7 +8662,7 @@
       <c r="E267" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F267" s="11" t="s">
+      <c r="F267" s="9" t="s">
         <v>388</v>
       </c>
       <c r="G267" s="3" t="s">
@@ -8658,7 +8671,7 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" s="3" t="s">
-        <v>528</v>
+        <v>640</v>
       </c>
       <c r="B268" s="3" t="s">
         <v>7</v>
@@ -8672,7 +8685,7 @@
       <c r="E268" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F268" s="11" t="s">
+      <c r="F268" s="9" t="s">
         <v>388</v>
       </c>
       <c r="G268" s="3" t="s">
@@ -8680,123 +8693,123 @@
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A269" s="9" t="s">
+      <c r="A269" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="E269" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F269" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="G269" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A270" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="B269" s="9" t="s">
+      <c r="B270" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C269" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D269" s="9" t="s">
+      <c r="C270" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D270" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="E269" s="9" t="s">
+      <c r="E270" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F269" s="10" t="s">
+      <c r="F270" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="G269" s="9" t="s">
+      <c r="G270" s="3" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A270" s="9" t="s">
-        <v>463</v>
-      </c>
-      <c r="B270" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="C270" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D270" s="9" t="s">
-        <v>464</v>
-      </c>
-      <c r="E270" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="F270" s="10">
-        <v>38055</v>
-      </c>
-      <c r="G270" s="9" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="B271" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C271" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="E271" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="F271" s="7">
+        <v>38055</v>
+      </c>
+      <c r="G271" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A272" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="B271" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C271" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D271" s="3" t="s">
+      <c r="B272" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D272" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E271" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F271" s="7">
+      <c r="E272" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F272" s="7">
         <v>20145</v>
       </c>
-      <c r="G271" s="3" t="s">
+      <c r="G272" s="3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A272" s="9" t="s">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A273" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="B272" s="9" t="s">
+      <c r="B273" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C272" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D272" s="9" t="s">
+      <c r="C273" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D273" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="E272" s="9" t="s">
+      <c r="E273" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="F272" s="10">
+      <c r="F273" s="7">
         <v>25010</v>
       </c>
-      <c r="G272" s="9" t="s">
+      <c r="G273" s="3" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A273" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="B273" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C273" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D273" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="E273" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F273" s="10">
-        <v>20123</v>
-      </c>
-      <c r="G273" s="9" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" s="3" t="s">
-        <v>618</v>
+        <v>391</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>32</v>
@@ -8818,380 +8831,403 @@
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A275" s="9" t="s">
+      <c r="A275" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C275" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E275" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F275" s="7">
+        <v>20123</v>
+      </c>
+      <c r="G275" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A276" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="B275" s="9" t="s">
+      <c r="B276" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C275" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D275" s="9" t="s">
+      <c r="C276" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D276" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="E275" s="9" t="s">
+      <c r="E276" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="F275" s="10">
+      <c r="F276" s="7">
         <v>71016</v>
       </c>
-      <c r="G275" s="9" t="s">
+      <c r="G276" s="3" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A276" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B276" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C276" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D276" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E276" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F276" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G276" s="9" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" s="3" t="s">
-        <v>638</v>
+        <v>14</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C277" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C277" s="3" t="s">
         <v>653</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>639</v>
+        <v>16</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F277" s="7">
-        <v>20123</v>
+        <v>17</v>
+      </c>
+      <c r="F277" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="G277" s="3" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="B278" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C278" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="E278" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F278" s="7">
+        <v>20123</v>
+      </c>
+      <c r="G278" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A279" s="3" t="s">
         <v>682</v>
       </c>
-      <c r="B278" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C278" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="D278" s="3" t="s">
+      <c r="B279" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C279" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D279" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="E278" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F278" s="7">
+      <c r="E279" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F279" s="7">
         <v>20145</v>
       </c>
-      <c r="G278" s="3" t="s">
+      <c r="G279" s="3" t="s">
         <v>134</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A279" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="B279" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="C279" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D279" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="E279" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="F279" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="G279" s="9" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C280" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E280" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F280" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="G280" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A281" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="B280" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C280" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D280" s="3" t="s">
+      <c r="B281" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C281" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D281" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="E280" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F280" s="7">
+      <c r="E281" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F281" s="7">
         <v>20122</v>
       </c>
-      <c r="G280" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A281" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="B281" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C281" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D281" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="E281" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F281" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G281" s="9" t="s">
+      <c r="G281" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" s="3" t="s">
-        <v>654</v>
+        <v>275</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C282" s="9" t="s">
+      <c r="C282" s="3" t="s">
         <v>653</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>655</v>
+        <v>276</v>
       </c>
       <c r="E282" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F282" s="7">
-        <v>20123</v>
+      <c r="F282" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="G282" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A283" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="B283" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C283" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D283" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="E283" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F283" s="10">
+      <c r="A283" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="B283" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C283" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D283" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="E283" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F283" s="7">
         <v>20123</v>
       </c>
-      <c r="G283" s="9" t="s">
+      <c r="G283" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" s="3" t="s">
-        <v>567</v>
+        <v>476</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C284" s="9" t="s">
+      <c r="C284" s="3" t="s">
         <v>653</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>568</v>
+        <v>477</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>569</v>
+        <v>34</v>
       </c>
       <c r="F284" s="7">
-        <v>20094</v>
+        <v>20123</v>
       </c>
       <c r="G284" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A285" s="9" t="s">
+      <c r="A285" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="B285" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C285" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D285" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="E285" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="F285" s="7">
+        <v>20094</v>
+      </c>
+      <c r="G285" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A286" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="B285" s="9" t="s">
+      <c r="B286" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C285" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D285" s="9" t="s">
+      <c r="C286" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D286" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E285" s="9" t="s">
+      <c r="E286" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F285" s="10" t="s">
+      <c r="F286" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="G285" s="9" t="s">
+      <c r="G286" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A286" s="9" t="s">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A287" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B286" s="9" t="s">
+      <c r="B287" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C286" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D286" s="9" t="s">
+      <c r="C287" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D287" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E286" s="9" t="s">
+      <c r="E287" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F286" s="10" t="s">
+      <c r="F287" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="G286" s="9" t="s">
+      <c r="G287" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A287" s="9" t="s">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A288" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B287" s="9" t="s">
+      <c r="B288" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C287" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D287" s="9" t="s">
+      <c r="C288" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D288" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E287" s="9" t="s">
+      <c r="E288" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="F287" s="10" t="s">
+      <c r="F288" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="G287" s="9" t="s">
+      <c r="G288" s="3" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A288" s="9" t="s">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A289" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="B288" s="9" t="s">
+      <c r="B289" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C288" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D288" s="9" t="s">
+      <c r="C289" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D289" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E288" s="9" t="s">
+      <c r="E289" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F288" s="10" t="s">
+      <c r="F289" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="G288" s="9" t="s">
+      <c r="G289" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A289" s="9" t="s">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A290" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B289" s="9" t="s">
+      <c r="B290" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C289" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D289" s="9" t="s">
+      <c r="C290" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D290" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E289" s="9" t="s">
+      <c r="E290" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F289" s="10" t="s">
+      <c r="F290" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="G289" s="9" t="s">
+      <c r="G290" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A290" s="9" t="s">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A291" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B290" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C290" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D290" s="9" t="s">
+      <c r="B291" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C291" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D291" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E290" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F290" s="10" t="s">
+      <c r="E291" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F291" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G290" s="9" t="s">
+      <c r="G291" s="3" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G218" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState ref="A2:G290">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G291">
       <sortCondition ref="A1:A218"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:G107">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G107">
     <sortCondition ref="A1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9200,23 +9236,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F040406D9EE34E48977C379A242BB45D" ma:contentTypeVersion="15" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="1ab2d492e43f6bec9a26aa4599c840e9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="877b7d34-4df7-40bf-9eb1-208952470e96" xmlns:ns4="05fc27dd-4454-4248-9c78-3d72b2b155c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebc604e5d4aadf5a992ba83f8d4fb519" ns3:_="" ns4:_="">
     <xsd:import namespace="877b7d34-4df7-40bf-9eb1-208952470e96"/>
@@ -9449,32 +9468,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBC6436E-C4E7-4E8D-94E8-64DAEC05792B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9491,4 +9502,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="05fc27dd-4454-4248-9c78-3d72b2b155c8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="877b7d34-4df7-40bf-9eb1-208952470e96"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgtedilizia-my.sharepoint.com/personal/emanuele_anzilotti_alayanrentals_it/Documents/Documenti/GitHub/pv_echarts/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B84DC042-1AB5-4E1E-967B-CC220D01D2F5}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AFEA3ED-8BB8-46FE-B691-B3615B6F3FE3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1877" uniqueCount="695">
   <si>
     <t>Nome account</t>
   </si>
@@ -2090,6 +2090,24 @@
   </si>
   <si>
     <t>CUTRO</t>
+  </si>
+  <si>
+    <t>CONCOM SOLAR ITALIA 02 SRL</t>
+  </si>
+  <si>
+    <t>PG</t>
+  </si>
+  <si>
+    <t>VIA GERARDO DOTTORI 85</t>
+  </si>
+  <si>
+    <t>PERUGIA</t>
+  </si>
+  <si>
+    <t>06132</t>
+  </si>
+  <si>
+    <t>Perugia</t>
   </si>
 </sst>
 </file>
@@ -2515,7 +2533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G291"/>
+  <dimension ref="A1:G292"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -3864,30 +3882,30 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>387</v>
+        <v>689</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C59" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>268</v>
+        <v>691</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F59" s="5">
-        <v>20123</v>
+        <v>692</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>693</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>36</v>
+        <v>694</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>435</v>
+        <v>387</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>32</v>
@@ -3910,7 +3928,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>395</v>
+        <v>435</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>32</v>
@@ -3933,7 +3951,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>267</v>
+        <v>395</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>32</v>
@@ -3947,8 +3965,8 @@
       <c r="E62" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F62" s="5" t="s">
-        <v>59</v>
+      <c r="F62" s="5">
+        <v>20123</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>36</v>
@@ -3956,53 +3974,53 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>685</v>
+        <v>267</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>686</v>
-      </c>
-      <c r="C63" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>687</v>
+        <v>268</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>688</v>
-      </c>
-      <c r="F63" s="5">
-        <v>88842</v>
+        <v>34</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>135</v>
+        <v>685</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C64" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="C64" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>120</v>
+        <v>687</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>56</v>
+        <v>688</v>
+      </c>
+      <c r="F64" s="5">
+        <v>88842</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>407</v>
+        <v>135</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>32</v>
@@ -4016,8 +4034,8 @@
       <c r="E65" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F65" s="5">
-        <v>20121</v>
+      <c r="F65" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>36</v>
@@ -4025,53 +4043,53 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>136</v>
+        <v>407</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>140</v>
+        <v>34</v>
+      </c>
+      <c r="F66" s="5">
+        <v>20121</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>612</v>
+        <v>123</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>15</v>
@@ -4085,8 +4103,8 @@
       <c r="E68" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F68" s="5">
-        <v>90139</v>
+      <c r="F68" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>10</v>
@@ -4094,173 +4112,173 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>442</v>
+        <v>612</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>187</v>
+        <v>124</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F69" s="5">
-        <v>20158</v>
+        <v>90139</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>157</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>223</v>
+        <v>442</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>29</v>
+        <v>34</v>
+      </c>
+      <c r="F70" s="5">
+        <v>20158</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>84</v>
+        <v>224</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>581</v>
+        <v>82</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>262</v>
+        <v>83</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>582</v>
+        <v>84</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="F72" s="5">
-        <v>38123</v>
+        <v>85</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>266</v>
+        <v>42</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>542</v>
+        <v>581</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>7</v>
+        <v>262</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>543</v>
+        <v>582</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>178</v>
+        <v>406</v>
+      </c>
+      <c r="F73" s="5">
+        <v>38123</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>75</v>
+        <v>266</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>485</v>
+        <v>542</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>486</v>
+        <v>7</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>487</v>
+        <v>543</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="F74" s="5">
-        <v>26015</v>
+        <v>8</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>680</v>
+        <v>485</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C75" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>333</v>
+        <v>487</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>216</v>
+        <v>488</v>
+      </c>
+      <c r="F75" s="5">
+        <v>26015</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>9</v>
+        <v>105</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>556</v>
+        <v>680</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -4269,7 +4287,7 @@
       <c r="E76" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F76" s="8" t="s">
+      <c r="F76" s="5" t="s">
         <v>216</v>
       </c>
       <c r="G76" s="4" t="s">
@@ -4278,7 +4296,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>332</v>
+        <v>556</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>7</v>
@@ -4292,7 +4310,7 @@
       <c r="E77" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F77" s="5" t="s">
+      <c r="F77" s="8" t="s">
         <v>216</v>
       </c>
       <c r="G77" s="4" t="s">
@@ -4301,145 +4319,145 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>590</v>
+        <v>332</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>591</v>
+        <v>333</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F78" s="5">
-        <v>20122</v>
+        <v>8</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>298</v>
+        <v>590</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>294</v>
+        <v>32</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>299</v>
+        <v>591</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>300</v>
+        <v>34</v>
       </c>
       <c r="F79" s="5">
-        <v>56025</v>
+        <v>20122</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>297</v>
+        <v>36</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>7</v>
+        <v>294</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>270</v>
+        <v>299</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>271</v>
+        <v>300</v>
+      </c>
+      <c r="F80" s="5">
+        <v>56025</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>9</v>
+        <v>297</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>373</v>
+        <v>269</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>374</v>
+        <v>270</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F81" s="5">
-        <v>20121</v>
+        <v>8</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>278</v>
+        <v>373</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>301</v>
+        <v>374</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>302</v>
+        <v>34</v>
       </c>
       <c r="F82" s="5">
-        <v>24060</v>
+        <v>20121</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>614</v>
+        <v>278</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>187</v>
+        <v>301</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>34</v>
+        <v>302</v>
       </c>
       <c r="F83" s="5">
-        <v>20158</v>
+        <v>24060</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>479</v>
+        <v>614</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>32</v>
@@ -4448,21 +4466,21 @@
         <v>653</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>256</v>
+        <v>187</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F84" s="5">
-        <v>20121</v>
+        <v>20158</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>173</v>
+        <v>479</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>32</v>
@@ -4471,21 +4489,21 @@
         <v>653</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>155</v>
+        <v>256</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F85" s="5" t="s">
-        <v>156</v>
+      <c r="F85" s="5">
+        <v>20121</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>32</v>
@@ -4508,53 +4526,53 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>657</v>
+        <v>154</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>290</v>
+        <v>32</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>658</v>
+        <v>155</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="F87" s="5">
-        <v>60035</v>
+        <v>34</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>156</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>251</v>
+        <v>657</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>32</v>
+        <v>290</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>228</v>
+        <v>658</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>229</v>
+        <v>292</v>
+      </c>
+      <c r="F88" s="5">
+        <v>60035</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>437</v>
+        <v>251</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>32</v>
@@ -4563,151 +4581,151 @@
         <v>653</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>438</v>
+        <v>228</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F89" s="5">
-        <v>20122</v>
+      <c r="F89" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>36</v>
+        <v>134</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>243</v>
+        <v>437</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>244</v>
+        <v>32</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>245</v>
+        <v>438</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>247</v>
+        <v>34</v>
+      </c>
+      <c r="F90" s="5">
+        <v>20122</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>248</v>
+        <v>36</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>81</v>
+        <v>248</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>360</v>
+        <v>249</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>361</v>
+        <v>77</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>362</v>
+        <v>250</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="F92" s="5">
-        <v>76123</v>
+        <v>79</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>423</v>
+        <v>360</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>26</v>
+        <v>361</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>130</v>
+        <v>362</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>28</v>
+        <v>363</v>
       </c>
       <c r="F93" s="5">
-        <v>39100</v>
+        <v>76123</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>549</v>
+        <v>423</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>550</v>
+        <v>26</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>551</v>
+        <v>130</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="F94" s="8" t="s">
-        <v>553</v>
+        <v>28</v>
+      </c>
+      <c r="F94" s="5">
+        <v>39100</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>646</v>
+        <v>549</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>7</v>
+        <v>550</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>647</v>
+        <v>551</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>8</v>
+        <v>552</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>178</v>
+        <v>553</v>
       </c>
       <c r="G95" s="4" t="s">
         <v>75</v>
@@ -4715,99 +4733,99 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>389</v>
+        <v>646</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>390</v>
+        <v>647</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F96" s="5">
-        <v>70043</v>
+        <v>8</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>217</v>
+        <v>389</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>218</v>
+        <v>390</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
+      </c>
+      <c r="F97" s="5">
+        <v>70043</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>48</v>
+        <v>217</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>45</v>
+        <v>218</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>32</v>
@@ -4816,13 +4834,13 @@
         <v>653</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G100" s="4" t="s">
         <v>36</v>
@@ -4830,7 +4848,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>32</v>
@@ -4853,7 +4871,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>32</v>
@@ -4876,53 +4894,53 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>369</v>
+        <v>128</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>370</v>
+        <v>32</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>371</v>
+        <v>120</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="F103" s="5">
-        <v>61121</v>
+        <v>34</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>163</v>
+        <v>36</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>662</v>
+        <v>369</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>32</v>
+        <v>370</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>187</v>
+        <v>371</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>34</v>
+        <v>372</v>
       </c>
       <c r="F104" s="5">
-        <v>20158</v>
+        <v>61121</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>199</v>
+        <v>662</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>32</v>
@@ -4936,8 +4954,8 @@
       <c r="E105" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F105" s="5" t="s">
-        <v>188</v>
+      <c r="F105" s="5">
+        <v>20158</v>
       </c>
       <c r="G105" s="4" t="s">
         <v>157</v>
@@ -4945,53 +4963,53 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>504</v>
+        <v>199</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>507</v>
+        <v>32</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>506</v>
+        <v>187</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="F106" s="5">
-        <v>35010</v>
+        <v>34</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>503</v>
+        <v>157</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>279</v>
+        <v>504</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>32</v>
+        <v>507</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>303</v>
+        <v>506</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>34</v>
+        <v>505</v>
       </c>
       <c r="F107" s="5">
-        <v>20123</v>
+        <v>35010</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>36</v>
+        <v>503</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>563</v>
+        <v>279</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>32</v>
@@ -5000,13 +5018,13 @@
         <v>653</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>562</v>
+        <v>303</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F108" s="5">
-        <v>20122</v>
+        <v>20123</v>
       </c>
       <c r="G108" s="4" t="s">
         <v>36</v>
@@ -5014,25 +5032,25 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>349</v>
+        <v>563</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>350</v>
+        <v>32</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>351</v>
+        <v>562</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="F109" s="5">
-        <v>15033</v>
+        <v>20122</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
@@ -5083,76 +5101,76 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>533</v>
+        <v>349</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>115</v>
+        <v>350</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>534</v>
+        <v>351</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>117</v>
+        <v>352</v>
       </c>
       <c r="F112" s="5">
-        <v>65127</v>
+        <v>15033</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>57</v>
+        <v>533</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>58</v>
+        <v>534</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>59</v>
+        <v>117</v>
+      </c>
+      <c r="F113" s="5">
+        <v>65127</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>334</v>
+        <v>57</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>335</v>
+        <v>58</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F114" s="5">
-        <v>10153</v>
+        <v>34</v>
+      </c>
+      <c r="F114" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>428</v>
+        <v>334</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>77</v>
@@ -5175,76 +5193,76 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>571</v>
+        <v>428</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>572</v>
+        <v>335</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="F116" s="5">
-        <v>20154</v>
+        <v>10153</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>280</v>
+        <v>571</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>304</v>
+        <v>572</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F117" s="5">
-        <v>183</v>
+        <v>20154</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>305</v>
+        <v>157</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>208</v>
+        <v>280</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>209</v>
+        <v>304</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>56</v>
+        <v>8</v>
+      </c>
+      <c r="F118" s="5">
+        <v>183</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>36</v>
+        <v>305</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>547</v>
+        <v>208</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>32</v>
@@ -5253,21 +5271,21 @@
         <v>653</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>548</v>
+        <v>209</v>
       </c>
       <c r="E119" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F119" s="5">
-        <v>20154</v>
+      <c r="F119" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>273</v>
+        <v>547</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>32</v>
@@ -5276,13 +5294,13 @@
         <v>653</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>274</v>
+        <v>548</v>
       </c>
       <c r="E120" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F120" s="5" t="s">
-        <v>156</v>
+      <c r="F120" s="5">
+        <v>20154</v>
       </c>
       <c r="G120" s="4" t="s">
         <v>157</v>
@@ -5290,30 +5308,30 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>126</v>
+        <v>273</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>127</v>
+        <v>274</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>29</v>
+        <v>156</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>240</v>
+        <v>126</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>26</v>
@@ -5336,168 +5354,168 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>412</v>
+        <v>240</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>413</v>
+        <v>127</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>178</v>
+        <v>29</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>272</v>
+        <v>412</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>27</v>
+        <v>413</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>29</v>
+        <v>178</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>144</v>
+        <v>26</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>237</v>
+        <v>27</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>238</v>
+        <v>28</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>239</v>
+        <v>29</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>148</v>
+        <v>30</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>596</v>
+        <v>236</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>597</v>
+        <v>237</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F126" s="5">
-        <v>20122</v>
+        <v>238</v>
+      </c>
+      <c r="F126" s="5" t="s">
+        <v>239</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>36</v>
+        <v>148</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>535</v>
+        <v>596</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>536</v>
+        <v>32</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>537</v>
+        <v>597</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>538</v>
+        <v>34</v>
       </c>
       <c r="F127" s="5">
-        <v>34133</v>
+        <v>20122</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>512</v>
+        <v>36</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>433</v>
+        <v>535</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>26</v>
+        <v>536</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>127</v>
+        <v>537</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>28</v>
+        <v>538</v>
       </c>
       <c r="F128" s="5">
-        <v>39100</v>
+        <v>34133</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>30</v>
+        <v>512</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>649</v>
+        <v>433</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>650</v>
+        <v>127</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F129" s="5">
-        <v>20121</v>
+        <v>39100</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>204</v>
+        <v>649</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>32</v>
@@ -5506,13 +5524,13 @@
         <v>653</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>58</v>
+        <v>650</v>
       </c>
       <c r="E130" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F130" s="5" t="s">
-        <v>59</v>
+      <c r="F130" s="5">
+        <v>20121</v>
       </c>
       <c r="G130" s="4" t="s">
         <v>36</v>
@@ -5520,7 +5538,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>364</v>
+        <v>204</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>32</v>
@@ -5534,8 +5552,8 @@
       <c r="E131" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F131" s="5">
-        <v>20123</v>
+      <c r="F131" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G131" s="4" t="s">
         <v>36</v>
@@ -5543,7 +5561,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>99</v>
+        <v>364</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>32</v>
@@ -5557,8 +5575,8 @@
       <c r="E132" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F132" s="5" t="s">
-        <v>59</v>
+      <c r="F132" s="5">
+        <v>20123</v>
       </c>
       <c r="G132" s="4" t="s">
         <v>36</v>
@@ -5566,237 +5584,237 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>491</v>
+        <v>99</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>492</v>
+        <v>58</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F133" s="8" t="s">
-        <v>271</v>
+        <v>34</v>
+      </c>
+      <c r="F133" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>518</v>
+        <v>492</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F134" s="5">
-        <v>80121</v>
+        <v>8</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>404</v>
+        <v>517</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>262</v>
+        <v>67</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>405</v>
+        <v>518</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>406</v>
+        <v>69</v>
       </c>
       <c r="F135" s="5">
-        <v>38121</v>
+        <v>80121</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>266</v>
+        <v>71</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>367</v>
+        <v>404</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>32</v>
+        <v>262</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>34</v>
+        <v>406</v>
       </c>
       <c r="F136" s="5">
-        <v>20123</v>
+        <v>38121</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>36</v>
+        <v>266</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F137" s="5">
-        <v>90139</v>
+        <v>20123</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>193</v>
+        <v>359</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F138" s="5">
-        <v>20123</v>
+        <v>90139</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>453</v>
+        <v>343</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>454</v>
+        <v>193</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F139" s="8" t="s">
-        <v>178</v>
+        <v>34</v>
+      </c>
+      <c r="F139" s="5">
+        <v>20123</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>281</v>
+        <v>453</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>306</v>
+        <v>7</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>307</v>
+        <v>454</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="F140" s="5">
-        <v>12037</v>
+        <v>8</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>305</v>
+        <v>75</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>11</v>
+        <v>281</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>7</v>
+        <v>306</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>12</v>
+        <v>307</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>13</v>
+        <v>308</v>
+      </c>
+      <c r="F141" s="5">
+        <v>12037</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>9</v>
+        <v>305</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>121</v>
+        <v>11</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>26</v>
@@ -5819,99 +5837,99 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>651</v>
+        <v>72</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>652</v>
+        <v>73</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F145" s="5">
-        <v>20124</v>
+        <v>8</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>676</v>
+        <v>651</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>350</v>
+        <v>32</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>677</v>
+        <v>652</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>678</v>
+        <v>34</v>
       </c>
       <c r="F146" s="5">
-        <v>15079</v>
+        <v>20124</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>679</v>
+        <v>157</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>25</v>
+        <v>676</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>26</v>
+        <v>350</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>27</v>
+        <v>677</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>29</v>
+        <v>678</v>
+      </c>
+      <c r="F147" s="5">
+        <v>15079</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>30</v>
+        <v>679</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>496</v>
+        <v>25</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>26</v>
@@ -5925,8 +5943,8 @@
       <c r="E148" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F148" s="5">
-        <v>39100</v>
+      <c r="F148" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G148" s="4" t="s">
         <v>30</v>
@@ -5934,12 +5952,12 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>684</v>
+        <v>496</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C149" s="4" t="s">
+      <c r="C149" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D149" s="4" t="s">
@@ -5957,53 +5975,53 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>231</v>
+        <v>684</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C150" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C150" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>232</v>
+        <v>27</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F150" s="5" t="s">
-        <v>216</v>
+        <v>28</v>
+      </c>
+      <c r="F150" s="5">
+        <v>39100</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>588</v>
+        <v>231</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>589</v>
+        <v>232</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F151" s="5">
-        <v>20122</v>
+        <v>8</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>186</v>
+        <v>588</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>32</v>
@@ -6012,44 +6030,44 @@
         <v>653</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>187</v>
+        <v>589</v>
       </c>
       <c r="E152" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F152" s="5" t="s">
-        <v>188</v>
+      <c r="F152" s="5">
+        <v>20122</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>481</v>
+        <v>186</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>482</v>
+        <v>32</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>483</v>
+        <v>187</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="F153" s="5">
-        <v>66020</v>
+        <v>34</v>
+      </c>
+      <c r="F153" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>75</v>
+        <v>157</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>619</v>
+        <v>481</v>
       </c>
       <c r="B154" s="4" t="s">
         <v>482</v>
@@ -6072,168 +6090,168 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>574</v>
+        <v>619</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>32</v>
+        <v>482</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>575</v>
+        <v>483</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>34</v>
+        <v>484</v>
       </c>
       <c r="F155" s="5">
-        <v>20124</v>
+        <v>66020</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>409</v>
+        <v>574</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>339</v>
+        <v>32</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>410</v>
+        <v>575</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="F156" s="5">
-        <v>37137</v>
+        <v>20124</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>341</v>
+        <v>157</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>458</v>
+        <v>409</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>7</v>
+        <v>339</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>459</v>
+        <v>410</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F157" s="8" t="s">
-        <v>216</v>
+        <v>411</v>
+      </c>
+      <c r="F157" s="5">
+        <v>37137</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>9</v>
+        <v>341</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>293</v>
+        <v>458</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>294</v>
+        <v>7</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>295</v>
+        <v>459</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="F158" s="5">
-        <v>56010</v>
+        <v>8</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>216</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>297</v>
+        <v>9</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>601</v>
+        <v>293</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>32</v>
+        <v>294</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>602</v>
+        <v>295</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="F159" s="5">
-        <v>20145</v>
+        <v>56010</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>134</v>
+        <v>297</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>309</v>
+        <v>601</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>310</v>
+        <v>602</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>311</v>
+        <v>34</v>
       </c>
       <c r="F160" s="5">
-        <v>40060</v>
+        <v>20145</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>382</v>
+        <v>309</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>383</v>
+        <v>310</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>34</v>
+        <v>311</v>
       </c>
       <c r="F161" s="5">
-        <v>20121</v>
+        <v>40060</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>32</v>
@@ -6247,8 +6265,8 @@
       <c r="E162" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F162" s="5" t="s">
-        <v>56</v>
+      <c r="F162" s="5">
+        <v>20121</v>
       </c>
       <c r="G162" s="4" t="s">
         <v>36</v>
@@ -6256,53 +6274,53 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>211</v>
+        <v>384</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>177</v>
+        <v>383</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>178</v>
+        <v>56</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>573</v>
+        <v>211</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F164" s="5">
-        <v>20124</v>
+        <v>8</v>
+      </c>
+      <c r="F164" s="5" t="s">
+        <v>178</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>32</v>
@@ -6325,99 +6343,99 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>629</v>
+        <v>587</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>630</v>
+        <v>190</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>631</v>
+        <v>34</v>
       </c>
       <c r="F166" s="5">
-        <v>39025</v>
+        <v>20124</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>66</v>
+        <v>629</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>68</v>
+        <v>630</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>70</v>
+        <v>631</v>
+      </c>
+      <c r="F167" s="5">
+        <v>39025</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>282</v>
+        <v>66</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>312</v>
+        <v>67</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>313</v>
+        <v>68</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="F168" s="5">
-        <v>57021</v>
+        <v>69</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>297</v>
+        <v>71</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>182</v>
+        <v>282</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>7</v>
+        <v>312</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>177</v>
+        <v>313</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>178</v>
+        <v>314</v>
+      </c>
+      <c r="F169" s="5">
+        <v>57021</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>75</v>
+        <v>297</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>460</v>
+        <v>182</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>7</v>
@@ -6431,7 +6449,7 @@
       <c r="E170" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F170" s="8" t="s">
+      <c r="F170" s="5" t="s">
         <v>178</v>
       </c>
       <c r="G170" s="4" t="s">
@@ -6440,145 +6458,145 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>87</v>
+        <v>460</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>89</v>
+        <v>177</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F171" s="5" t="s">
-        <v>91</v>
+        <v>8</v>
+      </c>
+      <c r="F171" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>344</v>
+        <v>87</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>345</v>
+        <v>89</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="F172" s="5">
-        <v>70124</v>
+        <v>90</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>187</v>
+        <v>345</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>34</v>
+        <v>346</v>
       </c>
       <c r="F173" s="5">
-        <v>20158</v>
+        <v>70124</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>157</v>
+        <v>42</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>644</v>
+        <v>331</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>645</v>
+        <v>187</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F174" s="5">
-        <v>39100</v>
+        <v>20158</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>355</v>
+        <v>644</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>306</v>
+        <v>26</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>356</v>
+        <v>645</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>357</v>
+        <v>28</v>
       </c>
       <c r="F175" s="5">
-        <v>12084</v>
+        <v>39100</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>305</v>
+        <v>30</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>192</v>
+        <v>355</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>32</v>
+        <v>306</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>193</v>
+        <v>356</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>59</v>
+        <v>357</v>
+      </c>
+      <c r="F176" s="5">
+        <v>12084</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>36</v>
+        <v>305</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>32</v>
@@ -6587,13 +6605,13 @@
         <v>653</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
       <c r="E177" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="G177" s="4" t="s">
         <v>36</v>
@@ -6601,99 +6619,99 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>455</v>
+        <v>225</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>456</v>
+        <v>226</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F178" s="8" t="s">
-        <v>457</v>
+        <v>34</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>106</v>
+        <v>455</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>107</v>
+        <v>7</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>108</v>
+        <v>456</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F179" s="5" t="s">
-        <v>110</v>
+        <v>8</v>
+      </c>
+      <c r="F179" s="8" t="s">
+        <v>457</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>429</v>
+        <v>106</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>306</v>
+        <v>107</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>430</v>
+        <v>108</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="F180" s="5">
-        <v>12100</v>
+        <v>109</v>
+      </c>
+      <c r="F180" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>305</v>
+        <v>111</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>393</v>
+        <v>429</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>20</v>
+        <v>306</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>21</v>
+        <v>430</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>22</v>
+        <v>431</v>
       </c>
       <c r="F181" s="5">
-        <v>40127</v>
+        <v>12100</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>24</v>
+        <v>305</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>609</v>
+        <v>393</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>20</v>
@@ -6702,13 +6720,13 @@
         <v>653</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>610</v>
+        <v>21</v>
       </c>
       <c r="E182" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F182" s="5">
-        <v>40122</v>
+        <v>40127</v>
       </c>
       <c r="G182" s="4" t="s">
         <v>24</v>
@@ -6716,30 +6734,30 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>353</v>
+        <v>609</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>354</v>
+        <v>610</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F183" s="5">
-        <v>20121</v>
+        <v>40122</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>656</v>
+        <v>353</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>32</v>
@@ -6762,7 +6780,7 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>554</v>
+        <v>656</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>32</v>
@@ -6771,21 +6789,21 @@
         <v>653</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>523</v>
+        <v>354</v>
       </c>
       <c r="E185" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F185" s="5">
-        <v>20154</v>
+        <v>20121</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>32</v>
@@ -6808,7 +6826,7 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>32</v>
@@ -6831,7 +6849,7 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>594</v>
+        <v>522</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>32</v>
@@ -6840,7 +6858,7 @@
         <v>653</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>595</v>
+        <v>523</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>34</v>
@@ -6854,30 +6872,30 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="10" t="s">
-        <v>513</v>
+        <v>594</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D189" s="10" t="s">
-        <v>27</v>
+        <v>595</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F189" s="11">
-        <v>39100</v>
+        <v>20154</v>
       </c>
       <c r="G189" s="10" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="3" t="s">
-        <v>230</v>
+        <v>513</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>26</v>
@@ -6891,8 +6909,8 @@
       <c r="E190" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F190" s="7" t="s">
-        <v>29</v>
+      <c r="F190" s="7">
+        <v>39100</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>30</v>
@@ -6900,30 +6918,30 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="3" t="s">
-        <v>141</v>
+        <v>230</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>142</v>
+        <v>27</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F191" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="3" t="s">
-        <v>664</v>
+        <v>141</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>32</v>
@@ -6932,13 +6950,13 @@
         <v>653</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>665</v>
+        <v>142</v>
       </c>
       <c r="E192" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F192" s="7">
-        <v>20123</v>
+      <c r="F192" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>36</v>
@@ -6946,7 +6964,7 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="3" t="s">
-        <v>54</v>
+        <v>664</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>32</v>
@@ -6955,13 +6973,13 @@
         <v>653</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>55</v>
+        <v>665</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F193" s="7" t="s">
-        <v>56</v>
+      <c r="F193" s="7">
+        <v>20123</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>36</v>
@@ -6969,7 +6987,7 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="3" t="s">
-        <v>439</v>
+        <v>54</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>32</v>
@@ -6978,159 +6996,159 @@
         <v>653</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>440</v>
+        <v>55</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="F194" s="7">
-        <v>20038</v>
+        <v>34</v>
+      </c>
+      <c r="F194" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>134</v>
+        <v>36</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="3" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>234</v>
+        <v>440</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>79</v>
+        <v>441</v>
       </c>
       <c r="F195" s="7">
-        <v>10121</v>
+        <v>20038</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>81</v>
+        <v>134</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="3" t="s">
-        <v>681</v>
+        <v>424</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C196" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C196" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>322</v>
+        <v>234</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="F196" s="7">
-        <v>20124</v>
+        <v>10121</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="3" t="s">
-        <v>93</v>
+        <v>681</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C197" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C197" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>95</v>
+        <v>322</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F197" s="7" t="s">
-        <v>97</v>
+        <v>34</v>
+      </c>
+      <c r="F197" s="7">
+        <v>20124</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>98</v>
+        <v>157</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="3" t="s">
-        <v>375</v>
+        <v>93</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>376</v>
+        <v>94</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>377</v>
+        <v>95</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="F198" s="7">
-        <v>64020</v>
+        <v>96</v>
+      </c>
+      <c r="F198" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="3" t="s">
-        <v>578</v>
+        <v>375</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>7</v>
+        <v>376</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>579</v>
+        <v>377</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F199" s="9" t="s">
-        <v>580</v>
+        <v>378</v>
+      </c>
+      <c r="F199" s="7">
+        <v>64020</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="3" t="s">
-        <v>408</v>
+        <v>578</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>209</v>
+        <v>579</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F200" s="7">
-        <v>20121</v>
+        <v>8</v>
+      </c>
+      <c r="F200" s="9" t="s">
+        <v>580</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="3" t="s">
-        <v>131</v>
+        <v>408</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>32</v>
@@ -7139,113 +7157,113 @@
         <v>653</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>132</v>
+        <v>209</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F201" s="7" t="s">
-        <v>133</v>
+      <c r="F201" s="7">
+        <v>20121</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>134</v>
+        <v>36</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="3" t="s">
-        <v>603</v>
+        <v>131</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>604</v>
+        <v>132</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F202" s="9" t="s">
-        <v>605</v>
+        <v>34</v>
+      </c>
+      <c r="F202" s="7" t="s">
+        <v>133</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="3" t="s">
-        <v>255</v>
+        <v>603</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>256</v>
+        <v>604</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F203" s="7" t="s">
-        <v>56</v>
+        <v>8</v>
+      </c>
+      <c r="F203" s="9" t="s">
+        <v>605</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="3" t="s">
-        <v>338</v>
+        <v>255</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>339</v>
+        <v>32</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>340</v>
+        <v>256</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="F204" s="7">
-        <v>37045</v>
+        <v>34</v>
+      </c>
+      <c r="F204" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>341</v>
+        <v>36</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="3" t="s">
-        <v>164</v>
+        <v>338</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>32</v>
+        <v>339</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>165</v>
+        <v>340</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F205" s="7" t="s">
-        <v>166</v>
+        <v>526</v>
+      </c>
+      <c r="F205" s="7">
+        <v>37045</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>157</v>
+        <v>341</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="3" t="s">
-        <v>527</v>
+        <v>164</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>32</v>
@@ -7259,8 +7277,8 @@
       <c r="E206" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F206" s="7">
-        <v>20126</v>
+      <c r="F206" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="G206" s="3" t="s">
         <v>157</v>
@@ -7268,7 +7286,7 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="3" t="s">
-        <v>599</v>
+        <v>527</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>32</v>
@@ -7277,21 +7295,21 @@
         <v>653</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>600</v>
+        <v>165</v>
       </c>
       <c r="E207" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F207" s="7">
-        <v>20138</v>
+        <v>20126</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>260</v>
+        <v>157</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="3" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>32</v>
@@ -7300,21 +7318,21 @@
         <v>653</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="E208" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F208" s="7">
-        <v>20122</v>
+        <v>20138</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>36</v>
+        <v>260</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="3" t="s">
-        <v>592</v>
+        <v>607</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>32</v>
@@ -7323,13 +7341,13 @@
         <v>653</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>392</v>
+        <v>608</v>
       </c>
       <c r="E209" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F209" s="7">
-        <v>20123</v>
+        <v>20122</v>
       </c>
       <c r="G209" s="3" t="s">
         <v>36</v>
@@ -7337,7 +7355,7 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="3" t="s">
-        <v>469</v>
+        <v>592</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>32</v>
@@ -7346,21 +7364,21 @@
         <v>653</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>258</v>
+        <v>392</v>
       </c>
       <c r="E210" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F210" s="7">
-        <v>20135</v>
+        <v>20123</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>260</v>
+        <v>36</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="3" t="s">
-        <v>620</v>
+        <v>469</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>32</v>
@@ -7383,7 +7401,7 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="3" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>32</v>
@@ -7406,7 +7424,7 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="3" t="s">
-        <v>403</v>
+        <v>632</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>32</v>
@@ -7429,30 +7447,30 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="3" t="s">
-        <v>642</v>
+        <v>403</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>183</v>
+        <v>32</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>643</v>
+        <v>258</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>184</v>
+        <v>34</v>
       </c>
       <c r="F214" s="7">
-        <v>85100</v>
+        <v>20135</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>317</v>
+        <v>260</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="3" t="s">
-        <v>202</v>
+        <v>642</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>183</v>
@@ -7461,13 +7479,13 @@
         <v>653</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>203</v>
+        <v>643</v>
       </c>
       <c r="E215" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="F215" s="7" t="s">
-        <v>185</v>
+      <c r="F215" s="7">
+        <v>85100</v>
       </c>
       <c r="G215" s="3" t="s">
         <v>317</v>
@@ -7475,30 +7493,30 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="3" t="s">
-        <v>451</v>
+        <v>202</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>32</v>
+        <v>183</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>452</v>
+        <v>203</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F216" s="7">
-        <v>20144</v>
+        <v>184</v>
+      </c>
+      <c r="F216" s="7" t="s">
+        <v>185</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>36</v>
+        <v>317</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="3" t="s">
-        <v>221</v>
+        <v>451</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>32</v>
@@ -7507,90 +7525,90 @@
         <v>653</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>222</v>
+        <v>452</v>
       </c>
       <c r="E217" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F217" s="7" t="s">
-        <v>133</v>
+      <c r="F217" s="7">
+        <v>20144</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>134</v>
+        <v>36</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="3" t="s">
-        <v>283</v>
+        <v>221</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>315</v>
+        <v>222</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="F218" s="7">
-        <v>40026</v>
+        <v>34</v>
+      </c>
+      <c r="F218" s="7" t="s">
+        <v>133</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="3" t="s">
-        <v>635</v>
+        <v>283</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>636</v>
+        <v>315</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>637</v>
+        <v>316</v>
       </c>
       <c r="F219" s="7">
-        <v>20068</v>
+        <v>40026</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>260</v>
+        <v>24</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="3" t="s">
-        <v>284</v>
+        <v>635</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>318</v>
+        <v>636</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F220" s="7" t="s">
-        <v>321</v>
+        <v>637</v>
+      </c>
+      <c r="F220" s="7">
+        <v>20068</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>9</v>
+        <v>260</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="3" t="s">
-        <v>659</v>
+        <v>284</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>7</v>
@@ -7599,13 +7617,13 @@
         <v>653</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>660</v>
+        <v>318</v>
       </c>
       <c r="E221" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F221" s="9" t="s">
-        <v>661</v>
+      <c r="F221" s="7" t="s">
+        <v>321</v>
       </c>
       <c r="G221" s="3" t="s">
         <v>9</v>
@@ -7613,237 +7631,237 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="3" t="s">
-        <v>531</v>
+        <v>659</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>27</v>
+        <v>660</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F222" s="7">
-        <v>39100</v>
+        <v>8</v>
+      </c>
+      <c r="F222" s="9" t="s">
+        <v>661</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="3" t="s">
-        <v>365</v>
+        <v>531</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>366</v>
+        <v>27</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F223" s="7">
-        <v>20123</v>
+        <v>39100</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="3" t="s">
-        <v>285</v>
+        <v>365</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>306</v>
+        <v>32</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>319</v>
+        <v>366</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>320</v>
+        <v>34</v>
       </c>
       <c r="F224" s="7">
-        <v>12020</v>
+        <v>20123</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>305</v>
+        <v>36</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="3" t="s">
-        <v>37</v>
+        <v>285</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>38</v>
+        <v>306</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>39</v>
+        <v>319</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F225" s="7" t="s">
-        <v>41</v>
+        <v>320</v>
+      </c>
+      <c r="F225" s="7">
+        <v>12020</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>42</v>
+        <v>305</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="3" t="s">
-        <v>419</v>
+        <v>37</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>420</v>
+        <v>38</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>421</v>
+        <v>39</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="F226" s="7">
-        <v>28053</v>
+        <v>40</v>
+      </c>
+      <c r="F226" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>134</v>
+        <v>42</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="3" t="s">
-        <v>170</v>
+        <v>419</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>32</v>
+        <v>420</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>167</v>
+        <v>421</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F227" s="7" t="s">
-        <v>169</v>
+        <v>422</v>
+      </c>
+      <c r="F227" s="7">
+        <v>28053</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="3" t="s">
-        <v>558</v>
+        <v>170</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>559</v>
+        <v>167</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F228" s="7">
-        <v>39100</v>
+        <v>168</v>
+      </c>
+      <c r="F228" s="7" t="s">
+        <v>169</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="3" t="s">
-        <v>196</v>
+        <v>558</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>197</v>
+        <v>559</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F229" s="7" t="s">
-        <v>198</v>
+        <v>28</v>
+      </c>
+      <c r="F229" s="7">
+        <v>39100</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="3" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="F230" s="7" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="3" t="s">
-        <v>242</v>
+        <v>205</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="F231" s="7" t="s">
-        <v>56</v>
+        <v>207</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="3" t="s">
-        <v>532</v>
+        <v>242</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>32</v>
@@ -7857,8 +7875,8 @@
       <c r="E232" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F232" s="7">
-        <v>20121</v>
+      <c r="F232" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="G232" s="3" t="s">
         <v>36</v>
@@ -7866,7 +7884,7 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="3" t="s">
-        <v>576</v>
+        <v>532</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>32</v>
@@ -7875,7 +7893,7 @@
         <v>653</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>577</v>
+        <v>175</v>
       </c>
       <c r="E233" s="3" t="s">
         <v>34</v>
@@ -7889,99 +7907,99 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="3" t="s">
-        <v>443</v>
+        <v>576</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>444</v>
+        <v>32</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>445</v>
+        <v>577</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="F234" s="7">
-        <v>53048</v>
+        <v>20121</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>447</v>
+        <v>36</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="3" t="s">
-        <v>514</v>
+        <v>443</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>507</v>
+        <v>444</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>516</v>
+        <v>446</v>
       </c>
       <c r="F235" s="7">
-        <v>35011</v>
+        <v>53048</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>503</v>
+        <v>447</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" s="3" t="s">
-        <v>241</v>
+        <v>514</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>32</v>
+        <v>507</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>175</v>
+        <v>515</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F236" s="7" t="s">
-        <v>56</v>
+        <v>516</v>
+      </c>
+      <c r="F236" s="7">
+        <v>35011</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>36</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="3" t="s">
-        <v>129</v>
+        <v>241</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F237" s="7" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="3" t="s">
-        <v>641</v>
+        <v>129</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>26</v>
@@ -7995,8 +8013,8 @@
       <c r="E238" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F238" s="7">
-        <v>39100</v>
+      <c r="F238" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="G238" s="3" t="s">
         <v>30</v>
@@ -8004,30 +8022,30 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" s="3" t="s">
-        <v>611</v>
+        <v>641</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>530</v>
+        <v>130</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F239" s="7">
-        <v>20121</v>
+        <v>39100</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="3" t="s">
-        <v>529</v>
+        <v>611</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>32</v>
@@ -8050,145 +8068,145 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" s="3" t="s">
-        <v>19</v>
+        <v>529</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>21</v>
+        <v>530</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F241" s="7" t="s">
-        <v>23</v>
+        <v>34</v>
+      </c>
+      <c r="F241" s="7">
+        <v>20121</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" s="3" t="s">
-        <v>564</v>
+        <v>19</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>565</v>
+        <v>21</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F242" s="9" t="s">
-        <v>566</v>
+        <v>22</v>
+      </c>
+      <c r="F242" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" s="3" t="s">
-        <v>379</v>
+        <v>564</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>380</v>
+        <v>565</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="F243" s="7">
-        <v>20089</v>
+        <v>8</v>
+      </c>
+      <c r="F243" s="9" t="s">
+        <v>566</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" s="3" t="s">
-        <v>473</v>
+        <v>379</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>474</v>
+        <v>380</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F244" s="9" t="s">
-        <v>475</v>
+        <v>381</v>
+      </c>
+      <c r="F244" s="7">
+        <v>20089</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" s="3" t="s">
-        <v>210</v>
+        <v>473</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>200</v>
+        <v>474</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F245" s="7" t="s">
-        <v>201</v>
+        <v>8</v>
+      </c>
+      <c r="F245" s="9" t="s">
+        <v>475</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F246" s="7" t="s">
-        <v>156</v>
+        <v>201</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>157</v>
+        <v>24</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" s="3" t="s">
-        <v>663</v>
+        <v>212</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>32</v>
@@ -8202,8 +8220,8 @@
       <c r="E247" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F247" s="7">
-        <v>20124</v>
+      <c r="F247" s="7" t="s">
+        <v>156</v>
       </c>
       <c r="G247" s="3" t="s">
         <v>157</v>
@@ -8211,7 +8229,7 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" s="3" t="s">
-        <v>436</v>
+        <v>663</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>32</v>
@@ -8234,53 +8252,53 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" s="3" t="s">
-        <v>633</v>
+        <v>436</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>634</v>
+        <v>213</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="F249" s="7">
-        <v>24050</v>
+        <v>20124</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" s="3" t="s">
-        <v>227</v>
+        <v>633</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>228</v>
+        <v>634</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F250" s="7" t="s">
-        <v>229</v>
+        <v>146</v>
+      </c>
+      <c r="F250" s="7">
+        <v>24050</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" s="3" t="s">
-        <v>621</v>
+        <v>227</v>
       </c>
       <c r="B251" s="3" t="s">
         <v>32</v>
@@ -8294,8 +8312,8 @@
       <c r="E251" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F251" s="7">
-        <v>20148</v>
+      <c r="F251" s="7" t="s">
+        <v>229</v>
       </c>
       <c r="G251" s="3" t="s">
         <v>134</v>
@@ -8303,12 +8321,12 @@
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" s="3" t="s">
-        <v>254</v>
+        <v>621</v>
       </c>
       <c r="B252" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C252" s="4" t="s">
+      <c r="C252" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D252" s="3" t="s">
@@ -8317,8 +8335,8 @@
       <c r="E252" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F252" s="7" t="s">
-        <v>229</v>
+      <c r="F252" s="7">
+        <v>20148</v>
       </c>
       <c r="G252" s="3" t="s">
         <v>134</v>
@@ -8326,76 +8344,76 @@
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" s="3" t="s">
-        <v>666</v>
+        <v>254</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>101</v>
+        <v>32</v>
       </c>
       <c r="C253" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>667</v>
+        <v>228</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="F253" s="7">
-        <v>25055</v>
+        <v>34</v>
+      </c>
+      <c r="F253" s="7" t="s">
+        <v>229</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" s="3" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>673</v>
+        <v>101</v>
       </c>
       <c r="C254" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="F254" s="7">
-        <v>50132</v>
+        <v>25055</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>447</v>
+        <v>105</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" s="3" t="s">
-        <v>470</v>
+        <v>672</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>32</v>
+        <v>673</v>
       </c>
       <c r="C255" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>462</v>
+        <v>674</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>34</v>
+        <v>675</v>
       </c>
       <c r="F255" s="7">
-        <v>20129</v>
+        <v>50132</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>260</v>
+        <v>447</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" s="3" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="B256" s="3" t="s">
         <v>32</v>
@@ -8418,7 +8436,7 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" s="3" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="B257" s="3" t="s">
         <v>32</v>
@@ -8441,7 +8459,7 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B258" s="3" t="s">
         <v>32</v>
@@ -8464,7 +8482,7 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" s="3" t="s">
-        <v>174</v>
+        <v>472</v>
       </c>
       <c r="B259" s="3" t="s">
         <v>32</v>
@@ -8473,205 +8491,205 @@
         <v>653</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>175</v>
+        <v>462</v>
       </c>
       <c r="E259" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F259" s="7" t="s">
-        <v>56</v>
+      <c r="F259" s="7">
+        <v>20129</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>36</v>
+        <v>260</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" s="3" t="s">
-        <v>329</v>
+        <v>174</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C260" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>330</v>
+        <v>175</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="F260" s="7">
-        <v>40026</v>
+        <v>34</v>
+      </c>
+      <c r="F260" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" s="3" t="s">
-        <v>286</v>
+        <v>329</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C261" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>34</v>
+        <v>316</v>
       </c>
       <c r="F261" s="7">
-        <v>20124</v>
+        <v>40026</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" s="3" t="s">
-        <v>448</v>
+        <v>286</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>306</v>
+        <v>32</v>
       </c>
       <c r="C262" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>449</v>
+        <v>322</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>450</v>
+        <v>34</v>
       </c>
       <c r="F262" s="7">
-        <v>12011</v>
+        <v>20124</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>305</v>
+        <v>36</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" s="3" t="s">
-        <v>623</v>
+        <v>448</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>32</v>
+        <v>306</v>
       </c>
       <c r="C263" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>624</v>
+        <v>449</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>34</v>
+        <v>450</v>
       </c>
       <c r="F263" s="7">
-        <v>20121</v>
+        <v>12011</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>36</v>
+        <v>305</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" s="3" t="s">
-        <v>149</v>
+        <v>623</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>150</v>
+        <v>32</v>
       </c>
       <c r="C264" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>151</v>
+        <v>624</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="F264" s="7" t="s">
-        <v>153</v>
+        <v>34</v>
+      </c>
+      <c r="F264" s="7">
+        <v>20121</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" s="3" t="s">
-        <v>417</v>
+        <v>149</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="C265" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>418</v>
+        <v>151</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F265" s="7">
-        <v>20123</v>
+        <v>152</v>
+      </c>
+      <c r="F265" s="7" t="s">
+        <v>153</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" s="3" t="s">
-        <v>489</v>
+        <v>417</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C266" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>490</v>
+        <v>418</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F266" s="7">
-        <v>90141</v>
+        <v>20123</v>
       </c>
       <c r="G266" s="3" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" s="3" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C267" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>386</v>
+        <v>490</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F267" s="9" t="s">
-        <v>388</v>
+        <v>17</v>
+      </c>
+      <c r="F267" s="7">
+        <v>90141</v>
       </c>
       <c r="G267" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" s="3" t="s">
-        <v>640</v>
+        <v>478</v>
       </c>
       <c r="B268" s="3" t="s">
         <v>7</v>
@@ -8694,7 +8712,7 @@
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" s="3" t="s">
-        <v>528</v>
+        <v>640</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>7</v>
@@ -8717,7 +8735,7 @@
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" s="3" t="s">
-        <v>385</v>
+        <v>528</v>
       </c>
       <c r="B270" s="3" t="s">
         <v>7</v>
@@ -8731,7 +8749,7 @@
       <c r="E270" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F270" s="7" t="s">
+      <c r="F270" s="9" t="s">
         <v>388</v>
       </c>
       <c r="G270" s="3" t="s">
@@ -8740,99 +8758,99 @@
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" s="3" t="s">
-        <v>463</v>
+        <v>385</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>262</v>
+        <v>7</v>
       </c>
       <c r="C271" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>464</v>
+        <v>386</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="F271" s="7">
-        <v>38055</v>
+        <v>8</v>
+      </c>
+      <c r="F271" s="7" t="s">
+        <v>388</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>266</v>
+        <v>9</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" s="3" t="s">
-        <v>570</v>
+        <v>463</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>32</v>
+        <v>262</v>
       </c>
       <c r="C272" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>132</v>
+        <v>464</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>34</v>
+        <v>465</v>
       </c>
       <c r="F272" s="7">
-        <v>20145</v>
+        <v>38055</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>134</v>
+        <v>266</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" s="3" t="s">
-        <v>425</v>
+        <v>570</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>101</v>
+        <v>32</v>
       </c>
       <c r="C273" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>426</v>
+        <v>132</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>427</v>
+        <v>34</v>
       </c>
       <c r="F273" s="7">
-        <v>25010</v>
+        <v>20145</v>
       </c>
       <c r="G273" s="3" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" s="3" t="s">
-        <v>391</v>
+        <v>425</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="C274" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>34</v>
+        <v>427</v>
       </c>
       <c r="F274" s="7">
-        <v>20123</v>
+        <v>25010</v>
       </c>
       <c r="G274" s="3" t="s">
-        <v>36</v>
+        <v>105</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" s="3" t="s">
-        <v>618</v>
+        <v>391</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>32</v>
@@ -8855,76 +8873,76 @@
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" s="3" t="s">
-        <v>414</v>
+        <v>618</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="C276" s="3" t="s">
         <v>653</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>415</v>
+        <v>392</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>416</v>
+        <v>34</v>
       </c>
       <c r="F276" s="7">
-        <v>71016</v>
+        <v>20123</v>
       </c>
       <c r="G276" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" s="3" t="s">
-        <v>14</v>
+        <v>414</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="C277" s="3" t="s">
         <v>653</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>16</v>
+        <v>415</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F277" s="7" t="s">
-        <v>18</v>
+        <v>416</v>
+      </c>
+      <c r="F277" s="7">
+        <v>71016</v>
       </c>
       <c r="G277" s="3" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" s="3" t="s">
-        <v>638</v>
+        <v>14</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C278" s="3" t="s">
         <v>653</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>639</v>
+        <v>16</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F278" s="7">
-        <v>20123</v>
+        <v>17</v>
+      </c>
+      <c r="F278" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="G278" s="3" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" s="3" t="s">
-        <v>682</v>
+        <v>638</v>
       </c>
       <c r="B279" s="3" t="s">
         <v>32</v>
@@ -8933,67 +8951,67 @@
         <v>653</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>222</v>
+        <v>639</v>
       </c>
       <c r="E279" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F279" s="7">
-        <v>20145</v>
+        <v>20123</v>
       </c>
       <c r="G279" s="3" t="s">
-        <v>134</v>
+        <v>36</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" s="3" t="s">
-        <v>323</v>
+        <v>682</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>324</v>
+        <v>32</v>
       </c>
       <c r="C280" s="3" t="s">
         <v>653</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>325</v>
+        <v>222</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="F280" s="7" t="s">
-        <v>327</v>
+        <v>34</v>
+      </c>
+      <c r="F280" s="7">
+        <v>20145</v>
       </c>
       <c r="G280" s="3" t="s">
-        <v>328</v>
+        <v>134</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" s="3" t="s">
-        <v>560</v>
+        <v>323</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>32</v>
+        <v>324</v>
       </c>
       <c r="C281" s="3" t="s">
         <v>653</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>561</v>
+        <v>325</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F281" s="7">
-        <v>20122</v>
+        <v>326</v>
+      </c>
+      <c r="F281" s="7" t="s">
+        <v>327</v>
       </c>
       <c r="G281" s="3" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" s="3" t="s">
-        <v>275</v>
+        <v>560</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>32</v>
@@ -9002,13 +9020,13 @@
         <v>653</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>276</v>
+        <v>561</v>
       </c>
       <c r="E282" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F282" s="7" t="s">
-        <v>35</v>
+      <c r="F282" s="7">
+        <v>20122</v>
       </c>
       <c r="G282" s="3" t="s">
         <v>36</v>
@@ -9016,7 +9034,7 @@
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" s="3" t="s">
-        <v>654</v>
+        <v>275</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>32</v>
@@ -9025,13 +9043,13 @@
         <v>653</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>655</v>
+        <v>276</v>
       </c>
       <c r="E283" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F283" s="7">
-        <v>20123</v>
+      <c r="F283" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="G283" s="3" t="s">
         <v>36</v>
@@ -9039,7 +9057,7 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" s="3" t="s">
-        <v>476</v>
+        <v>654</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>32</v>
@@ -9048,7 +9066,7 @@
         <v>653</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>477</v>
+        <v>655</v>
       </c>
       <c r="E284" s="3" t="s">
         <v>34</v>
@@ -9062,7 +9080,7 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" s="3" t="s">
-        <v>567</v>
+        <v>476</v>
       </c>
       <c r="B285" s="3" t="s">
         <v>32</v>
@@ -9071,13 +9089,13 @@
         <v>653</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>568</v>
+        <v>477</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>569</v>
+        <v>34</v>
       </c>
       <c r="F285" s="7">
-        <v>20094</v>
+        <v>20123</v>
       </c>
       <c r="G285" s="3" t="s">
         <v>36</v>
@@ -9085,30 +9103,30 @@
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286" s="3" t="s">
-        <v>394</v>
+        <v>567</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C286" s="3" t="s">
         <v>653</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>215</v>
+        <v>568</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F286" s="7" t="s">
-        <v>216</v>
+        <v>569</v>
+      </c>
+      <c r="F286" s="7">
+        <v>20094</v>
       </c>
       <c r="G286" s="3" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287" s="3" t="s">
-        <v>214</v>
+        <v>394</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>7</v>
@@ -9131,53 +9149,53 @@
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288" s="3" t="s">
-        <v>158</v>
+        <v>214</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>159</v>
+        <v>7</v>
       </c>
       <c r="C288" s="3" t="s">
         <v>653</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>160</v>
+        <v>215</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>161</v>
+        <v>8</v>
       </c>
       <c r="F288" s="7" t="s">
-        <v>162</v>
+        <v>216</v>
       </c>
       <c r="G288" s="3" t="s">
-        <v>163</v>
+        <v>9</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" s="3" t="s">
-        <v>432</v>
+        <v>158</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>7</v>
+        <v>159</v>
       </c>
       <c r="C289" s="3" t="s">
         <v>653</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>215</v>
+        <v>160</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>8</v>
+        <v>161</v>
       </c>
       <c r="F289" s="7" t="s">
-        <v>216</v>
+        <v>162</v>
       </c>
       <c r="G289" s="3" t="s">
-        <v>9</v>
+        <v>163</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290" s="3" t="s">
-        <v>253</v>
+        <v>432</v>
       </c>
       <c r="B290" s="3" t="s">
         <v>7</v>
@@ -9200,30 +9218,53 @@
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B291" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C291" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D291" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E291" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F291" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="G291" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A292" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B291" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C291" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="D291" s="3" t="s">
+      <c r="B292" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C292" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D292" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E291" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F291" s="7" t="s">
+      <c r="E292" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F292" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G291" s="3" t="s">
+      <c r="G292" s="3" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G218" xr:uid="{4ADADD25-6A54-4E60-A13A-9027EC52867A}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G291">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G292">
       <sortCondition ref="A1:A218"/>
     </sortState>
   </autoFilter>
@@ -9469,20 +9510,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="877b7d34-4df7-40bf-9eb1-208952470e96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9505,14 +9546,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE79E41D-BA06-4EF8-ACBE-C56D68C307F4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -9527,4 +9560,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA79ED2-AACE-4F44-81A0-3A123B8ABD11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/input/report_salesforce.xlsx
+++ b/input/report_salesforce.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgtedilizia-my.sharepoint.com/personal/emanuele_anzilotti_alayanrentals_it/Documents/Documenti/GitHub/pv_echarts/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AFEA3ED-8BB8-46FE-B691-B3615B6F3FE3}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="113_{059DA938-E7FC-48A2-944C-3CB6F01E26AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AF19C48-C7FA-4FB1-8D7B-E995968E46D9}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1877" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="705">
   <si>
     <t>Nome account</t>
   </si>
@@ -2108,6 +2108,36 @@
   </si>
   <si>
     <t>Perugia</t>
+  </si>
+  <si>
+    <t>PERILLO QUAGLIETTA SRL</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>VIA DANTE ALIGHIERI 82/BIS</t>
+  </si>
+  <si>
+    <t>MATERA</t>
+  </si>
+  <si>
+    <t>ENVIROSUN SRL</t>
+  </si>
+  <si>
+    <t>ATLAS STORAGE 13 SRL</t>
+  </si>
+  <si>
+    <t>SOLAR PV 34 SRL</t>
+  </si>
+  <si>
+    <t>SOLARVIA SRL</t>
+  </si>
+  <si>
+    <t>VIA GIACINTO ANDREA LONGHIN 23</t>
+  </si>
+  <si>
+    <t>PADOVA</t>
   </si>
 </sst>
 </file>
@@ -2230,10 +2260,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2533,7 +2559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G292"/>
+  <dimension ref="A1:G297"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="82" style="3" customWidth="1"/>
@@ -3399,53 +3425,53 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>277</v>
+        <v>700</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C38" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>287</v>
+        <v>545</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>288</v>
+        <v>546</v>
       </c>
       <c r="F38" s="5">
-        <v>39042</v>
+        <v>33100</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>30</v>
+        <v>512</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>521</v>
+        <v>277</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>337</v>
+        <v>287</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>34</v>
+        <v>288</v>
       </c>
       <c r="F39" s="5">
-        <v>20121</v>
+        <v>39042</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>336</v>
+        <v>521</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>32</v>
@@ -3468,7 +3494,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>31</v>
+        <v>336</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>32</v>
@@ -3477,13 +3503,13 @@
         <v>653</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>33</v>
+        <v>337</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F41" s="5" t="s">
-        <v>35</v>
+      <c r="F41" s="5">
+        <v>20121</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>36</v>
@@ -3491,45 +3517,45 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>219</v>
+        <v>31</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>220</v>
+        <v>33</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>178</v>
+        <v>35</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>114</v>
+        <v>219</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>115</v>
+        <v>7</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>116</v>
+        <v>220</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>118</v>
+        <v>178</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>75</v>
@@ -3537,7 +3563,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>525</v>
+        <v>114</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>115</v>
@@ -3551,8 +3577,8 @@
       <c r="E44" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F44" s="5">
-        <v>65125</v>
+      <c r="F44" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>75</v>
@@ -3560,7 +3586,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>252</v>
+        <v>525</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>115</v>
@@ -3574,8 +3600,8 @@
       <c r="E45" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F45" s="5" t="s">
-        <v>118</v>
+      <c r="F45" s="5">
+        <v>65125</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>75</v>
@@ -3583,12 +3609,12 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>683</v>
+        <v>252</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D46" s="4" t="s">
@@ -3597,8 +3623,8 @@
       <c r="E46" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F46" s="5">
-        <v>65125</v>
+      <c r="F46" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>75</v>
@@ -3606,168 +3632,168 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>60</v>
+        <v>683</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C47" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>64</v>
+        <v>117</v>
+      </c>
+      <c r="F47" s="5">
+        <v>65125</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>143</v>
+        <v>60</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>144</v>
+        <v>61</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>148</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>519</v>
+        <v>143</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>520</v>
+        <v>145</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F49" s="5">
-        <v>20033</v>
+        <v>146</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>147</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>289</v>
+        <v>519</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>290</v>
+        <v>32</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>291</v>
+        <v>520</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>292</v>
+        <v>34</v>
       </c>
       <c r="F50" s="5">
-        <v>60035</v>
+        <v>20033</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>648</v>
+        <v>289</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>26</v>
+        <v>290</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>27</v>
+        <v>291</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>28</v>
+        <v>292</v>
       </c>
       <c r="F51" s="5">
-        <v>39100</v>
+        <v>60035</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>30</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>583</v>
+        <v>648</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>115</v>
+        <v>26</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>116</v>
+        <v>27</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>117</v>
+        <v>28</v>
       </c>
       <c r="F52" s="5">
-        <v>65125</v>
+        <v>39100</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>555</v>
+        <v>583</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>213</v>
+        <v>116</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="F53" s="5">
-        <v>20124</v>
+        <v>65125</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>539</v>
+        <v>555</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>32</v>
@@ -3776,21 +3802,21 @@
         <v>653</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>540</v>
+        <v>213</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F54" s="5">
-        <v>20121</v>
+        <v>20124</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>32</v>
@@ -3813,7 +3839,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>32</v>
@@ -3836,99 +3862,99 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>497</v>
+        <v>557</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>498</v>
+        <v>540</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="F57" s="5">
-        <v>10143</v>
+        <v>20121</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>615</v>
+        <v>497</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>616</v>
+        <v>498</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>617</v>
+        <v>79</v>
       </c>
       <c r="F58" s="5">
-        <v>25038</v>
+        <v>10143</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>689</v>
+        <v>615</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>690</v>
-      </c>
-      <c r="C59" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>691</v>
+        <v>616</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>692</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>693</v>
+        <v>617</v>
+      </c>
+      <c r="F59" s="5">
+        <v>25038</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>694</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>387</v>
+        <v>689</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C60" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="C60" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>268</v>
+        <v>691</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F60" s="5">
-        <v>20123</v>
+        <v>692</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>693</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>36</v>
+        <v>694</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>435</v>
+        <v>387</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>32</v>
@@ -3951,7 +3977,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>395</v>
+        <v>435</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>32</v>
@@ -3974,7 +4000,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>267</v>
+        <v>395</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>32</v>
@@ -3988,8 +4014,8 @@
       <c r="E63" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F63" s="5" t="s">
-        <v>59</v>
+      <c r="F63" s="5">
+        <v>20123</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>36</v>
@@ -3997,53 +4023,53 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>685</v>
+        <v>267</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>686</v>
-      </c>
-      <c r="C64" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>687</v>
+        <v>268</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>688</v>
-      </c>
-      <c r="F64" s="5">
-        <v>88842</v>
+        <v>34</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>135</v>
+        <v>685</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C65" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="C65" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>120</v>
+        <v>687</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>56</v>
+        <v>688</v>
+      </c>
+      <c r="F65" s="5">
+        <v>88842</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>407</v>
+        <v>135</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>32</v>
@@ -4057,8 +4083,8 @@
       <c r="E66" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F66" s="5">
-        <v>20121</v>
+      <c r="F66" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>36</v>
@@ -4066,53 +4092,53 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>136</v>
+        <v>407</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>140</v>
+        <v>34</v>
+      </c>
+      <c r="F67" s="5">
+        <v>20121</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>612</v>
+        <v>123</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>15</v>
@@ -4126,8 +4152,8 @@
       <c r="E69" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F69" s="5">
-        <v>90139</v>
+      <c r="F69" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="G69" s="4" t="s">
         <v>10</v>
@@ -4135,173 +4161,173 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>442</v>
+        <v>612</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>187</v>
+        <v>124</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F70" s="5">
-        <v>20158</v>
+        <v>90139</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>157</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>223</v>
+        <v>442</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>29</v>
+        <v>34</v>
+      </c>
+      <c r="F71" s="5">
+        <v>20158</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>84</v>
+        <v>224</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>581</v>
+        <v>82</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>262</v>
+        <v>83</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>582</v>
+        <v>84</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="F73" s="5">
-        <v>38123</v>
+        <v>85</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>266</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>542</v>
+        <v>581</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>7</v>
+        <v>262</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>543</v>
+        <v>582</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>178</v>
+        <v>406</v>
+      </c>
+      <c r="F74" s="5">
+        <v>38123</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>75</v>
+        <v>266</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>485</v>
+        <v>542</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>486</v>
+        <v>7</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>487</v>
+        <v>543</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="F75" s="5">
-        <v>26015</v>
+        <v>8</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>680</v>
+        <v>485</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>333</v>
+        <v>487</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>216</v>
+        <v>488</v>
+      </c>
+      <c r="F76" s="5">
+        <v>26015</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>9</v>
+        <v>105</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>556</v>
+        <v>680</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D77" s="4" t="s">
@@ -4310,7 +4336,7 @@
       <c r="E77" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F77" s="8" t="s">
+      <c r="F77" s="5" t="s">
         <v>216</v>
       </c>
       <c r="G77" s="4" t="s">
@@ -4319,7 +4345,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>332</v>
+        <v>556</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>7</v>
@@ -4333,7 +4359,7 @@
       <c r="E78" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F78" s="5" t="s">
+      <c r="F78" s="8" t="s">
         <v>216</v>
       </c>
       <c r="G78" s="4" t="s">
@@ -4342,145 +4368,145 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>590</v>
+        <v>332</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>591</v>
+        <v>333</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F79" s="5">
-        <v>20122</v>
+        <v>8</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>298</v>
+        <v>590</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>294</v>
+        <v>32</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>299</v>
+        <v>591</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>300</v>
+        <v>34</v>
       </c>
       <c r="F80" s="5">
-        <v>56025</v>
+        <v>20122</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>297</v>
+        <v>36</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>7</v>
+        <v>294</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>270</v>
+        <v>299</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>271</v>
+        <v>300</v>
+      </c>
+      <c r="F81" s="5">
+        <v>56025</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>9</v>
+        <v>297</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>373</v>
+        <v>269</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>374</v>
+        <v>270</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F82" s="5">
-        <v>20121</v>
+        <v>8</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>278</v>
+        <v>373</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>301</v>
+        <v>374</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>302</v>
+        <v>34</v>
       </c>
       <c r="F83" s="5">
-        <v>24060</v>
+        <v>20121</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>614</v>
+        <v>278</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>187</v>
+        <v>301</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>34</v>
+        <v>302</v>
       </c>
       <c r="F84" s="5">
-        <v>20158</v>
+        <v>24060</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>479</v>
+        <v>614</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>32</v>
@@ -4489,21 +4515,21 @@
         <v>653</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>256</v>
+        <v>187</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F85" s="5">
-        <v>20121</v>
+        <v>20158</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>173</v>
+        <v>479</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>32</v>
@@ -4512,21 +4538,21 @@
         <v>653</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>155</v>
+        <v>256</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F86" s="5" t="s">
-        <v>156</v>
+      <c r="F86" s="5">
+        <v>20121</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>32</v>
@@ -4549,53 +4575,53 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>657</v>
+        <v>154</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>290</v>
+        <v>32</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>658</v>
+        <v>155</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="F88" s="5">
-        <v>60035</v>
+        <v>34</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>156</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>251</v>
+        <v>657</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>32</v>
+        <v>290</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>228</v>
+        <v>658</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>229</v>
+        <v>292</v>
+      </c>
+      <c r="F89" s="5">
+        <v>60035</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>437</v>
+        <v>251</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>32</v>
@@ -4604,151 +4630,151 @@
         <v>653</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>438</v>
+        <v>228</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F90" s="5">
-        <v>20122</v>
+      <c r="F90" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>36</v>
+        <v>134</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>243</v>
+        <v>437</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>244</v>
+        <v>32</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>245</v>
+        <v>438</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>247</v>
+        <v>34</v>
+      </c>
+      <c r="F91" s="5">
+        <v>20122</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>248</v>
+        <v>36</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>81</v>
+        <v>248</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>360</v>
+        <v>249</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>361</v>
+        <v>77</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>362</v>
+        <v>250</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="F93" s="5">
-        <v>76123</v>
+        <v>79</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>423</v>
+        <v>360</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>26</v>
+        <v>361</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>130</v>
+        <v>362</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>28</v>
+        <v>363</v>
       </c>
       <c r="F94" s="5">
-        <v>39100</v>
+        <v>76123</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>549</v>
+        <v>423</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>550</v>
+        <v>26</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>551</v>
+        <v>130</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="F95" s="8" t="s">
-        <v>553</v>
+        <v>28</v>
+      </c>
+      <c r="F95" s="5">
+        <v>39100</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>646</v>
+        <v>549</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>7</v>
+        <v>550</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>647</v>
+        <v>551</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>8</v>
+        <v>552</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>178</v>
+        <v>553</v>
       </c>
       <c r="G96" s="4" t="s">
         <v>75</v>
@@ -4756,99 +4782,99 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>389</v>
+        <v>646</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>390</v>
+        <v>647</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F97" s="5">
-        <v>70043</v>
+        <v>8</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>217</v>
+        <v>389</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>218</v>
+        <v>390</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
+      </c>
+      <c r="F98" s="5">
+        <v>70043</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>48</v>
+        <v>217</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>45</v>
+        <v>218</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>32</v>
@@ -4857,13 +4883,13 @@
         <v>653</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G101" s="4" t="s">
         <v>36</v>
@@ -4871,7 +4897,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>32</v>
@@ -4894,7 +4920,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>32</v>
@@ -4917,99 +4943,99 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>369</v>
+        <v>128</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>370</v>
+        <v>32</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>371</v>
+        <v>120</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="F104" s="5">
-        <v>61121</v>
+        <v>34</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>163</v>
+        <v>36</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>662</v>
+        <v>699</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C105" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C105" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F105" s="5">
-        <v>20158</v>
+        <v>40129</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>157</v>
+        <v>24</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>199</v>
+        <v>369</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>32</v>
+        <v>370</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>187</v>
+        <v>371</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>188</v>
+        <v>372</v>
+      </c>
+      <c r="F106" s="5">
+        <v>61121</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>504</v>
+        <v>662</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>507</v>
+        <v>32</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>506</v>
+        <v>187</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>505</v>
+        <v>34</v>
       </c>
       <c r="F107" s="5">
-        <v>35010</v>
+        <v>20158</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>503</v>
+        <v>157</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>279</v>
+        <v>199</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>32</v>
@@ -5018,85 +5044,85 @@
         <v>653</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>303</v>
+        <v>187</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F108" s="5">
-        <v>20123</v>
+      <c r="F108" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>563</v>
+        <v>504</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>32</v>
+        <v>507</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>562</v>
+        <v>506</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>34</v>
+        <v>505</v>
       </c>
       <c r="F109" s="5">
-        <v>20122</v>
+        <v>35010</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>36</v>
+        <v>503</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>349</v>
+        <v>279</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>350</v>
+        <v>32</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>351</v>
+        <v>303</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="F110" s="5">
-        <v>15033</v>
+        <v>20123</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>349</v>
+        <v>563</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>350</v>
+        <v>32</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>351</v>
+        <v>562</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="F111" s="5">
-        <v>15033</v>
+        <v>20122</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
@@ -5124,145 +5150,145 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>533</v>
+        <v>349</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>115</v>
+        <v>350</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>534</v>
+        <v>351</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>117</v>
+        <v>352</v>
       </c>
       <c r="F113" s="5">
-        <v>65127</v>
+        <v>15033</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>57</v>
+        <v>349</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>32</v>
+        <v>350</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>58</v>
+        <v>351</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>59</v>
+        <v>352</v>
+      </c>
+      <c r="F114" s="5">
+        <v>15033</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>334</v>
+        <v>533</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>335</v>
+        <v>534</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="F115" s="5">
-        <v>10153</v>
+        <v>65127</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>428</v>
+        <v>57</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>335</v>
+        <v>58</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F116" s="5">
-        <v>10153</v>
+        <v>34</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>571</v>
+        <v>334</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>572</v>
+        <v>335</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="F117" s="5">
-        <v>20154</v>
+        <v>10153</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>280</v>
+        <v>428</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>304</v>
+        <v>335</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="F118" s="5">
-        <v>183</v>
+        <v>10153</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>305</v>
+        <v>81</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>208</v>
+        <v>571</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>32</v>
@@ -5271,44 +5297,44 @@
         <v>653</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>209</v>
+        <v>572</v>
       </c>
       <c r="E119" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F119" s="5" t="s">
-        <v>56</v>
+      <c r="F119" s="5">
+        <v>20154</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>547</v>
+        <v>280</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>548</v>
+        <v>304</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F120" s="5">
-        <v>20154</v>
+        <v>183</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>157</v>
+        <v>305</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>273</v>
+        <v>208</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>32</v>
@@ -5317,90 +5343,90 @@
         <v>653</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>274</v>
+        <v>209</v>
       </c>
       <c r="E121" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>126</v>
+        <v>547</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>127</v>
+        <v>548</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>29</v>
+        <v>34</v>
+      </c>
+      <c r="F122" s="5">
+        <v>20154</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>240</v>
+        <v>273</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>127</v>
+        <v>274</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>29</v>
+        <v>156</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>412</v>
+        <v>126</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>413</v>
+        <v>127</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>178</v>
+        <v>29</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>272</v>
+        <v>240</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>26</v>
@@ -5409,7 +5435,7 @@
         <v>653</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>27</v>
+        <v>127</v>
       </c>
       <c r="E125" s="4" t="s">
         <v>28</v>
@@ -5423,145 +5449,145 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>236</v>
+        <v>412</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>144</v>
+        <v>7</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>237</v>
+        <v>413</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>238</v>
+        <v>8</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>239</v>
+        <v>178</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>596</v>
+        <v>272</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>597</v>
+        <v>27</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F127" s="5">
-        <v>20122</v>
+        <v>28</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>535</v>
+        <v>236</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>536</v>
+        <v>144</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>537</v>
+        <v>237</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>538</v>
-      </c>
-      <c r="F128" s="5">
-        <v>34133</v>
+        <v>238</v>
+      </c>
+      <c r="F128" s="5" t="s">
+        <v>239</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>512</v>
+        <v>148</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>433</v>
+        <v>596</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>127</v>
+        <v>597</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F129" s="5">
-        <v>39100</v>
+        <v>20122</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>649</v>
+        <v>535</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>32</v>
+        <v>536</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>650</v>
+        <v>537</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>34</v>
+        <v>538</v>
       </c>
       <c r="F130" s="5">
-        <v>20121</v>
+        <v>34133</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>36</v>
+        <v>512</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>204</v>
+        <v>433</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>58</v>
+        <v>127</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F131" s="5" t="s">
-        <v>59</v>
+        <v>28</v>
+      </c>
+      <c r="F131" s="5">
+        <v>39100</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>364</v>
+        <v>649</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>32</v>
@@ -5570,13 +5596,13 @@
         <v>653</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>58</v>
+        <v>650</v>
       </c>
       <c r="E132" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F132" s="5">
-        <v>20123</v>
+        <v>20121</v>
       </c>
       <c r="G132" s="4" t="s">
         <v>36</v>
@@ -5584,7 +5610,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>99</v>
+        <v>204</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>32</v>
@@ -5607,122 +5633,122 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>491</v>
+        <v>364</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>492</v>
+        <v>58</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F134" s="8" t="s">
-        <v>271</v>
+        <v>34</v>
+      </c>
+      <c r="F134" s="5">
+        <v>20123</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>517</v>
+        <v>99</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>518</v>
+        <v>58</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F135" s="5">
-        <v>80121</v>
+        <v>34</v>
+      </c>
+      <c r="F135" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>404</v>
+        <v>491</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>262</v>
+        <v>7</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>405</v>
+        <v>492</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="F136" s="5">
-        <v>38121</v>
+        <v>8</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>266</v>
+        <v>9</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>367</v>
+        <v>517</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>368</v>
+        <v>518</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="F137" s="5">
-        <v>20123</v>
+        <v>80121</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>358</v>
+        <v>404</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>15</v>
+        <v>262</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>359</v>
+        <v>405</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>17</v>
+        <v>406</v>
       </c>
       <c r="F138" s="5">
-        <v>90139</v>
+        <v>38121</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>10</v>
+        <v>266</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>32</v>
@@ -5731,7 +5757,7 @@
         <v>653</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>193</v>
+        <v>368</v>
       </c>
       <c r="E139" s="4" t="s">
         <v>34</v>
@@ -5745,53 +5771,53 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>453</v>
+        <v>358</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>454</v>
+        <v>359</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F140" s="8" t="s">
-        <v>178</v>
+        <v>17</v>
+      </c>
+      <c r="F140" s="5">
+        <v>90139</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>75</v>
+        <v>10</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>281</v>
+        <v>343</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>306</v>
+        <v>32</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>307</v>
+        <v>193</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="F141" s="5">
-        <v>12037</v>
+        <v>20123</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>305</v>
+        <v>36</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>11</v>
+        <v>453</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>7</v>
@@ -5800,187 +5826,187 @@
         <v>653</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>12</v>
+        <v>454</v>
       </c>
       <c r="E142" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F142" s="5" t="s">
-        <v>13</v>
+      <c r="F142" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>121</v>
+        <v>281</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>26</v>
+        <v>306</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>53</v>
+        <v>307</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F143" s="5" t="s">
-        <v>29</v>
+        <v>308</v>
+      </c>
+      <c r="F143" s="5">
+        <v>12037</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>30</v>
+        <v>305</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>651</v>
+        <v>52</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>652</v>
+        <v>53</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F146" s="5">
-        <v>20124</v>
+        <v>28</v>
+      </c>
+      <c r="F146" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>157</v>
+        <v>30</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>676</v>
+        <v>72</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>350</v>
+        <v>7</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>677</v>
+        <v>73</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>678</v>
-      </c>
-      <c r="F147" s="5">
-        <v>15079</v>
+        <v>8</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>679</v>
+        <v>75</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>25</v>
+        <v>651</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>27</v>
+        <v>652</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>29</v>
+        <v>34</v>
+      </c>
+      <c r="F148" s="5">
+        <v>20124</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>496</v>
+        <v>676</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>26</v>
+        <v>350</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>27</v>
+        <v>677</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>28</v>
+        <v>678</v>
       </c>
       <c r="F149" s="5">
-        <v>39100</v>
+        <v>15079</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>30</v>
+        <v>679</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>684</v>
+        <v>25</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C150" s="4" t="s">
+      <c r="C150" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D150" s="4" t="s">
@@ -5989,8 +6015,8 @@
       <c r="E150" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F150" s="5">
-        <v>39100</v>
+      <c r="F150" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G150" s="4" t="s">
         <v>30</v>
@@ -5998,260 +6024,260 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>231</v>
+        <v>496</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>232</v>
+        <v>27</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F151" s="5" t="s">
-        <v>216</v>
+        <v>28</v>
+      </c>
+      <c r="F151" s="5">
+        <v>39100</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>588</v>
+        <v>684</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C152" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C152" s="4" t="s">
         <v>653</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>589</v>
+        <v>27</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F152" s="5">
-        <v>20122</v>
+        <v>39100</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>186</v>
+        <v>231</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>187</v>
+        <v>232</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>157</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>481</v>
+        <v>588</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>482</v>
+        <v>32</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>483</v>
+        <v>589</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>484</v>
+        <v>34</v>
       </c>
       <c r="F154" s="5">
-        <v>66020</v>
+        <v>20122</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>619</v>
+        <v>186</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>482</v>
+        <v>32</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>483</v>
+        <v>187</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="F155" s="5">
-        <v>66020</v>
+        <v>34</v>
+      </c>
+      <c r="F155" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>75</v>
+        <v>157</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>574</v>
+        <v>481</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>32</v>
+        <v>482</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>575</v>
+        <v>483</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>34</v>
+        <v>484</v>
       </c>
       <c r="F156" s="5">
-        <v>20124</v>
+        <v>66020</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>409</v>
+        <v>619</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>339</v>
+        <v>482</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>410</v>
+        <v>483</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>411</v>
+        <v>484</v>
       </c>
       <c r="F157" s="5">
-        <v>37137</v>
+        <v>66020</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>341</v>
+        <v>75</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
-        <v>458</v>
+        <v>574</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>459</v>
+        <v>575</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F158" s="8" t="s">
-        <v>216</v>
+        <v>34</v>
+      </c>
+      <c r="F158" s="5">
+        <v>20124</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>9</v>
+        <v>157</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>293</v>
+        <v>409</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>294</v>
+        <v>339</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>295</v>
+        <v>410</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>296</v>
+        <v>411</v>
       </c>
       <c r="F159" s="5">
-        <v>56010</v>
+        <v>37137</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>601</v>
+        <v>458</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>602</v>
+        <v>459</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F160" s="5">
-        <v>20145</v>
+        <v>8</v>
+      </c>
+      <c r="F160" s="8" t="s">
+        <v>216</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>134</v>
+        <v>9</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>20</v>
+        <v>294</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="F161" s="5">
-        <v>40060</v>
+        <v>56010</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>24</v>
+        <v>297</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
-        <v>382</v>
+        <v>601</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>32</v>
@@ -6260,67 +6286,67 @@
         <v>653</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>383</v>
+        <v>602</v>
       </c>
       <c r="E162" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F162" s="5">
-        <v>20121</v>
+        <v>20145</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>36</v>
+        <v>134</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>384</v>
+        <v>309</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>383</v>
+        <v>310</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>56</v>
+        <v>311</v>
+      </c>
+      <c r="F163" s="5">
+        <v>40060</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>211</v>
+        <v>382</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>177</v>
+        <v>383</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F164" s="5" t="s">
-        <v>178</v>
+        <v>34</v>
+      </c>
+      <c r="F164" s="5">
+        <v>20121</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>573</v>
+        <v>384</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>32</v>
@@ -6329,481 +6355,481 @@
         <v>653</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>190</v>
+        <v>383</v>
       </c>
       <c r="E165" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F165" s="5">
-        <v>20124</v>
+      <c r="F165" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>587</v>
+        <v>211</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F166" s="5">
-        <v>20124</v>
+        <v>8</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>178</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>629</v>
+        <v>573</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>630</v>
+        <v>190</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>631</v>
+        <v>34</v>
       </c>
       <c r="F167" s="5">
-        <v>39025</v>
+        <v>20124</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>66</v>
+        <v>587</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>68</v>
+        <v>190</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>70</v>
+        <v>34</v>
+      </c>
+      <c r="F168" s="5">
+        <v>20124</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>71</v>
+        <v>157</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>282</v>
+        <v>629</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>312</v>
+        <v>26</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>653</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>313</v>
+        <v>630</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>314</v>
+        <v>631</v>
       </c>
       <c r="F169" s="5">
-        <v>57021</v>
+        <v>39025</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>297</v>
+        <v>30</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>182</v>
+        <v>66</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>7</v>
+  